--- a/ProjectManagement/EvaluationHW.xlsx
+++ b/ProjectManagement/EvaluationHW.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FH\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sherwin\EmdenLeer University\ML\ML24-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2FF9487-E29F-4253-A513-8B676CF689DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="510" windowWidth="25380" windowHeight="16740"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="2" r:id="rId1"/>
     <sheet name="Formalities" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,12 +35,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Elmar Wings</author>
   </authors>
   <commentList>
-    <comment ref="K359" authorId="0" shapeId="0">
+    <comment ref="K359" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -78,12 +77,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Elmar Wings</author>
   </authors>
   <commentList>
-    <comment ref="B14" authorId="0" shapeId="0">
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -91,7 +90,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Segoe UI"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Elmar Wings:</t>
         </r>
@@ -100,7 +99,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Segoe UI"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 main page
@@ -110,7 +109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B15" authorId="0" shapeId="0">
+    <comment ref="B15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -118,7 +117,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Segoe UI"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Elmar Wings:</t>
         </r>
@@ -127,7 +126,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Segoe UI"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 in all possible files:
@@ -138,7 +137,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B34" authorId="0" shapeId="0">
+    <comment ref="B34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
@@ -175,7 +174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="370">
   <si>
     <t>Literature</t>
   </si>
@@ -741,12 +740,6 @@
     <t>student 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Keyword Spotting with an Arduino Nano 33 BLE Sense		</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application of TinyML for training datasets for Arduino Nano BLE sense 33 to blink RGB whenever it senses trained word for sample of trained data. </t>
-  </si>
-  <si>
     <t>Wintee</t>
   </si>
   <si>
@@ -1273,16 +1266,34 @@
   </si>
   <si>
     <t>Test protocol</t>
+  </si>
+  <si>
+    <t>Mansour Ahmady Phoulady</t>
+  </si>
+  <si>
+    <t>Hemanth Jadiswami Prabhakaran</t>
+  </si>
+  <si>
+    <t>Ranjeetsing Dhansing Tawar</t>
+  </si>
+  <si>
+    <t>Business Intelligen ans Data Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machine Learning Project - Car Licence Plate Identification with a Jetson Nano	</t>
+  </si>
+  <si>
+    <t>Application of Using Jetson Nano to Detect the Licence Plate Number of Cars, Applying it on a Database of Licence Plates.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1349,19 +1360,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Segoe UI"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Segoe UI"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1470,7 +1468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1496,34 +1494,29 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1800,11 +1793,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:Q543"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:M543"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
@@ -1812,11 +1805,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A2" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
+      <c r="A2" s="22" t="s">
+        <v>368</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -1824,11 +1817,11 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
+      <c r="A6" s="24" t="s">
+        <v>369</v>
+      </c>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1867,13 +1860,16 @@
       <c r="A14" s="1" t="s">
         <v>76</v>
       </c>
+      <c r="B14" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1893,7 +1889,7 @@
         <v>80</v>
       </c>
       <c r="B21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1901,7 +1897,7 @@
         <v>81</v>
       </c>
       <c r="B22" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
@@ -1931,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1948,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1965,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1982,7 +1978,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1999,10 +1995,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" s="19" customFormat="1" x14ac:dyDescent="0.25">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="11" t="s">
         <v>140</v>
@@ -2016,13 +2012,12 @@
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" s="19" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:8" s="19" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="24" t="s">
-        <v>284</v>
+        <v>337</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -2062,7 +2057,6 @@
       <c r="F38" s="11">
         <v>10</v>
       </c>
-      <c r="G38" s="19"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="11"/>
@@ -2091,7 +2085,7 @@
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
       <c r="B41" s="11" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
@@ -2106,7 +2100,7 @@
         <v>1</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
@@ -2154,7 +2148,7 @@
       <c r="A46" s="11"/>
       <c r="B46" s="11"/>
       <c r="C46" s="11" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D46" s="11"/>
       <c r="E46" s="11"/>
@@ -2190,10 +2184,10 @@
       <c r="A49" s="11"/>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E49" s="22">
+      <c r="D49" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E49" s="20">
         <f>-SUM(E36:E48)</f>
         <v>0</v>
       </c>
@@ -2212,7 +2206,7 @@
     </row>
     <row r="52" spans="1:12" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="K52"/>
       <c r="L52"/>
@@ -2222,24 +2216,24 @@
         <v>112</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="12"/>
       <c r="F53" s="12">
         <v>10</v>
       </c>
-      <c r="G53" s="30" t="s">
-        <v>341</v>
+      <c r="G53" s="25" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="14"/>
       <c r="B54" s="14" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>113</v>
@@ -2249,7 +2243,7 @@
       <c r="F54" s="12">
         <v>5</v>
       </c>
-      <c r="G54" s="30"/>
+      <c r="G54" s="25"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="14"/>
@@ -2262,20 +2256,20 @@
       <c r="F55" s="12">
         <v>5</v>
       </c>
-      <c r="G55" s="30"/>
+      <c r="G55" s="25"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="14"/>
       <c r="B56" s="12"/>
       <c r="C56" s="12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D56" s="12"/>
       <c r="E56" s="12"/>
       <c r="F56" s="12">
         <v>5</v>
       </c>
-      <c r="G56" s="30"/>
+      <c r="G56" s="25"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="14"/>
@@ -2288,7 +2282,7 @@
       <c r="F57" s="12">
         <v>10</v>
       </c>
-      <c r="G57" s="30"/>
+      <c r="G57" s="25"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="14"/>
@@ -2301,7 +2295,7 @@
       <c r="F58" s="12">
         <v>5</v>
       </c>
-      <c r="G58" s="30"/>
+      <c r="G58" s="25"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="14"/>
@@ -2314,7 +2308,7 @@
       <c r="F59" s="12">
         <v>15</v>
       </c>
-      <c r="G59" s="30"/>
+      <c r="G59" s="25"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="14"/>
@@ -2327,7 +2321,7 @@
       <c r="F60" s="12">
         <v>5</v>
       </c>
-      <c r="G60" s="30"/>
+      <c r="G60" s="25"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="14"/>
@@ -2340,7 +2334,7 @@
       <c r="F61" s="12">
         <v>10</v>
       </c>
-      <c r="G61" s="30"/>
+      <c r="G61" s="25"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="14"/>
@@ -2353,35 +2347,35 @@
       <c r="F62" s="12">
         <v>5</v>
       </c>
-      <c r="G62" s="30"/>
+      <c r="G62" s="25"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="14"/>
       <c r="B63" s="14" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D63" s="12"/>
       <c r="E63" s="12"/>
       <c r="F63" s="12">
         <v>5</v>
       </c>
-      <c r="G63" s="30"/>
+      <c r="G63" s="25"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="14"/>
       <c r="B64" s="14"/>
       <c r="C64" s="12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D64" s="12"/>
       <c r="E64" s="12"/>
       <c r="F64" s="12">
         <v>20</v>
       </c>
-      <c r="G64" s="30"/>
+      <c r="G64" s="25"/>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="14"/>
@@ -2394,26 +2388,25 @@
       <c r="F65" s="12">
         <v>10</v>
       </c>
-      <c r="G65" s="30"/>
+      <c r="G65" s="25"/>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="14"/>
       <c r="B66" s="14"/>
       <c r="C66" s="12"/>
-      <c r="D66" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E66" s="22">
+      <c r="D66" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E66" s="20">
         <f>-SUM(E53:E65)</f>
         <v>0</v>
       </c>
       <c r="F66" s="12"/>
-      <c r="G66" s="30"/>
+      <c r="G66" s="25"/>
     </row>
     <row r="67" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
-      <c r="D67" s="19"/>
       <c r="E67">
         <f>-SUM(E53:E66)</f>
         <v>0</v>
@@ -2427,7 +2420,7 @@
     </row>
     <row r="68" spans="1:13" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="K68"/>
       <c r="L68"/>
@@ -2438,10 +2431,10 @@
         <v>Document Manufacturing and Assembly</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D69" s="10"/>
       <c r="E69" s="10"/>
@@ -2452,7 +2445,7 @@
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="9"/>
       <c r="B70" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>42</v>
@@ -2467,7 +2460,7 @@
       <c r="A71" s="9"/>
       <c r="B71" s="9"/>
       <c r="C71" s="10" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D71" s="10"/>
       <c r="E71" s="10"/>
@@ -2491,7 +2484,7 @@
       <c r="A73" s="9"/>
       <c r="B73" s="9"/>
       <c r="C73" s="10" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D73" s="10"/>
       <c r="E73" s="10"/>
@@ -2503,7 +2496,7 @@
       <c r="A74" s="9"/>
       <c r="B74" s="9"/>
       <c r="C74" s="10" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D74" s="10"/>
       <c r="E74" s="10"/>
@@ -2515,10 +2508,10 @@
       <c r="A75" s="9"/>
       <c r="B75" s="9"/>
       <c r="C75" s="10"/>
-      <c r="D75" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E75" s="22">
+      <c r="D75" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E75" s="20">
         <f>-SUM(E69:E74)</f>
         <v>0</v>
       </c>
@@ -2527,7 +2520,6 @@
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
-      <c r="D76" s="19"/>
       <c r="E76">
         <f>-SUM(E69:E75)</f>
         <v>0</v>
@@ -2539,23 +2531,21 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
-      <c r="C77" s="19"/>
     </row>
     <row r="78" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="C78" s="19"/>
+        <v>342</v>
+      </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D79" s="11"/>
       <c r="E79" s="11"/>
@@ -2579,7 +2569,7 @@
       <c r="A81" s="13"/>
       <c r="B81" s="11"/>
       <c r="C81" s="11" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D81" s="11"/>
       <c r="E81" s="11"/>
@@ -2590,7 +2580,7 @@
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="13"/>
       <c r="B82" s="13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C82" s="11" t="s">
         <v>7</v>
@@ -2641,10 +2631,10 @@
       <c r="A86" s="13"/>
       <c r="B86" s="13"/>
       <c r="C86" s="13"/>
-      <c r="D86" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E86" s="22">
+      <c r="D86" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E86" s="20">
         <f>-SUM(E79:E85)</f>
         <v>0</v>
       </c>
@@ -2653,7 +2643,6 @@
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
-      <c r="D87" s="19"/>
       <c r="E87">
         <f>-SUM(E79:E86)</f>
         <v>0</v>
@@ -2663,23 +2652,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="19"/>
-      <c r="B88" s="19"/>
-      <c r="C88" s="19"/>
-      <c r="D88" s="19"/>
-      <c r="E88" s="19"/>
-      <c r="F88" s="19"/>
-    </row>
+    <row r="88" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="89" spans="1:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="A89" s="25" t="s">
-        <v>345</v>
-      </c>
-      <c r="B89" s="19"/>
-      <c r="C89" s="19"/>
-      <c r="D89" s="19"/>
-      <c r="E89" s="19"/>
-      <c r="F89" s="19"/>
+      <c r="A89" s="21" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="90" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
@@ -2764,10 +2741,10 @@
       <c r="A97" s="12"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
-      <c r="D97" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E97" s="22">
+      <c r="D97" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E97" s="20">
         <f>-SUM(E91:E96)</f>
         <v>0</v>
       </c>
@@ -2785,15 +2762,15 @@
     </row>
     <row r="99" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="10"/>
@@ -2890,10 +2867,10 @@
       <c r="A108" s="10"/>
       <c r="B108" s="16"/>
       <c r="C108" s="10"/>
-      <c r="D108" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E108" s="22">
+      <c r="D108" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E108" s="20">
         <f>-SUM(E100:E107)</f>
         <v>0</v>
       </c>
@@ -2910,30 +2887,30 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="13" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B113" s="11" t="s">
         <v>5</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F113" s="11">
         <v>20</v>
       </c>
-      <c r="G113" s="31" t="s">
+      <c r="G113" s="26" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="13" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B114" s="11"/>
       <c r="C114" s="11" t="s">
@@ -2941,12 +2918,12 @@
       </c>
       <c r="D114" s="11"/>
       <c r="E114" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F114" s="11">
         <v>10</v>
       </c>
-      <c r="G114" s="31"/>
+      <c r="G114" s="26"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="11"/>
@@ -2956,12 +2933,12 @@
       </c>
       <c r="D115" s="11"/>
       <c r="E115" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F115" s="11">
         <v>10</v>
       </c>
-      <c r="G115" s="31"/>
+      <c r="G115" s="26"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="11"/>
@@ -2971,27 +2948,27 @@
       </c>
       <c r="D116" s="11"/>
       <c r="E116" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F116" s="11">
         <v>10</v>
       </c>
-      <c r="G116" s="31"/>
+      <c r="G116" s="26"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="13"/>
       <c r="B117" s="11"/>
       <c r="C117" s="11" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D117" s="11"/>
       <c r="E117" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F117" s="11">
         <v>10</v>
       </c>
-      <c r="G117" s="31"/>
+      <c r="G117" s="26"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="11"/>
@@ -3003,12 +2980,12 @@
         <v>101</v>
       </c>
       <c r="E118" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F118" s="11">
         <v>10</v>
       </c>
-      <c r="G118" s="31"/>
+      <c r="G118" s="26"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="11"/>
@@ -3018,12 +2995,12 @@
         <v>102</v>
       </c>
       <c r="E119" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F119" s="11">
         <v>10</v>
       </c>
-      <c r="G119" s="31"/>
+      <c r="G119" s="26"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
@@ -3033,12 +3010,12 @@
         <v>90</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F120" s="11">
         <v>10</v>
       </c>
-      <c r="G120" s="31"/>
+      <c r="G120" s="26"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="13"/>
@@ -3048,168 +3025,161 @@
         <v>12</v>
       </c>
       <c r="E121" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F121" s="11">
         <v>10</v>
       </c>
-      <c r="G121" s="31"/>
+      <c r="G121" s="26"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="13"/>
       <c r="B122" s="11"/>
       <c r="C122" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D122" s="11"/>
       <c r="E122" s="11" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F122" s="11">
         <v>20</v>
       </c>
-      <c r="G122" s="31"/>
+      <c r="G122" s="26"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="11"/>
       <c r="B123" s="11"/>
       <c r="C123" s="11"/>
-      <c r="D123" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E123" s="22">
+      <c r="D123" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E123" s="20">
         <f>-SUM(E113:E122)</f>
         <v>0</v>
       </c>
-      <c r="G123" s="31"/>
+      <c r="G123" s="26"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A124" s="19"/>
-      <c r="B124" s="19"/>
-      <c r="C124" s="19"/>
       <c r="E124">
         <f>SUM(E117:E123)</f>
         <v>0</v>
       </c>
-      <c r="F124" s="19">
+      <c r="F124">
         <f>SUM(F113:F122)</f>
         <v>120</v>
       </c>
-      <c r="G124" s="31"/>
+      <c r="G124" s="26"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="19"/>
-      <c r="B125" s="19"/>
-      <c r="C125" s="19"/>
-      <c r="F125" s="19"/>
-      <c r="G125" s="31"/>
+      <c r="G125" s="26"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="14" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B126" s="12" t="s">
         <v>5</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D126" s="12"/>
       <c r="E126" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F126" s="12">
         <v>10</v>
       </c>
-      <c r="G126" s="31"/>
+      <c r="G126" s="26"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="14" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B127" s="12"/>
       <c r="C127" s="12" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D127" s="12"/>
       <c r="E127" s="12"/>
       <c r="F127" s="12">
         <v>7</v>
       </c>
-      <c r="G127" s="31"/>
+      <c r="G127" s="26"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="14"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D128" s="12"/>
       <c r="E128" s="12"/>
       <c r="F128" s="12">
         <v>10</v>
       </c>
-      <c r="G128" s="31"/>
+      <c r="G128" s="26"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="14"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D129" s="12"/>
       <c r="E129" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F129" s="12">
         <v>10</v>
       </c>
-      <c r="G129" s="31"/>
+      <c r="G129" s="26"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D130" s="12"/>
       <c r="E130" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F130" s="12">
         <v>10</v>
       </c>
-      <c r="G130" s="31"/>
+      <c r="G130" s="26"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="12"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D131" s="12"/>
       <c r="E131" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F131" s="12">
         <v>8</v>
       </c>
-      <c r="G131" s="31"/>
+      <c r="G131" s="26"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="12"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D132" s="12"/>
       <c r="E132" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F132" s="12">
         <v>8</v>
       </c>
-      <c r="G132" s="31"/>
+      <c r="G132" s="26"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="12"/>
@@ -3222,60 +3192,53 @@
       <c r="F133" s="12">
         <v>7</v>
       </c>
-      <c r="G133" s="31"/>
+      <c r="G133" s="26"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D134" s="12"/>
       <c r="E134" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F134" s="12">
         <v>5</v>
       </c>
-      <c r="G134" s="31"/>
+      <c r="G134" s="26"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="12"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
-      <c r="D135" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E135" s="22">
+      <c r="D135" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E135" s="20">
         <f>-SUM(E126:E134)</f>
         <v>0</v>
       </c>
-      <c r="G135" s="31"/>
+      <c r="G135" s="26"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136" s="19"/>
-      <c r="B136" s="19"/>
-      <c r="C136" s="19"/>
       <c r="E136">
         <f>SUM(E126:E135)</f>
         <v>0</v>
       </c>
-      <c r="F136" s="19">
+      <c r="F136">
         <f>SUM(F126:F134)</f>
         <v>75</v>
       </c>
-      <c r="G136" s="31"/>
+      <c r="G136" s="26"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="19"/>
-      <c r="B137" s="19"/>
-      <c r="C137" s="19"/>
-      <c r="F137" s="19"/>
-      <c r="G137" s="31"/>
+      <c r="G137" s="26"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="9" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B138" s="10" t="s">
         <v>5</v>
@@ -3286,13 +3249,13 @@
       </c>
       <c r="D138" s="10"/>
       <c r="E138" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F138" s="10">
         <f t="shared" ref="F138:F146" si="1">F126</f>
         <v>10</v>
       </c>
-      <c r="G138" s="31"/>
+      <c r="G138" s="26"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="10" t="str">
@@ -3306,13 +3269,13 @@
       </c>
       <c r="D139" s="10"/>
       <c r="E139" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F139" s="10">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="G139" s="31"/>
+      <c r="G139" s="26"/>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="10"/>
@@ -3323,13 +3286,13 @@
       </c>
       <c r="D140" s="10"/>
       <c r="E140" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F140" s="10">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G140" s="31"/>
+      <c r="G140" s="26"/>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="9"/>
@@ -3340,13 +3303,13 @@
       </c>
       <c r="D141" s="10"/>
       <c r="E141" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F141" s="10">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G141" s="31"/>
+      <c r="G141" s="26"/>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="9"/>
@@ -3357,13 +3320,13 @@
       </c>
       <c r="D142" s="10"/>
       <c r="E142" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F142" s="10">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G142" s="31"/>
+      <c r="G142" s="26"/>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="9"/>
@@ -3378,7 +3341,7 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G143" s="31"/>
+      <c r="G143" s="26"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="9"/>
@@ -3389,15 +3352,15 @@
       </c>
       <c r="D144" s="10"/>
       <c r="E144" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F144" s="10">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G144" s="31"/>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G144" s="26"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="10"/>
       <c r="B145" s="10"/>
       <c r="C145" s="10" t="str">
@@ -3406,15 +3369,15 @@
       </c>
       <c r="D145" s="10"/>
       <c r="E145" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F145" s="10">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="G145" s="31"/>
-    </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G145" s="26"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="10"/>
       <c r="B146" s="10"/>
       <c r="C146" s="10" t="str">
@@ -3423,42 +3386,39 @@
       </c>
       <c r="D146" s="10"/>
       <c r="E146" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F146" s="10">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="G146" s="31"/>
-    </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G146" s="26"/>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="10"/>
       <c r="B147" s="10"/>
       <c r="C147" s="10"/>
-      <c r="D147" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E147" s="22">
+      <c r="D147" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E147" s="20">
         <f>-SUM(E138:E146)</f>
         <v>0</v>
       </c>
-      <c r="G147" s="31"/>
-    </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A148" s="19"/>
-      <c r="B148" s="19"/>
-      <c r="C148" s="19"/>
+      <c r="G147" s="26"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E148">
         <f>SUM(E138:E147)</f>
         <v>0</v>
       </c>
-      <c r="F148" s="19">
+      <c r="F148">
         <f>SUM(F138:F146)</f>
         <v>75</v>
       </c>
-      <c r="G148" s="31"/>
-    </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G148" s="26"/>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="13" t="str">
         <f t="shared" ref="A149:A150" si="2">A138</f>
         <v>domain sensor/actor</v>
@@ -3477,9 +3437,9 @@
         <f t="shared" ref="F149:F157" si="4">F138</f>
         <v>10</v>
       </c>
-      <c r="G149" s="31"/>
-    </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G149" s="26"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="13" t="str">
         <f t="shared" si="2"/>
         <v>e.g. camera, IMU, SPI</v>
@@ -3495,9 +3455,9 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="G150" s="31"/>
-    </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G150" s="26"/>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="13"/>
       <c r="B151" s="13"/>
       <c r="C151" s="11" t="str">
@@ -3510,9 +3470,9 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="G151" s="31"/>
-    </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G151" s="26"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="13"/>
       <c r="B152" s="13"/>
       <c r="C152" s="11" t="str">
@@ -3525,9 +3485,9 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="G152" s="31"/>
-    </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G152" s="26"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="13"/>
       <c r="B153" s="13"/>
       <c r="C153" s="11" t="str">
@@ -3540,9 +3500,9 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="G153" s="31"/>
-    </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G153" s="26"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="13"/>
       <c r="B154" s="13"/>
       <c r="C154" s="11" t="str">
@@ -3555,9 +3515,9 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="G154" s="31"/>
-    </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G154" s="26"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="13"/>
       <c r="B155" s="13"/>
       <c r="C155" s="11" t="str">
@@ -3570,9 +3530,9 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="G155" s="31"/>
-    </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G155" s="26"/>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="13"/>
       <c r="B156" s="13"/>
       <c r="C156" s="11" t="str">
@@ -3585,9 +3545,9 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="G156" s="31"/>
-    </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G156" s="26"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="13"/>
       <c r="B157" s="13"/>
       <c r="C157" s="11" t="str">
@@ -3600,42 +3560,38 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="G157" s="31"/>
-    </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G157" s="26"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="13"/>
       <c r="B158" s="13"/>
       <c r="C158" s="11"/>
-      <c r="D158" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E158" s="22">
+      <c r="D158" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E158" s="20">
         <f>-SUM(E149:E157)</f>
         <v>0</v>
       </c>
       <c r="F158" s="11"/>
-      <c r="G158" s="31"/>
-      <c r="L158" s="19"/>
-      <c r="M158" s="19"/>
-    </row>
-    <row r="159" spans="1:13" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="20"/>
-      <c r="B159" s="20"/>
+      <c r="G158" s="26"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" s="1"/>
+      <c r="B159" s="1"/>
       <c r="E159">
         <f>-SUM(E149:E158)</f>
         <v>0</v>
       </c>
-      <c r="F159" s="19">
+      <c r="F159">
         <f>SUM(F149:F157)</f>
         <v>75</v>
       </c>
-      <c r="G159" s="31"/>
-      <c r="L159"/>
-      <c r="M159"/>
-    </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G159" s="26"/>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="14" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B160" s="12"/>
       <c r="C160" s="12" t="s">
@@ -3643,66 +3599,66 @@
       </c>
       <c r="D160" s="12"/>
       <c r="E160" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F160" s="12">
         <v>10</v>
       </c>
-      <c r="G160" s="31"/>
+      <c r="G160" s="26"/>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="14" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B161" s="12"/>
       <c r="C161" s="12" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D161" s="12"/>
       <c r="E161" s="12"/>
       <c r="F161" s="12">
         <v>10</v>
       </c>
-      <c r="G161" s="31"/>
+      <c r="G161" s="26"/>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="14"/>
       <c r="B162" s="12"/>
       <c r="C162" s="12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D162" s="12"/>
       <c r="E162" s="12"/>
       <c r="F162" s="12">
         <v>10</v>
       </c>
-      <c r="G162" s="31"/>
+      <c r="G162" s="26"/>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="14"/>
       <c r="B163" s="12"/>
       <c r="C163" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D163" s="12"/>
       <c r="E163" s="12"/>
       <c r="F163" s="12">
         <v>10</v>
       </c>
-      <c r="G163" s="31"/>
+      <c r="G163" s="26"/>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="14"/>
       <c r="B164" s="12"/>
       <c r="C164" s="12" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D164" s="12"/>
       <c r="E164" s="12"/>
       <c r="F164" s="12">
         <v>10</v>
       </c>
-      <c r="G164" s="31"/>
+      <c r="G164" s="26"/>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="14"/>
@@ -3715,20 +3671,20 @@
       <c r="F165" s="12">
         <v>6</v>
       </c>
-      <c r="G165" s="31"/>
+      <c r="G165" s="26"/>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="14"/>
       <c r="B166" s="12"/>
       <c r="C166" s="12" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D166" s="12"/>
       <c r="E166" s="12"/>
       <c r="F166" s="12">
         <v>6</v>
       </c>
-      <c r="G166" s="31"/>
+      <c r="G166" s="26"/>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="14"/>
@@ -3737,15 +3693,15 @@
         <v>100</v>
       </c>
       <c r="D167" s="12" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E167" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F167" s="12">
         <v>6</v>
       </c>
-      <c r="G167" s="31"/>
+      <c r="G167" s="26"/>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="12"/>
@@ -3755,12 +3711,12 @@
         <v>89</v>
       </c>
       <c r="E168" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F168" s="12">
         <v>6</v>
       </c>
-      <c r="G168" s="31"/>
+      <c r="G168" s="26"/>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" s="12"/>
@@ -3770,12 +3726,12 @@
       </c>
       <c r="D169" s="12"/>
       <c r="E169" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F169" s="12">
         <v>6</v>
       </c>
-      <c r="G169" s="31"/>
+      <c r="G169" s="26"/>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" s="12"/>
@@ -3785,12 +3741,12 @@
       </c>
       <c r="D170" s="12"/>
       <c r="E170" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F170" s="12">
         <v>5</v>
       </c>
-      <c r="G170" s="31"/>
+      <c r="G170" s="26"/>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" s="12"/>
@@ -3800,54 +3756,44 @@
       </c>
       <c r="D171" s="12"/>
       <c r="E171" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F171" s="12">
         <v>5</v>
       </c>
-      <c r="G171" s="31"/>
+      <c r="G171" s="26"/>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" s="12"/>
       <c r="B172" s="12"/>
       <c r="C172" s="12"/>
-      <c r="D172" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E172" s="22">
+      <c r="D172" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E172" s="20">
         <f>-SUM(E160:E171)</f>
         <v>0</v>
       </c>
-      <c r="G172" s="31"/>
+      <c r="G172" s="26"/>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A173" s="19"/>
-      <c r="B173" s="19"/>
-      <c r="C173" s="19"/>
       <c r="E173">
         <f>SUM(E160:E172)</f>
         <v>0</v>
       </c>
-      <c r="F173" s="19">
+      <c r="F173">
         <f>SUM(F160:F171)</f>
         <v>90</v>
       </c>
-      <c r="G173" s="31"/>
+      <c r="G173" s="26"/>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A174" s="19"/>
-      <c r="B174" s="19"/>
-      <c r="C174" s="19"/>
-      <c r="F174" s="19"/>
-      <c r="G174" s="31"/>
+      <c r="G174" s="26"/>
     </row>
     <row r="175" spans="1:12" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A175" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="B175" s="24"/>
-      <c r="C175" s="24"/>
-      <c r="F175" s="24"/>
+      <c r="A175" s="5" t="s">
+        <v>308</v>
+      </c>
       <c r="K175"/>
       <c r="L175"/>
     </row>
@@ -3867,7 +3813,6 @@
       <c r="F177" s="11">
         <v>10</v>
       </c>
-      <c r="G177" s="19"/>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="11"/>
@@ -3957,10 +3902,10 @@
       <c r="A185" s="11"/>
       <c r="B185" s="11"/>
       <c r="C185" s="11"/>
-      <c r="D185" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E185" s="22">
+      <c r="D185" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E185" s="20">
         <f>-SUM(E177:E184)</f>
         <v>0</v>
       </c>
@@ -3977,7 +3922,7 @@
     </row>
     <row r="188" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A188" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -3993,13 +3938,13 @@
       <c r="F189" s="10">
         <v>5</v>
       </c>
-      <c r="G189" s="32" t="s">
+      <c r="G189" s="27" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="9" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B190" s="9"/>
       <c r="C190" s="10" t="s">
@@ -4010,7 +3955,7 @@
       <c r="F190" s="10">
         <v>10</v>
       </c>
-      <c r="G190" s="32"/>
+      <c r="G190" s="27"/>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="9"/>
@@ -4023,7 +3968,7 @@
       <c r="F191" s="10">
         <v>10</v>
       </c>
-      <c r="G191" s="32"/>
+      <c r="G191" s="27"/>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="9"/>
@@ -4036,7 +3981,7 @@
       <c r="F192" s="10">
         <v>5</v>
       </c>
-      <c r="G192" s="32"/>
+      <c r="G192" s="27"/>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="9"/>
@@ -4049,39 +3994,38 @@
       <c r="F193" s="10">
         <v>5</v>
       </c>
-      <c r="G193" s="32"/>
+      <c r="G193" s="27"/>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="9"/>
       <c r="B194" s="9"/>
       <c r="C194" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D194" s="10"/>
       <c r="E194" s="10"/>
       <c r="F194" s="10">
         <v>5</v>
       </c>
-      <c r="G194" s="32"/>
+      <c r="G194" s="27"/>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="9"/>
       <c r="B195" s="9"/>
       <c r="C195" s="10"/>
-      <c r="D195" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E195" s="22">
+      <c r="D195" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E195" s="20">
         <f>-SUM(E189:E194)</f>
         <v>0</v>
       </c>
       <c r="F195" s="10"/>
-      <c r="G195" s="32"/>
+      <c r="G195" s="27"/>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
-      <c r="D196" s="19"/>
       <c r="E196">
         <f>-SUM(E189:E195)</f>
         <v>0</v>
@@ -4090,7 +4034,7 @@
         <f>SUM(F189:F194)</f>
         <v>40</v>
       </c>
-      <c r="G196" s="32"/>
+      <c r="G196" s="27"/>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="9" t="s">
@@ -4105,11 +4049,11 @@
       <c r="F197" s="10">
         <v>5</v>
       </c>
-      <c r="G197" s="32"/>
+      <c r="G197" s="27"/>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B198" s="9"/>
       <c r="C198" s="10" t="s">
@@ -4120,11 +4064,11 @@
       <c r="F198" s="10">
         <v>10</v>
       </c>
-      <c r="G198" s="32"/>
+      <c r="G198" s="27"/>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="9" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B199" s="9"/>
       <c r="C199" s="10" t="s">
@@ -4135,7 +4079,7 @@
       <c r="F199" s="10">
         <v>10</v>
       </c>
-      <c r="G199" s="32"/>
+      <c r="G199" s="27"/>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="9"/>
@@ -4148,52 +4092,51 @@
       <c r="F200" s="10">
         <v>5</v>
       </c>
-      <c r="G200" s="32"/>
+      <c r="G200" s="27"/>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="9"/>
       <c r="B201" s="9"/>
       <c r="C201" s="10" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D201" s="10"/>
       <c r="E201" s="10"/>
       <c r="F201" s="10">
         <v>5</v>
       </c>
-      <c r="G201" s="32"/>
+      <c r="G201" s="27"/>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="9"/>
       <c r="B202" s="9"/>
       <c r="C202" s="10" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D202" s="10"/>
       <c r="E202" s="10"/>
       <c r="F202" s="10">
         <v>5</v>
       </c>
-      <c r="G202" s="32"/>
+      <c r="G202" s="27"/>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="9"/>
       <c r="B203" s="9"/>
       <c r="C203" s="10"/>
-      <c r="D203" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E203" s="22">
+      <c r="D203" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E203" s="20">
         <f>-SUM(E197:E202)</f>
         <v>0</v>
       </c>
       <c r="F203" s="10"/>
-      <c r="G203" s="32"/>
+      <c r="G203" s="27"/>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
-      <c r="D204" s="19"/>
       <c r="E204">
         <f>-SUM(E197:E203)</f>
         <v>0</v>
@@ -4202,11 +4145,11 @@
         <f>SUM(F197:F202)</f>
         <v>40</v>
       </c>
-      <c r="G204" s="32"/>
+      <c r="G204" s="27"/>
     </row>
     <row r="205" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A205" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -4257,7 +4200,7 @@
       <c r="A210" s="8"/>
       <c r="B210" s="8"/>
       <c r="C210" s="8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D210" s="8"/>
       <c r="E210" s="8"/>
@@ -4273,12 +4216,12 @@
     </row>
     <row r="212" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A212" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A213" s="13" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B213" s="11"/>
       <c r="C213" s="11"/>
@@ -4295,7 +4238,7 @@
       <c r="B214" s="11"/>
       <c r="C214" s="11"/>
       <c r="D214" s="11" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E214" s="11"/>
       <c r="F214" s="11">
@@ -4307,7 +4250,7 @@
       <c r="B215" s="11"/>
       <c r="C215" s="11"/>
       <c r="D215" s="11" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E215" s="11"/>
       <c r="F215" s="11">
@@ -4342,10 +4285,10 @@
       <c r="A218" s="13"/>
       <c r="B218" s="11"/>
       <c r="C218" s="11"/>
-      <c r="D218" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E218" s="22">
+      <c r="D218" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E218" s="20">
         <f>-SUM(E213:E217)</f>
         <v>0</v>
       </c>
@@ -4361,16 +4304,7 @@
         <f>SUM(F213:F218)</f>
         <v>25</v>
       </c>
-      <c r="M219" s="21"/>
-    </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A220" s="19"/>
-      <c r="B220" s="19"/>
-      <c r="C220" s="19"/>
-      <c r="D220" s="19"/>
-      <c r="E220" s="19"/>
-      <c r="F220" s="19"/>
-      <c r="G220" s="19"/>
+      <c r="M219" s="19"/>
     </row>
     <row r="221" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A221" s="9" t="s">
@@ -4401,7 +4335,7 @@
     <row r="223" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A223" s="9"/>
       <c r="B223" s="10" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C223" s="10"/>
       <c r="D223" s="10"/>
@@ -4426,10 +4360,10 @@
       <c r="A225" s="9"/>
       <c r="B225" s="10"/>
       <c r="C225" s="10"/>
-      <c r="D225" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E225" s="22">
+      <c r="D225" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E225" s="20">
         <f>-SUM(E221:E224)</f>
         <v>0</v>
       </c>
@@ -4448,10 +4382,10 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="9" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C227" s="10" t="s">
         <v>62</v>
@@ -4481,7 +4415,7 @@
       <c r="B229" s="10"/>
       <c r="C229" s="10"/>
       <c r="D229" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E229" s="10"/>
       <c r="F229" s="10">
@@ -4505,7 +4439,7 @@
       <c r="B231" s="10"/>
       <c r="C231" s="10"/>
       <c r="D231" s="10" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E231" s="10"/>
       <c r="F231" s="10">
@@ -4517,7 +4451,7 @@
       <c r="B232" s="10"/>
       <c r="C232" s="10"/>
       <c r="D232" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E232" s="10"/>
       <c r="F232" s="10">
@@ -4528,10 +4462,10 @@
       <c r="A233" s="10"/>
       <c r="B233" s="10"/>
       <c r="C233" s="10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D233" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E233" s="10"/>
       <c r="F233" s="10">
@@ -4543,7 +4477,7 @@
       <c r="B234" s="10"/>
       <c r="C234" s="10"/>
       <c r="D234" s="10" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E234" s="10"/>
       <c r="F234" s="10">
@@ -4579,7 +4513,7 @@
       <c r="B237" s="10"/>
       <c r="C237" s="10"/>
       <c r="D237" s="10" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E237" s="10"/>
       <c r="F237" s="10">
@@ -4590,32 +4524,28 @@
       <c r="A238" s="10"/>
       <c r="B238" s="10"/>
       <c r="C238" s="10"/>
-      <c r="D238" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E238" s="22">
+      <c r="D238" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E238" s="20">
         <f>-SUM(E211:E232)</f>
         <v>0</v>
       </c>
       <c r="F238" s="10"/>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A239" s="19"/>
-      <c r="B239" s="19"/>
-      <c r="C239" s="19"/>
-      <c r="D239" s="19"/>
-      <c r="E239" s="19">
+      <c r="E239">
         <f>SUM(E227:E232)</f>
         <v>0</v>
       </c>
-      <c r="F239" s="19">
+      <c r="F239">
         <f>SUM(F227:F237)</f>
         <v>55</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B240" s="7" t="s">
         <v>63</v>
@@ -4633,7 +4563,7 @@
         <v>20</v>
       </c>
       <c r="C241" s="8" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D241" s="8"/>
       <c r="E241" s="8"/>
@@ -4657,7 +4587,7 @@
       <c r="A243" s="8"/>
       <c r="B243" s="8"/>
       <c r="C243" s="8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D243" s="8"/>
       <c r="E243" s="8"/>
@@ -4669,7 +4599,7 @@
       <c r="A244" s="8"/>
       <c r="B244" s="8"/>
       <c r="C244" s="8" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D244" s="8"/>
       <c r="E244" s="8"/>
@@ -4681,7 +4611,7 @@
       <c r="A245" s="8"/>
       <c r="B245" s="8"/>
       <c r="C245" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D245" s="8"/>
       <c r="E245" s="8"/>
@@ -4693,7 +4623,7 @@
       <c r="A246" s="8"/>
       <c r="B246" s="8"/>
       <c r="C246" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D246" s="8"/>
       <c r="E246" s="8"/>
@@ -4705,10 +4635,10 @@
       <c r="A247" s="8"/>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
-      <c r="D247" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E247" s="22">
+      <c r="D247" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E247" s="20">
         <f>-SUM(E244:E246)</f>
         <v>0</v>
       </c>
@@ -4753,7 +4683,7 @@
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="7"/>
       <c r="B251" s="8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C251" s="8"/>
       <c r="D251" s="8"/>
@@ -4852,7 +4782,7 @@
       <c r="A259" s="7"/>
       <c r="B259" s="7"/>
       <c r="C259" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D259" s="8"/>
       <c r="E259" s="8"/>
@@ -4926,10 +4856,10 @@
       <c r="A265" s="7"/>
       <c r="B265" s="7"/>
       <c r="C265" s="8"/>
-      <c r="D265" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E265" s="22">
+      <c r="D265" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E265" s="20">
         <f>-SUM(E255:E264)</f>
         <v>0</v>
       </c>
@@ -4947,10 +4877,10 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B268" s="8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C268" s="8"/>
       <c r="D268" s="8"/>
@@ -4961,10 +4891,10 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B269" s="8" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C269" s="8"/>
       <c r="D269" s="8"/>
@@ -4976,7 +4906,7 @@
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="7"/>
       <c r="B270" s="8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C270" s="8"/>
       <c r="D270" s="8"/>
@@ -4988,7 +4918,7 @@
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="8"/>
       <c r="B271" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C271" s="8"/>
       <c r="D271" s="8"/>
@@ -5000,7 +4930,7 @@
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="8"/>
       <c r="B272" s="8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C272" s="8"/>
       <c r="D272" s="8"/>
@@ -5013,10 +4943,10 @@
       <c r="A273" s="8"/>
       <c r="B273" s="8"/>
       <c r="C273" s="8"/>
-      <c r="D273" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E273" s="22">
+      <c r="D273" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E273" s="20">
         <f>-SUM(E268:E272)</f>
         <v>0</v>
       </c>
@@ -5037,7 +4967,7 @@
         <v>34</v>
       </c>
       <c r="B275" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C275" s="10"/>
       <c r="D275" s="10"/>
@@ -5049,7 +4979,7 @@
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="10"/>
       <c r="B276" s="10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C276" s="10"/>
       <c r="D276" s="10"/>
@@ -5061,12 +4991,12 @@
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="9"/>
       <c r="B277" s="10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C277" s="10"/>
       <c r="D277" s="10"/>
       <c r="E277" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F277" s="10">
         <v>10</v>
@@ -5075,12 +5005,12 @@
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="10"/>
       <c r="B278" s="10" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C278" s="10"/>
       <c r="D278" s="10"/>
       <c r="E278" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F278" s="10">
         <v>10</v>
@@ -5089,12 +5019,12 @@
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="9"/>
       <c r="B279" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C279" s="10"/>
       <c r="D279" s="10"/>
       <c r="E279" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F279" s="10">
         <v>10</v>
@@ -5103,12 +5033,12 @@
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="9"/>
       <c r="B280" s="10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C280" s="10"/>
       <c r="D280" s="10"/>
       <c r="E280" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F280" s="10">
         <v>5</v>
@@ -5117,7 +5047,7 @@
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="9"/>
       <c r="B281" s="10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C281" s="10"/>
       <c r="D281" s="10"/>
@@ -5129,7 +5059,7 @@
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="10"/>
       <c r="B282" s="10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C282" s="10"/>
       <c r="D282" s="10"/>
@@ -5141,7 +5071,7 @@
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="10"/>
       <c r="B283" s="10" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C283" s="10"/>
       <c r="D283" s="10"/>
@@ -5166,10 +5096,10 @@
       <c r="A285" s="10"/>
       <c r="B285" s="10"/>
       <c r="C285" s="10"/>
-      <c r="D285" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E285" s="22">
+      <c r="D285" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E285" s="20">
         <f>-SUM(E273:E284)</f>
         <v>0</v>
       </c>
@@ -5187,15 +5117,15 @@
     </row>
     <row r="289" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A289" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B290" s="12" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C290" s="12"/>
       <c r="D290" s="12"/>
@@ -5232,7 +5162,7 @@
       <c r="A293" s="14"/>
       <c r="B293" s="14"/>
       <c r="C293" s="12" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D293" s="12"/>
       <c r="E293" s="12"/>
@@ -5255,7 +5185,7 @@
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="12"/>
       <c r="B295" s="12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C295" s="12" t="s">
         <v>56</v>
@@ -5270,7 +5200,7 @@
       <c r="A296" s="12"/>
       <c r="B296" s="12"/>
       <c r="C296" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D296" s="12"/>
       <c r="E296" s="12"/>
@@ -5282,7 +5212,7 @@
       <c r="A297" s="12"/>
       <c r="B297" s="12"/>
       <c r="C297" s="12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D297" s="12"/>
       <c r="E297" s="12"/>
@@ -5293,7 +5223,7 @@
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="12"/>
       <c r="B298" s="12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C298" s="12" t="s">
         <v>56</v>
@@ -5308,7 +5238,7 @@
       <c r="A299" s="12"/>
       <c r="B299" s="12"/>
       <c r="C299" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D299" s="12"/>
       <c r="E299" s="12"/>
@@ -5320,7 +5250,7 @@
       <c r="A300" s="12"/>
       <c r="B300" s="12"/>
       <c r="C300" s="12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D300" s="12"/>
       <c r="E300" s="12"/>
@@ -5382,7 +5312,7 @@
       <c r="A305" s="14"/>
       <c r="B305" s="14"/>
       <c r="C305" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D305" s="12"/>
       <c r="E305" s="12"/>
@@ -5456,24 +5386,21 @@
       <c r="A311" s="12"/>
       <c r="B311" s="12"/>
       <c r="C311" s="12"/>
-      <c r="D311" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E311" s="22">
+      <c r="D311" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E311" s="20">
         <f>-SUM(E290:E300)</f>
         <v>0</v>
       </c>
       <c r="F311" s="12"/>
-      <c r="K311" s="19"/>
-      <c r="L311" s="19"/>
-    </row>
-    <row r="312" spans="1:12" s="19" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D312"/>
+    </row>
+    <row r="312" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="E312">
         <f>SUM(E290:E311)</f>
         <v>0</v>
       </c>
-      <c r="F312" s="19">
+      <c r="F312">
         <f>SUM(F290:F310)</f>
         <v>225</v>
       </c>
@@ -5482,153 +5409,140 @@
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A313" s="9" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B313" s="9"/>
       <c r="C313" s="10" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D313" s="10"/>
       <c r="E313" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F313" s="10">
         <v>10</v>
       </c>
-      <c r="G313" s="19"/>
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A314" s="10" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B314" s="10"/>
       <c r="C314" s="10" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D314" s="10"/>
       <c r="E314" s="10"/>
       <c r="F314" s="10">
         <v>5</v>
       </c>
-      <c r="G314" s="19"/>
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A315" s="9"/>
       <c r="B315" s="10"/>
       <c r="C315" s="10" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D315" s="10"/>
       <c r="E315" s="10"/>
       <c r="F315" s="10">
         <v>5</v>
       </c>
-      <c r="G315" s="19"/>
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A316" s="10"/>
       <c r="B316" s="10"/>
       <c r="C316" s="10" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D316" s="10"/>
       <c r="E316" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F316" s="10">
         <v>5</v>
       </c>
-      <c r="G316" s="19"/>
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A317" s="10"/>
       <c r="B317" s="10"/>
       <c r="C317" s="10" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D317" s="10"/>
       <c r="E317" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F317" s="10">
         <v>5</v>
       </c>
-      <c r="G317" s="19"/>
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A318" s="9"/>
       <c r="B318" s="10"/>
       <c r="C318" s="10" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D318" s="10"/>
       <c r="E318" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F318" s="10">
         <v>10</v>
       </c>
-      <c r="G318" s="19"/>
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A319" s="9"/>
       <c r="B319" s="10"/>
       <c r="C319" s="10" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D319" s="10"/>
       <c r="E319" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F319" s="10">
         <v>10</v>
       </c>
-      <c r="G319" s="19"/>
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A320" s="10"/>
       <c r="B320" s="10"/>
       <c r="C320" s="10"/>
-      <c r="D320" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E320" s="22">
+      <c r="D320" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E320" s="20">
         <f>-SUM(E313:E319)</f>
         <v>0</v>
       </c>
-      <c r="G320" s="19"/>
-    </row>
-    <row r="321" spans="1:12" s="19" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D321"/>
-      <c r="E321" s="19">
+    </row>
+    <row r="321" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E321">
         <f>SUM(E313:E320)</f>
         <v>0</v>
       </c>
-      <c r="F321" s="19">
+      <c r="F321">
         <f>SUM(F313:F319)</f>
         <v>50</v>
       </c>
       <c r="K321" s="17"/>
       <c r="L321" s="17"/>
     </row>
-    <row r="322" spans="1:12" s="19" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D322"/>
-      <c r="E322"/>
+    <row r="322" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="K322" s="17"/>
       <c r="L322" s="17"/>
     </row>
-    <row r="323" spans="1:12" s="19" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D323"/>
-      <c r="E323"/>
+    <row r="323" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="K323" s="17"/>
       <c r="L323" s="17"/>
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A324" s="13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B324" s="11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C324" s="11"/>
       <c r="D324" s="11"/>
@@ -5640,7 +5554,7 @@
     <row r="325" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A325" s="11"/>
       <c r="B325" s="11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C325" s="11"/>
       <c r="D325" s="11"/>
@@ -5663,10 +5577,10 @@
     </row>
     <row r="327" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A327" s="13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B327" s="11" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C327" s="11"/>
       <c r="D327" s="11"/>
@@ -5678,7 +5592,7 @@
     <row r="328" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A328" s="11"/>
       <c r="B328" s="11" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C328" s="11"/>
       <c r="D328" s="11"/>
@@ -5689,11 +5603,11 @@
     </row>
     <row r="329" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A329" s="13" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B329" s="11"/>
       <c r="C329" s="11" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D329" s="11"/>
       <c r="E329" s="11"/>
@@ -5705,7 +5619,7 @@
       <c r="A330" s="11"/>
       <c r="B330" s="11"/>
       <c r="C330" s="11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D330" s="11"/>
       <c r="E330" s="11"/>
@@ -5717,7 +5631,7 @@
       <c r="A331" s="11"/>
       <c r="B331" s="11"/>
       <c r="C331" s="11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D331" s="11"/>
       <c r="E331" s="11"/>
@@ -5729,10 +5643,10 @@
       <c r="A332" s="11"/>
       <c r="B332" s="11"/>
       <c r="C332" s="11"/>
-      <c r="D332" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E332" s="22">
+      <c r="D332" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E332" s="20">
         <f>-SUM(E324:E331)</f>
         <v>0</v>
       </c>
@@ -5750,13 +5664,13 @@
     </row>
     <row r="335" spans="1:12" s="17" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A335" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="K335"/>
       <c r="L335"/>
     </row>
     <row r="336" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A336" s="26" t="s">
+      <c r="A336" s="11" t="s">
         <v>154</v>
       </c>
       <c r="B336" s="11" t="s">
@@ -5772,8 +5686,6 @@
       <c r="F336" s="11">
         <v>4</v>
       </c>
-      <c r="G336" s="19"/>
-      <c r="H336" s="19"/>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="11"/>
@@ -5849,10 +5761,10 @@
       <c r="A342" s="11"/>
       <c r="B342" s="11"/>
       <c r="C342" s="11"/>
-      <c r="D342" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E342" s="22">
+      <c r="D342" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E342" s="20">
         <f>-SUM(E336:E341)</f>
         <v>0</v>
       </c>
@@ -5961,7 +5873,7 @@
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="13" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B352" s="13"/>
       <c r="C352" s="11" t="s">
@@ -6001,10 +5913,10 @@
       <c r="A355" s="13"/>
       <c r="B355" s="13"/>
       <c r="C355" s="11"/>
-      <c r="D355" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E355" s="22">
+      <c r="D355" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E355" s="20">
         <f>-SUM(E344:E354)</f>
         <v>0</v>
       </c>
@@ -6021,7 +5933,7 @@
         <f>SUM(F344:F354)</f>
         <v>50</v>
       </c>
-      <c r="M356" s="21"/>
+      <c r="M356" s="19"/>
     </row>
     <row r="357" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A357" s="14" t="s">
@@ -6029,14 +5941,14 @@
       </c>
       <c r="B357" s="14"/>
       <c r="C357" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D357" s="12"/>
       <c r="E357" s="12"/>
       <c r="F357" s="12">
         <v>5</v>
       </c>
-      <c r="M357" s="21"/>
+      <c r="M357" s="19"/>
     </row>
     <row r="358" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A358" s="14"/>
@@ -6049,21 +5961,21 @@
       <c r="F358" s="12">
         <v>5</v>
       </c>
-      <c r="M358" s="21"/>
+      <c r="M358" s="19"/>
     </row>
     <row r="359" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A359" s="14"/>
       <c r="B359" s="14"/>
       <c r="C359" s="12"/>
-      <c r="D359" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E359" s="22">
+      <c r="D359" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E359" s="20">
         <f>-SUM(E357:E358)</f>
         <v>0</v>
       </c>
       <c r="F359" s="12"/>
-      <c r="M359" s="21"/>
+      <c r="M359" s="19"/>
     </row>
     <row r="360" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
@@ -6095,7 +6007,7 @@
     </row>
     <row r="363" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B363" s="10"/>
       <c r="C363" s="10" t="s">
@@ -6123,7 +6035,7 @@
       <c r="A365" s="1"/>
       <c r="B365" s="10"/>
       <c r="C365" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D365" s="10"/>
       <c r="E365" s="10"/>
@@ -6135,7 +6047,7 @@
       <c r="A366" s="1"/>
       <c r="B366" s="10"/>
       <c r="C366" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D366" s="10"/>
       <c r="E366" s="10"/>
@@ -6147,7 +6059,7 @@
       <c r="A367" s="1"/>
       <c r="B367" s="10"/>
       <c r="C367" s="10" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D367" s="10"/>
       <c r="E367" s="10"/>
@@ -6167,7 +6079,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="10"/>
       <c r="C369" s="10" t="s">
@@ -6179,20 +6091,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="10"/>
       <c r="C370" s="10"/>
-      <c r="D370" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E370" s="22">
+      <c r="D370" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E370" s="20">
         <f>-SUM(E362:E369)</f>
         <v>0</v>
       </c>
       <c r="F370" s="10"/>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="E371">
@@ -6204,7 +6116,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="13" t="s">
         <v>54</v>
@@ -6218,7 +6130,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="11"/>
       <c r="C373" s="11" t="s">
@@ -6230,7 +6142,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="11"/>
       <c r="C374" s="11" t="s">
@@ -6242,11 +6154,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="11"/>
       <c r="C375" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D375" s="11"/>
       <c r="E375" s="11"/>
@@ -6254,11 +6166,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="11"/>
       <c r="C376" s="11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D376" s="11"/>
       <c r="E376" s="11"/>
@@ -6266,21 +6178,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="11"/>
       <c r="C377" s="11" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D377" s="11"/>
       <c r="E377" s="11"/>
       <c r="F377" s="11">
         <v>5</v>
       </c>
-      <c r="K377" s="19"/>
-      <c r="L377" s="19"/>
-    </row>
-    <row r="378" spans="1:12" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="11"/>
       <c r="C378" s="11" t="s">
@@ -6291,10 +6201,8 @@
       <c r="F378" s="11">
         <v>5</v>
       </c>
-      <c r="K378"/>
-      <c r="L378"/>
-    </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="11"/>
       <c r="C379" s="11" t="s">
@@ -6306,20 +6214,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="11"/>
       <c r="C380" s="11"/>
-      <c r="D380" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E380" s="22">
+      <c r="D380" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E380" s="20">
         <f>-SUM(E372:E379)</f>
         <v>0</v>
       </c>
       <c r="F380" s="11"/>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="E381">
@@ -6331,7 +6239,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="14" t="s">
         <v>54</v>
@@ -6345,7 +6253,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="12"/>
       <c r="C383" s="12" t="s">
@@ -6357,7 +6265,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="12"/>
       <c r="C384" s="12" t="s">
@@ -6437,10 +6345,10 @@
       <c r="A390" s="1"/>
       <c r="B390" s="12"/>
       <c r="C390" s="12"/>
-      <c r="D390" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E390" s="22">
+      <c r="D390" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E390" s="20">
         <f>-SUM(E382:E389)</f>
         <v>0</v>
       </c>
@@ -6460,12 +6368,12 @@
     </row>
     <row r="393" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A393" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" s="7" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B394" s="8"/>
       <c r="C394" s="8"/>
@@ -6607,10 +6515,10 @@
       <c r="A406" s="7"/>
       <c r="B406" s="8"/>
       <c r="C406" s="8"/>
-      <c r="D406" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E406" s="22">
+      <c r="D406" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E406" s="20">
         <f>-SUM(E289:E405)</f>
         <v>0</v>
       </c>
@@ -6730,7 +6638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" s="10"/>
       <c r="B417" s="10" t="s">
         <v>122</v>
@@ -6742,7 +6650,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="418" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A418" s="10"/>
       <c r="B418" s="10"/>
       <c r="C418" s="10"/>
@@ -6750,74 +6658,35 @@
       <c r="E418" s="10"/>
       <c r="F418" s="10"/>
     </row>
-    <row r="419" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" s="10"/>
       <c r="B419" s="10"/>
       <c r="C419" s="10"/>
-      <c r="D419" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E419" s="22">
+      <c r="D419" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E419" s="20">
         <f>-SUM(E409:E418)</f>
         <v>600</v>
       </c>
       <c r="F419" s="10"/>
-      <c r="G419"/>
-      <c r="H419"/>
-      <c r="I419"/>
-      <c r="J419"/>
-      <c r="K419"/>
-      <c r="L419"/>
-      <c r="M419"/>
-      <c r="N419"/>
-      <c r="O419"/>
-      <c r="P419"/>
-      <c r="Q419"/>
-    </row>
-    <row r="420" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D420"/>
+    </row>
+    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E420">
         <f>SUM(E409:E419)</f>
         <v>0</v>
       </c>
-      <c r="F420" s="19">
+      <c r="F420">
         <f>SUM(F409:F418)</f>
         <v>550</v>
       </c>
-      <c r="G420"/>
-      <c r="H420"/>
-      <c r="I420"/>
-      <c r="J420"/>
-      <c r="K420"/>
-      <c r="L420"/>
-      <c r="M420"/>
-      <c r="N420"/>
-      <c r="O420"/>
-      <c r="P420"/>
-      <c r="Q420"/>
-    </row>
-    <row r="421" spans="1:17" s="19" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="421" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A421" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="B421"/>
-      <c r="C421"/>
-      <c r="D421"/>
-      <c r="E421"/>
-      <c r="F421"/>
-      <c r="G421"/>
-      <c r="H421"/>
-      <c r="I421"/>
-      <c r="J421"/>
-      <c r="K421"/>
-      <c r="L421"/>
-      <c r="M421"/>
-      <c r="N421"/>
-      <c r="O421"/>
-      <c r="P421"/>
-      <c r="Q421"/>
-    </row>
-    <row r="422" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" s="7" t="s">
         <v>36</v>
       </c>
@@ -6832,19 +6701,8 @@
       <c r="F422" s="8">
         <v>2</v>
       </c>
-      <c r="G422"/>
-      <c r="H422"/>
-      <c r="I422"/>
-      <c r="J422"/>
-      <c r="K422"/>
-      <c r="L422"/>
-      <c r="M422"/>
-      <c r="N422"/>
-      <c r="O422"/>
-      <c r="P422"/>
-      <c r="Q422"/>
-    </row>
-    <row r="423" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" s="7"/>
       <c r="B423" s="8"/>
       <c r="C423" s="8" t="s">
@@ -6855,19 +6713,8 @@
       <c r="F423" s="8">
         <v>2</v>
       </c>
-      <c r="G423"/>
-      <c r="H423"/>
-      <c r="I423"/>
-      <c r="J423"/>
-      <c r="K423"/>
-      <c r="L423"/>
-      <c r="M423"/>
-      <c r="N423"/>
-      <c r="O423"/>
-      <c r="P423"/>
-      <c r="Q423"/>
-    </row>
-    <row r="424" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" s="7"/>
       <c r="B424" s="8"/>
       <c r="C424" s="8" t="s">
@@ -6878,19 +6725,8 @@
       <c r="F424" s="8">
         <v>2</v>
       </c>
-      <c r="G424"/>
-      <c r="H424"/>
-      <c r="I424"/>
-      <c r="J424"/>
-      <c r="K424"/>
-      <c r="L424"/>
-      <c r="M424"/>
-      <c r="N424"/>
-      <c r="O424"/>
-      <c r="P424"/>
-      <c r="Q424"/>
-    </row>
-    <row r="425" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" s="7"/>
       <c r="B425" s="8"/>
       <c r="C425" s="8" t="s">
@@ -6901,19 +6737,8 @@
       <c r="F425" s="8">
         <v>2</v>
       </c>
-      <c r="G425"/>
-      <c r="H425"/>
-      <c r="I425"/>
-      <c r="J425"/>
-      <c r="K425"/>
-      <c r="L425"/>
-      <c r="M425"/>
-      <c r="N425"/>
-      <c r="O425"/>
-      <c r="P425"/>
-      <c r="Q425"/>
-    </row>
-    <row r="426" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" s="7"/>
       <c r="B426" s="8"/>
       <c r="C426" s="8" t="s">
@@ -6924,19 +6749,8 @@
       <c r="F426" s="8">
         <v>2</v>
       </c>
-      <c r="G426"/>
-      <c r="H426"/>
-      <c r="I426"/>
-      <c r="J426"/>
-      <c r="K426"/>
-      <c r="L426"/>
-      <c r="M426"/>
-      <c r="N426"/>
-      <c r="O426"/>
-      <c r="P426"/>
-      <c r="Q426"/>
-    </row>
-    <row r="427" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A427" s="8"/>
       <c r="B427" s="8" t="s">
         <v>12</v>
@@ -6947,19 +6761,8 @@
       <c r="F427" s="8">
         <v>5</v>
       </c>
-      <c r="G427"/>
-      <c r="H427"/>
-      <c r="I427"/>
-      <c r="J427"/>
-      <c r="K427"/>
-      <c r="L427"/>
-      <c r="M427"/>
-      <c r="N427"/>
-      <c r="O427"/>
-      <c r="P427"/>
-      <c r="Q427"/>
-    </row>
-    <row r="428" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" s="8"/>
       <c r="B428" s="8" t="s">
         <v>39</v>
@@ -6970,19 +6773,8 @@
       <c r="F428" s="8">
         <v>5</v>
       </c>
-      <c r="G428"/>
-      <c r="H428"/>
-      <c r="I428"/>
-      <c r="J428"/>
-      <c r="K428"/>
-      <c r="L428"/>
-      <c r="M428"/>
-      <c r="N428"/>
-      <c r="O428"/>
-      <c r="P428"/>
-      <c r="Q428"/>
-    </row>
-    <row r="429" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" s="8"/>
       <c r="B429" s="8" t="s">
         <v>68</v>
@@ -6994,7 +6786,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A430" s="8"/>
       <c r="B430" s="8" t="s">
         <v>86</v>
@@ -7006,20 +6798,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="431" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A431" s="8"/>
       <c r="B431" s="8"/>
       <c r="C431" s="8"/>
-      <c r="D431" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E431" s="22">
+      <c r="D431" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E431" s="20">
         <f>-SUM(E422:E430)</f>
         <v>0</v>
       </c>
       <c r="F431" s="8"/>
     </row>
-    <row r="432" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E432">
         <f>SUM(E422:E431)</f>
         <v>0</v>
@@ -7028,10 +6820,8 @@
         <f>SUM(F422:F430)</f>
         <v>30</v>
       </c>
-      <c r="K432" s="19"/>
-      <c r="L432" s="19"/>
-    </row>
-    <row r="433" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" s="8" t="s">
         <v>123</v>
       </c>
@@ -7044,19 +6834,8 @@
       <c r="F433" s="8">
         <v>3</v>
       </c>
-      <c r="G433" s="19"/>
-      <c r="H433" s="19"/>
-      <c r="I433" s="19"/>
-      <c r="J433" s="19"/>
-      <c r="K433" s="19"/>
-      <c r="L433" s="19"/>
-      <c r="M433" s="19"/>
-      <c r="N433" s="19"/>
-      <c r="O433" s="19"/>
-      <c r="P433" s="19"/>
-      <c r="Q433" s="19"/>
-    </row>
-    <row r="434" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" s="8"/>
       <c r="B434" s="8" t="s">
         <v>125</v>
@@ -7067,19 +6846,8 @@
       <c r="F434" s="8">
         <v>4</v>
       </c>
-      <c r="G434" s="19"/>
-      <c r="H434" s="19"/>
-      <c r="I434" s="19"/>
-      <c r="J434" s="19"/>
-      <c r="K434" s="19"/>
-      <c r="L434" s="19"/>
-      <c r="M434" s="19"/>
-      <c r="N434" s="19"/>
-      <c r="O434" s="19"/>
-      <c r="P434" s="19"/>
-      <c r="Q434" s="19"/>
-    </row>
-    <row r="435" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" s="8"/>
       <c r="B435" s="8" t="s">
         <v>126</v>
@@ -7090,19 +6858,8 @@
       <c r="F435" s="8">
         <v>4</v>
       </c>
-      <c r="G435" s="19"/>
-      <c r="H435" s="19"/>
-      <c r="I435" s="19"/>
-      <c r="J435" s="19"/>
-      <c r="K435" s="19"/>
-      <c r="L435" s="19"/>
-      <c r="M435" s="19"/>
-      <c r="N435" s="19"/>
-      <c r="O435" s="19"/>
-      <c r="P435" s="19"/>
-      <c r="Q435" s="19"/>
-    </row>
-    <row r="436" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" s="8"/>
       <c r="B436" s="8" t="s">
         <v>127</v>
@@ -7114,7 +6871,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="437" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" s="8"/>
       <c r="B437" s="8" t="s">
         <v>128</v>
@@ -7126,10 +6883,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="438" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A438" s="8"/>
       <c r="B438" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C438" s="8"/>
       <c r="D438" s="8"/>
@@ -7138,7 +6895,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="439" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A439" s="8"/>
       <c r="B439" s="8" t="s">
         <v>129</v>
@@ -7150,10 +6907,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="440" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A440" s="8"/>
       <c r="B440" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C440" s="8"/>
       <c r="D440" s="8"/>
@@ -7162,7 +6919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="441" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A441" s="8"/>
       <c r="B441" s="8" t="s">
         <v>130</v>
@@ -7174,24 +6931,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="442" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A442" s="8"/>
       <c r="B442" s="8"/>
       <c r="C442" s="8"/>
-      <c r="D442" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E442" s="22">
+      <c r="D442" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E442" s="20">
         <f>-SUM(E433:E441)</f>
         <v>0</v>
       </c>
       <c r="F442" s="8"/>
     </row>
-    <row r="443" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A443"/>
-      <c r="B443"/>
-      <c r="C443"/>
-      <c r="D443"/>
+    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E443">
         <f>SUM(E433:E442)</f>
         <v>0</v>
@@ -7200,19 +6953,8 @@
         <f>SUM(F433:F441)</f>
         <v>35</v>
       </c>
-      <c r="G443"/>
-      <c r="H443"/>
-      <c r="I443"/>
-      <c r="J443"/>
-      <c r="K443"/>
-      <c r="L443"/>
-      <c r="M443"/>
-      <c r="N443"/>
-      <c r="O443"/>
-      <c r="P443"/>
-      <c r="Q443"/>
-    </row>
-    <row r="444" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A444" s="8" t="s">
         <v>131</v>
       </c>
@@ -7225,19 +6967,8 @@
       <c r="F444" s="8">
         <v>3</v>
       </c>
-      <c r="G444"/>
-      <c r="H444"/>
-      <c r="I444"/>
-      <c r="J444"/>
-      <c r="K444"/>
-      <c r="L444"/>
-      <c r="M444"/>
-      <c r="N444"/>
-      <c r="O444"/>
-      <c r="P444"/>
-      <c r="Q444"/>
-    </row>
-    <row r="445" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A445" s="8"/>
       <c r="B445" s="8" t="s">
         <v>133</v>
@@ -7248,19 +6979,8 @@
       <c r="F445" s="8">
         <v>5</v>
       </c>
-      <c r="G445"/>
-      <c r="H445"/>
-      <c r="I445"/>
-      <c r="J445"/>
-      <c r="K445"/>
-      <c r="L445"/>
-      <c r="M445"/>
-      <c r="N445"/>
-      <c r="O445"/>
-      <c r="P445"/>
-      <c r="Q445"/>
-    </row>
-    <row r="446" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A446" s="8"/>
       <c r="B446" s="8" t="s">
         <v>7</v>
@@ -7271,19 +6991,8 @@
       <c r="F446" s="8">
         <v>3</v>
       </c>
-      <c r="G446"/>
-      <c r="H446"/>
-      <c r="I446"/>
-      <c r="J446"/>
-      <c r="K446"/>
-      <c r="L446"/>
-      <c r="M446"/>
-      <c r="N446"/>
-      <c r="O446"/>
-      <c r="P446"/>
-      <c r="Q446"/>
-    </row>
-    <row r="447" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A447" s="8"/>
       <c r="B447" s="8" t="s">
         <v>134</v>
@@ -7294,19 +7003,8 @@
       <c r="F447" s="8">
         <v>3</v>
       </c>
-      <c r="G447"/>
-      <c r="H447"/>
-      <c r="I447"/>
-      <c r="J447"/>
-      <c r="K447"/>
-      <c r="L447"/>
-      <c r="M447"/>
-      <c r="N447"/>
-      <c r="O447"/>
-      <c r="P447"/>
-      <c r="Q447"/>
-    </row>
-    <row r="448" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A448" s="8"/>
       <c r="B448" s="8" t="s">
         <v>135</v>
@@ -7317,19 +7015,8 @@
       <c r="F448" s="8">
         <v>3</v>
       </c>
-      <c r="G448"/>
-      <c r="H448"/>
-      <c r="I448"/>
-      <c r="J448"/>
-      <c r="K448"/>
-      <c r="L448"/>
-      <c r="M448"/>
-      <c r="N448"/>
-      <c r="O448"/>
-      <c r="P448"/>
-      <c r="Q448"/>
-    </row>
-    <row r="449" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A449" s="8"/>
       <c r="B449" s="8" t="s">
         <v>136</v>
@@ -7340,17 +7027,8 @@
       <c r="F449" s="8">
         <v>3</v>
       </c>
-      <c r="G449"/>
-      <c r="H449"/>
-      <c r="I449"/>
-      <c r="J449"/>
-      <c r="M449"/>
-      <c r="N449"/>
-      <c r="O449"/>
-      <c r="P449"/>
-      <c r="Q449"/>
-    </row>
-    <row r="450" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A450" s="8"/>
       <c r="B450" s="8" t="s">
         <v>137</v>
@@ -7362,24 +7040,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="451" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A451" s="8"/>
       <c r="B451" s="8"/>
       <c r="C451" s="8"/>
-      <c r="D451" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E451" s="22">
+      <c r="D451" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E451" s="20">
         <f>-SUM(E444:E450)</f>
         <v>0</v>
       </c>
       <c r="F451" s="8"/>
     </row>
-    <row r="452" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A452"/>
-      <c r="B452"/>
-      <c r="C452"/>
-      <c r="D452"/>
+    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E452">
         <f>SUM(E444:E451)</f>
         <v>0</v>
@@ -7389,9 +7063,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="453" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A453" s="7" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B453" s="7"/>
       <c r="C453" s="8" t="s">
@@ -7405,7 +7079,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="454" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A454" s="7"/>
       <c r="B454" s="7"/>
       <c r="C454" s="8"/>
@@ -7417,7 +7091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="455" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A455" s="7"/>
       <c r="B455" s="7"/>
       <c r="C455" s="8"/>
@@ -7429,7 +7103,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="456" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A456" s="7"/>
       <c r="B456" s="7"/>
       <c r="C456" s="8" t="s">
@@ -7443,7 +7117,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="457" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A457" s="7"/>
       <c r="B457" s="7"/>
       <c r="C457" s="8"/>
@@ -7455,7 +7129,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="458" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A458" s="7"/>
       <c r="B458" s="7"/>
       <c r="C458" s="8"/>
@@ -7467,7 +7141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="459" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A459" s="7"/>
       <c r="B459" s="7"/>
       <c r="C459" s="8"/>
@@ -7479,7 +7153,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="460" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A460" s="7"/>
       <c r="B460" s="7"/>
       <c r="C460" s="8"/>
@@ -7491,11 +7165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="461" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A461"/>
-      <c r="B461"/>
-      <c r="C461"/>
-      <c r="D461"/>
+    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E461">
         <f>SUM(E453:E460)</f>
         <v>0</v>
@@ -7505,25 +7175,20 @@
         <v>40</v>
       </c>
     </row>
-    <row r="462" spans="1:17" s="19" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A462" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="B462"/>
-      <c r="C462"/>
-      <c r="D462"/>
-      <c r="E462"/>
-      <c r="F462"/>
-    </row>
-    <row r="463" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A463" s="7" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B463" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C463" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D463" s="8"/>
       <c r="E463" s="8"/>
@@ -7531,11 +7196,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="464" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A464" s="7"/>
       <c r="B464" s="8"/>
       <c r="C464" s="8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D464" s="8"/>
       <c r="E464" s="8"/>
@@ -7543,10 +7208,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="465" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A465" s="8"/>
       <c r="B465" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C465" s="8" t="s">
         <v>126</v>
@@ -7557,11 +7222,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="466" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A466" s="8"/>
       <c r="B466" s="8"/>
       <c r="C466" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D466" s="8"/>
       <c r="E466" s="8"/>
@@ -7569,7 +7234,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="467" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A467" s="8"/>
       <c r="B467" s="8"/>
       <c r="C467" s="8" t="s">
@@ -7581,11 +7246,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="468" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A468" s="8"/>
       <c r="B468" s="8"/>
       <c r="C468" s="8" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D468" s="8"/>
       <c r="E468" s="8"/>
@@ -7593,11 +7258,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="469" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A469" s="8"/>
       <c r="B469" s="8"/>
       <c r="C469" s="8" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D469" s="8"/>
       <c r="E469" s="8"/>
@@ -7605,40 +7270,39 @@
         <v>5</v>
       </c>
     </row>
-    <row r="470" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A470" s="8"/>
       <c r="B470" s="8"/>
       <c r="C470" s="8"/>
-      <c r="D470" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E470" s="22">
+      <c r="D470" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E470" s="20">
         <f>-SUM(E467:E469)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E471">
         <f>SUM(E463:E470)</f>
         <v>0</v>
       </c>
-      <c r="F471" s="19">
+      <c r="F471">
         <f>SUM(F463:F470)</f>
         <v>45</v>
       </c>
     </row>
-    <row r="472" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A472" s="20" t="s">
+    <row r="472" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A472" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="473" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A473" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="B473" s="12" t="s">
         <v>332</v>
-      </c>
-      <c r="E472"/>
-    </row>
-    <row r="473" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A473" s="14" t="s">
-        <v>333</v>
-      </c>
-      <c r="B473" s="12" t="s">
-        <v>334</v>
       </c>
       <c r="C473" s="12"/>
       <c r="D473" s="12"/>
@@ -7649,12 +7313,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="474" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A474" s="14" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B474" s="12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C474" s="12" t="s">
         <v>46</v>
@@ -7667,11 +7331,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="475" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A475" s="14"/>
       <c r="B475" s="12"/>
       <c r="C475" s="12" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D475" s="12"/>
       <c r="E475" s="12">
@@ -7681,21 +7345,17 @@
         <v>10</v>
       </c>
     </row>
-    <row r="476" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A476" s="20"/>
-      <c r="D476" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E476" s="22">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A476" s="1"/>
+      <c r="D476" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E476" s="20">
         <f>-SUM(E468:E475)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A477"/>
-      <c r="B477"/>
-      <c r="C477"/>
-      <c r="D477"/>
+    <row r="477" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E477">
         <f>SUM(E473:E476)</f>
         <v>0</v>
@@ -7705,41 +7365,17 @@
         <v>30</v>
       </c>
     </row>
-    <row r="478" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="G478" s="19"/>
-      <c r="H478" s="19"/>
-      <c r="I478" s="19"/>
-      <c r="J478" s="19"/>
-      <c r="K478" s="19"/>
-      <c r="L478" s="19"/>
-      <c r="M478" s="19"/>
-      <c r="N478" s="19"/>
-      <c r="O478" s="19"/>
-      <c r="P478" s="19"/>
-      <c r="Q478" s="19"/>
-    </row>
-    <row r="479" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A479" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="G479" s="19"/>
-      <c r="H479" s="19"/>
-      <c r="I479" s="19"/>
-      <c r="J479" s="19"/>
-      <c r="K479" s="19"/>
-      <c r="L479" s="19"/>
-      <c r="M479" s="19"/>
-      <c r="N479" s="19"/>
-      <c r="O479" s="19"/>
-      <c r="P479" s="19"/>
-      <c r="Q479" s="19"/>
-    </row>
-    <row r="480" spans="1:17" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A480" s="14" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B480" s="12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C480" s="12"/>
       <c r="D480" s="12"/>
@@ -7747,21 +7383,10 @@
       <c r="F480" s="12">
         <v>10</v>
       </c>
-      <c r="G480" s="19"/>
-      <c r="H480" s="19"/>
-      <c r="I480" s="19"/>
-      <c r="J480" s="19"/>
-      <c r="K480" s="19"/>
-      <c r="L480" s="19"/>
-      <c r="M480" s="19"/>
-      <c r="N480" s="19"/>
-      <c r="O480" s="19"/>
-      <c r="P480" s="19"/>
-      <c r="Q480" s="19"/>
-    </row>
-    <row r="481" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B481" s="12" t="s">
         <v>103</v>
@@ -7772,22 +7397,11 @@
       <c r="F481" s="12">
         <v>5</v>
       </c>
-      <c r="G481" s="19"/>
-      <c r="H481" s="19"/>
-      <c r="I481" s="19"/>
-      <c r="J481" s="19"/>
-      <c r="K481" s="19"/>
-      <c r="L481" s="19"/>
-      <c r="M481" s="19"/>
-      <c r="N481" s="19"/>
-      <c r="O481" s="19"/>
-      <c r="P481" s="19"/>
-      <c r="Q481" s="19"/>
-    </row>
-    <row r="482" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A482" s="12"/>
       <c r="B482" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C482" s="12"/>
       <c r="D482" s="12"/>
@@ -7795,22 +7409,11 @@
       <c r="F482" s="12">
         <v>5</v>
       </c>
-      <c r="G482" s="19"/>
-      <c r="H482" s="19"/>
-      <c r="I482" s="19"/>
-      <c r="J482" s="19"/>
-      <c r="K482" s="19"/>
-      <c r="L482" s="19"/>
-      <c r="M482" s="19"/>
-      <c r="N482" s="19"/>
-      <c r="O482" s="19"/>
-      <c r="P482" s="19"/>
-      <c r="Q482" s="19"/>
-    </row>
-    <row r="483" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A483" s="12"/>
       <c r="B483" s="12" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C483" s="12"/>
       <c r="D483" s="12"/>
@@ -7818,22 +7421,11 @@
       <c r="F483" s="12">
         <v>5</v>
       </c>
-      <c r="G483" s="19"/>
-      <c r="H483" s="19"/>
-      <c r="I483" s="19"/>
-      <c r="J483" s="19"/>
-      <c r="K483" s="19"/>
-      <c r="L483" s="19"/>
-      <c r="M483" s="19"/>
-      <c r="N483" s="19"/>
-      <c r="O483" s="19"/>
-      <c r="P483" s="19"/>
-      <c r="Q483" s="19"/>
-    </row>
-    <row r="484" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A484" s="12"/>
       <c r="B484" s="12" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C484" s="12"/>
       <c r="D484" s="12"/>
@@ -7841,22 +7433,11 @@
       <c r="F484" s="12">
         <v>5</v>
       </c>
-      <c r="G484" s="19"/>
-      <c r="H484" s="19"/>
-      <c r="I484" s="19"/>
-      <c r="J484" s="19"/>
-      <c r="K484" s="19"/>
-      <c r="L484" s="19"/>
-      <c r="M484" s="19"/>
-      <c r="N484" s="19"/>
-      <c r="O484" s="19"/>
-      <c r="P484" s="19"/>
-      <c r="Q484" s="19"/>
-    </row>
-    <row r="485" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A485" s="12"/>
       <c r="B485" s="12" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C485" s="12"/>
       <c r="D485" s="12"/>
@@ -7864,22 +7445,11 @@
       <c r="F485" s="12">
         <v>5</v>
       </c>
-      <c r="G485" s="19"/>
-      <c r="H485" s="19"/>
-      <c r="I485" s="19"/>
-      <c r="J485" s="19"/>
-      <c r="K485" s="19"/>
-      <c r="L485" s="19"/>
-      <c r="M485" s="19"/>
-      <c r="N485" s="19"/>
-      <c r="O485" s="19"/>
-      <c r="P485" s="19"/>
-      <c r="Q485" s="19"/>
-    </row>
-    <row r="486" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A486" s="12"/>
       <c r="B486" s="12" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C486" s="12"/>
       <c r="D486" s="12"/>
@@ -7887,19 +7457,8 @@
       <c r="F486" s="12">
         <v>5</v>
       </c>
-      <c r="G486" s="19"/>
-      <c r="H486" s="19"/>
-      <c r="I486" s="19"/>
-      <c r="J486" s="19"/>
-      <c r="K486" s="19"/>
-      <c r="L486" s="19"/>
-      <c r="M486" s="19"/>
-      <c r="N486" s="19"/>
-      <c r="O486" s="19"/>
-      <c r="P486" s="19"/>
-      <c r="Q486" s="19"/>
-    </row>
-    <row r="487" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A487" s="12"/>
       <c r="B487" s="12" t="s">
         <v>25</v>
@@ -7910,19 +7469,8 @@
       <c r="F487" s="12">
         <v>5</v>
       </c>
-      <c r="G487" s="19"/>
-      <c r="H487" s="19"/>
-      <c r="I487" s="19"/>
-      <c r="J487" s="19"/>
-      <c r="K487" s="19"/>
-      <c r="L487" s="19"/>
-      <c r="M487" s="19"/>
-      <c r="N487" s="19"/>
-      <c r="O487" s="19"/>
-      <c r="P487" s="19"/>
-      <c r="Q487" s="19"/>
-    </row>
-    <row r="488" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A488" s="12"/>
       <c r="B488" s="12" t="s">
         <v>26</v>
@@ -7933,22 +7481,11 @@
       <c r="F488" s="12">
         <v>5</v>
       </c>
-      <c r="G488" s="19"/>
-      <c r="H488" s="19"/>
-      <c r="I488" s="19"/>
-      <c r="J488" s="19"/>
-      <c r="K488" s="19"/>
-      <c r="L488" s="19"/>
-      <c r="M488" s="19"/>
-      <c r="N488" s="19"/>
-      <c r="O488" s="19"/>
-      <c r="P488" s="19"/>
-      <c r="Q488" s="19"/>
-    </row>
-    <row r="489" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A489" s="12"/>
       <c r="B489" s="12" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C489" s="12"/>
       <c r="D489" s="12"/>
@@ -7956,22 +7493,11 @@
       <c r="F489" s="12">
         <v>5</v>
       </c>
-      <c r="G489" s="19"/>
-      <c r="H489" s="19"/>
-      <c r="I489" s="19"/>
-      <c r="J489" s="19"/>
-      <c r="K489" s="19"/>
-      <c r="L489" s="19"/>
-      <c r="M489" s="19"/>
-      <c r="N489" s="19"/>
-      <c r="O489" s="19"/>
-      <c r="P489" s="19"/>
-      <c r="Q489" s="19"/>
-    </row>
-    <row r="490" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A490" s="12"/>
       <c r="B490" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C490" s="12"/>
       <c r="D490" s="12"/>
@@ -7979,68 +7505,35 @@
       <c r="F490" s="12">
         <v>5</v>
       </c>
-      <c r="G490" s="19"/>
-      <c r="H490" s="19"/>
-      <c r="I490" s="19"/>
-      <c r="J490" s="19"/>
-      <c r="K490" s="19"/>
-      <c r="L490" s="19"/>
-      <c r="M490" s="19"/>
-      <c r="N490" s="19"/>
-      <c r="O490" s="19"/>
-      <c r="P490" s="19"/>
-      <c r="Q490" s="19"/>
-    </row>
-    <row r="491" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" s="12"/>
       <c r="B491" s="12"/>
       <c r="C491" s="12"/>
-      <c r="D491" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E491" s="22">
+      <c r="D491" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E491" s="20">
         <f>-SUM(E484:E490)</f>
         <v>0</v>
       </c>
-      <c r="F491" s="19"/>
-      <c r="G491" s="19"/>
-      <c r="H491" s="19"/>
-      <c r="I491" s="19"/>
-      <c r="J491" s="19"/>
-      <c r="M491" s="19"/>
-      <c r="N491" s="19"/>
-      <c r="O491" s="19"/>
-      <c r="P491" s="19"/>
-      <c r="Q491" s="19"/>
-    </row>
-    <row r="492" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A492" s="19"/>
-      <c r="B492" s="19"/>
-      <c r="C492" s="19"/>
-      <c r="D492" s="19"/>
+    </row>
+    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E492">
         <f>SUM(E480:E491)</f>
         <v>0</v>
       </c>
-      <c r="F492" s="19">
+      <c r="F492">
         <f>SUM(F480:F491)</f>
         <v>60</v>
       </c>
     </row>
-    <row r="493" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A493" s="19"/>
-      <c r="B493" s="19"/>
-      <c r="C493" s="19"/>
-      <c r="D493" s="19"/>
-      <c r="E493" s="19"/>
-      <c r="F493" s="19"/>
-    </row>
-    <row r="494" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A494" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B494" s="10" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C494" s="10"/>
       <c r="D494" s="10"/>
@@ -8050,9 +7543,9 @@
       </c>
       <c r="H494" s="18"/>
     </row>
-    <row r="495" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A495" s="9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B495" s="10" t="s">
         <v>103</v>
@@ -8065,10 +7558,10 @@
       </c>
       <c r="H495" s="18"/>
     </row>
-    <row r="496" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A496" s="10"/>
       <c r="B496" s="10" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C496" s="10"/>
       <c r="D496" s="10"/>
@@ -8081,7 +7574,7 @@
     <row r="497" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A497" s="10"/>
       <c r="B497" s="10" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C497" s="10"/>
       <c r="D497" s="10"/>
@@ -8094,7 +7587,7 @@
     <row r="498" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A498" s="10"/>
       <c r="B498" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C498" s="10"/>
       <c r="D498" s="10"/>
@@ -8106,7 +7599,7 @@
     <row r="499" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A499" s="10"/>
       <c r="B499" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C499" s="10"/>
       <c r="D499" s="10"/>
@@ -8118,7 +7611,7 @@
     <row r="500" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A500" s="10"/>
       <c r="B500" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C500" s="10"/>
       <c r="D500" s="10"/>
@@ -8154,7 +7647,7 @@
     <row r="503" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A503" s="10"/>
       <c r="B503" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C503" s="10"/>
       <c r="D503" s="10"/>
@@ -8166,7 +7659,7 @@
     <row r="504" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A504" s="10"/>
       <c r="B504" s="10" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C504" s="10"/>
       <c r="D504" s="10"/>
@@ -8179,43 +7672,30 @@
       <c r="A505" s="10"/>
       <c r="B505" s="10"/>
       <c r="C505" s="10"/>
-      <c r="D505" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E505" s="22">
+      <c r="D505" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E505" s="20">
         <f>-SUM(E498:E504)</f>
         <v>0</v>
       </c>
-      <c r="F505" s="19"/>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A506" s="19"/>
-      <c r="B506" s="19"/>
-      <c r="C506" s="19"/>
-      <c r="D506" s="19"/>
       <c r="E506">
         <f>SUM(E494:E505)</f>
         <v>0</v>
       </c>
-      <c r="F506" s="19">
+      <c r="F506">
         <f>SUM(F494:F505)</f>
         <v>60</v>
       </c>
     </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A507" s="19"/>
-      <c r="B507" s="19"/>
-      <c r="C507" s="19"/>
-      <c r="D507" s="19"/>
-      <c r="E507" s="19"/>
-      <c r="F507" s="19"/>
-    </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A508" s="13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B508" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C508" s="11"/>
       <c r="D508" s="11"/>
@@ -8226,7 +7706,7 @@
     </row>
     <row r="509" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A509" s="13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B509" s="11" t="s">
         <v>103</v>
@@ -8241,7 +7721,7 @@
     <row r="510" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A510" s="11"/>
       <c r="B510" s="11" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C510" s="11"/>
       <c r="D510" s="11"/>
@@ -8253,7 +7733,7 @@
     <row r="511" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A511" s="11"/>
       <c r="B511" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C511" s="11"/>
       <c r="D511" s="11"/>
@@ -8265,7 +7745,7 @@
     <row r="512" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A512" s="11"/>
       <c r="B512" s="11" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C512" s="11"/>
       <c r="D512" s="11"/>
@@ -8277,7 +7757,7 @@
     <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" s="11"/>
       <c r="B513" s="11" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C513" s="11"/>
       <c r="D513" s="11"/>
@@ -8289,7 +7769,7 @@
     <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" s="11"/>
       <c r="B514" s="11" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C514" s="11"/>
       <c r="D514" s="11"/>
@@ -8325,7 +7805,7 @@
     <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" s="11"/>
       <c r="B517" s="11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C517" s="11"/>
       <c r="D517" s="11"/>
@@ -8337,7 +7817,7 @@
     <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" s="11"/>
       <c r="B518" s="11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C518" s="11"/>
       <c r="D518" s="11"/>
@@ -8350,36 +7830,24 @@
       <c r="A519" s="11"/>
       <c r="B519" s="11"/>
       <c r="C519" s="11"/>
-      <c r="D519" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="E519" s="22">
+      <c r="D519" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E519" s="20">
         <f>-SUM(E512:E518)</f>
         <v>0</v>
       </c>
       <c r="F519" s="11"/>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A520" s="19"/>
-      <c r="B520" s="19"/>
-      <c r="C520" s="19"/>
-      <c r="D520" s="19"/>
       <c r="E520">
         <f>SUM(E508:E519)</f>
         <v>0</v>
       </c>
-      <c r="F520" s="19">
+      <c r="F520">
         <f>SUM(F508:F519)</f>
         <v>60</v>
       </c>
-    </row>
-    <row r="521" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A521" s="19"/>
-      <c r="B521" s="19"/>
-      <c r="C521" s="19"/>
-      <c r="D521" s="19"/>
-      <c r="E521" s="19"/>
-      <c r="F521" s="19"/>
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" s="7"/>
@@ -8400,7 +7868,9 @@
       </c>
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A525" s="9"/>
+      <c r="A525" s="9" t="s">
+        <v>365</v>
+      </c>
       <c r="B525" t="s">
         <v>185</v>
       </c>
@@ -8418,7 +7888,9 @@
       </c>
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A526" s="13"/>
+      <c r="A526" s="13" t="s">
+        <v>366</v>
+      </c>
       <c r="B526" t="s">
         <v>186</v>
       </c>
@@ -8436,7 +7908,9 @@
       </c>
     </row>
     <row r="527" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A527" s="14"/>
+      <c r="A527" s="14" t="s">
+        <v>364</v>
+      </c>
       <c r="B527" t="s">
         <v>187</v>
       </c>
@@ -8455,22 +7929,22 @@
     </row>
     <row r="531" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F531" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G531" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="532" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D532" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G532" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="533" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="F533" s="28">
+      <c r="F533" s="23">
         <v>0.45</v>
       </c>
       <c r="G533">
@@ -8478,7 +7952,7 @@
       </c>
     </row>
     <row r="534" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="F534" s="28">
+      <c r="F534" s="23">
         <f>F533+(F542-F533)/9</f>
         <v>0.5</v>
       </c>
@@ -8487,7 +7961,7 @@
       </c>
     </row>
     <row r="535" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="F535" s="28">
+      <c r="F535" s="23">
         <f>F534+(F542-F533)/9</f>
         <v>0.55000000000000004</v>
       </c>
@@ -8496,7 +7970,7 @@
       </c>
     </row>
     <row r="536" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="F536" s="28">
+      <c r="F536" s="23">
         <f>F535+(F542-F533)/9</f>
         <v>0.60000000000000009</v>
       </c>
@@ -8505,7 +7979,7 @@
       </c>
     </row>
     <row r="537" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="F537" s="28">
+      <c r="F537" s="23">
         <f>F536+(F542-F533)/9</f>
         <v>0.65000000000000013</v>
       </c>
@@ -8514,7 +7988,7 @@
       </c>
     </row>
     <row r="538" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="F538" s="28">
+      <c r="F538" s="23">
         <f>F537+(F542-F533)/9</f>
         <v>0.70000000000000018</v>
       </c>
@@ -8523,7 +7997,7 @@
       </c>
     </row>
     <row r="539" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="F539" s="28">
+      <c r="F539" s="23">
         <f>F538+(F542-F533)/9</f>
         <v>0.75000000000000022</v>
       </c>
@@ -8532,7 +8006,7 @@
       </c>
     </row>
     <row r="540" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="F540" s="28">
+      <c r="F540" s="23">
         <f>F539+(F542-F533)/9</f>
         <v>0.80000000000000027</v>
       </c>
@@ -8541,7 +8015,7 @@
       </c>
     </row>
     <row r="541" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="F541" s="28">
+      <c r="F541" s="23">
         <f>F540+(F542-F533)/9</f>
         <v>0.85000000000000031</v>
       </c>
@@ -8550,7 +8024,7 @@
       </c>
     </row>
     <row r="542" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="F542" s="28">
+      <c r="F542" s="23">
         <v>0.9</v>
       </c>
       <c r="G542">
@@ -8559,7 +8033,7 @@
     </row>
     <row r="543" spans="4:7" x14ac:dyDescent="0.25">
       <c r="E543" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -8570,8 +8044,8 @@
     <mergeCell ref="G189:G204"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B21"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B14">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B21" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B14" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8582,31 +8056,31 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="21"/>
+    <col min="4" max="4" width="11.42578125" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="33" t="s">
-        <v>226</v>
-      </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
+      <c r="A1" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>210</v>
-      </c>
-      <c r="D4" s="21">
+        <v>208</v>
+      </c>
+      <c r="D4" s="19">
         <v>-1</v>
       </c>
     </row>
@@ -8614,39 +8088,39 @@
       <c r="B5" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="19">
         <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D6" s="21">
+        <v>210</v>
+      </c>
+      <c r="D6" s="19">
         <v>-0.5</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>213</v>
-      </c>
-      <c r="D7" s="21">
+        <v>211</v>
+      </c>
+      <c r="D7" s="19">
         <v>-0.5</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>214</v>
-      </c>
-      <c r="D8" s="21">
+        <v>212</v>
+      </c>
+      <c r="D8" s="19">
         <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D9" s="21">
+        <v>213</v>
+      </c>
+      <c r="D9" s="19">
         <v>-1</v>
       </c>
     </row>
@@ -8654,261 +8128,205 @@
       <c r="B10" t="s">
         <v>175</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="19">
         <v>-0.5</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>211</v>
-      </c>
-      <c r="D11" s="21">
+        <v>209</v>
+      </c>
+      <c r="D11" s="19">
         <v>-0.5</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D12" s="21">
+        <v>215</v>
+      </c>
+      <c r="D12" s="19">
         <v>-0.5</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>216</v>
-      </c>
-      <c r="D13" s="21">
+        <v>214</v>
+      </c>
+      <c r="D13" s="19">
         <v>-0.5</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>218</v>
-      </c>
-      <c r="D14" s="21">
+        <v>216</v>
+      </c>
+      <c r="D14" s="19">
         <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>219</v>
-      </c>
-      <c r="D15" s="21">
+        <v>217</v>
+      </c>
+      <c r="D15" s="19">
         <v>-0.3</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
+        <v>223</v>
+      </c>
+      <c r="D16" s="19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
         <v>225</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D17" s="19">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>226</v>
+      </c>
+      <c r="D18" s="19">
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>227</v>
-      </c>
-      <c r="D17" s="21">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>228</v>
-      </c>
-      <c r="D18" s="21">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" s="19">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>144</v>
+      </c>
+      <c r="D23" s="19">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>145</v>
+      </c>
+      <c r="D24" s="19">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C25" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="19">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>148</v>
+      </c>
+      <c r="D26" s="19">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>149</v>
+      </c>
+      <c r="D27" s="19">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>150</v>
+      </c>
+      <c r="D28" s="19">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>163</v>
+      </c>
+      <c r="C31" t="s">
+        <v>166</v>
+      </c>
+      <c r="D31" s="19">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>167</v>
+      </c>
+      <c r="D32" s="19">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>149</v>
+      </c>
+      <c r="D33" s="19">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>221</v>
+      </c>
+      <c r="D34" s="19">
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="D22" s="23">
-        <v>-0.25</v>
-      </c>
-      <c r="E22" s="19"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D23" s="23">
-        <v>-0.25</v>
-      </c>
-      <c r="E23" s="19"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="D24" s="23">
-        <v>-0.25</v>
-      </c>
-      <c r="E24" s="19"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="D25" s="23">
-        <v>-0.25</v>
-      </c>
-      <c r="E25" s="19"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="D26" s="23">
-        <v>-0.25</v>
-      </c>
-      <c r="E26" s="19"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="D27" s="23">
-        <v>-0.25</v>
-      </c>
-      <c r="E27" s="19"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="D28" s="23">
-        <v>-0.25</v>
-      </c>
-      <c r="E28" s="19"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="19"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="19"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="D31" s="23">
-        <v>-0.25</v>
-      </c>
-      <c r="E31" s="19"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="D32" s="23">
-        <v>-0.25</v>
-      </c>
-      <c r="E32" s="19"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="D33" s="23">
-        <v>-0.25</v>
-      </c>
-      <c r="E33" s="19"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="23">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>168</v>
+      </c>
+      <c r="C35" t="s">
+        <v>169</v>
+      </c>
+      <c r="D35" s="19">
         <v>-1</v>
       </c>
-      <c r="E34" s="19"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="19"/>
-      <c r="B35" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="C35" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="D35" s="23">
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
+        <v>170</v>
+      </c>
+      <c r="D36" s="19">
         <v>-1</v>
       </c>
-      <c r="E35" s="19"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="19"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="D36" s="23">
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>171</v>
+      </c>
+      <c r="D37" s="19">
         <v>-1</v>
       </c>
-      <c r="E36" s="19"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="19"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="D37" s="23">
-        <v>-1</v>
-      </c>
-      <c r="E37" s="19"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="19"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ProjectManagement/EvaluationHW.xlsx
+++ b/ProjectManagement/EvaluationHW.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sherwin\EmdenLeer University\ML\ML24-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\Winter 2024-25\ML project\ML24-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2FF9487-E29F-4253-A513-8B676CF689DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F786C5-4C32-42E1-9CB1-A19D8C16ADDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="2" r:id="rId1"/>
@@ -20,15 +20,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -174,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="378">
   <si>
     <t>Literature</t>
   </si>
@@ -386,9 +377,6 @@
     <t>Short Description</t>
   </si>
   <si>
-    <t>github Project</t>
-  </si>
-  <si>
     <t>Author:</t>
   </si>
   <si>
@@ -1283,7 +1271,34 @@
     <t xml:space="preserve">Machine Learning Project - Car Licence Plate Identification with a Jetson Nano	</t>
   </si>
   <si>
-    <t>Application of Using Jetson Nano to Detect the Licence Plate Number of Cars, Applying it on a Database of Licence Plates.</t>
+    <t>Ranjeetsing Tawar</t>
+  </si>
+  <si>
+    <t>Ranjeetsing</t>
+  </si>
+  <si>
+    <t>Tawar</t>
+  </si>
+  <si>
+    <t>Ranjeet9823</t>
+  </si>
+  <si>
+    <t>Efficient license plate recognition using a Jetson Nano for real-time car license plate identification.</t>
+  </si>
+  <si>
+    <t>Mansour</t>
+  </si>
+  <si>
+    <t>Phoulady</t>
+  </si>
+  <si>
+    <t>Hemanth</t>
+  </si>
+  <si>
+    <t>Prabhakaran</t>
+  </si>
+  <si>
+    <t>Hemanth-Jp</t>
   </si>
 </sst>
 </file>
@@ -1456,10 +1471,19 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="mediumDashed">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1468,7 +1492,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1513,6 +1537,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1795,128 +1822,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M543"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="33.75" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:6" ht="33.6" x14ac:dyDescent="0.65">
       <c r="A2" s="22" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B6" s="24"/>
       <c r="C6" s="24"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="F10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>369</v>
+      </c>
+      <c r="B11" t="s">
+        <v>370</v>
+      </c>
+      <c r="C11" s="29">
+        <v>7026116</v>
+      </c>
+      <c r="D11" t="s">
+        <v>371</v>
+      </c>
+      <c r="F11" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>373</v>
+      </c>
+      <c r="B12" t="s">
+        <v>374</v>
+      </c>
+      <c r="C12" s="3">
+        <v>7025671</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>375</v>
+      </c>
+      <c r="B13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C13" s="3">
+        <v>7026000</v>
+      </c>
+      <c r="D13" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F10" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C11" s="3"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C12" s="3"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B14" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B14" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B16" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B18" s="4">
+        <v>45565</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="4">
+        <v>45688</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B18" s="4"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B19" s="4"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+    <row r="25" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A25" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B22" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A25" s="6" t="s">
+    </row>
+    <row r="27" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+      <c r="A27" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
       <c r="B28" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
@@ -1927,13 +1989,13 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="12"/>
       <c r="B29" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
@@ -1944,13 +2006,13 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
@@ -1961,13 +2023,13 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="10"/>
       <c r="B31" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="10"/>
@@ -1978,13 +2040,13 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="12"/>
       <c r="B32" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
@@ -1995,13 +2057,13 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="11"/>
       <c r="B33" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
@@ -2012,15 +2074,15 @@
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>0</v>
       </c>
@@ -2034,7 +2096,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>
       <c r="B37" s="11" t="s">
         <v>27</v>
@@ -2046,7 +2108,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="11"/>
       <c r="B38" s="11" t="s">
         <v>3</v>
@@ -2058,7 +2120,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="11"/>
       <c r="B39" s="11" t="s">
         <v>4</v>
@@ -2070,7 +2132,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="11"/>
       <c r="B40" s="11" t="s">
         <v>5</v>
@@ -2082,10 +2144,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="11"/>
       <c r="B41" s="11" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
@@ -2094,13 +2156,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>
       <c r="B42" s="11" t="s">
         <v>1</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
@@ -2108,11 +2170,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>
       <c r="B43" s="11"/>
       <c r="C43" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D43" s="11"/>
       <c r="E43" s="11"/>
@@ -2120,11 +2182,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="11"/>
       <c r="B44" s="11"/>
       <c r="C44" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
@@ -2132,11 +2194,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="11"/>
       <c r="B45" s="11"/>
       <c r="C45" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D45" s="11"/>
       <c r="E45" s="11"/>
@@ -2144,11 +2206,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="11"/>
       <c r="B46" s="11"/>
       <c r="C46" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D46" s="11"/>
       <c r="E46" s="11"/>
@@ -2156,11 +2218,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="11"/>
       <c r="B47" s="11"/>
       <c r="C47" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D47" s="11"/>
       <c r="E47" s="11"/>
@@ -2168,11 +2230,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="11"/>
       <c r="B48" s="11"/>
       <c r="C48" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D48" s="11"/>
       <c r="E48" s="11"/>
@@ -2180,12 +2242,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="11"/>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
       <c r="D49" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E49" s="20">
         <f>-SUM(E36:E48)</f>
@@ -2193,7 +2255,7 @@
       </c>
       <c r="F49" s="11"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="11"/>
       <c r="E50">
         <f>SUM(E36:E49)</f>
@@ -2204,22 +2266,22 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:12" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K52"/>
       <c r="L52"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="12"/>
@@ -2227,16 +2289,16 @@
         <v>10</v>
       </c>
       <c r="G53" s="25" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="14"/>
       <c r="B54" s="14" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="12"/>
@@ -2245,7 +2307,7 @@
       </c>
       <c r="G54" s="25"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="14"/>
       <c r="B55" s="14"/>
       <c r="C55" s="12" t="s">
@@ -2258,11 +2320,11 @@
       </c>
       <c r="G55" s="25"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="14"/>
       <c r="B56" s="12"/>
       <c r="C56" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D56" s="12"/>
       <c r="E56" s="12"/>
@@ -2271,11 +2333,11 @@
       </c>
       <c r="G56" s="25"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="14"/>
       <c r="B57" s="14"/>
       <c r="C57" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D57" s="12"/>
       <c r="E57" s="12"/>
@@ -2284,7 +2346,7 @@
       </c>
       <c r="G57" s="25"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="14"/>
       <c r="B58" s="14"/>
       <c r="C58" s="12" t="s">
@@ -2297,7 +2359,7 @@
       </c>
       <c r="G58" s="25"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="14"/>
       <c r="B59" s="14"/>
       <c r="C59" s="12" t="s">
@@ -2310,11 +2372,11 @@
       </c>
       <c r="G59" s="25"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="14"/>
       <c r="B60" s="14"/>
       <c r="C60" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D60" s="12"/>
       <c r="E60" s="12"/>
@@ -2323,11 +2385,11 @@
       </c>
       <c r="G60" s="25"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="14"/>
       <c r="B61" s="14"/>
       <c r="C61" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D61" s="12"/>
       <c r="E61" s="12"/>
@@ -2336,11 +2398,11 @@
       </c>
       <c r="G61" s="25"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="14"/>
       <c r="B62" s="14"/>
       <c r="C62" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D62" s="12"/>
       <c r="E62" s="12"/>
@@ -2349,13 +2411,13 @@
       </c>
       <c r="G62" s="25"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="14"/>
       <c r="B63" s="14" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D63" s="12"/>
       <c r="E63" s="12"/>
@@ -2364,11 +2426,11 @@
       </c>
       <c r="G63" s="25"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="14"/>
       <c r="B64" s="14"/>
       <c r="C64" s="12" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D64" s="12"/>
       <c r="E64" s="12"/>
@@ -2377,11 +2439,11 @@
       </c>
       <c r="G64" s="25"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="14"/>
       <c r="B65" s="14"/>
       <c r="C65" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D65" s="12"/>
       <c r="E65" s="12"/>
@@ -2390,12 +2452,12 @@
       </c>
       <c r="G65" s="25"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="14"/>
       <c r="B66" s="14"/>
       <c r="C66" s="12"/>
       <c r="D66" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E66" s="20">
         <f>-SUM(E53:E65)</f>
@@ -2404,7 +2466,7 @@
       <c r="F66" s="12"/>
       <c r="G66" s="25"/>
     </row>
-    <row r="67" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="E67">
@@ -2418,23 +2480,23 @@
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
     </row>
-    <row r="68" spans="1:13" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="K68"/>
       <c r="L68"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="str">
         <f>$A$68</f>
         <v>Document Manufacturing and Assembly</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D69" s="10"/>
       <c r="E69" s="10"/>
@@ -2442,10 +2504,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="9"/>
       <c r="B70" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>42</v>
@@ -2456,11 +2518,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="9"/>
       <c r="B71" s="9"/>
       <c r="C71" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D71" s="10"/>
       <c r="E71" s="10"/>
@@ -2468,7 +2530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="9"/>
       <c r="B72" s="9"/>
       <c r="C72" s="10" t="s">
@@ -2480,11 +2542,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="9"/>
       <c r="B73" s="9"/>
       <c r="C73" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D73" s="10"/>
       <c r="E73" s="10"/>
@@ -2492,11 +2554,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="9"/>
       <c r="B74" s="9"/>
       <c r="C74" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D74" s="10"/>
       <c r="E74" s="10"/>
@@ -2504,12 +2566,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="9"/>
       <c r="B75" s="9"/>
       <c r="C75" s="10"/>
       <c r="D75" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E75" s="20">
         <f>-SUM(E69:E74)</f>
@@ -2517,7 +2579,7 @@
       </c>
       <c r="F75" s="10"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="E76">
@@ -2529,23 +2591,23 @@
         <v>40</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
     </row>
-    <row r="78" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D79" s="11"/>
       <c r="E79" s="11"/>
@@ -2553,11 +2615,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="13"/>
       <c r="B80" s="11"/>
       <c r="C80" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D80" s="11"/>
       <c r="E80" s="11"/>
@@ -2565,11 +2627,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="13"/>
       <c r="B81" s="11"/>
       <c r="C81" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D81" s="11"/>
       <c r="E81" s="11"/>
@@ -2577,10 +2639,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="13"/>
       <c r="B82" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C82" s="11" t="s">
         <v>7</v>
@@ -2591,11 +2653,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="13"/>
       <c r="B83" s="13"/>
       <c r="C83" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D83" s="11"/>
       <c r="E83" s="11"/>
@@ -2603,11 +2665,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="13"/>
       <c r="B84" s="13"/>
       <c r="C84" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D84" s="11"/>
       <c r="E84" s="11"/>
@@ -2615,11 +2677,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="13"/>
       <c r="B85" s="13"/>
       <c r="C85" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D85" s="11"/>
       <c r="E85" s="11"/>
@@ -2627,12 +2689,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="13"/>
       <c r="B86" s="13"/>
       <c r="C86" s="13"/>
       <c r="D86" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E86" s="20">
         <f>-SUM(E79:E85)</f>
@@ -2640,7 +2702,7 @@
       </c>
       <c r="F86" s="13"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="E87">
@@ -2652,18 +2714,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="1:6" ht="21" x14ac:dyDescent="0.4">
       <c r="A89" s="21" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="14" t="s">
         <v>6</v>
       </c>
@@ -2677,7 +2739,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="12"/>
       <c r="B92" s="12"/>
       <c r="C92" s="12" t="s">
@@ -2689,7 +2751,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="12"/>
       <c r="B93" s="12"/>
       <c r="C93" s="12" t="s">
@@ -2701,7 +2763,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="12"/>
       <c r="B94" s="12"/>
       <c r="C94" s="12" t="s">
@@ -2713,7 +2775,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="12"/>
       <c r="B95" s="12"/>
       <c r="C95" s="12" t="s">
@@ -2725,11 +2787,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="12"/>
       <c r="B96" s="12"/>
       <c r="C96" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D96" s="12"/>
       <c r="E96" s="12"/>
@@ -2737,12 +2799,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="12"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
       <c r="D97" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E97" s="20">
         <f>-SUM(E91:E96)</f>
@@ -2750,7 +2812,7 @@
       </c>
       <c r="F97" s="12"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E98">
         <f>SUM(E91:E97)</f>
         <v>0</v>
@@ -2760,17 +2822,17 @@
         <v>40</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="10"/>
@@ -2779,7 +2841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="9"/>
       <c r="B101" s="10" t="s">
         <v>13</v>
@@ -2791,7 +2853,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="10"/>
       <c r="B102" s="10" t="s">
         <v>14</v>
@@ -2803,7 +2865,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="10"/>
       <c r="B103" s="10" t="s">
         <v>15</v>
@@ -2815,7 +2877,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="10"/>
       <c r="B104" s="10" t="s">
         <v>16</v>
@@ -2827,7 +2889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="10"/>
       <c r="B105" s="10" t="s">
         <v>17</v>
@@ -2839,7 +2901,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="10"/>
       <c r="B106" s="10" t="s">
         <v>19</v>
@@ -2851,7 +2913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="10"/>
       <c r="B107" s="16" t="s">
         <v>18</v>
@@ -2863,19 +2925,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="10"/>
       <c r="B108" s="16"/>
       <c r="C108" s="10"/>
       <c r="D108" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E108" s="20">
         <f>-SUM(E100:E107)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E109">
         <f>SUM(E100:E108)</f>
         <v>0</v>
@@ -2885,139 +2947,139 @@
         <v>40</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="13" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B113" s="11" t="s">
         <v>5</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F113" s="11">
         <v>20</v>
       </c>
       <c r="G113" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B114" s="11"/>
       <c r="C114" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D114" s="11"/>
       <c r="E114" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F114" s="11">
         <v>10</v>
       </c>
       <c r="G114" s="26"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="11"/>
       <c r="B115" s="11"/>
       <c r="C115" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D115" s="11"/>
       <c r="E115" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F115" s="11">
         <v>10</v>
       </c>
       <c r="G115" s="26"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="11"/>
       <c r="B116" s="11"/>
       <c r="C116" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D116" s="11"/>
       <c r="E116" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F116" s="11">
         <v>10</v>
       </c>
       <c r="G116" s="26"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="13"/>
       <c r="B117" s="11"/>
       <c r="C117" s="11" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D117" s="11"/>
       <c r="E117" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F117" s="11">
         <v>10</v>
       </c>
       <c r="G117" s="26"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="11"/>
       <c r="B118" s="11"/>
       <c r="C118" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D118" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D118" s="11" t="s">
-        <v>101</v>
-      </c>
       <c r="E118" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F118" s="11">
         <v>10</v>
       </c>
       <c r="G118" s="26"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="11"/>
       <c r="B119" s="11"/>
       <c r="C119" s="11"/>
       <c r="D119" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E119" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F119" s="11">
         <v>10</v>
       </c>
       <c r="G119" s="26"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="13"/>
       <c r="B120" s="11"/>
       <c r="C120" s="11"/>
       <c r="D120" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F120" s="11">
         <v>10</v>
       </c>
       <c r="G120" s="26"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="13"/>
       <c r="B121" s="11"/>
       <c r="C121" s="11"/>
@@ -3025,34 +3087,34 @@
         <v>12</v>
       </c>
       <c r="E121" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F121" s="11">
         <v>10</v>
       </c>
       <c r="G121" s="26"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="13"/>
       <c r="B122" s="11"/>
       <c r="C122" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D122" s="11"/>
       <c r="E122" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F122" s="11">
         <v>20</v>
       </c>
       <c r="G122" s="26"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="11"/>
       <c r="B123" s="11"/>
       <c r="C123" s="11"/>
       <c r="D123" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E123" s="20">
         <f>-SUM(E113:E122)</f>
@@ -3060,7 +3122,7 @@
       </c>
       <c r="G123" s="26"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E124">
         <f>SUM(E117:E123)</f>
         <v>0</v>
@@ -3071,35 +3133,35 @@
       </c>
       <c r="G124" s="26"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G125" s="26"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B126" s="12" t="s">
         <v>5</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D126" s="12"/>
       <c r="E126" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F126" s="12">
         <v>10</v>
       </c>
       <c r="G126" s="26"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="14" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B127" s="12"/>
       <c r="C127" s="12" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D127" s="12"/>
       <c r="E127" s="12"/>
@@ -3108,11 +3170,11 @@
       </c>
       <c r="G127" s="26"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="14"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D128" s="12"/>
       <c r="E128" s="12"/>
@@ -3121,71 +3183,71 @@
       </c>
       <c r="G128" s="26"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="14"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D129" s="12"/>
       <c r="E129" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F129" s="12">
         <v>10</v>
       </c>
       <c r="G129" s="26"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D130" s="12"/>
       <c r="E130" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F130" s="12">
         <v>10</v>
       </c>
       <c r="G130" s="26"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="12"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D131" s="12"/>
       <c r="E131" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F131" s="12">
         <v>8</v>
       </c>
       <c r="G131" s="26"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="12"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D132" s="12"/>
       <c r="E132" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F132" s="12">
         <v>8</v>
       </c>
       <c r="G132" s="26"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D133" s="12"/>
       <c r="E133" s="12"/>
@@ -3194,27 +3256,27 @@
       </c>
       <c r="G133" s="26"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D134" s="12"/>
       <c r="E134" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F134" s="12">
         <v>5</v>
       </c>
       <c r="G134" s="26"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="12"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
       <c r="D135" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E135" s="20">
         <f>-SUM(E126:E134)</f>
@@ -3222,7 +3284,7 @@
       </c>
       <c r="G135" s="26"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E136">
         <f>SUM(E126:E135)</f>
         <v>0</v>
@@ -3233,12 +3295,12 @@
       </c>
       <c r="G136" s="26"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G137" s="26"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B138" s="10" t="s">
         <v>5</v>
@@ -3249,7 +3311,7 @@
       </c>
       <c r="D138" s="10"/>
       <c r="E138" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F138" s="10">
         <f t="shared" ref="F138:F146" si="1">F126</f>
@@ -3257,7 +3319,7 @@
       </c>
       <c r="G138" s="26"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="10" t="str">
         <f>$A$127</f>
         <v>e.g. camera, IMU, SPI</v>
@@ -3269,7 +3331,7 @@
       </c>
       <c r="D139" s="10"/>
       <c r="E139" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F139" s="10">
         <f t="shared" si="1"/>
@@ -3277,7 +3339,7 @@
       </c>
       <c r="G139" s="26"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="10"/>
       <c r="B140" s="10"/>
       <c r="C140" s="10" t="str">
@@ -3286,7 +3348,7 @@
       </c>
       <c r="D140" s="10"/>
       <c r="E140" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F140" s="10">
         <f t="shared" si="1"/>
@@ -3294,7 +3356,7 @@
       </c>
       <c r="G140" s="26"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="9"/>
       <c r="B141" s="10"/>
       <c r="C141" s="10" t="str">
@@ -3303,7 +3365,7 @@
       </c>
       <c r="D141" s="10"/>
       <c r="E141" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F141" s="10">
         <f t="shared" si="1"/>
@@ -3311,7 +3373,7 @@
       </c>
       <c r="G141" s="26"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="9"/>
       <c r="B142" s="10"/>
       <c r="C142" s="10" t="str">
@@ -3320,7 +3382,7 @@
       </c>
       <c r="D142" s="10"/>
       <c r="E142" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F142" s="10">
         <f t="shared" si="1"/>
@@ -3328,7 +3390,7 @@
       </c>
       <c r="G142" s="26"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="9"/>
       <c r="B143" s="10"/>
       <c r="C143" s="10" t="str">
@@ -3343,7 +3405,7 @@
       </c>
       <c r="G143" s="26"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="9"/>
       <c r="B144" s="10"/>
       <c r="C144" s="10" t="str">
@@ -3352,7 +3414,7 @@
       </c>
       <c r="D144" s="10"/>
       <c r="E144" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F144" s="10">
         <f t="shared" si="1"/>
@@ -3360,7 +3422,7 @@
       </c>
       <c r="G144" s="26"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="10"/>
       <c r="B145" s="10"/>
       <c r="C145" s="10" t="str">
@@ -3369,7 +3431,7 @@
       </c>
       <c r="D145" s="10"/>
       <c r="E145" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F145" s="10">
         <f t="shared" si="1"/>
@@ -3377,7 +3439,7 @@
       </c>
       <c r="G145" s="26"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="10"/>
       <c r="B146" s="10"/>
       <c r="C146" s="10" t="str">
@@ -3386,7 +3448,7 @@
       </c>
       <c r="D146" s="10"/>
       <c r="E146" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F146" s="10">
         <f t="shared" si="1"/>
@@ -3394,12 +3456,12 @@
       </c>
       <c r="G146" s="26"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="10"/>
       <c r="B147" s="10"/>
       <c r="C147" s="10"/>
       <c r="D147" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E147" s="20">
         <f>-SUM(E138:E146)</f>
@@ -3407,7 +3469,7 @@
       </c>
       <c r="G147" s="26"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E148">
         <f>SUM(E138:E147)</f>
         <v>0</v>
@@ -3418,7 +3480,7 @@
       </c>
       <c r="G148" s="26"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="13" t="str">
         <f t="shared" ref="A149:A150" si="2">A138</f>
         <v>domain sensor/actor</v>
@@ -3439,7 +3501,7 @@
       </c>
       <c r="G149" s="26"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="13" t="str">
         <f t="shared" si="2"/>
         <v>e.g. camera, IMU, SPI</v>
@@ -3457,7 +3519,7 @@
       </c>
       <c r="G150" s="26"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="13"/>
       <c r="B151" s="13"/>
       <c r="C151" s="11" t="str">
@@ -3472,7 +3534,7 @@
       </c>
       <c r="G151" s="26"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="13"/>
       <c r="B152" s="13"/>
       <c r="C152" s="11" t="str">
@@ -3487,7 +3549,7 @@
       </c>
       <c r="G152" s="26"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="13"/>
       <c r="B153" s="13"/>
       <c r="C153" s="11" t="str">
@@ -3502,7 +3564,7 @@
       </c>
       <c r="G153" s="26"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="13"/>
       <c r="B154" s="13"/>
       <c r="C154" s="11" t="str">
@@ -3517,7 +3579,7 @@
       </c>
       <c r="G154" s="26"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="13"/>
       <c r="B155" s="13"/>
       <c r="C155" s="11" t="str">
@@ -3532,7 +3594,7 @@
       </c>
       <c r="G155" s="26"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="13"/>
       <c r="B156" s="13"/>
       <c r="C156" s="11" t="str">
@@ -3547,7 +3609,7 @@
       </c>
       <c r="G156" s="26"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="13"/>
       <c r="B157" s="13"/>
       <c r="C157" s="11" t="str">
@@ -3562,12 +3624,12 @@
       </c>
       <c r="G157" s="26"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="13"/>
       <c r="B158" s="13"/>
       <c r="C158" s="11"/>
       <c r="D158" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E158" s="20">
         <f>-SUM(E149:E157)</f>
@@ -3576,7 +3638,7 @@
       <c r="F158" s="11"/>
       <c r="G158" s="26"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="E159">
@@ -3589,9 +3651,9 @@
       </c>
       <c r="G159" s="26"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B160" s="12"/>
       <c r="C160" s="12" t="s">
@@ -3599,20 +3661,20 @@
       </c>
       <c r="D160" s="12"/>
       <c r="E160" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F160" s="12">
         <v>10</v>
       </c>
       <c r="G160" s="26"/>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B161" s="12"/>
       <c r="C161" s="12" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D161" s="12"/>
       <c r="E161" s="12"/>
@@ -3621,11 +3683,11 @@
       </c>
       <c r="G161" s="26"/>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="14"/>
       <c r="B162" s="12"/>
       <c r="C162" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D162" s="12"/>
       <c r="E162" s="12"/>
@@ -3634,11 +3696,11 @@
       </c>
       <c r="G162" s="26"/>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="14"/>
       <c r="B163" s="12"/>
       <c r="C163" s="12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D163" s="12"/>
       <c r="E163" s="12"/>
@@ -3647,11 +3709,11 @@
       </c>
       <c r="G163" s="26"/>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="14"/>
       <c r="B164" s="12"/>
       <c r="C164" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D164" s="12"/>
       <c r="E164" s="12"/>
@@ -3660,7 +3722,7 @@
       </c>
       <c r="G164" s="26"/>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="14"/>
       <c r="B165" s="12"/>
       <c r="C165" s="12" t="s">
@@ -3673,11 +3735,11 @@
       </c>
       <c r="G165" s="26"/>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="14"/>
       <c r="B166" s="12"/>
       <c r="C166" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D166" s="12"/>
       <c r="E166" s="12"/>
@@ -3686,89 +3748,89 @@
       </c>
       <c r="G166" s="26"/>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="14"/>
       <c r="B167" s="12"/>
       <c r="C167" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D167" s="12" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E167" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F167" s="12">
         <v>6</v>
       </c>
       <c r="G167" s="26"/>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="12"/>
       <c r="B168" s="12"/>
       <c r="C168" s="12"/>
       <c r="D168" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E168" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F168" s="12">
         <v>6</v>
       </c>
       <c r="G168" s="26"/>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="12"/>
       <c r="B169" s="12"/>
       <c r="C169" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D169" s="12"/>
       <c r="E169" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F169" s="12">
         <v>6</v>
       </c>
       <c r="G169" s="26"/>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="12"/>
       <c r="B170" s="12"/>
       <c r="C170" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D170" s="12"/>
       <c r="E170" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F170" s="12">
         <v>5</v>
       </c>
       <c r="G170" s="26"/>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="12"/>
       <c r="B171" s="12"/>
       <c r="C171" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D171" s="12"/>
       <c r="E171" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F171" s="12">
         <v>5</v>
       </c>
       <c r="G171" s="26"/>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="12"/>
       <c r="B172" s="12"/>
       <c r="C172" s="12"/>
       <c r="D172" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E172" s="20">
         <f>-SUM(E160:E171)</f>
@@ -3776,7 +3838,7 @@
       </c>
       <c r="G172" s="26"/>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E173">
         <f>SUM(E160:E172)</f>
         <v>0</v>
@@ -3787,20 +3849,20 @@
       </c>
       <c r="G173" s="26"/>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="G174" s="26"/>
     </row>
-    <row r="175" spans="1:12" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A175" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K175"/>
       <c r="L175"/>
     </row>
-    <row r="176" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" s="13" t="s">
         <v>21</v>
       </c>
@@ -3814,7 +3876,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" s="11"/>
       <c r="B178" s="11"/>
       <c r="C178" s="11" t="s">
@@ -3826,7 +3888,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" s="11"/>
       <c r="B179" s="11"/>
       <c r="C179" s="11" t="s">
@@ -3838,7 +3900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" s="11"/>
       <c r="B180" s="11"/>
       <c r="C180" s="11" t="s">
@@ -3850,7 +3912,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" s="11"/>
       <c r="B181" s="11"/>
       <c r="C181" s="11" t="s">
@@ -3862,7 +3924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" s="11"/>
       <c r="B182" s="11"/>
       <c r="C182" s="11" t="s">
@@ -3874,7 +3936,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" s="11"/>
       <c r="B183" s="11"/>
       <c r="C183" s="11" t="s">
@@ -3886,7 +3948,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" s="11"/>
       <c r="B184" s="11"/>
       <c r="C184" s="11" t="s">
@@ -3898,19 +3960,19 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" s="11"/>
       <c r="B185" s="11"/>
       <c r="C185" s="11"/>
       <c r="D185" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E185" s="20">
         <f>-SUM(E177:E184)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E186">
         <f>SUM(E177:E185)</f>
         <v>0</v>
@@ -3920,18 +3982,18 @@
         <v>80</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A188" s="5" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B189" s="9"/>
       <c r="C189" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D189" s="10"/>
       <c r="E189" s="10"/>
@@ -3939,12 +4001,12 @@
         <v>5</v>
       </c>
       <c r="G189" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B190" s="9"/>
       <c r="C190" s="10" t="s">
@@ -3957,7 +4019,7 @@
       </c>
       <c r="G190" s="27"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="9"/>
       <c r="B191" s="9"/>
       <c r="C191" s="10" t="s">
@@ -3970,11 +4032,11 @@
       </c>
       <c r="G191" s="27"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="9"/>
       <c r="B192" s="9"/>
       <c r="C192" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D192" s="10"/>
       <c r="E192" s="10"/>
@@ -3983,7 +4045,7 @@
       </c>
       <c r="G192" s="27"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" s="9"/>
       <c r="B193" s="9"/>
       <c r="C193" s="10" t="s">
@@ -3996,11 +4058,11 @@
       </c>
       <c r="G193" s="27"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" s="9"/>
       <c r="B194" s="9"/>
       <c r="C194" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D194" s="10"/>
       <c r="E194" s="10"/>
@@ -4009,12 +4071,12 @@
       </c>
       <c r="G194" s="27"/>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" s="9"/>
       <c r="B195" s="9"/>
       <c r="C195" s="10"/>
       <c r="D195" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E195" s="20">
         <f>-SUM(E189:E194)</f>
@@ -4023,7 +4085,7 @@
       <c r="F195" s="10"/>
       <c r="G195" s="27"/>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="E196">
@@ -4036,13 +4098,13 @@
       </c>
       <c r="G196" s="27"/>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B197" s="9"/>
       <c r="C197" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D197" s="10"/>
       <c r="E197" s="10"/>
@@ -4051,9 +4113,9 @@
       </c>
       <c r="G197" s="27"/>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B198" s="9"/>
       <c r="C198" s="10" t="s">
@@ -4066,9 +4128,9 @@
       </c>
       <c r="G198" s="27"/>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B199" s="9"/>
       <c r="C199" s="10" t="s">
@@ -4081,11 +4143,11 @@
       </c>
       <c r="G199" s="27"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="9"/>
       <c r="B200" s="9"/>
       <c r="C200" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D200" s="10"/>
       <c r="E200" s="10"/>
@@ -4094,11 +4156,11 @@
       </c>
       <c r="G200" s="27"/>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" s="9"/>
       <c r="B201" s="9"/>
       <c r="C201" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D201" s="10"/>
       <c r="E201" s="10"/>
@@ -4107,11 +4169,11 @@
       </c>
       <c r="G201" s="27"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" s="9"/>
       <c r="B202" s="9"/>
       <c r="C202" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D202" s="10"/>
       <c r="E202" s="10"/>
@@ -4120,12 +4182,12 @@
       </c>
       <c r="G202" s="27"/>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="9"/>
       <c r="B203" s="9"/>
       <c r="C203" s="10"/>
       <c r="D203" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E203" s="20">
         <f>-SUM(E197:E202)</f>
@@ -4134,7 +4196,7 @@
       <c r="F203" s="10"/>
       <c r="G203" s="27"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="E204">
@@ -4147,12 +4209,12 @@
       </c>
       <c r="G204" s="27"/>
     </row>
-    <row r="205" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A205" s="5" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" s="7" t="s">
         <v>28</v>
       </c>
@@ -4164,7 +4226,7 @@
       <c r="E206" s="8"/>
       <c r="F206" s="8"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" s="8"/>
       <c r="B207" s="8"/>
       <c r="C207" s="8" t="s">
@@ -4176,7 +4238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" s="8"/>
       <c r="B208" s="8"/>
       <c r="C208" s="8" t="s">
@@ -4186,7 +4248,7 @@
       <c r="E208" s="8"/>
       <c r="F208" s="8"/>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A209" s="8"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8" t="s">
@@ -4196,11 +4258,11 @@
       <c r="E209" s="8"/>
       <c r="F209" s="8"/>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A210" s="8"/>
       <c r="B210" s="8"/>
       <c r="C210" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D210" s="8"/>
       <c r="E210" s="8"/>
@@ -4208,20 +4270,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F211">
         <f>SUM(F206:F210)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="212" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A212" s="5" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A213" s="13" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B213" s="11"/>
       <c r="C213" s="11"/>
@@ -4233,31 +4295,31 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A214" s="13"/>
       <c r="B214" s="11"/>
       <c r="C214" s="11"/>
       <c r="D214" s="11" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E214" s="11"/>
       <c r="F214" s="11">
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A215" s="13"/>
       <c r="B215" s="11"/>
       <c r="C215" s="11"/>
       <c r="D215" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E215" s="11"/>
       <c r="F215" s="11">
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A216" s="13"/>
       <c r="B216" s="11"/>
       <c r="C216" s="11"/>
@@ -4269,7 +4331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A217" s="13"/>
       <c r="B217" s="11"/>
       <c r="C217" s="11"/>
@@ -4281,12 +4343,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A218" s="13"/>
       <c r="B218" s="11"/>
       <c r="C218" s="11"/>
       <c r="D218" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E218" s="20">
         <f>-SUM(E213:E217)</f>
@@ -4294,7 +4356,7 @@
       </c>
       <c r="F218" s="11"/>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A219" s="1"/>
       <c r="E219">
         <f>-SUM(E213:E218)</f>
@@ -4306,7 +4368,7 @@
       </c>
       <c r="M219" s="19"/>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A221" s="9" t="s">
         <v>66</v>
       </c>
@@ -4320,7 +4382,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A222" s="9"/>
       <c r="B222" s="10" t="s">
         <v>42</v>
@@ -4332,10 +4394,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A223" s="9"/>
       <c r="B223" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C223" s="10"/>
       <c r="D223" s="10"/>
@@ -4344,7 +4406,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A224" s="9"/>
       <c r="B224" s="10" t="s">
         <v>67</v>
@@ -4356,12 +4418,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="9"/>
       <c r="B225" s="10"/>
       <c r="C225" s="10"/>
       <c r="D225" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E225" s="20">
         <f>-SUM(E221:E224)</f>
@@ -4369,7 +4431,7 @@
       </c>
       <c r="F225" s="10"/>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="1"/>
       <c r="E226">
         <f>-SUM(E221:E225)</f>
@@ -4380,12 +4442,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C227" s="10" t="s">
         <v>62</v>
@@ -4398,93 +4460,93 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="10"/>
       <c r="B228" s="10"/>
       <c r="C228" s="10"/>
       <c r="D228" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E228" s="10"/>
       <c r="F228" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="10"/>
       <c r="B229" s="10"/>
       <c r="C229" s="10"/>
       <c r="D229" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E229" s="10"/>
       <c r="F229" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="10"/>
       <c r="B230" s="10"/>
       <c r="C230" s="10"/>
       <c r="D230" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E230" s="10"/>
       <c r="F230" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="10"/>
       <c r="B231" s="10"/>
       <c r="C231" s="10"/>
       <c r="D231" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E231" s="10"/>
       <c r="F231" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="10"/>
       <c r="B232" s="10"/>
       <c r="C232" s="10"/>
       <c r="D232" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E232" s="10"/>
       <c r="F232" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="10"/>
       <c r="B233" s="10"/>
       <c r="C233" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="D233" s="10" t="s">
         <v>258</v>
-      </c>
-      <c r="D233" s="10" t="s">
-        <v>259</v>
       </c>
       <c r="E233" s="10"/>
       <c r="F233" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="10"/>
       <c r="B234" s="10"/>
       <c r="C234" s="10"/>
       <c r="D234" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E234" s="10"/>
       <c r="F234" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="10"/>
       <c r="B235" s="10"/>
       <c r="C235" s="10"/>
@@ -4496,7 +4558,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="10"/>
       <c r="B236" s="10"/>
       <c r="C236" s="10"/>
@@ -4508,24 +4570,24 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="10"/>
       <c r="B237" s="10"/>
       <c r="C237" s="10"/>
       <c r="D237" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E237" s="10"/>
       <c r="F237" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="10"/>
       <c r="B238" s="10"/>
       <c r="C238" s="10"/>
       <c r="D238" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E238" s="20">
         <f>-SUM(E211:E232)</f>
@@ -4533,7 +4595,7 @@
       </c>
       <c r="F238" s="10"/>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E239">
         <f>SUM(E227:E232)</f>
         <v>0</v>
@@ -4543,9 +4605,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B240" s="7" t="s">
         <v>63</v>
@@ -4557,13 +4619,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="8"/>
       <c r="B241" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C241" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D241" s="8"/>
       <c r="E241" s="8"/>
@@ -4571,7 +4633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="8"/>
       <c r="B242" s="8"/>
       <c r="C242" s="8" t="s">
@@ -4583,11 +4645,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="8"/>
       <c r="B243" s="8"/>
       <c r="C243" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D243" s="8"/>
       <c r="E243" s="8"/>
@@ -4595,11 +4657,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="8"/>
       <c r="B244" s="8"/>
       <c r="C244" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D244" s="8"/>
       <c r="E244" s="8"/>
@@ -4607,11 +4669,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="8"/>
       <c r="B245" s="8"/>
       <c r="C245" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D245" s="8"/>
       <c r="E245" s="8"/>
@@ -4619,11 +4681,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="8"/>
       <c r="B246" s="8"/>
       <c r="C246" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D246" s="8"/>
       <c r="E246" s="8"/>
@@ -4631,12 +4693,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="8"/>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
       <c r="D247" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E247" s="20">
         <f>-SUM(E244:E246)</f>
@@ -4644,7 +4706,7 @@
       </c>
       <c r="F247" s="8"/>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E248">
         <f>SUM(E240:E246)</f>
         <v>0</v>
@@ -4654,7 +4716,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="7" t="s">
         <v>66</v>
       </c>
@@ -4668,7 +4730,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="7"/>
       <c r="B250" s="8" t="s">
         <v>42</v>
@@ -4680,10 +4742,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="7"/>
       <c r="B251" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C251" s="8"/>
       <c r="D251" s="8"/>
@@ -4692,10 +4754,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="7"/>
       <c r="B252" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C252" s="8"/>
       <c r="D252" s="8"/>
@@ -4704,7 +4766,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="7"/>
       <c r="B253" s="8" t="s">
         <v>65</v>
@@ -4716,7 +4778,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="7"/>
       <c r="B254" s="8" t="s">
         <v>67</v>
@@ -4728,7 +4790,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="7"/>
       <c r="B255" s="7" t="s">
         <v>49</v>
@@ -4742,7 +4804,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="7"/>
       <c r="B256" s="7"/>
       <c r="C256" s="8" t="s">
@@ -4754,7 +4816,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="7"/>
       <c r="B257" s="7"/>
       <c r="C257" s="8" t="s">
@@ -4766,7 +4828,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="7"/>
       <c r="B258" s="7"/>
       <c r="C258" s="8" t="s">
@@ -4778,11 +4840,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="7"/>
       <c r="B259" s="7"/>
       <c r="C259" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D259" s="8"/>
       <c r="E259" s="8"/>
@@ -4790,7 +4852,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="7"/>
       <c r="B260" s="7"/>
       <c r="C260" s="8" t="s">
@@ -4804,7 +4866,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="7"/>
       <c r="B261" s="7"/>
       <c r="C261" s="8"/>
@@ -4816,7 +4878,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="7"/>
       <c r="B262" s="7"/>
       <c r="C262" s="8"/>
@@ -4828,7 +4890,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="7"/>
       <c r="B263" s="7"/>
       <c r="C263" s="8"/>
@@ -4840,7 +4902,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="7"/>
       <c r="B264" s="7"/>
       <c r="C264" s="8"/>
@@ -4852,12 +4914,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="7"/>
       <c r="B265" s="7"/>
       <c r="C265" s="8"/>
       <c r="D265" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E265" s="20">
         <f>-SUM(E255:E264)</f>
@@ -4865,7 +4927,7 @@
       </c>
       <c r="F265" s="8"/>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E266">
         <f>SUM(E249:E265)</f>
         <v>0</v>
@@ -4875,12 +4937,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="B268" s="8" t="s">
         <v>268</v>
-      </c>
-      <c r="B268" s="8" t="s">
-        <v>269</v>
       </c>
       <c r="C268" s="8"/>
       <c r="D268" s="8"/>
@@ -4889,12 +4951,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="B269" s="8" t="s">
         <v>270</v>
-      </c>
-      <c r="B269" s="8" t="s">
-        <v>271</v>
       </c>
       <c r="C269" s="8"/>
       <c r="D269" s="8"/>
@@ -4903,10 +4965,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="7"/>
       <c r="B270" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C270" s="8"/>
       <c r="D270" s="8"/>
@@ -4915,10 +4977,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="8"/>
       <c r="B271" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C271" s="8"/>
       <c r="D271" s="8"/>
@@ -4927,10 +4989,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="8"/>
       <c r="B272" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C272" s="8"/>
       <c r="D272" s="8"/>
@@ -4939,12 +5001,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="8"/>
       <c r="B273" s="8"/>
       <c r="C273" s="8"/>
       <c r="D273" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E273" s="20">
         <f>-SUM(E268:E272)</f>
@@ -4952,7 +5014,7 @@
       </c>
       <c r="F273" s="8"/>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E274">
         <f>SUM(E268:E272)</f>
         <v>0</v>
@@ -4962,12 +5024,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="9" t="s">
         <v>34</v>
       </c>
       <c r="B275" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C275" s="10"/>
       <c r="D275" s="10"/>
@@ -4976,10 +5038,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="10"/>
       <c r="B276" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C276" s="10"/>
       <c r="D276" s="10"/>
@@ -4988,66 +5050,66 @@
         <v>10</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="9"/>
       <c r="B277" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C277" s="10"/>
       <c r="D277" s="10"/>
       <c r="E277" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F277" s="10">
         <v>10</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="10"/>
       <c r="B278" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C278" s="10"/>
       <c r="D278" s="10"/>
       <c r="E278" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F278" s="10">
         <v>10</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="9"/>
       <c r="B279" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C279" s="10"/>
       <c r="D279" s="10"/>
       <c r="E279" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F279" s="10">
         <v>10</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="9"/>
       <c r="B280" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C280" s="10"/>
       <c r="D280" s="10"/>
       <c r="E280" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F280" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="9"/>
       <c r="B281" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C281" s="10"/>
       <c r="D281" s="10"/>
@@ -5056,10 +5118,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="10"/>
       <c r="B282" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C282" s="10"/>
       <c r="D282" s="10"/>
@@ -5068,10 +5130,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="10"/>
       <c r="B283" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C283" s="10"/>
       <c r="D283" s="10"/>
@@ -5080,7 +5142,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="10"/>
       <c r="B284" s="10" t="s">
         <v>36</v>
@@ -5092,12 +5154,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285" s="10"/>
       <c r="B285" s="10"/>
       <c r="C285" s="10"/>
       <c r="D285" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E285" s="20">
         <f>-SUM(E273:E284)</f>
@@ -5105,7 +5167,7 @@
       </c>
       <c r="F285" s="10"/>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E286">
         <f>SUM(E275:E284)</f>
         <v>0</v>
@@ -5115,17 +5177,17 @@
         <v>80</v>
       </c>
     </row>
-    <row r="289" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A289" s="5" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B290" s="12" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C290" s="12"/>
       <c r="D290" s="12"/>
@@ -5134,7 +5196,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="14"/>
       <c r="B291" s="14"/>
       <c r="C291" s="12" t="s">
@@ -5146,7 +5208,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" s="14"/>
       <c r="B292" s="14"/>
       <c r="C292" s="12" t="s">
@@ -5158,11 +5220,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" s="14"/>
       <c r="B293" s="14"/>
       <c r="C293" s="12" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D293" s="12"/>
       <c r="E293" s="12"/>
@@ -5170,7 +5232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" s="14"/>
       <c r="B294" s="14"/>
       <c r="C294" s="12" t="s">
@@ -5182,10 +5244,10 @@
         <v>20</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" s="12"/>
       <c r="B295" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C295" s="12" t="s">
         <v>56</v>
@@ -5196,11 +5258,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="12"/>
       <c r="B296" s="12"/>
       <c r="C296" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D296" s="12"/>
       <c r="E296" s="12"/>
@@ -5208,11 +5270,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="12"/>
       <c r="B297" s="12"/>
       <c r="C297" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D297" s="12"/>
       <c r="E297" s="12"/>
@@ -5220,10 +5282,10 @@
         <v>15</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" s="12"/>
       <c r="B298" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C298" s="12" t="s">
         <v>56</v>
@@ -5234,11 +5296,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" s="12"/>
       <c r="B299" s="12"/>
       <c r="C299" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D299" s="12"/>
       <c r="E299" s="12"/>
@@ -5246,11 +5308,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="12"/>
       <c r="B300" s="12"/>
       <c r="C300" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D300" s="12"/>
       <c r="E300" s="12"/>
@@ -5258,7 +5320,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" s="14" t="s">
         <v>49</v>
       </c>
@@ -5272,7 +5334,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" s="14"/>
       <c r="B302" s="14"/>
       <c r="C302" s="12" t="s">
@@ -5284,7 +5346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" s="14"/>
       <c r="B303" s="14"/>
       <c r="C303" s="12" t="s">
@@ -5296,7 +5358,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" s="14"/>
       <c r="B304" s="14"/>
       <c r="C304" s="12" t="s">
@@ -5308,11 +5370,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" s="14"/>
       <c r="B305" s="14"/>
       <c r="C305" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D305" s="12"/>
       <c r="E305" s="12"/>
@@ -5320,7 +5382,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" s="14"/>
       <c r="B306" s="14"/>
       <c r="C306" s="12" t="s">
@@ -5334,7 +5396,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" s="14"/>
       <c r="B307" s="14"/>
       <c r="C307" s="12"/>
@@ -5346,7 +5408,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308" s="14"/>
       <c r="B308" s="14"/>
       <c r="C308" s="12"/>
@@ -5358,7 +5420,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309" s="14"/>
       <c r="B309" s="14"/>
       <c r="C309" s="12"/>
@@ -5370,7 +5432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310" s="14"/>
       <c r="B310" s="14"/>
       <c r="C310" s="12"/>
@@ -5382,12 +5444,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311" s="12"/>
       <c r="B311" s="12"/>
       <c r="C311" s="12"/>
       <c r="D311" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E311" s="20">
         <f>-SUM(E290:E300)</f>
@@ -5395,7 +5457,7 @@
       </c>
       <c r="F311" s="12"/>
     </row>
-    <row r="312" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E312">
         <f>SUM(E290:E311)</f>
         <v>0</v>
@@ -5407,29 +5469,29 @@
       <c r="K312" s="17"/>
       <c r="L312" s="17"/>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B313" s="9"/>
       <c r="C313" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D313" s="10"/>
       <c r="E313" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F313" s="10">
         <v>10</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A314" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B314" s="10"/>
       <c r="C314" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D314" s="10"/>
       <c r="E314" s="10"/>
@@ -5437,11 +5499,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315" s="9"/>
       <c r="B315" s="10"/>
       <c r="C315" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D315" s="10"/>
       <c r="E315" s="10"/>
@@ -5449,75 +5511,75 @@
         <v>5</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316" s="10"/>
       <c r="B316" s="10"/>
       <c r="C316" s="10" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D316" s="10"/>
       <c r="E316" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F316" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317" s="10"/>
       <c r="B317" s="10"/>
       <c r="C317" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D317" s="10"/>
       <c r="E317" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F317" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" s="9"/>
       <c r="B318" s="10"/>
       <c r="C318" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D318" s="10"/>
       <c r="E318" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F318" s="10">
         <v>10</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A319" s="9"/>
       <c r="B319" s="10"/>
       <c r="C319" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D319" s="10"/>
       <c r="E319" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F319" s="10">
         <v>10</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A320" s="10"/>
       <c r="B320" s="10"/>
       <c r="C320" s="10"/>
       <c r="D320" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E320" s="20">
         <f>-SUM(E313:E319)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E321">
         <f>SUM(E313:E320)</f>
         <v>0</v>
@@ -5529,20 +5591,20 @@
       <c r="K321" s="17"/>
       <c r="L321" s="17"/>
     </row>
-    <row r="322" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K322" s="17"/>
       <c r="L322" s="17"/>
     </row>
-    <row r="323" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K323" s="17"/>
       <c r="L323" s="17"/>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A324" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="B324" s="11" t="s">
         <v>272</v>
-      </c>
-      <c r="B324" s="11" t="s">
-        <v>273</v>
       </c>
       <c r="C324" s="11"/>
       <c r="D324" s="11"/>
@@ -5551,10 +5613,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A325" s="11"/>
       <c r="B325" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C325" s="11"/>
       <c r="D325" s="11"/>
@@ -5563,10 +5625,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A326" s="11"/>
       <c r="B326" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C326" s="11"/>
       <c r="D326" s="11"/>
@@ -5575,12 +5637,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A327" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="B327" s="11" t="s">
         <v>275</v>
-      </c>
-      <c r="B327" s="11" t="s">
-        <v>276</v>
       </c>
       <c r="C327" s="11"/>
       <c r="D327" s="11"/>
@@ -5589,10 +5651,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A328" s="11"/>
       <c r="B328" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C328" s="11"/>
       <c r="D328" s="11"/>
@@ -5601,13 +5663,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B329" s="11"/>
       <c r="C329" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D329" s="11"/>
       <c r="E329" s="11"/>
@@ -5615,11 +5677,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A330" s="11"/>
       <c r="B330" s="11"/>
       <c r="C330" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D330" s="11"/>
       <c r="E330" s="11"/>
@@ -5627,11 +5689,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" s="11"/>
       <c r="B331" s="11"/>
       <c r="C331" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D331" s="11"/>
       <c r="E331" s="11"/>
@@ -5639,12 +5701,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A332" s="11"/>
       <c r="B332" s="11"/>
       <c r="C332" s="11"/>
       <c r="D332" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E332" s="20">
         <f>-SUM(E324:E331)</f>
@@ -5652,7 +5714,7 @@
       </c>
       <c r="F332" s="11"/>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E333">
         <f>SUM(E324:E328)</f>
         <v>0</v>
@@ -5662,22 +5724,22 @@
         <v>60</v>
       </c>
     </row>
-    <row r="335" spans="1:12" s="17" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:12" s="17" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A335" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K335"/>
       <c r="L335"/>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A336" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B336" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C336" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D336" s="11"/>
       <c r="E336" s="11">
@@ -5687,11 +5749,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337" s="11"/>
       <c r="B337" s="11"/>
       <c r="C337" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D337" s="11"/>
       <c r="E337" s="11">
@@ -5701,7 +5763,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A338" s="11"/>
       <c r="B338" s="11"/>
       <c r="C338" s="11" t="s">
@@ -5715,11 +5777,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A339" s="11"/>
       <c r="B339" s="11"/>
       <c r="C339" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D339" s="11"/>
       <c r="E339" s="11">
@@ -5729,11 +5791,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A340" s="11"/>
       <c r="B340" s="11"/>
       <c r="C340" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D340" s="11"/>
       <c r="E340" s="11">
@@ -5743,11 +5805,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A341" s="11"/>
       <c r="B341" s="11"/>
       <c r="C341" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D341" s="11"/>
       <c r="E341" s="11">
@@ -5757,19 +5819,19 @@
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A342" s="11"/>
       <c r="B342" s="11"/>
       <c r="C342" s="11"/>
       <c r="D342" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E342" s="20">
         <f>-SUM(E336:E341)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E343">
         <f>SUM(E336:E342)</f>
         <v>0</v>
@@ -5779,7 +5841,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344" s="13" t="s">
         <v>40</v>
       </c>
@@ -5793,7 +5855,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A345" s="13"/>
       <c r="B345" s="13"/>
       <c r="C345" s="15" t="s">
@@ -5805,11 +5867,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A346" s="13"/>
       <c r="B346" s="13"/>
       <c r="C346" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D346" s="11"/>
       <c r="E346" s="11"/>
@@ -5817,7 +5879,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A347" s="13"/>
       <c r="B347" s="13"/>
       <c r="C347" s="11"/>
@@ -5825,9 +5887,9 @@
       <c r="E347" s="11"/>
       <c r="F347" s="11"/>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A348" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B348" s="13"/>
       <c r="C348" s="11" t="s">
@@ -5839,11 +5901,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A349" s="13"/>
       <c r="B349" s="13"/>
       <c r="C349" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D349" s="11"/>
       <c r="E349" s="11"/>
@@ -5851,11 +5913,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A350" s="13"/>
       <c r="B350" s="13"/>
       <c r="C350" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D350" s="11"/>
       <c r="E350" s="11"/>
@@ -5863,7 +5925,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A351" s="13"/>
       <c r="B351" s="13"/>
       <c r="C351" s="11"/>
@@ -5871,9 +5933,9 @@
       <c r="E351" s="11"/>
       <c r="F351" s="11"/>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A352" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B352" s="13"/>
       <c r="C352" s="11" t="s">
@@ -5885,11 +5947,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A353" s="13"/>
       <c r="B353" s="13"/>
       <c r="C353" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D353" s="11"/>
       <c r="E353" s="11"/>
@@ -5897,11 +5959,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A354" s="13"/>
       <c r="B354" s="13"/>
       <c r="C354" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D354" s="11"/>
       <c r="E354" s="11"/>
@@ -5909,12 +5971,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A355" s="13"/>
       <c r="B355" s="13"/>
       <c r="C355" s="11"/>
       <c r="D355" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E355" s="20">
         <f>-SUM(E344:E354)</f>
@@ -5922,7 +5984,7 @@
       </c>
       <c r="F355" s="11"/>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="E356">
@@ -5935,13 +5997,13 @@
       </c>
       <c r="M356" s="19"/>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A357" s="14" t="s">
         <v>41</v>
       </c>
       <c r="B357" s="14"/>
       <c r="C357" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D357" s="12"/>
       <c r="E357" s="12"/>
@@ -5950,7 +6012,7 @@
       </c>
       <c r="M357" s="19"/>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A358" s="14"/>
       <c r="B358" s="14"/>
       <c r="C358" s="12" t="s">
@@ -5963,12 +6025,12 @@
       </c>
       <c r="M358" s="19"/>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A359" s="14"/>
       <c r="B359" s="14"/>
       <c r="C359" s="12"/>
       <c r="D359" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E359" s="20">
         <f>-SUM(E357:E358)</f>
@@ -5977,7 +6039,7 @@
       <c r="F359" s="12"/>
       <c r="M359" s="19"/>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="E360">
@@ -5989,7 +6051,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>5</v>
       </c>
@@ -6005,9 +6067,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B363" s="10"/>
       <c r="C363" s="10" t="s">
@@ -6019,7 +6081,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A364" s="1"/>
       <c r="B364" s="10"/>
       <c r="C364" s="10" t="s">
@@ -6031,11 +6093,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A365" s="1"/>
       <c r="B365" s="10"/>
       <c r="C365" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D365" s="10"/>
       <c r="E365" s="10"/>
@@ -6043,11 +6105,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A366" s="1"/>
       <c r="B366" s="10"/>
       <c r="C366" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D366" s="10"/>
       <c r="E366" s="10"/>
@@ -6055,11 +6117,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A367" s="1"/>
       <c r="B367" s="10"/>
       <c r="C367" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D367" s="10"/>
       <c r="E367" s="10"/>
@@ -6067,7 +6129,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A368" s="1"/>
       <c r="B368" s="10"/>
       <c r="C368" s="10" t="s">
@@ -6079,11 +6141,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A369" s="1"/>
       <c r="B369" s="10"/>
       <c r="C369" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D369" s="10"/>
       <c r="E369" s="10"/>
@@ -6091,12 +6153,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A370" s="1"/>
       <c r="B370" s="10"/>
       <c r="C370" s="10"/>
       <c r="D370" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E370" s="20">
         <f>-SUM(E362:E369)</f>
@@ -6104,7 +6166,7 @@
       </c>
       <c r="F370" s="10"/>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="E371">
@@ -6116,7 +6178,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A372" s="1"/>
       <c r="B372" s="13" t="s">
         <v>54</v>
@@ -6130,7 +6192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A373" s="1"/>
       <c r="B373" s="11"/>
       <c r="C373" s="11" t="s">
@@ -6142,7 +6204,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A374" s="1"/>
       <c r="B374" s="11"/>
       <c r="C374" s="11" t="s">
@@ -6154,11 +6216,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A375" s="1"/>
       <c r="B375" s="11"/>
       <c r="C375" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D375" s="11"/>
       <c r="E375" s="11"/>
@@ -6166,11 +6228,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A376" s="1"/>
       <c r="B376" s="11"/>
       <c r="C376" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D376" s="11"/>
       <c r="E376" s="11"/>
@@ -6178,11 +6240,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A377" s="1"/>
       <c r="B377" s="11"/>
       <c r="C377" s="11" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D377" s="11"/>
       <c r="E377" s="11"/>
@@ -6190,7 +6252,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A378" s="1"/>
       <c r="B378" s="11"/>
       <c r="C378" s="11" t="s">
@@ -6202,11 +6264,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A379" s="1"/>
       <c r="B379" s="11"/>
       <c r="C379" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D379" s="11"/>
       <c r="E379" s="11"/>
@@ -6214,12 +6276,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A380" s="1"/>
       <c r="B380" s="11"/>
       <c r="C380" s="11"/>
       <c r="D380" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E380" s="20">
         <f>-SUM(E372:E379)</f>
@@ -6227,7 +6289,7 @@
       </c>
       <c r="F380" s="11"/>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="E381">
@@ -6239,7 +6301,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A382" s="1"/>
       <c r="B382" s="14" t="s">
         <v>54</v>
@@ -6253,7 +6315,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A383" s="1"/>
       <c r="B383" s="12"/>
       <c r="C383" s="12" t="s">
@@ -6265,7 +6327,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A384" s="1"/>
       <c r="B384" s="12"/>
       <c r="C384" s="12" t="s">
@@ -6277,7 +6339,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A385" s="1"/>
       <c r="B385" s="12"/>
       <c r="C385" s="12" t="str">
@@ -6290,7 +6352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A386" s="1"/>
       <c r="B386" s="12"/>
       <c r="C386" s="12" t="str">
@@ -6303,7 +6365,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A387" s="1"/>
       <c r="B387" s="12"/>
       <c r="C387" s="12" t="str">
@@ -6316,7 +6378,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A388" s="1"/>
       <c r="B388" s="12"/>
       <c r="C388" s="12" t="str">
@@ -6329,11 +6391,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A389" s="1"/>
       <c r="B389" s="12"/>
       <c r="C389" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D389" s="12"/>
       <c r="E389" s="12"/>
@@ -6341,12 +6403,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A390" s="1"/>
       <c r="B390" s="12"/>
       <c r="C390" s="12"/>
       <c r="D390" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E390" s="20">
         <f>-SUM(E382:E389)</f>
@@ -6354,7 +6416,7 @@
       </c>
       <c r="F390" s="12"/>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="E391">
@@ -6366,14 +6428,14 @@
         <v>40</v>
       </c>
     </row>
-    <row r="393" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A393" s="5" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A394" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B394" s="8"/>
       <c r="C394" s="8"/>
@@ -6381,7 +6443,7 @@
       <c r="E394" s="8"/>
       <c r="F394" s="8"/>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A395" s="7"/>
       <c r="B395" s="8"/>
       <c r="C395" s="8"/>
@@ -6389,20 +6451,20 @@
       <c r="E395" s="8"/>
       <c r="F395" s="8"/>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A396" s="7"/>
       <c r="B396" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C396" s="8"/>
       <c r="D396" s="8"/>
       <c r="E396" s="8"/>
       <c r="F396" s="8"/>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A397" s="7"/>
       <c r="B397" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C397" s="8"/>
       <c r="D397" s="8"/>
@@ -6411,10 +6473,10 @@
         <v>25</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A398" s="7"/>
       <c r="B398" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C398" s="8"/>
       <c r="D398" s="8"/>
@@ -6423,13 +6485,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A399" s="7"/>
       <c r="B399" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C399" s="8" t="s">
         <v>161</v>
-      </c>
-      <c r="C399" s="8" t="s">
-        <v>162</v>
       </c>
       <c r="D399" s="8"/>
       <c r="E399" s="8"/>
@@ -6437,7 +6499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A400" s="7"/>
       <c r="B400" s="8"/>
       <c r="C400" s="8" t="s">
@@ -6449,13 +6511,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A401" s="7"/>
       <c r="B401" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="C401" s="8" t="s">
         <v>163</v>
-      </c>
-      <c r="C401" s="8" t="s">
-        <v>164</v>
       </c>
       <c r="D401" s="8"/>
       <c r="E401" s="8"/>
@@ -6463,7 +6525,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A402" s="7"/>
       <c r="B402" s="8"/>
       <c r="C402" s="8" t="s">
@@ -6475,11 +6537,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A403" s="7"/>
       <c r="B403" s="8"/>
       <c r="C403" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D403" s="8"/>
       <c r="E403" s="8"/>
@@ -6487,11 +6549,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A404" s="7"/>
       <c r="B404" s="8"/>
       <c r="C404" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D404" s="8"/>
       <c r="E404" s="8"/>
@@ -6499,7 +6561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A405" s="7"/>
       <c r="B405" s="8"/>
       <c r="C405" s="8" t="s">
@@ -6511,12 +6573,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A406" s="7"/>
       <c r="B406" s="8"/>
       <c r="C406" s="8"/>
       <c r="D406" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E406" s="20">
         <f>-SUM(E289:E405)</f>
@@ -6524,7 +6586,7 @@
       </c>
       <c r="F406" s="8"/>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A407" s="1"/>
       <c r="E407">
         <f>SUM(E394:E406)</f>
@@ -6535,15 +6597,15 @@
         <v>65</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A408" s="1"/>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A409" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B409" s="10" t="s">
         <v>91</v>
-      </c>
-      <c r="B409" s="10" t="s">
-        <v>92</v>
       </c>
       <c r="C409" s="10"/>
       <c r="D409" s="10"/>
@@ -6552,10 +6614,10 @@
         <v>100</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A410" s="10"/>
       <c r="B410" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C410" s="10"/>
       <c r="D410" s="10"/>
@@ -6564,10 +6626,10 @@
         <v>100</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A411" s="10"/>
       <c r="B411" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C411" s="10"/>
       <c r="D411" s="10"/>
@@ -6576,10 +6638,10 @@
         <v>100</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A412" s="10"/>
       <c r="B412" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C412" s="10"/>
       <c r="D412" s="10"/>
@@ -6588,9 +6650,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A413" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B413" s="10"/>
       <c r="C413" s="10"/>
@@ -6598,10 +6660,10 @@
       <c r="E413" s="10"/>
       <c r="F413" s="10"/>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A414" s="9"/>
       <c r="B414" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C414" s="10"/>
       <c r="D414" s="10"/>
@@ -6610,10 +6672,10 @@
         <v>50</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A415" s="10"/>
       <c r="B415" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C415" s="10"/>
       <c r="D415" s="10"/>
@@ -6624,10 +6686,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A416" s="10"/>
       <c r="B416" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C416" s="10"/>
       <c r="D416" s="10"/>
@@ -6638,10 +6700,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A417" s="10"/>
       <c r="B417" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C417" s="10"/>
       <c r="D417" s="10"/>
@@ -6650,7 +6712,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A418" s="10"/>
       <c r="B418" s="10"/>
       <c r="C418" s="10"/>
@@ -6658,12 +6720,12 @@
       <c r="E418" s="10"/>
       <c r="F418" s="10"/>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A419" s="10"/>
       <c r="B419" s="10"/>
       <c r="C419" s="10"/>
       <c r="D419" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E419" s="20">
         <f>-SUM(E409:E418)</f>
@@ -6671,7 +6733,7 @@
       </c>
       <c r="F419" s="10"/>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E420">
         <f>SUM(E409:E419)</f>
         <v>0</v>
@@ -6681,12 +6743,12 @@
         <v>550</v>
       </c>
     </row>
-    <row r="421" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A421" s="5" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="422" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A422" s="7" t="s">
         <v>36</v>
       </c>
@@ -6694,7 +6756,7 @@
         <v>37</v>
       </c>
       <c r="C422" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D422" s="8"/>
       <c r="E422" s="8"/>
@@ -6702,11 +6764,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A423" s="7"/>
       <c r="B423" s="8"/>
       <c r="C423" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D423" s="8"/>
       <c r="E423" s="8"/>
@@ -6714,11 +6776,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A424" s="7"/>
       <c r="B424" s="8"/>
       <c r="C424" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D424" s="8"/>
       <c r="E424" s="8"/>
@@ -6726,11 +6788,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A425" s="7"/>
       <c r="B425" s="8"/>
       <c r="C425" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D425" s="8"/>
       <c r="E425" s="8"/>
@@ -6738,11 +6800,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A426" s="7"/>
       <c r="B426" s="8"/>
       <c r="C426" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D426" s="8"/>
       <c r="E426" s="8"/>
@@ -6750,7 +6812,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A427" s="8"/>
       <c r="B427" s="8" t="s">
         <v>12</v>
@@ -6762,7 +6824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A428" s="8"/>
       <c r="B428" s="8" t="s">
         <v>39</v>
@@ -6774,7 +6836,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A429" s="8"/>
       <c r="B429" s="8" t="s">
         <v>68</v>
@@ -6786,10 +6848,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A430" s="8"/>
       <c r="B430" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C430" s="8"/>
       <c r="D430" s="8"/>
@@ -6798,12 +6860,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A431" s="8"/>
       <c r="B431" s="8"/>
       <c r="C431" s="8"/>
       <c r="D431" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E431" s="20">
         <f>-SUM(E422:E430)</f>
@@ -6811,7 +6873,7 @@
       </c>
       <c r="F431" s="8"/>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E432">
         <f>SUM(E422:E431)</f>
         <v>0</v>
@@ -6821,12 +6883,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A433" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="B433" s="8" t="s">
         <v>123</v>
-      </c>
-      <c r="B433" s="8" t="s">
-        <v>124</v>
       </c>
       <c r="C433" s="8"/>
       <c r="D433" s="8"/>
@@ -6835,10 +6897,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A434" s="8"/>
       <c r="B434" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C434" s="8"/>
       <c r="D434" s="8"/>
@@ -6847,10 +6909,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A435" s="8"/>
       <c r="B435" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C435" s="8"/>
       <c r="D435" s="8"/>
@@ -6859,10 +6921,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A436" s="8"/>
       <c r="B436" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C436" s="8"/>
       <c r="D436" s="8"/>
@@ -6871,10 +6933,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A437" s="8"/>
       <c r="B437" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C437" s="8"/>
       <c r="D437" s="8"/>
@@ -6883,10 +6945,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A438" s="8"/>
       <c r="B438" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C438" s="8"/>
       <c r="D438" s="8"/>
@@ -6895,10 +6957,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A439" s="8"/>
       <c r="B439" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C439" s="8"/>
       <c r="D439" s="8"/>
@@ -6907,10 +6969,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A440" s="8"/>
       <c r="B440" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C440" s="8"/>
       <c r="D440" s="8"/>
@@ -6919,10 +6981,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A441" s="8"/>
       <c r="B441" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C441" s="8"/>
       <c r="D441" s="8"/>
@@ -6931,12 +6993,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A442" s="8"/>
       <c r="B442" s="8"/>
       <c r="C442" s="8"/>
       <c r="D442" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E442" s="20">
         <f>-SUM(E433:E441)</f>
@@ -6944,7 +7006,7 @@
       </c>
       <c r="F442" s="8"/>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E443">
         <f>SUM(E433:E442)</f>
         <v>0</v>
@@ -6954,12 +7016,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A444" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B444" s="8" t="s">
         <v>131</v>
-      </c>
-      <c r="B444" s="8" t="s">
-        <v>132</v>
       </c>
       <c r="C444" s="8"/>
       <c r="D444" s="8"/>
@@ -6968,10 +7030,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A445" s="8"/>
       <c r="B445" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C445" s="8"/>
       <c r="D445" s="8"/>
@@ -6980,7 +7042,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A446" s="8"/>
       <c r="B446" s="8" t="s">
         <v>7</v>
@@ -6992,10 +7054,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A447" s="8"/>
       <c r="B447" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C447" s="8"/>
       <c r="D447" s="8"/>
@@ -7004,10 +7066,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A448" s="8"/>
       <c r="B448" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C448" s="8"/>
       <c r="D448" s="8"/>
@@ -7016,10 +7078,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A449" s="8"/>
       <c r="B449" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C449" s="8"/>
       <c r="D449" s="8"/>
@@ -7028,10 +7090,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A450" s="8"/>
       <c r="B450" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C450" s="8"/>
       <c r="D450" s="8"/>
@@ -7040,12 +7102,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A451" s="8"/>
       <c r="B451" s="8"/>
       <c r="C451" s="8"/>
       <c r="D451" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E451" s="20">
         <f>-SUM(E444:E450)</f>
@@ -7053,7 +7115,7 @@
       </c>
       <c r="F451" s="8"/>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E452">
         <f>SUM(E444:E451)</f>
         <v>0</v>
@@ -7063,109 +7125,109 @@
         <v>23</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A453" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B453" s="7"/>
       <c r="C453" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D453" s="8" t="s">
         <v>142</v>
-      </c>
-      <c r="D453" s="8" t="s">
-        <v>143</v>
       </c>
       <c r="E453" s="8"/>
       <c r="F453" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A454" s="7"/>
       <c r="B454" s="7"/>
       <c r="C454" s="8"/>
       <c r="D454" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E454" s="8"/>
       <c r="F454" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A455" s="7"/>
       <c r="B455" s="7"/>
       <c r="C455" s="8"/>
       <c r="D455" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E455" s="8"/>
       <c r="F455" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A456" s="7"/>
       <c r="B456" s="7"/>
       <c r="C456" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D456" s="8" t="s">
         <v>146</v>
-      </c>
-      <c r="D456" s="8" t="s">
-        <v>147</v>
       </c>
       <c r="E456" s="8"/>
       <c r="F456" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A457" s="7"/>
       <c r="B457" s="7"/>
       <c r="C457" s="8"/>
       <c r="D457" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E457" s="8"/>
       <c r="F457" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A458" s="7"/>
       <c r="B458" s="7"/>
       <c r="C458" s="8"/>
       <c r="D458" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E458" s="8"/>
       <c r="F458" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A459" s="7"/>
       <c r="B459" s="7"/>
       <c r="C459" s="8"/>
       <c r="D459" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E459" s="8"/>
       <c r="F459" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A460" s="7"/>
       <c r="B460" s="7"/>
       <c r="C460" s="8"/>
       <c r="D460" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E460" s="8"/>
       <c r="F460" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E461">
         <f>SUM(E453:E460)</f>
         <v>0</v>
@@ -7175,20 +7237,20 @@
         <v>40</v>
       </c>
     </row>
-    <row r="462" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A462" s="5" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="463" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A463" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B463" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C463" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D463" s="8"/>
       <c r="E463" s="8"/>
@@ -7196,11 +7258,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A464" s="7"/>
       <c r="B464" s="8"/>
       <c r="C464" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D464" s="8"/>
       <c r="E464" s="8"/>
@@ -7208,13 +7270,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A465" s="8"/>
       <c r="B465" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C465" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D465" s="8"/>
       <c r="E465" s="8"/>
@@ -7222,11 +7284,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A466" s="8"/>
       <c r="B466" s="8"/>
       <c r="C466" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D466" s="8"/>
       <c r="E466" s="8"/>
@@ -7234,11 +7296,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A467" s="8"/>
       <c r="B467" s="8"/>
       <c r="C467" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D467" s="8"/>
       <c r="E467" s="8"/>
@@ -7246,11 +7308,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A468" s="8"/>
       <c r="B468" s="8"/>
       <c r="C468" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D468" s="8"/>
       <c r="E468" s="8"/>
@@ -7258,11 +7320,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A469" s="8"/>
       <c r="B469" s="8"/>
       <c r="C469" s="8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D469" s="8"/>
       <c r="E469" s="8"/>
@@ -7270,19 +7332,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A470" s="8"/>
       <c r="B470" s="8"/>
       <c r="C470" s="8"/>
       <c r="D470" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E470" s="20">
         <f>-SUM(E467:E469)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E471">
         <f>SUM(E463:E470)</f>
         <v>0</v>
@@ -7292,17 +7354,17 @@
         <v>45</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="473" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A473" s="14" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A473" s="14" t="s">
+      <c r="B473" s="12" t="s">
         <v>331</v>
-      </c>
-      <c r="B473" s="12" t="s">
-        <v>332</v>
       </c>
       <c r="C473" s="12"/>
       <c r="D473" s="12"/>
@@ -7313,12 +7375,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A474" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B474" s="12" t="s">
         <v>333</v>
-      </c>
-      <c r="B474" s="12" t="s">
-        <v>334</v>
       </c>
       <c r="C474" s="12" t="s">
         <v>46</v>
@@ -7331,11 +7393,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A475" s="14"/>
       <c r="B475" s="12"/>
       <c r="C475" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D475" s="12"/>
       <c r="E475" s="12">
@@ -7345,17 +7407,17 @@
         <v>10</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A476" s="1"/>
       <c r="D476" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E476" s="20">
         <f>-SUM(E468:E475)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E477">
         <f>SUM(E473:E476)</f>
         <v>0</v>
@@ -7365,17 +7427,17 @@
         <v>30</v>
       </c>
     </row>
-    <row r="479" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A479" s="5" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="480" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A480" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B480" s="12" t="s">
         <v>236</v>
-      </c>
-      <c r="B480" s="12" t="s">
-        <v>237</v>
       </c>
       <c r="C480" s="12"/>
       <c r="D480" s="12"/>
@@ -7384,12 +7446,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A481" s="14" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B481" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C481" s="12"/>
       <c r="D481" s="12"/>
@@ -7398,10 +7460,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A482" s="12"/>
       <c r="B482" s="12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C482" s="12"/>
       <c r="D482" s="12"/>
@@ -7410,10 +7472,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A483" s="12"/>
       <c r="B483" s="12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C483" s="12"/>
       <c r="D483" s="12"/>
@@ -7422,10 +7484,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A484" s="12"/>
       <c r="B484" s="12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C484" s="12"/>
       <c r="D484" s="12"/>
@@ -7434,10 +7496,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A485" s="12"/>
       <c r="B485" s="12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C485" s="12"/>
       <c r="D485" s="12"/>
@@ -7446,10 +7508,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A486" s="12"/>
       <c r="B486" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C486" s="12"/>
       <c r="D486" s="12"/>
@@ -7458,7 +7520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A487" s="12"/>
       <c r="B487" s="12" t="s">
         <v>25</v>
@@ -7470,7 +7532,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A488" s="12"/>
       <c r="B488" s="12" t="s">
         <v>26</v>
@@ -7482,10 +7544,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A489" s="12"/>
       <c r="B489" s="12" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C489" s="12"/>
       <c r="D489" s="12"/>
@@ -7494,10 +7556,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A490" s="12"/>
       <c r="B490" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C490" s="12"/>
       <c r="D490" s="12"/>
@@ -7506,19 +7568,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A491" s="12"/>
       <c r="B491" s="12"/>
       <c r="C491" s="12"/>
       <c r="D491" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E491" s="20">
         <f>-SUM(E484:E490)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E492">
         <f>SUM(E480:E491)</f>
         <v>0</v>
@@ -7528,12 +7590,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A494" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B494" s="10" t="s">
         <v>236</v>
-      </c>
-      <c r="B494" s="10" t="s">
-        <v>237</v>
       </c>
       <c r="C494" s="10"/>
       <c r="D494" s="10"/>
@@ -7543,12 +7605,12 @@
       </c>
       <c r="H494" s="18"/>
     </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A495" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B495" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C495" s="10"/>
       <c r="D495" s="10"/>
@@ -7558,10 +7620,10 @@
       </c>
       <c r="H495" s="18"/>
     </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A496" s="10"/>
       <c r="B496" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C496" s="10"/>
       <c r="D496" s="10"/>
@@ -7571,10 +7633,10 @@
       </c>
       <c r="H496" s="18"/>
     </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A497" s="10"/>
       <c r="B497" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C497" s="10"/>
       <c r="D497" s="10"/>
@@ -7584,10 +7646,10 @@
       </c>
       <c r="H497" s="18"/>
     </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A498" s="10"/>
       <c r="B498" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C498" s="10"/>
       <c r="D498" s="10"/>
@@ -7596,10 +7658,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A499" s="10"/>
       <c r="B499" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C499" s="10"/>
       <c r="D499" s="10"/>
@@ -7608,10 +7670,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A500" s="10"/>
       <c r="B500" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C500" s="10"/>
       <c r="D500" s="10"/>
@@ -7620,7 +7682,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A501" s="10"/>
       <c r="B501" s="10" t="s">
         <v>25</v>
@@ -7632,7 +7694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A502" s="10"/>
       <c r="B502" s="10" t="s">
         <v>26</v>
@@ -7644,10 +7706,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A503" s="10"/>
       <c r="B503" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C503" s="10"/>
       <c r="D503" s="10"/>
@@ -7656,10 +7718,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A504" s="10"/>
       <c r="B504" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C504" s="10"/>
       <c r="D504" s="10"/>
@@ -7668,19 +7730,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A505" s="10"/>
       <c r="B505" s="10"/>
       <c r="C505" s="10"/>
       <c r="D505" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E505" s="20">
         <f>-SUM(E498:E504)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E506">
         <f>SUM(E494:E505)</f>
         <v>0</v>
@@ -7690,12 +7752,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A508" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="B508" s="11" t="s">
         <v>236</v>
-      </c>
-      <c r="B508" s="11" t="s">
-        <v>237</v>
       </c>
       <c r="C508" s="11"/>
       <c r="D508" s="11"/>
@@ -7704,12 +7766,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A509" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B509" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C509" s="11"/>
       <c r="D509" s="11"/>
@@ -7718,10 +7780,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A510" s="11"/>
       <c r="B510" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C510" s="11"/>
       <c r="D510" s="11"/>
@@ -7730,10 +7792,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A511" s="11"/>
       <c r="B511" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C511" s="11"/>
       <c r="D511" s="11"/>
@@ -7742,10 +7804,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A512" s="11"/>
       <c r="B512" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C512" s="11"/>
       <c r="D512" s="11"/>
@@ -7754,10 +7816,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="513" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A513" s="11"/>
       <c r="B513" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C513" s="11"/>
       <c r="D513" s="11"/>
@@ -7766,10 +7828,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="514" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A514" s="11"/>
       <c r="B514" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C514" s="11"/>
       <c r="D514" s="11"/>
@@ -7778,7 +7840,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="515" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A515" s="11"/>
       <c r="B515" s="11" t="s">
         <v>25</v>
@@ -7790,7 +7852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="516" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A516" s="11"/>
       <c r="B516" s="11" t="s">
         <v>26</v>
@@ -7802,10 +7864,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="517" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A517" s="11"/>
       <c r="B517" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C517" s="11"/>
       <c r="D517" s="11"/>
@@ -7814,10 +7876,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="518" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A518" s="11"/>
       <c r="B518" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C518" s="11"/>
       <c r="D518" s="11"/>
@@ -7826,12 +7888,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="519" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A519" s="11"/>
       <c r="B519" s="11"/>
       <c r="C519" s="11"/>
       <c r="D519" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E519" s="20">
         <f>-SUM(E512:E518)</f>
@@ -7839,7 +7901,7 @@
       </c>
       <c r="F519" s="11"/>
     </row>
-    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E520">
         <f>SUM(E508:E519)</f>
         <v>0</v>
@@ -7849,10 +7911,10 @@
         <v>60</v>
       </c>
     </row>
-    <row r="524" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A524" s="7"/>
       <c r="B524" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E524">
         <f>E452+E432+E407+E14</f>
@@ -7867,12 +7929,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A525" s="9" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B525" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E525">
         <f>E76+E30+E31+E109+E148+E174+E371+E196+E204+E239+E286+E420+E506+E321</f>
@@ -7887,12 +7949,12 @@
         <v>-0.12820512820512819</v>
       </c>
     </row>
-    <row r="526" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A526" s="13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B526" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E526">
         <f>E50+E28+E33+E87+E124+E159+E381+E186+E333+E343+E356+E520</f>
@@ -7907,12 +7969,12 @@
         <v>-0.1762114537444934</v>
       </c>
     </row>
-    <row r="527" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A527" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B527" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E527">
         <f>E67+E29+E32+E98+E136+E173+E391+E312+E360+E492</f>
@@ -7927,23 +7989,23 @@
         <v>-0.17699115044247787</v>
       </c>
     </row>
-    <row r="531" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="531" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F531" t="s">
+        <v>230</v>
+      </c>
+      <c r="G531" t="s">
         <v>231</v>
       </c>
-      <c r="G531" t="s">
+    </row>
+    <row r="532" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D532" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="532" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D532" t="s">
+      <c r="G532" t="s">
         <v>233</v>
       </c>
-      <c r="G532" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="533" spans="4:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="533" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F533" s="23">
         <v>0.45</v>
       </c>
@@ -7951,7 +8013,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="534" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="534" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F534" s="23">
         <f>F533+(F542-F533)/9</f>
         <v>0.5</v>
@@ -7960,7 +8022,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="535" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="535" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F535" s="23">
         <f>F534+(F542-F533)/9</f>
         <v>0.55000000000000004</v>
@@ -7969,7 +8031,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="536" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="536" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F536" s="23">
         <f>F535+(F542-F533)/9</f>
         <v>0.60000000000000009</v>
@@ -7978,7 +8040,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="537" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="537" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F537" s="23">
         <f>F536+(F542-F533)/9</f>
         <v>0.65000000000000013</v>
@@ -7987,7 +8049,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="538" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="538" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F538" s="23">
         <f>F537+(F542-F533)/9</f>
         <v>0.70000000000000018</v>
@@ -7996,7 +8058,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="539" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="539" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F539" s="23">
         <f>F538+(F542-F533)/9</f>
         <v>0.75000000000000022</v>
@@ -8005,7 +8067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="540" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="540" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F540" s="23">
         <f>F539+(F542-F533)/9</f>
         <v>0.80000000000000027</v>
@@ -8014,7 +8076,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="541" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="541" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F541" s="23">
         <f>F540+(F542-F533)/9</f>
         <v>0.85000000000000031</v>
@@ -8023,7 +8085,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="542" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="542" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F542" s="23">
         <v>0.9</v>
       </c>
@@ -8031,9 +8093,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="543" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="543" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E543" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -8043,7 +8105,7 @@
     <mergeCell ref="G113:G174"/>
     <mergeCell ref="G189:G204"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations disablePrompts="1" count="2">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B21" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B14" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
@@ -8058,33 +8120,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="19"/>
+    <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A1" s="28" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
       <c r="D1" s="28"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D4" s="19">
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>38</v>
       </c>
@@ -8092,237 +8154,237 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D6" s="19">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D7" s="19">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D8" s="19">
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D9" s="19">
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D10" s="19">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D11" s="19">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D12" s="19">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D13" s="19">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D14" s="19">
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D15" s="19">
         <v>-0.3</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D16" s="19">
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D17" s="19">
         <v>-0.2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D18" s="19">
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>38</v>
       </c>
       <c r="B22" t="s">
+        <v>141</v>
+      </c>
+      <c r="C22" t="s">
         <v>142</v>
-      </c>
-      <c r="C22" t="s">
-        <v>143</v>
       </c>
       <c r="D22" s="19">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D23" s="19">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D24" s="19">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" t="s">
         <v>146</v>
-      </c>
-      <c r="C25" t="s">
-        <v>147</v>
       </c>
       <c r="D25" s="19">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D26" s="19">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D27" s="19">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D28" s="19">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C31" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D31" s="19">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D32" s="19">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D33" s="19">
         <v>-0.25</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D34" s="19">
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
+        <v>167</v>
+      </c>
+      <c r="C35" t="s">
         <v>168</v>
-      </c>
-      <c r="C35" t="s">
-        <v>169</v>
       </c>
       <c r="D35" s="19">
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D36" s="19">
         <v>-1</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D37" s="19">
         <v>-1</v>

--- a/ProjectManagement/EvaluationHW.xlsx
+++ b/ProjectManagement/EvaluationHW.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\Winter 2024-25\ML project\ML24-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F786C5-4C32-42E1-9CB1-A19D8C16ADDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F2117E-344A-493D-8AA8-50759C27F80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="2" r:id="rId1"/>
@@ -165,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="379">
   <si>
     <t>Literature</t>
   </si>
@@ -1299,6 +1299,9 @@
   </si>
   <si>
     <t>Hemanth-Jp</t>
+  </si>
+  <si>
+    <t>MansourAP</t>
   </si>
 </sst>
 </file>
@@ -1523,6 +1526,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1537,9 +1543,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1844,11 +1847,11 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="25" t="s">
         <v>372</v>
       </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
     </row>
     <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
@@ -1879,7 +1882,7 @@
       <c r="B11" t="s">
         <v>370</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="24">
         <v>7026116</v>
       </c>
       <c r="D11" t="s">
@@ -1898,6 +1901,9 @@
       </c>
       <c r="C12" s="3">
         <v>7025671</v>
+      </c>
+      <c r="D12" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -2288,7 +2294,7 @@
       <c r="F53" s="12">
         <v>10</v>
       </c>
-      <c r="G53" s="25" t="s">
+      <c r="G53" s="26" t="s">
         <v>338</v>
       </c>
     </row>
@@ -2305,7 +2311,7 @@
       <c r="F54" s="12">
         <v>5</v>
       </c>
-      <c r="G54" s="25"/>
+      <c r="G54" s="26"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="14"/>
@@ -2318,7 +2324,7 @@
       <c r="F55" s="12">
         <v>5</v>
       </c>
-      <c r="G55" s="25"/>
+      <c r="G55" s="26"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="14"/>
@@ -2331,7 +2337,7 @@
       <c r="F56" s="12">
         <v>5</v>
       </c>
-      <c r="G56" s="25"/>
+      <c r="G56" s="26"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="14"/>
@@ -2344,7 +2350,7 @@
       <c r="F57" s="12">
         <v>10</v>
       </c>
-      <c r="G57" s="25"/>
+      <c r="G57" s="26"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="14"/>
@@ -2357,7 +2363,7 @@
       <c r="F58" s="12">
         <v>5</v>
       </c>
-      <c r="G58" s="25"/>
+      <c r="G58" s="26"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="14"/>
@@ -2370,7 +2376,7 @@
       <c r="F59" s="12">
         <v>15</v>
       </c>
-      <c r="G59" s="25"/>
+      <c r="G59" s="26"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="14"/>
@@ -2383,7 +2389,7 @@
       <c r="F60" s="12">
         <v>5</v>
       </c>
-      <c r="G60" s="25"/>
+      <c r="G60" s="26"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="14"/>
@@ -2396,7 +2402,7 @@
       <c r="F61" s="12">
         <v>10</v>
       </c>
-      <c r="G61" s="25"/>
+      <c r="G61" s="26"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="14"/>
@@ -2409,7 +2415,7 @@
       <c r="F62" s="12">
         <v>5</v>
       </c>
-      <c r="G62" s="25"/>
+      <c r="G62" s="26"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="14"/>
@@ -2424,7 +2430,7 @@
       <c r="F63" s="12">
         <v>5</v>
       </c>
-      <c r="G63" s="25"/>
+      <c r="G63" s="26"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="14"/>
@@ -2437,7 +2443,7 @@
       <c r="F64" s="12">
         <v>20</v>
       </c>
-      <c r="G64" s="25"/>
+      <c r="G64" s="26"/>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="14"/>
@@ -2450,7 +2456,7 @@
       <c r="F65" s="12">
         <v>10</v>
       </c>
-      <c r="G65" s="25"/>
+      <c r="G65" s="26"/>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="14"/>
@@ -2464,7 +2470,7 @@
         <v>0</v>
       </c>
       <c r="F66" s="12"/>
-      <c r="G66" s="25"/>
+      <c r="G66" s="26"/>
     </row>
     <row r="67" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
@@ -2966,7 +2972,7 @@
       <c r="F113" s="11">
         <v>20</v>
       </c>
-      <c r="G113" s="26" t="s">
+      <c r="G113" s="27" t="s">
         <v>95</v>
       </c>
     </row>
@@ -2985,7 +2991,7 @@
       <c r="F114" s="11">
         <v>10</v>
       </c>
-      <c r="G114" s="26"/>
+      <c r="G114" s="27"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="11"/>
@@ -3000,7 +3006,7 @@
       <c r="F115" s="11">
         <v>10</v>
       </c>
-      <c r="G115" s="26"/>
+      <c r="G115" s="27"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="11"/>
@@ -3015,7 +3021,7 @@
       <c r="F116" s="11">
         <v>10</v>
       </c>
-      <c r="G116" s="26"/>
+      <c r="G116" s="27"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="13"/>
@@ -3030,7 +3036,7 @@
       <c r="F117" s="11">
         <v>10</v>
       </c>
-      <c r="G117" s="26"/>
+      <c r="G117" s="27"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="11"/>
@@ -3047,7 +3053,7 @@
       <c r="F118" s="11">
         <v>10</v>
       </c>
-      <c r="G118" s="26"/>
+      <c r="G118" s="27"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="11"/>
@@ -3062,7 +3068,7 @@
       <c r="F119" s="11">
         <v>10</v>
       </c>
-      <c r="G119" s="26"/>
+      <c r="G119" s="27"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="13"/>
@@ -3077,7 +3083,7 @@
       <c r="F120" s="11">
         <v>10</v>
       </c>
-      <c r="G120" s="26"/>
+      <c r="G120" s="27"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="13"/>
@@ -3092,7 +3098,7 @@
       <c r="F121" s="11">
         <v>10</v>
       </c>
-      <c r="G121" s="26"/>
+      <c r="G121" s="27"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="13"/>
@@ -3107,7 +3113,7 @@
       <c r="F122" s="11">
         <v>20</v>
       </c>
-      <c r="G122" s="26"/>
+      <c r="G122" s="27"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="11"/>
@@ -3120,7 +3126,7 @@
         <f>-SUM(E113:E122)</f>
         <v>0</v>
       </c>
-      <c r="G123" s="26"/>
+      <c r="G123" s="27"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E124">
@@ -3131,10 +3137,10 @@
         <f>SUM(F113:F122)</f>
         <v>120</v>
       </c>
-      <c r="G124" s="26"/>
+      <c r="G124" s="27"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G125" s="26"/>
+      <c r="G125" s="27"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="14" t="s">
@@ -3153,7 +3159,7 @@
       <c r="F126" s="12">
         <v>10</v>
       </c>
-      <c r="G126" s="26"/>
+      <c r="G126" s="27"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="14" t="s">
@@ -3168,7 +3174,7 @@
       <c r="F127" s="12">
         <v>7</v>
       </c>
-      <c r="G127" s="26"/>
+      <c r="G127" s="27"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="14"/>
@@ -3181,7 +3187,7 @@
       <c r="F128" s="12">
         <v>10</v>
       </c>
-      <c r="G128" s="26"/>
+      <c r="G128" s="27"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="14"/>
@@ -3196,7 +3202,7 @@
       <c r="F129" s="12">
         <v>10</v>
       </c>
-      <c r="G129" s="26"/>
+      <c r="G129" s="27"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="12"/>
@@ -3211,7 +3217,7 @@
       <c r="F130" s="12">
         <v>10</v>
       </c>
-      <c r="G130" s="26"/>
+      <c r="G130" s="27"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="12"/>
@@ -3226,7 +3232,7 @@
       <c r="F131" s="12">
         <v>8</v>
       </c>
-      <c r="G131" s="26"/>
+      <c r="G131" s="27"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="12"/>
@@ -3241,7 +3247,7 @@
       <c r="F132" s="12">
         <v>8</v>
       </c>
-      <c r="G132" s="26"/>
+      <c r="G132" s="27"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="12"/>
@@ -3254,7 +3260,7 @@
       <c r="F133" s="12">
         <v>7</v>
       </c>
-      <c r="G133" s="26"/>
+      <c r="G133" s="27"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="12"/>
@@ -3269,7 +3275,7 @@
       <c r="F134" s="12">
         <v>5</v>
       </c>
-      <c r="G134" s="26"/>
+      <c r="G134" s="27"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="12"/>
@@ -3282,7 +3288,7 @@
         <f>-SUM(E126:E134)</f>
         <v>0</v>
       </c>
-      <c r="G135" s="26"/>
+      <c r="G135" s="27"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E136">
@@ -3293,10 +3299,10 @@
         <f>SUM(F126:F134)</f>
         <v>75</v>
       </c>
-      <c r="G136" s="26"/>
+      <c r="G136" s="27"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G137" s="26"/>
+      <c r="G137" s="27"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="9" t="s">
@@ -3317,7 +3323,7 @@
         <f t="shared" ref="F138:F146" si="1">F126</f>
         <v>10</v>
       </c>
-      <c r="G138" s="26"/>
+      <c r="G138" s="27"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="10" t="str">
@@ -3337,7 +3343,7 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="G139" s="26"/>
+      <c r="G139" s="27"/>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="10"/>
@@ -3354,7 +3360,7 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G140" s="26"/>
+      <c r="G140" s="27"/>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="9"/>
@@ -3371,7 +3377,7 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G141" s="26"/>
+      <c r="G141" s="27"/>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="9"/>
@@ -3388,7 +3394,7 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G142" s="26"/>
+      <c r="G142" s="27"/>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="9"/>
@@ -3403,7 +3409,7 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G143" s="26"/>
+      <c r="G143" s="27"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="9"/>
@@ -3420,7 +3426,7 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G144" s="26"/>
+      <c r="G144" s="27"/>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="10"/>
@@ -3437,7 +3443,7 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="G145" s="26"/>
+      <c r="G145" s="27"/>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="10"/>
@@ -3454,7 +3460,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="G146" s="26"/>
+      <c r="G146" s="27"/>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="10"/>
@@ -3467,7 +3473,7 @@
         <f>-SUM(E138:E146)</f>
         <v>0</v>
       </c>
-      <c r="G147" s="26"/>
+      <c r="G147" s="27"/>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E148">
@@ -3478,7 +3484,7 @@
         <f>SUM(F138:F146)</f>
         <v>75</v>
       </c>
-      <c r="G148" s="26"/>
+      <c r="G148" s="27"/>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="13" t="str">
@@ -3499,7 +3505,7 @@
         <f t="shared" ref="F149:F157" si="4">F138</f>
         <v>10</v>
       </c>
-      <c r="G149" s="26"/>
+      <c r="G149" s="27"/>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="13" t="str">
@@ -3517,7 +3523,7 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="G150" s="26"/>
+      <c r="G150" s="27"/>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="13"/>
@@ -3532,7 +3538,7 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="G151" s="26"/>
+      <c r="G151" s="27"/>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="13"/>
@@ -3547,7 +3553,7 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="G152" s="26"/>
+      <c r="G152" s="27"/>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="13"/>
@@ -3562,7 +3568,7 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="G153" s="26"/>
+      <c r="G153" s="27"/>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="13"/>
@@ -3577,7 +3583,7 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="G154" s="26"/>
+      <c r="G154" s="27"/>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="13"/>
@@ -3592,7 +3598,7 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="G155" s="26"/>
+      <c r="G155" s="27"/>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="13"/>
@@ -3607,7 +3613,7 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="G156" s="26"/>
+      <c r="G156" s="27"/>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="13"/>
@@ -3622,7 +3628,7 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="G157" s="26"/>
+      <c r="G157" s="27"/>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="13"/>
@@ -3636,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="F158" s="11"/>
-      <c r="G158" s="26"/>
+      <c r="G158" s="27"/>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="1"/>
@@ -3649,7 +3655,7 @@
         <f>SUM(F149:F157)</f>
         <v>75</v>
       </c>
-      <c r="G159" s="26"/>
+      <c r="G159" s="27"/>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="14" t="s">
@@ -3666,7 +3672,7 @@
       <c r="F160" s="12">
         <v>10</v>
       </c>
-      <c r="G160" s="26"/>
+      <c r="G160" s="27"/>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="14" t="s">
@@ -3681,7 +3687,7 @@
       <c r="F161" s="12">
         <v>10</v>
       </c>
-      <c r="G161" s="26"/>
+      <c r="G161" s="27"/>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="14"/>
@@ -3694,7 +3700,7 @@
       <c r="F162" s="12">
         <v>10</v>
       </c>
-      <c r="G162" s="26"/>
+      <c r="G162" s="27"/>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="14"/>
@@ -3707,7 +3713,7 @@
       <c r="F163" s="12">
         <v>10</v>
       </c>
-      <c r="G163" s="26"/>
+      <c r="G163" s="27"/>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="14"/>
@@ -3720,7 +3726,7 @@
       <c r="F164" s="12">
         <v>10</v>
       </c>
-      <c r="G164" s="26"/>
+      <c r="G164" s="27"/>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="14"/>
@@ -3733,7 +3739,7 @@
       <c r="F165" s="12">
         <v>6</v>
       </c>
-      <c r="G165" s="26"/>
+      <c r="G165" s="27"/>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="14"/>
@@ -3746,7 +3752,7 @@
       <c r="F166" s="12">
         <v>6</v>
       </c>
-      <c r="G166" s="26"/>
+      <c r="G166" s="27"/>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="14"/>
@@ -3763,7 +3769,7 @@
       <c r="F167" s="12">
         <v>6</v>
       </c>
-      <c r="G167" s="26"/>
+      <c r="G167" s="27"/>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="12"/>
@@ -3778,7 +3784,7 @@
       <c r="F168" s="12">
         <v>6</v>
       </c>
-      <c r="G168" s="26"/>
+      <c r="G168" s="27"/>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="12"/>
@@ -3793,7 +3799,7 @@
       <c r="F169" s="12">
         <v>6</v>
       </c>
-      <c r="G169" s="26"/>
+      <c r="G169" s="27"/>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="12"/>
@@ -3808,7 +3814,7 @@
       <c r="F170" s="12">
         <v>5</v>
       </c>
-      <c r="G170" s="26"/>
+      <c r="G170" s="27"/>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="12"/>
@@ -3823,7 +3829,7 @@
       <c r="F171" s="12">
         <v>5</v>
       </c>
-      <c r="G171" s="26"/>
+      <c r="G171" s="27"/>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="12"/>
@@ -3836,7 +3842,7 @@
         <f>-SUM(E160:E171)</f>
         <v>0</v>
       </c>
-      <c r="G172" s="26"/>
+      <c r="G172" s="27"/>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E173">
@@ -3847,10 +3853,10 @@
         <f>SUM(F160:F171)</f>
         <v>90</v>
       </c>
-      <c r="G173" s="26"/>
+      <c r="G173" s="27"/>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="G174" s="26"/>
+      <c r="G174" s="27"/>
     </row>
     <row r="175" spans="1:12" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A175" s="5" t="s">
@@ -4000,7 +4006,7 @@
       <c r="F189" s="10">
         <v>5</v>
       </c>
-      <c r="G189" s="27" t="s">
+      <c r="G189" s="28" t="s">
         <v>95</v>
       </c>
     </row>
@@ -4017,7 +4023,7 @@
       <c r="F190" s="10">
         <v>10</v>
       </c>
-      <c r="G190" s="27"/>
+      <c r="G190" s="28"/>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="9"/>
@@ -4030,7 +4036,7 @@
       <c r="F191" s="10">
         <v>10</v>
       </c>
-      <c r="G191" s="27"/>
+      <c r="G191" s="28"/>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="9"/>
@@ -4043,7 +4049,7 @@
       <c r="F192" s="10">
         <v>5</v>
       </c>
-      <c r="G192" s="27"/>
+      <c r="G192" s="28"/>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" s="9"/>
@@ -4056,7 +4062,7 @@
       <c r="F193" s="10">
         <v>5</v>
       </c>
-      <c r="G193" s="27"/>
+      <c r="G193" s="28"/>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" s="9"/>
@@ -4069,7 +4075,7 @@
       <c r="F194" s="10">
         <v>5</v>
       </c>
-      <c r="G194" s="27"/>
+      <c r="G194" s="28"/>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" s="9"/>
@@ -4083,7 +4089,7 @@
         <v>0</v>
       </c>
       <c r="F195" s="10"/>
-      <c r="G195" s="27"/>
+      <c r="G195" s="28"/>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="1"/>
@@ -4096,7 +4102,7 @@
         <f>SUM(F189:F194)</f>
         <v>40</v>
       </c>
-      <c r="G196" s="27"/>
+      <c r="G196" s="28"/>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" s="9" t="s">
@@ -4111,7 +4117,7 @@
       <c r="F197" s="10">
         <v>5</v>
       </c>
-      <c r="G197" s="27"/>
+      <c r="G197" s="28"/>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" s="9" t="s">
@@ -4126,7 +4132,7 @@
       <c r="F198" s="10">
         <v>10</v>
       </c>
-      <c r="G198" s="27"/>
+      <c r="G198" s="28"/>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="9" t="s">
@@ -4141,7 +4147,7 @@
       <c r="F199" s="10">
         <v>10</v>
       </c>
-      <c r="G199" s="27"/>
+      <c r="G199" s="28"/>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="9"/>
@@ -4154,7 +4160,7 @@
       <c r="F200" s="10">
         <v>5</v>
       </c>
-      <c r="G200" s="27"/>
+      <c r="G200" s="28"/>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" s="9"/>
@@ -4167,7 +4173,7 @@
       <c r="F201" s="10">
         <v>5</v>
       </c>
-      <c r="G201" s="27"/>
+      <c r="G201" s="28"/>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" s="9"/>
@@ -4180,7 +4186,7 @@
       <c r="F202" s="10">
         <v>5</v>
       </c>
-      <c r="G202" s="27"/>
+      <c r="G202" s="28"/>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="9"/>
@@ -4194,7 +4200,7 @@
         <v>0</v>
       </c>
       <c r="F203" s="10"/>
-      <c r="G203" s="27"/>
+      <c r="G203" s="28"/>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" s="1"/>
@@ -4207,7 +4213,7 @@
         <f>SUM(F197:F202)</f>
         <v>40</v>
       </c>
-      <c r="G204" s="27"/>
+      <c r="G204" s="28"/>
     </row>
     <row r="205" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A205" s="5" t="s">
@@ -8128,12 +8134,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>223</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>

--- a/ProjectManagement/EvaluationHW.xlsx
+++ b/ProjectManagement/EvaluationHW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\Winter 2024-25\ML project\ML24-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Wings_Hub\Wings-Hub\ML2425\ML24-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F2117E-344A-493D-8AA8-50759C27F80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4B475B-C655-4B92-8C52-913CE8828D79}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="2" r:id="rId1"/>
@@ -165,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="387">
   <si>
     <t>Literature</t>
   </si>
@@ -1302,6 +1302,30 @@
   </si>
   <si>
     <t>MansourAP</t>
+  </si>
+  <si>
+    <t>citations, tikz</t>
+  </si>
+  <si>
+    <t>Segementation and Tree Models</t>
+  </si>
+  <si>
+    <t>no file</t>
+  </si>
+  <si>
+    <t>no description</t>
+  </si>
+  <si>
+    <t>example with images, but no pictures</t>
+  </si>
+  <si>
+    <t>citations</t>
+  </si>
+  <si>
+    <t>no latex for summary</t>
+  </si>
+  <si>
+    <t>no code files, no doxygen</t>
   </si>
 </sst>
 </file>
@@ -1546,7 +1570,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1825,40 +1849,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M543"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" customWidth="1"/>
-    <col min="2" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="33.6" x14ac:dyDescent="0.65">
+    <row r="2" spans="1:6" ht="33.75" x14ac:dyDescent="0.5">
       <c r="A2" s="22" t="s">
         <v>367</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>372</v>
       </c>
       <c r="B6" s="25"/>
       <c r="C6" s="25"/>
     </row>
-    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>71</v>
       </c>
@@ -1875,7 +1899,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>369</v>
       </c>
@@ -1892,7 +1916,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>373</v>
       </c>
@@ -1906,7 +1930,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>375</v>
       </c>
@@ -1920,7 +1944,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>75</v>
       </c>
@@ -1928,7 +1952,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>76</v>
       </c>
@@ -1936,7 +1960,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>77</v>
       </c>
@@ -1944,7 +1968,7 @@
         <v>45565</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>78</v>
       </c>
@@ -1952,7 +1976,7 @@
         <v>45688</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>79</v>
       </c>
@@ -1960,7 +1984,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>80</v>
       </c>
@@ -1968,12 +1992,12 @@
         <v>189</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>82</v>
       </c>
@@ -1981,7 +2005,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="11"/>
       <c r="B28" s="11" t="s">
         <v>138</v>
@@ -1998,7 +2022,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="12"/>
       <c r="B29" s="12" t="s">
         <v>138</v>
@@ -2015,7 +2039,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
         <v>138</v>
@@ -2032,7 +2056,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="10"/>
       <c r="B31" s="10" t="s">
         <v>139</v>
@@ -2049,7 +2073,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
       <c r="B32" s="12" t="s">
         <v>139</v>
@@ -2066,7 +2090,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="11" t="s">
         <v>139</v>
@@ -2083,12 +2107,12 @@
         <v>336</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>0</v>
       </c>
@@ -2102,7 +2126,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="13"/>
       <c r="B37" s="11" t="s">
         <v>27</v>
@@ -2114,7 +2138,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
       <c r="B38" s="11" t="s">
         <v>3</v>
@@ -2126,7 +2150,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="11"/>
       <c r="B39" s="11" t="s">
         <v>4</v>
@@ -2138,7 +2162,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="11"/>
       <c r="B40" s="11" t="s">
         <v>5</v>
@@ -2150,7 +2174,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
       <c r="B41" s="11" t="s">
         <v>337</v>
@@ -2162,7 +2186,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="13"/>
       <c r="B42" s="11" t="s">
         <v>1</v>
@@ -2176,7 +2200,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="13"/>
       <c r="B43" s="11"/>
       <c r="C43" s="11" t="s">
@@ -2188,7 +2212,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="11"/>
       <c r="B44" s="11"/>
       <c r="C44" s="11" t="s">
@@ -2200,7 +2224,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="11"/>
       <c r="B45" s="11"/>
       <c r="C45" s="11" t="s">
@@ -2212,7 +2236,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="11"/>
       <c r="B46" s="11"/>
       <c r="C46" s="11" t="s">
@@ -2224,7 +2248,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="11"/>
       <c r="B47" s="11"/>
       <c r="C47" s="11" t="s">
@@ -2236,7 +2260,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="11"/>
       <c r="B48" s="11"/>
       <c r="C48" s="11" t="s">
@@ -2248,7 +2272,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="11"/>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
@@ -2261,7 +2285,7 @@
       </c>
       <c r="F49" s="11"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="11"/>
       <c r="E50">
         <f>SUM(E36:E49)</f>
@@ -2272,14 +2296,14 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:12" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>339</v>
       </c>
       <c r="K52"/>
       <c r="L52"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
         <v>111</v>
       </c>
@@ -2298,7 +2322,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="14"/>
       <c r="B54" s="14" t="s">
         <v>236</v>
@@ -2313,7 +2337,7 @@
       </c>
       <c r="G54" s="26"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="14"/>
       <c r="B55" s="14"/>
       <c r="C55" s="12" t="s">
@@ -2326,7 +2350,7 @@
       </c>
       <c r="G55" s="26"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="14"/>
       <c r="B56" s="12"/>
       <c r="C56" s="12" t="s">
@@ -2339,7 +2363,7 @@
       </c>
       <c r="G56" s="26"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="14"/>
       <c r="B57" s="14"/>
       <c r="C57" s="12" t="s">
@@ -2352,7 +2376,7 @@
       </c>
       <c r="G57" s="26"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="14"/>
       <c r="B58" s="14"/>
       <c r="C58" s="12" t="s">
@@ -2365,7 +2389,7 @@
       </c>
       <c r="G58" s="26"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="14"/>
       <c r="B59" s="14"/>
       <c r="C59" s="12" t="s">
@@ -2378,7 +2402,7 @@
       </c>
       <c r="G59" s="26"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="14"/>
       <c r="B60" s="14"/>
       <c r="C60" s="12" t="s">
@@ -2391,7 +2415,7 @@
       </c>
       <c r="G60" s="26"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="14"/>
       <c r="B61" s="14"/>
       <c r="C61" s="12" t="s">
@@ -2404,7 +2428,7 @@
       </c>
       <c r="G61" s="26"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="14"/>
       <c r="B62" s="14"/>
       <c r="C62" s="12" t="s">
@@ -2417,7 +2441,7 @@
       </c>
       <c r="G62" s="26"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="14"/>
       <c r="B63" s="14" t="s">
         <v>223</v>
@@ -2432,7 +2456,7 @@
       </c>
       <c r="G63" s="26"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="14"/>
       <c r="B64" s="14"/>
       <c r="C64" s="12" t="s">
@@ -2445,7 +2469,7 @@
       </c>
       <c r="G64" s="26"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="14"/>
       <c r="B65" s="14"/>
       <c r="C65" s="12" t="s">
@@ -2458,7 +2482,7 @@
       </c>
       <c r="G65" s="26"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="14"/>
       <c r="B66" s="14"/>
       <c r="C66" s="12"/>
@@ -2472,7 +2496,7 @@
       <c r="F66" s="12"/>
       <c r="G66" s="26"/>
     </row>
-    <row r="67" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="E67">
@@ -2486,14 +2510,14 @@
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
     </row>
-    <row r="68" spans="1:13" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:13" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>340</v>
       </c>
       <c r="K68"/>
       <c r="L68"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="str">
         <f>$A$68</f>
         <v>Document Manufacturing and Assembly</v>
@@ -2510,7 +2534,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="9"/>
       <c r="B70" s="9" t="s">
         <v>236</v>
@@ -2524,7 +2548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="9"/>
       <c r="B71" s="9"/>
       <c r="C71" s="10" t="s">
@@ -2536,7 +2560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="9"/>
       <c r="B72" s="9"/>
       <c r="C72" s="10" t="s">
@@ -2548,7 +2572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="9"/>
       <c r="B73" s="9"/>
       <c r="C73" s="10" t="s">
@@ -2560,7 +2584,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="9"/>
       <c r="B74" s="9"/>
       <c r="C74" s="10" t="s">
@@ -2572,7 +2596,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="9"/>
       <c r="B75" s="9"/>
       <c r="C75" s="10"/>
@@ -2585,7 +2609,7 @@
       </c>
       <c r="F75" s="10"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="E76">
@@ -2597,15 +2621,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
     </row>
-    <row r="78" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="13" t="s">
         <v>283</v>
       </c>
@@ -2621,7 +2645,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="13"/>
       <c r="B80" s="11"/>
       <c r="C80" s="11" t="s">
@@ -2633,7 +2657,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="13"/>
       <c r="B81" s="11"/>
       <c r="C81" s="11" t="s">
@@ -2645,7 +2669,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="13"/>
       <c r="B82" s="13" t="s">
         <v>236</v>
@@ -2659,7 +2683,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="13"/>
       <c r="B83" s="13"/>
       <c r="C83" s="11" t="s">
@@ -2671,7 +2695,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="13"/>
       <c r="B84" s="13"/>
       <c r="C84" s="11" t="s">
@@ -2683,7 +2707,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="13"/>
       <c r="B85" s="13"/>
       <c r="C85" s="11" t="s">
@@ -2695,7 +2719,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="13"/>
       <c r="B86" s="13"/>
       <c r="C86" s="13"/>
@@ -2708,7 +2732,7 @@
       </c>
       <c r="F86" s="13"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="E87">
@@ -2720,18 +2744,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A89" s="21" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="14" t="s">
         <v>6</v>
       </c>
@@ -2745,7 +2769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="12"/>
       <c r="B92" s="12"/>
       <c r="C92" s="12" t="s">
@@ -2757,7 +2781,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="12"/>
       <c r="B93" s="12"/>
       <c r="C93" s="12" t="s">
@@ -2769,7 +2793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="12"/>
       <c r="B94" s="12"/>
       <c r="C94" s="12" t="s">
@@ -2781,7 +2805,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="12"/>
       <c r="B95" s="12"/>
       <c r="C95" s="12" t="s">
@@ -2793,7 +2817,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="12"/>
       <c r="B96" s="12"/>
       <c r="C96" s="12" t="s">
@@ -2805,7 +2829,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="12"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
@@ -2818,7 +2842,7 @@
       </c>
       <c r="F97" s="12"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E98">
         <f>SUM(E91:E97)</f>
         <v>0</v>
@@ -2828,12 +2852,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="9" t="s">
         <v>273</v>
       </c>
@@ -2847,7 +2871,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="9"/>
       <c r="B101" s="10" t="s">
         <v>13</v>
@@ -2859,7 +2883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="10"/>
       <c r="B102" s="10" t="s">
         <v>14</v>
@@ -2871,7 +2895,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="10"/>
       <c r="B103" s="10" t="s">
         <v>15</v>
@@ -2883,7 +2907,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="10"/>
       <c r="B104" s="10" t="s">
         <v>16</v>
@@ -2895,7 +2919,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="10"/>
       <c r="B105" s="10" t="s">
         <v>17</v>
@@ -2907,7 +2931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="10"/>
       <c r="B106" s="10" t="s">
         <v>19</v>
@@ -2919,7 +2943,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="10"/>
       <c r="B107" s="16" t="s">
         <v>18</v>
@@ -2931,7 +2955,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="10"/>
       <c r="B108" s="16"/>
       <c r="C108" s="10"/>
@@ -2943,7 +2967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E109">
         <f>SUM(E100:E108)</f>
         <v>0</v>
@@ -2953,7 +2977,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="13" t="s">
         <v>299</v>
       </c>
@@ -2976,7 +3000,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="13" t="s">
         <v>295</v>
       </c>
@@ -2993,7 +3017,7 @@
       </c>
       <c r="G114" s="27"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="11"/>
       <c r="B115" s="11"/>
       <c r="C115" s="11" t="s">
@@ -3008,7 +3032,7 @@
       </c>
       <c r="G115" s="27"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="11"/>
       <c r="B116" s="11"/>
       <c r="C116" s="11" t="s">
@@ -3023,7 +3047,7 @@
       </c>
       <c r="G116" s="27"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="13"/>
       <c r="B117" s="11"/>
       <c r="C117" s="11" t="s">
@@ -3038,7 +3062,7 @@
       </c>
       <c r="G117" s="27"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="11"/>
       <c r="B118" s="11"/>
       <c r="C118" s="11" t="s">
@@ -3055,7 +3079,7 @@
       </c>
       <c r="G118" s="27"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="11"/>
       <c r="B119" s="11"/>
       <c r="C119" s="11"/>
@@ -3070,7 +3094,7 @@
       </c>
       <c r="G119" s="27"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
       <c r="B120" s="11"/>
       <c r="C120" s="11"/>
@@ -3085,7 +3109,7 @@
       </c>
       <c r="G120" s="27"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="13"/>
       <c r="B121" s="11"/>
       <c r="C121" s="11"/>
@@ -3100,7 +3124,7 @@
       </c>
       <c r="G121" s="27"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="13"/>
       <c r="B122" s="11"/>
       <c r="C122" s="11" t="s">
@@ -3115,7 +3139,7 @@
       </c>
       <c r="G122" s="27"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="11"/>
       <c r="B123" s="11"/>
       <c r="C123" s="11"/>
@@ -3128,7 +3152,7 @@
       </c>
       <c r="G123" s="27"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E124">
         <f>SUM(E117:E123)</f>
         <v>0</v>
@@ -3139,10 +3163,10 @@
       </c>
       <c r="G124" s="27"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G125" s="27"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="14" t="s">
         <v>298</v>
       </c>
@@ -3161,7 +3185,7 @@
       </c>
       <c r="G126" s="27"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="14" t="s">
         <v>352</v>
       </c>
@@ -3176,7 +3200,7 @@
       </c>
       <c r="G127" s="27"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="14"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12" t="s">
@@ -3189,7 +3213,7 @@
       </c>
       <c r="G128" s="27"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="14"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12" t="s">
@@ -3204,7 +3228,7 @@
       </c>
       <c r="G129" s="27"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12" t="s">
@@ -3219,7 +3243,7 @@
       </c>
       <c r="G130" s="27"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="12"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12" t="s">
@@ -3234,7 +3258,7 @@
       </c>
       <c r="G131" s="27"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="12"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12" t="s">
@@ -3249,7 +3273,7 @@
       </c>
       <c r="G132" s="27"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12" t="s">
@@ -3262,7 +3286,7 @@
       </c>
       <c r="G133" s="27"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12" t="s">
@@ -3277,7 +3301,7 @@
       </c>
       <c r="G134" s="27"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="12"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
@@ -3290,7 +3314,7 @@
       </c>
       <c r="G135" s="27"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E136">
         <f>SUM(E126:E135)</f>
         <v>0</v>
@@ -3301,10 +3325,10 @@
       </c>
       <c r="G136" s="27"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G137" s="27"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="9" t="s">
         <v>351</v>
       </c>
@@ -3325,7 +3349,7 @@
       </c>
       <c r="G138" s="27"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="10" t="str">
         <f>$A$127</f>
         <v>e.g. camera, IMU, SPI</v>
@@ -3345,7 +3369,7 @@
       </c>
       <c r="G139" s="27"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="10"/>
       <c r="B140" s="10"/>
       <c r="C140" s="10" t="str">
@@ -3362,7 +3386,7 @@
       </c>
       <c r="G140" s="27"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="9"/>
       <c r="B141" s="10"/>
       <c r="C141" s="10" t="str">
@@ -3379,7 +3403,7 @@
       </c>
       <c r="G141" s="27"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="9"/>
       <c r="B142" s="10"/>
       <c r="C142" s="10" t="str">
@@ -3396,7 +3420,7 @@
       </c>
       <c r="G142" s="27"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="9"/>
       <c r="B143" s="10"/>
       <c r="C143" s="10" t="str">
@@ -3411,7 +3435,7 @@
       </c>
       <c r="G143" s="27"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="9"/>
       <c r="B144" s="10"/>
       <c r="C144" s="10" t="str">
@@ -3428,7 +3452,7 @@
       </c>
       <c r="G144" s="27"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="10"/>
       <c r="B145" s="10"/>
       <c r="C145" s="10" t="str">
@@ -3445,7 +3469,7 @@
       </c>
       <c r="G145" s="27"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="10"/>
       <c r="B146" s="10"/>
       <c r="C146" s="10" t="str">
@@ -3462,7 +3486,7 @@
       </c>
       <c r="G146" s="27"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="10"/>
       <c r="B147" s="10"/>
       <c r="C147" s="10"/>
@@ -3475,7 +3499,7 @@
       </c>
       <c r="G147" s="27"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E148">
         <f>SUM(E138:E147)</f>
         <v>0</v>
@@ -3486,7 +3510,7 @@
       </c>
       <c r="G148" s="27"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="13" t="str">
         <f t="shared" ref="A149:A150" si="2">A138</f>
         <v>domain sensor/actor</v>
@@ -3507,7 +3531,7 @@
       </c>
       <c r="G149" s="27"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="13" t="str">
         <f t="shared" si="2"/>
         <v>e.g. camera, IMU, SPI</v>
@@ -3525,7 +3549,7 @@
       </c>
       <c r="G150" s="27"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="13"/>
       <c r="B151" s="13"/>
       <c r="C151" s="11" t="str">
@@ -3540,7 +3564,7 @@
       </c>
       <c r="G151" s="27"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="13"/>
       <c r="B152" s="13"/>
       <c r="C152" s="11" t="str">
@@ -3555,7 +3579,7 @@
       </c>
       <c r="G152" s="27"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="13"/>
       <c r="B153" s="13"/>
       <c r="C153" s="11" t="str">
@@ -3570,7 +3594,7 @@
       </c>
       <c r="G153" s="27"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="13"/>
       <c r="B154" s="13"/>
       <c r="C154" s="11" t="str">
@@ -3585,7 +3609,7 @@
       </c>
       <c r="G154" s="27"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="13"/>
       <c r="B155" s="13"/>
       <c r="C155" s="11" t="str">
@@ -3600,7 +3624,7 @@
       </c>
       <c r="G155" s="27"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="13"/>
       <c r="B156" s="13"/>
       <c r="C156" s="11" t="str">
@@ -3615,7 +3639,7 @@
       </c>
       <c r="G156" s="27"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="13"/>
       <c r="B157" s="13"/>
       <c r="C157" s="11" t="str">
@@ -3630,7 +3654,7 @@
       </c>
       <c r="G157" s="27"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="13"/>
       <c r="B158" s="13"/>
       <c r="C158" s="11"/>
@@ -3644,7 +3668,7 @@
       <c r="F158" s="11"/>
       <c r="G158" s="27"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="E159">
@@ -3657,7 +3681,7 @@
       </c>
       <c r="G159" s="27"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="14" t="s">
         <v>301</v>
       </c>
@@ -3674,7 +3698,7 @@
       </c>
       <c r="G160" s="27"/>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="14" t="s">
         <v>302</v>
       </c>
@@ -3689,7 +3713,7 @@
       </c>
       <c r="G161" s="27"/>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="14"/>
       <c r="B162" s="12"/>
       <c r="C162" s="12" t="s">
@@ -3702,7 +3726,7 @@
       </c>
       <c r="G162" s="27"/>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="14"/>
       <c r="B163" s="12"/>
       <c r="C163" s="12" t="s">
@@ -3715,7 +3739,7 @@
       </c>
       <c r="G163" s="27"/>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="14"/>
       <c r="B164" s="12"/>
       <c r="C164" s="12" t="s">
@@ -3728,7 +3752,7 @@
       </c>
       <c r="G164" s="27"/>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="14"/>
       <c r="B165" s="12"/>
       <c r="C165" s="12" t="s">
@@ -3741,7 +3765,7 @@
       </c>
       <c r="G165" s="27"/>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="14"/>
       <c r="B166" s="12"/>
       <c r="C166" s="12" t="s">
@@ -3754,7 +3778,7 @@
       </c>
       <c r="G166" s="27"/>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="14"/>
       <c r="B167" s="12"/>
       <c r="C167" s="12" t="s">
@@ -3771,7 +3795,7 @@
       </c>
       <c r="G167" s="27"/>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="12"/>
       <c r="B168" s="12"/>
       <c r="C168" s="12"/>
@@ -3786,7 +3810,7 @@
       </c>
       <c r="G168" s="27"/>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" s="12"/>
       <c r="B169" s="12"/>
       <c r="C169" s="12" t="s">
@@ -3801,7 +3825,7 @@
       </c>
       <c r="G169" s="27"/>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" s="12"/>
       <c r="B170" s="12"/>
       <c r="C170" s="12" t="s">
@@ -3816,7 +3840,7 @@
       </c>
       <c r="G170" s="27"/>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" s="12"/>
       <c r="B171" s="12"/>
       <c r="C171" s="12" t="s">
@@ -3831,7 +3855,7 @@
       </c>
       <c r="G171" s="27"/>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" s="12"/>
       <c r="B172" s="12"/>
       <c r="C172" s="12"/>
@@ -3844,7 +3868,7 @@
       </c>
       <c r="G172" s="27"/>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E173">
         <f>SUM(E160:E172)</f>
         <v>0</v>
@@ -3855,20 +3879,20 @@
       </c>
       <c r="G173" s="27"/>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G174" s="27"/>
     </row>
-    <row r="175" spans="1:12" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:12" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A175" s="5" t="s">
         <v>307</v>
       </c>
       <c r="K175"/>
       <c r="L175"/>
     </row>
-    <row r="176" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="13" t="s">
         <v>21</v>
       </c>
@@ -3882,7 +3906,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="11"/>
       <c r="B178" s="11"/>
       <c r="C178" s="11" t="s">
@@ -3894,7 +3918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="11"/>
       <c r="B179" s="11"/>
       <c r="C179" s="11" t="s">
@@ -3906,7 +3930,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="11"/>
       <c r="B180" s="11"/>
       <c r="C180" s="11" t="s">
@@ -3918,7 +3942,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="11"/>
       <c r="B181" s="11"/>
       <c r="C181" s="11" t="s">
@@ -3930,7 +3954,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="11"/>
       <c r="B182" s="11"/>
       <c r="C182" s="11" t="s">
@@ -3942,7 +3966,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="11"/>
       <c r="B183" s="11"/>
       <c r="C183" s="11" t="s">
@@ -3954,7 +3978,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="11"/>
       <c r="B184" s="11"/>
       <c r="C184" s="11" t="s">
@@ -3966,7 +3990,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="11"/>
       <c r="B185" s="11"/>
       <c r="C185" s="11"/>
@@ -3978,7 +4002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E186">
         <f>SUM(E177:E185)</f>
         <v>0</v>
@@ -3988,12 +4012,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A188" s="5" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="9" t="s">
         <v>176</v>
       </c>
@@ -4010,7 +4034,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="9" t="s">
         <v>290</v>
       </c>
@@ -4025,7 +4049,7 @@
       </c>
       <c r="G190" s="28"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="9"/>
       <c r="B191" s="9"/>
       <c r="C191" s="10" t="s">
@@ -4038,7 +4062,7 @@
       </c>
       <c r="G191" s="28"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="9"/>
       <c r="B192" s="9"/>
       <c r="C192" s="10" t="s">
@@ -4051,7 +4075,7 @@
       </c>
       <c r="G192" s="28"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="9"/>
       <c r="B193" s="9"/>
       <c r="C193" s="10" t="s">
@@ -4064,7 +4088,7 @@
       </c>
       <c r="G193" s="28"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="9"/>
       <c r="B194" s="9"/>
       <c r="C194" s="10" t="s">
@@ -4077,7 +4101,7 @@
       </c>
       <c r="G194" s="28"/>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="9"/>
       <c r="B195" s="9"/>
       <c r="C195" s="10"/>
@@ -4091,7 +4115,7 @@
       <c r="F195" s="10"/>
       <c r="G195" s="28"/>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="E196">
@@ -4104,7 +4128,7 @@
       </c>
       <c r="G196" s="28"/>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="9" t="s">
         <v>176</v>
       </c>
@@ -4119,7 +4143,7 @@
       </c>
       <c r="G197" s="28"/>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="9" t="s">
         <v>292</v>
       </c>
@@ -4134,7 +4158,7 @@
       </c>
       <c r="G198" s="28"/>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="9" t="s">
         <v>291</v>
       </c>
@@ -4149,7 +4173,7 @@
       </c>
       <c r="G199" s="28"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="9"/>
       <c r="B200" s="9"/>
       <c r="C200" s="10" t="s">
@@ -4162,7 +4186,7 @@
       </c>
       <c r="G200" s="28"/>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="9"/>
       <c r="B201" s="9"/>
       <c r="C201" s="10" t="s">
@@ -4175,7 +4199,7 @@
       </c>
       <c r="G201" s="28"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="9"/>
       <c r="B202" s="9"/>
       <c r="C202" s="10" t="s">
@@ -4188,7 +4212,7 @@
       </c>
       <c r="G202" s="28"/>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="9"/>
       <c r="B203" s="9"/>
       <c r="C203" s="10"/>
@@ -4202,7 +4226,7 @@
       <c r="F203" s="10"/>
       <c r="G203" s="28"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="E204">
@@ -4215,12 +4239,12 @@
       </c>
       <c r="G204" s="28"/>
     </row>
-    <row r="205" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A205" s="5" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="7" t="s">
         <v>28</v>
       </c>
@@ -4232,7 +4256,7 @@
       <c r="E206" s="8"/>
       <c r="F206" s="8"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="8"/>
       <c r="B207" s="8"/>
       <c r="C207" s="8" t="s">
@@ -4244,7 +4268,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="8"/>
       <c r="B208" s="8"/>
       <c r="C208" s="8" t="s">
@@ -4254,7 +4278,7 @@
       <c r="E208" s="8"/>
       <c r="F208" s="8"/>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A209" s="8"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8" t="s">
@@ -4264,7 +4288,7 @@
       <c r="E209" s="8"/>
       <c r="F209" s="8"/>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A210" s="8"/>
       <c r="B210" s="8"/>
       <c r="C210" s="8" t="s">
@@ -4276,18 +4300,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
       <c r="F211">
         <f>SUM(F206:F210)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="212" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A212" s="5" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A213" s="13" t="s">
         <v>325</v>
       </c>
@@ -4301,7 +4325,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A214" s="13"/>
       <c r="B214" s="11"/>
       <c r="C214" s="11"/>
@@ -4313,7 +4337,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A215" s="13"/>
       <c r="B215" s="11"/>
       <c r="C215" s="11"/>
@@ -4325,7 +4349,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A216" s="13"/>
       <c r="B216" s="11"/>
       <c r="C216" s="11"/>
@@ -4337,7 +4361,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A217" s="13"/>
       <c r="B217" s="11"/>
       <c r="C217" s="11"/>
@@ -4349,7 +4373,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A218" s="13"/>
       <c r="B218" s="11"/>
       <c r="C218" s="11"/>
@@ -4362,7 +4386,7 @@
       </c>
       <c r="F218" s="11"/>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="E219">
         <f>-SUM(E213:E218)</f>
@@ -4374,7 +4398,7 @@
       </c>
       <c r="M219" s="19"/>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A221" s="9" t="s">
         <v>66</v>
       </c>
@@ -4388,7 +4412,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A222" s="9"/>
       <c r="B222" s="10" t="s">
         <v>42</v>
@@ -4400,7 +4424,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A223" s="9"/>
       <c r="B223" s="10" t="s">
         <v>328</v>
@@ -4412,7 +4436,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A224" s="9"/>
       <c r="B224" s="10" t="s">
         <v>67</v>
@@ -4424,7 +4448,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="9"/>
       <c r="B225" s="10"/>
       <c r="C225" s="10"/>
@@ -4437,7 +4461,7 @@
       </c>
       <c r="F225" s="10"/>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="E226">
         <f>-SUM(E221:E225)</f>
@@ -4448,7 +4472,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="9" t="s">
         <v>261</v>
       </c>
@@ -4466,7 +4490,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="10"/>
       <c r="B228" s="10"/>
       <c r="C228" s="10"/>
@@ -4478,7 +4502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="10"/>
       <c r="B229" s="10"/>
       <c r="C229" s="10"/>
@@ -4490,7 +4514,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="10"/>
       <c r="B230" s="10"/>
       <c r="C230" s="10"/>
@@ -4502,7 +4526,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="10"/>
       <c r="B231" s="10"/>
       <c r="C231" s="10"/>
@@ -4514,7 +4538,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="10"/>
       <c r="B232" s="10"/>
       <c r="C232" s="10"/>
@@ -4526,7 +4550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="10"/>
       <c r="B233" s="10"/>
       <c r="C233" s="10" t="s">
@@ -4540,7 +4564,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="10"/>
       <c r="B234" s="10"/>
       <c r="C234" s="10"/>
@@ -4552,7 +4576,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="10"/>
       <c r="B235" s="10"/>
       <c r="C235" s="10"/>
@@ -4564,7 +4588,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="10"/>
       <c r="B236" s="10"/>
       <c r="C236" s="10"/>
@@ -4576,7 +4600,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="10"/>
       <c r="B237" s="10"/>
       <c r="C237" s="10"/>
@@ -4588,7 +4612,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="10"/>
       <c r="B238" s="10"/>
       <c r="C238" s="10"/>
@@ -4601,7 +4625,7 @@
       </c>
       <c r="F238" s="10"/>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E239">
         <f>SUM(E227:E232)</f>
         <v>0</v>
@@ -4611,7 +4635,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="7" t="s">
         <v>261</v>
       </c>
@@ -4625,7 +4649,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="8"/>
       <c r="B241" s="7" t="s">
         <v>20</v>
@@ -4639,7 +4663,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="8"/>
       <c r="B242" s="8"/>
       <c r="C242" s="8" t="s">
@@ -4651,7 +4675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="8"/>
       <c r="B243" s="8"/>
       <c r="C243" s="8" t="s">
@@ -4663,7 +4687,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="8"/>
       <c r="B244" s="8"/>
       <c r="C244" s="8" t="s">
@@ -4675,7 +4699,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="8"/>
       <c r="B245" s="8"/>
       <c r="C245" s="8" t="s">
@@ -4687,7 +4711,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="8"/>
       <c r="B246" s="8"/>
       <c r="C246" s="8" t="s">
@@ -4699,7 +4723,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="8"/>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4712,7 +4736,7 @@
       </c>
       <c r="F247" s="8"/>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E248">
         <f>SUM(E240:E246)</f>
         <v>0</v>
@@ -4722,7 +4746,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="7" t="s">
         <v>66</v>
       </c>
@@ -4736,7 +4760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="7"/>
       <c r="B250" s="8" t="s">
         <v>42</v>
@@ -4748,7 +4772,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="7"/>
       <c r="B251" s="8" t="s">
         <v>217</v>
@@ -4760,7 +4784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="7"/>
       <c r="B252" s="8" t="s">
         <v>140</v>
@@ -4772,7 +4796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="7"/>
       <c r="B253" s="8" t="s">
         <v>65</v>
@@ -4784,7 +4808,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="7"/>
       <c r="B254" s="8" t="s">
         <v>67</v>
@@ -4796,7 +4820,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="7"/>
       <c r="B255" s="7" t="s">
         <v>49</v>
@@ -4810,7 +4834,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="7"/>
       <c r="B256" s="7"/>
       <c r="C256" s="8" t="s">
@@ -4822,7 +4846,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="7"/>
       <c r="B257" s="7"/>
       <c r="C257" s="8" t="s">
@@ -4834,7 +4858,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="7"/>
       <c r="B258" s="7"/>
       <c r="C258" s="8" t="s">
@@ -4846,7 +4870,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="7"/>
       <c r="B259" s="7"/>
       <c r="C259" s="8" t="s">
@@ -4858,7 +4882,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="7"/>
       <c r="B260" s="7"/>
       <c r="C260" s="8" t="s">
@@ -4872,7 +4896,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="7"/>
       <c r="B261" s="7"/>
       <c r="C261" s="8"/>
@@ -4884,7 +4908,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="7"/>
       <c r="B262" s="7"/>
       <c r="C262" s="8"/>
@@ -4896,7 +4920,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="7"/>
       <c r="B263" s="7"/>
       <c r="C263" s="8"/>
@@ -4908,7 +4932,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="7"/>
       <c r="B264" s="7"/>
       <c r="C264" s="8"/>
@@ -4920,7 +4944,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="7"/>
       <c r="B265" s="7"/>
       <c r="C265" s="8"/>
@@ -4933,7 +4957,7 @@
       </c>
       <c r="F265" s="8"/>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E266">
         <f>SUM(E249:E265)</f>
         <v>0</v>
@@ -4943,7 +4967,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="7" t="s">
         <v>267</v>
       </c>
@@ -4957,7 +4981,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="7" t="s">
         <v>269</v>
       </c>
@@ -4971,7 +4995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="7"/>
       <c r="B270" s="8" t="s">
         <v>318</v>
@@ -4983,7 +5007,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="8"/>
       <c r="B271" s="8" t="s">
         <v>316</v>
@@ -4995,7 +5019,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="8"/>
       <c r="B272" s="8" t="s">
         <v>317</v>
@@ -5007,7 +5031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="8"/>
       <c r="B273" s="8"/>
       <c r="C273" s="8"/>
@@ -5020,7 +5044,7 @@
       </c>
       <c r="F273" s="8"/>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E274">
         <f>SUM(E268:E272)</f>
         <v>0</v>
@@ -5030,7 +5054,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="9" t="s">
         <v>34</v>
       </c>
@@ -5044,7 +5068,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="10"/>
       <c r="B276" s="10" t="s">
         <v>221</v>
@@ -5056,7 +5080,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="9"/>
       <c r="B277" s="10" t="s">
         <v>285</v>
@@ -5070,7 +5094,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="10"/>
       <c r="B278" s="10" t="s">
         <v>278</v>
@@ -5084,7 +5108,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="9"/>
       <c r="B279" s="10" t="s">
         <v>200</v>
@@ -5098,7 +5122,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="9"/>
       <c r="B280" s="10" t="s">
         <v>286</v>
@@ -5112,7 +5136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="9"/>
       <c r="B281" s="10" t="s">
         <v>287</v>
@@ -5124,7 +5148,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="10"/>
       <c r="B282" s="10" t="s">
         <v>279</v>
@@ -5136,7 +5160,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="10"/>
       <c r="B283" s="10" t="s">
         <v>280</v>
@@ -5148,7 +5172,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="10"/>
       <c r="B284" s="10" t="s">
         <v>36</v>
@@ -5160,7 +5184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="10"/>
       <c r="B285" s="10"/>
       <c r="C285" s="10"/>
@@ -5173,7 +5197,7 @@
       </c>
       <c r="F285" s="10"/>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E286">
         <f>SUM(E275:E284)</f>
         <v>0</v>
@@ -5183,12 +5207,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="289" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A289" s="5" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="12" t="s">
         <v>191</v>
       </c>
@@ -5202,7 +5226,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="14"/>
       <c r="B291" s="14"/>
       <c r="C291" s="12" t="s">
@@ -5214,7 +5238,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="14"/>
       <c r="B292" s="14"/>
       <c r="C292" s="12" t="s">
@@ -5226,7 +5250,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="14"/>
       <c r="B293" s="14"/>
       <c r="C293" s="12" t="s">
@@ -5238,7 +5262,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="14"/>
       <c r="B294" s="14"/>
       <c r="C294" s="12" t="s">
@@ -5250,7 +5274,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="12"/>
       <c r="B295" s="12" t="s">
         <v>192</v>
@@ -5264,7 +5288,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="12"/>
       <c r="B296" s="12"/>
       <c r="C296" s="12" t="s">
@@ -5276,7 +5300,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="12"/>
       <c r="B297" s="12"/>
       <c r="C297" s="12" t="s">
@@ -5288,7 +5312,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="12"/>
       <c r="B298" s="12" t="s">
         <v>194</v>
@@ -5302,7 +5326,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="12"/>
       <c r="B299" s="12"/>
       <c r="C299" s="12" t="s">
@@ -5314,7 +5338,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="12"/>
       <c r="B300" s="12"/>
       <c r="C300" s="12" t="s">
@@ -5326,7 +5350,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="14" t="s">
         <v>49</v>
       </c>
@@ -5340,7 +5364,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="14"/>
       <c r="B302" s="14"/>
       <c r="C302" s="12" t="s">
@@ -5352,7 +5376,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="14"/>
       <c r="B303" s="14"/>
       <c r="C303" s="12" t="s">
@@ -5364,7 +5388,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="14"/>
       <c r="B304" s="14"/>
       <c r="C304" s="12" t="s">
@@ -5376,7 +5400,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A305" s="14"/>
       <c r="B305" s="14"/>
       <c r="C305" s="12" t="s">
@@ -5388,7 +5412,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A306" s="14"/>
       <c r="B306" s="14"/>
       <c r="C306" s="12" t="s">
@@ -5402,7 +5426,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A307" s="14"/>
       <c r="B307" s="14"/>
       <c r="C307" s="12"/>
@@ -5414,7 +5438,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A308" s="14"/>
       <c r="B308" s="14"/>
       <c r="C308" s="12"/>
@@ -5426,7 +5450,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A309" s="14"/>
       <c r="B309" s="14"/>
       <c r="C309" s="12"/>
@@ -5438,7 +5462,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A310" s="14"/>
       <c r="B310" s="14"/>
       <c r="C310" s="12"/>
@@ -5450,7 +5474,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A311" s="12"/>
       <c r="B311" s="12"/>
       <c r="C311" s="12"/>
@@ -5463,7 +5487,7 @@
       </c>
       <c r="F311" s="12"/>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="E312">
         <f>SUM(E290:E311)</f>
         <v>0</v>
@@ -5475,7 +5499,7 @@
       <c r="K312" s="17"/>
       <c r="L312" s="17"/>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A313" s="9" t="s">
         <v>355</v>
       </c>
@@ -5491,7 +5515,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A314" s="10" t="s">
         <v>302</v>
       </c>
@@ -5505,7 +5529,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A315" s="9"/>
       <c r="B315" s="10"/>
       <c r="C315" s="10" t="s">
@@ -5517,7 +5541,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A316" s="10"/>
       <c r="B316" s="10"/>
       <c r="C316" s="10" t="s">
@@ -5531,7 +5555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A317" s="10"/>
       <c r="B317" s="10"/>
       <c r="C317" s="10" t="s">
@@ -5545,7 +5569,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A318" s="9"/>
       <c r="B318" s="10"/>
       <c r="C318" s="10" t="s">
@@ -5559,7 +5583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A319" s="9"/>
       <c r="B319" s="10"/>
       <c r="C319" s="10" t="s">
@@ -5573,7 +5597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A320" s="10"/>
       <c r="B320" s="10"/>
       <c r="C320" s="10"/>
@@ -5585,7 +5609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="E321">
         <f>SUM(E313:E320)</f>
         <v>0</v>
@@ -5597,15 +5621,15 @@
       <c r="K321" s="17"/>
       <c r="L321" s="17"/>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="K322" s="17"/>
       <c r="L322" s="17"/>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="K323" s="17"/>
       <c r="L323" s="17"/>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A324" s="13" t="s">
         <v>271</v>
       </c>
@@ -5619,7 +5643,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A325" s="11"/>
       <c r="B325" s="11" t="s">
         <v>273</v>
@@ -5631,7 +5655,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A326" s="11"/>
       <c r="B326" s="11" t="s">
         <v>110</v>
@@ -5643,7 +5667,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A327" s="13" t="s">
         <v>274</v>
       </c>
@@ -5657,7 +5681,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A328" s="11"/>
       <c r="B328" s="11" t="s">
         <v>276</v>
@@ -5669,7 +5693,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A329" s="13" t="s">
         <v>319</v>
       </c>
@@ -5683,7 +5707,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A330" s="11"/>
       <c r="B330" s="11"/>
       <c r="C330" s="11" t="s">
@@ -5695,7 +5719,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A331" s="11"/>
       <c r="B331" s="11"/>
       <c r="C331" s="11" t="s">
@@ -5707,7 +5731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A332" s="11"/>
       <c r="B332" s="11"/>
       <c r="C332" s="11"/>
@@ -5720,7 +5744,7 @@
       </c>
       <c r="F332" s="11"/>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E333">
         <f>SUM(E324:E328)</f>
         <v>0</v>
@@ -5730,14 +5754,14 @@
         <v>60</v>
       </c>
     </row>
-    <row r="335" spans="1:12" s="17" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:12" s="17" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A335" s="5" t="s">
         <v>251</v>
       </c>
       <c r="K335"/>
       <c r="L335"/>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A336" s="11" t="s">
         <v>153</v>
       </c>
@@ -5755,7 +5779,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="11"/>
       <c r="B337" s="11"/>
       <c r="C337" s="11" t="s">
@@ -5769,7 +5793,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="11"/>
       <c r="B338" s="11"/>
       <c r="C338" s="11" t="s">
@@ -5783,7 +5807,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="11"/>
       <c r="B339" s="11"/>
       <c r="C339" s="11" t="s">
@@ -5797,7 +5821,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="11"/>
       <c r="B340" s="11"/>
       <c r="C340" s="11" t="s">
@@ -5811,7 +5835,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="11"/>
       <c r="B341" s="11"/>
       <c r="C341" s="11" t="s">
@@ -5825,7 +5849,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="11"/>
       <c r="B342" s="11"/>
       <c r="C342" s="11"/>
@@ -5837,7 +5861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E343">
         <f>SUM(E336:E342)</f>
         <v>0</v>
@@ -5847,7 +5871,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="13" t="s">
         <v>40</v>
       </c>
@@ -5861,7 +5885,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="13"/>
       <c r="B345" s="13"/>
       <c r="C345" s="15" t="s">
@@ -5873,7 +5897,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="13"/>
       <c r="B346" s="13"/>
       <c r="C346" s="15" t="s">
@@ -5885,7 +5909,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="13"/>
       <c r="B347" s="13"/>
       <c r="C347" s="11"/>
@@ -5893,7 +5917,7 @@
       <c r="E347" s="11"/>
       <c r="F347" s="11"/>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="13" t="s">
         <v>103</v>
       </c>
@@ -5907,7 +5931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="13"/>
       <c r="B349" s="13"/>
       <c r="C349" s="11" t="s">
@@ -5919,7 +5943,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="13"/>
       <c r="B350" s="13"/>
       <c r="C350" s="11" t="s">
@@ -5931,7 +5955,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="13"/>
       <c r="B351" s="13"/>
       <c r="C351" s="11"/>
@@ -5939,7 +5963,7 @@
       <c r="E351" s="11"/>
       <c r="F351" s="11"/>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="13" t="s">
         <v>199</v>
       </c>
@@ -5953,7 +5977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A353" s="13"/>
       <c r="B353" s="13"/>
       <c r="C353" s="11" t="s">
@@ -5965,7 +5989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A354" s="13"/>
       <c r="B354" s="13"/>
       <c r="C354" s="11" t="s">
@@ -5977,7 +6001,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A355" s="13"/>
       <c r="B355" s="13"/>
       <c r="C355" s="11"/>
@@ -5990,7 +6014,7 @@
       </c>
       <c r="F355" s="11"/>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="E356">
@@ -6003,7 +6027,7 @@
       </c>
       <c r="M356" s="19"/>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A357" s="14" t="s">
         <v>41</v>
       </c>
@@ -6018,7 +6042,7 @@
       </c>
       <c r="M357" s="19"/>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A358" s="14"/>
       <c r="B358" s="14"/>
       <c r="C358" s="12" t="s">
@@ -6031,7 +6055,7 @@
       </c>
       <c r="M358" s="19"/>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A359" s="14"/>
       <c r="B359" s="14"/>
       <c r="C359" s="12"/>
@@ -6045,7 +6069,7 @@
       <c r="F359" s="12"/>
       <c r="M359" s="19"/>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="E360">
@@ -6057,7 +6081,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>5</v>
       </c>
@@ -6073,7 +6097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>314</v>
       </c>
@@ -6087,7 +6111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="10"/>
       <c r="C364" s="10" t="s">
@@ -6099,7 +6123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="10"/>
       <c r="C365" s="10" t="s">
@@ -6111,7 +6135,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="10"/>
       <c r="C366" s="10" t="s">
@@ -6123,7 +6147,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="10"/>
       <c r="C367" s="10" t="s">
@@ -6135,7 +6159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="10"/>
       <c r="C368" s="10" t="s">
@@ -6147,7 +6171,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="10"/>
       <c r="C369" s="10" t="s">
@@ -6159,7 +6183,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="10"/>
       <c r="C370" s="10"/>
@@ -6172,7 +6196,7 @@
       </c>
       <c r="F370" s="10"/>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="E371">
@@ -6184,7 +6208,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="13" t="s">
         <v>54</v>
@@ -6198,7 +6222,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="11"/>
       <c r="C373" s="11" t="s">
@@ -6210,7 +6234,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="11"/>
       <c r="C374" s="11" t="s">
@@ -6222,7 +6246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="11"/>
       <c r="C375" s="11" t="s">
@@ -6234,7 +6258,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="11"/>
       <c r="C376" s="11" t="s">
@@ -6246,7 +6270,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="11"/>
       <c r="C377" s="11" t="s">
@@ -6258,7 +6282,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="11"/>
       <c r="C378" s="11" t="s">
@@ -6270,7 +6294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="11"/>
       <c r="C379" s="11" t="s">
@@ -6282,7 +6306,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="11"/>
       <c r="C380" s="11"/>
@@ -6295,7 +6319,7 @@
       </c>
       <c r="F380" s="11"/>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="E381">
@@ -6307,7 +6331,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="14" t="s">
         <v>54</v>
@@ -6321,7 +6345,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="12"/>
       <c r="C383" s="12" t="s">
@@ -6333,7 +6357,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="12"/>
       <c r="C384" s="12" t="s">
@@ -6345,7 +6369,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="12"/>
       <c r="C385" s="12" t="str">
@@ -6358,7 +6382,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="12"/>
       <c r="C386" s="12" t="str">
@@ -6371,7 +6395,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="12"/>
       <c r="C387" s="12" t="str">
@@ -6384,7 +6408,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="12"/>
       <c r="C388" s="12" t="str">
@@ -6397,7 +6421,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="12"/>
       <c r="C389" s="12" t="s">
@@ -6409,7 +6433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="12"/>
       <c r="C390" s="12"/>
@@ -6422,7 +6446,7 @@
       </c>
       <c r="F390" s="12"/>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="E391">
@@ -6434,12 +6458,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="393" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A393" s="5" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" s="7" t="s">
         <v>309</v>
       </c>
@@ -6449,7 +6473,7 @@
       <c r="E394" s="8"/>
       <c r="F394" s="8"/>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" s="7"/>
       <c r="B395" s="8"/>
       <c r="C395" s="8"/>
@@ -6457,7 +6481,7 @@
       <c r="E395" s="8"/>
       <c r="F395" s="8"/>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" s="7"/>
       <c r="B396" s="8" t="s">
         <v>157</v>
@@ -6467,7 +6491,7 @@
       <c r="E396" s="8"/>
       <c r="F396" s="8"/>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" s="7"/>
       <c r="B397" s="8" t="s">
         <v>158</v>
@@ -6479,7 +6503,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" s="7"/>
       <c r="B398" s="8" t="s">
         <v>159</v>
@@ -6491,7 +6515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A399" s="7"/>
       <c r="B399" s="8" t="s">
         <v>160</v>
@@ -6505,7 +6529,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A400" s="7"/>
       <c r="B400" s="8"/>
       <c r="C400" s="8" t="s">
@@ -6517,7 +6541,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" s="7"/>
       <c r="B401" s="8" t="s">
         <v>162</v>
@@ -6531,7 +6555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" s="7"/>
       <c r="B402" s="8"/>
       <c r="C402" s="8" t="s">
@@ -6543,7 +6567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" s="7"/>
       <c r="B403" s="8"/>
       <c r="C403" s="8" t="s">
@@ -6555,7 +6579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" s="7"/>
       <c r="B404" s="8"/>
       <c r="C404" s="8" t="s">
@@ -6567,7 +6591,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" s="7"/>
       <c r="B405" s="8"/>
       <c r="C405" s="8" t="s">
@@ -6579,7 +6603,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" s="7"/>
       <c r="B406" s="8"/>
       <c r="C406" s="8"/>
@@ -6592,7 +6616,7 @@
       </c>
       <c r="F406" s="8"/>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A407" s="1"/>
       <c r="E407">
         <f>SUM(E394:E406)</f>
@@ -6603,10 +6627,10 @@
         <v>65</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" s="1"/>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" s="9" t="s">
         <v>90</v>
       </c>
@@ -6620,7 +6644,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" s="10"/>
       <c r="B410" s="10" t="s">
         <v>92</v>
@@ -6632,7 +6656,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" s="10"/>
       <c r="B411" s="10" t="s">
         <v>93</v>
@@ -6644,7 +6668,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" s="10"/>
       <c r="B412" s="10" t="s">
         <v>94</v>
@@ -6656,7 +6680,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" s="9" t="s">
         <v>102</v>
       </c>
@@ -6666,7 +6690,7 @@
       <c r="E413" s="10"/>
       <c r="F413" s="10"/>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" s="9"/>
       <c r="B414" s="10" t="s">
         <v>118</v>
@@ -6678,7 +6702,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" s="10"/>
       <c r="B415" s="10" t="s">
         <v>119</v>
@@ -6692,7 +6716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A416" s="10"/>
       <c r="B416" s="10" t="s">
         <v>120</v>
@@ -6706,7 +6730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" s="10"/>
       <c r="B417" s="10" t="s">
         <v>121</v>
@@ -6718,7 +6742,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A418" s="10"/>
       <c r="B418" s="10"/>
       <c r="C418" s="10"/>
@@ -6726,7 +6750,7 @@
       <c r="E418" s="10"/>
       <c r="F418" s="10"/>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" s="10"/>
       <c r="B419" s="10"/>
       <c r="C419" s="10"/>
@@ -6739,7 +6763,7 @@
       </c>
       <c r="F419" s="10"/>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E420">
         <f>SUM(E409:E419)</f>
         <v>0</v>
@@ -6749,12 +6773,12 @@
         <v>550</v>
       </c>
     </row>
-    <row r="421" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A421" s="5" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" s="7" t="s">
         <v>36</v>
       </c>
@@ -6770,7 +6794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" s="7"/>
       <c r="B423" s="8"/>
       <c r="C423" s="8" t="s">
@@ -6782,7 +6806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" s="7"/>
       <c r="B424" s="8"/>
       <c r="C424" s="8" t="s">
@@ -6794,7 +6818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" s="7"/>
       <c r="B425" s="8"/>
       <c r="C425" s="8" t="s">
@@ -6806,7 +6830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" s="7"/>
       <c r="B426" s="8"/>
       <c r="C426" s="8" t="s">
@@ -6818,7 +6842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A427" s="8"/>
       <c r="B427" s="8" t="s">
         <v>12</v>
@@ -6830,7 +6854,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" s="8"/>
       <c r="B428" s="8" t="s">
         <v>39</v>
@@ -6842,7 +6866,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" s="8"/>
       <c r="B429" s="8" t="s">
         <v>68</v>
@@ -6854,7 +6878,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A430" s="8"/>
       <c r="B430" s="8" t="s">
         <v>85</v>
@@ -6866,7 +6890,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A431" s="8"/>
       <c r="B431" s="8"/>
       <c r="C431" s="8"/>
@@ -6879,7 +6903,7 @@
       </c>
       <c r="F431" s="8"/>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E432">
         <f>SUM(E422:E431)</f>
         <v>0</v>
@@ -6889,7 +6913,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" s="8" t="s">
         <v>122</v>
       </c>
@@ -6903,7 +6927,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" s="8"/>
       <c r="B434" s="8" t="s">
         <v>124</v>
@@ -6915,7 +6939,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" s="8"/>
       <c r="B435" s="8" t="s">
         <v>125</v>
@@ -6927,7 +6951,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" s="8"/>
       <c r="B436" s="8" t="s">
         <v>126</v>
@@ -6939,7 +6963,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" s="8"/>
       <c r="B437" s="8" t="s">
         <v>127</v>
@@ -6951,7 +6975,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A438" s="8"/>
       <c r="B438" s="8" t="s">
         <v>228</v>
@@ -6963,7 +6987,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A439" s="8"/>
       <c r="B439" s="8" t="s">
         <v>128</v>
@@ -6975,7 +6999,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A440" s="8"/>
       <c r="B440" s="8" t="s">
         <v>229</v>
@@ -6987,7 +7011,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A441" s="8"/>
       <c r="B441" s="8" t="s">
         <v>129</v>
@@ -6999,7 +7023,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A442" s="8"/>
       <c r="B442" s="8"/>
       <c r="C442" s="8"/>
@@ -7012,7 +7036,7 @@
       </c>
       <c r="F442" s="8"/>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E443">
         <f>SUM(E433:E442)</f>
         <v>0</v>
@@ -7022,7 +7046,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A444" s="8" t="s">
         <v>130</v>
       </c>
@@ -7036,7 +7060,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A445" s="8"/>
       <c r="B445" s="8" t="s">
         <v>132</v>
@@ -7048,7 +7072,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A446" s="8"/>
       <c r="B446" s="8" t="s">
         <v>7</v>
@@ -7060,7 +7084,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A447" s="8"/>
       <c r="B447" s="8" t="s">
         <v>133</v>
@@ -7072,7 +7096,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A448" s="8"/>
       <c r="B448" s="8" t="s">
         <v>134</v>
@@ -7084,7 +7108,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A449" s="8"/>
       <c r="B449" s="8" t="s">
         <v>135</v>
@@ -7096,7 +7120,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A450" s="8"/>
       <c r="B450" s="8" t="s">
         <v>136</v>
@@ -7108,7 +7132,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A451" s="8"/>
       <c r="B451" s="8"/>
       <c r="C451" s="8"/>
@@ -7121,7 +7145,7 @@
       </c>
       <c r="F451" s="8"/>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E452">
         <f>SUM(E444:E451)</f>
         <v>0</v>
@@ -7131,7 +7155,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A453" s="7" t="s">
         <v>312</v>
       </c>
@@ -7147,7 +7171,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A454" s="7"/>
       <c r="B454" s="7"/>
       <c r="C454" s="8"/>
@@ -7159,7 +7183,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A455" s="7"/>
       <c r="B455" s="7"/>
       <c r="C455" s="8"/>
@@ -7171,7 +7195,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A456" s="7"/>
       <c r="B456" s="7"/>
       <c r="C456" s="8" t="s">
@@ -7185,7 +7209,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A457" s="7"/>
       <c r="B457" s="7"/>
       <c r="C457" s="8"/>
@@ -7197,7 +7221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A458" s="7"/>
       <c r="B458" s="7"/>
       <c r="C458" s="8"/>
@@ -7209,7 +7233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A459" s="7"/>
       <c r="B459" s="7"/>
       <c r="C459" s="8"/>
@@ -7221,7 +7245,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A460" s="7"/>
       <c r="B460" s="7"/>
       <c r="C460" s="8"/>
@@ -7233,7 +7257,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E461">
         <f>SUM(E453:E460)</f>
         <v>0</v>
@@ -7243,12 +7267,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="462" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A462" s="5" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A463" s="7" t="s">
         <v>235</v>
       </c>
@@ -7264,7 +7288,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A464" s="7"/>
       <c r="B464" s="8"/>
       <c r="C464" s="8" t="s">
@@ -7276,7 +7300,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A465" s="8"/>
       <c r="B465" s="7" t="s">
         <v>236</v>
@@ -7290,7 +7314,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A466" s="8"/>
       <c r="B466" s="8"/>
       <c r="C466" s="8" t="s">
@@ -7302,7 +7326,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A467" s="8"/>
       <c r="B467" s="8"/>
       <c r="C467" s="8" t="s">
@@ -7314,7 +7338,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A468" s="8"/>
       <c r="B468" s="8"/>
       <c r="C468" s="8" t="s">
@@ -7326,7 +7350,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A469" s="8"/>
       <c r="B469" s="8"/>
       <c r="C469" s="8" t="s">
@@ -7338,7 +7362,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A470" s="8"/>
       <c r="B470" s="8"/>
       <c r="C470" s="8"/>
@@ -7350,7 +7374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E471">
         <f>SUM(E463:E470)</f>
         <v>0</v>
@@ -7360,12 +7384,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A473" s="14" t="s">
         <v>330</v>
       </c>
@@ -7381,7 +7405,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A474" s="14" t="s">
         <v>332</v>
       </c>
@@ -7399,7 +7423,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A475" s="14"/>
       <c r="B475" s="12"/>
       <c r="C475" s="12" t="s">
@@ -7413,7 +7437,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A476" s="1"/>
       <c r="D476" s="20" t="s">
         <v>206</v>
@@ -7423,7 +7447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E477">
         <f>SUM(E473:E476)</f>
         <v>0</v>
@@ -7433,12 +7457,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="479" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A479" s="5" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A480" s="14" t="s">
         <v>235</v>
       </c>
@@ -7452,7 +7476,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" s="14" t="s">
         <v>240</v>
       </c>
@@ -7466,7 +7490,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A482" s="12"/>
       <c r="B482" s="12" t="s">
         <v>238</v>
@@ -7478,7 +7502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A483" s="12"/>
       <c r="B483" s="12" t="s">
         <v>237</v>
@@ -7490,7 +7514,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A484" s="12"/>
       <c r="B484" s="12" t="s">
         <v>239</v>
@@ -7502,7 +7526,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A485" s="12"/>
       <c r="B485" s="12" t="s">
         <v>241</v>
@@ -7514,7 +7538,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A486" s="12"/>
       <c r="B486" s="12" t="s">
         <v>242</v>
@@ -7526,7 +7550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A487" s="12"/>
       <c r="B487" s="12" t="s">
         <v>25</v>
@@ -7538,7 +7562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A488" s="12"/>
       <c r="B488" s="12" t="s">
         <v>26</v>
@@ -7550,7 +7574,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A489" s="12"/>
       <c r="B489" s="12" t="s">
         <v>243</v>
@@ -7562,7 +7586,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A490" s="12"/>
       <c r="B490" s="12" t="s">
         <v>244</v>
@@ -7574,7 +7598,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" s="12"/>
       <c r="B491" s="12"/>
       <c r="C491" s="12"/>
@@ -7586,7 +7610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E492">
         <f>SUM(E480:E491)</f>
         <v>0</v>
@@ -7596,7 +7620,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A494" s="9" t="s">
         <v>235</v>
       </c>
@@ -7611,7 +7635,7 @@
       </c>
       <c r="H494" s="18"/>
     </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A495" s="9" t="s">
         <v>240</v>
       </c>
@@ -7626,7 +7650,7 @@
       </c>
       <c r="H495" s="18"/>
     </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A496" s="10"/>
       <c r="B496" s="10" t="s">
         <v>238</v>
@@ -7639,7 +7663,7 @@
       </c>
       <c r="H496" s="18"/>
     </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A497" s="10"/>
       <c r="B497" s="10" t="s">
         <v>237</v>
@@ -7652,7 +7676,7 @@
       </c>
       <c r="H497" s="18"/>
     </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A498" s="10"/>
       <c r="B498" s="10" t="s">
         <v>239</v>
@@ -7664,7 +7688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A499" s="10"/>
       <c r="B499" s="10" t="s">
         <v>241</v>
@@ -7676,7 +7700,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A500" s="10"/>
       <c r="B500" s="10" t="s">
         <v>242</v>
@@ -7688,7 +7712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="501" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A501" s="10"/>
       <c r="B501" s="10" t="s">
         <v>25</v>
@@ -7700,7 +7724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A502" s="10"/>
       <c r="B502" s="10" t="s">
         <v>26</v>
@@ -7712,7 +7736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="503" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A503" s="10"/>
       <c r="B503" s="10" t="s">
         <v>243</v>
@@ -7724,7 +7748,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A504" s="10"/>
       <c r="B504" s="10" t="s">
         <v>244</v>
@@ -7736,7 +7760,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A505" s="10"/>
       <c r="B505" s="10"/>
       <c r="C505" s="10"/>
@@ -7748,7 +7772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E506">
         <f>SUM(E494:E505)</f>
         <v>0</v>
@@ -7758,7 +7782,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A508" s="13" t="s">
         <v>235</v>
       </c>
@@ -7767,12 +7791,14 @@
       </c>
       <c r="C508" s="11"/>
       <c r="D508" s="11"/>
-      <c r="E508" s="11"/>
+      <c r="E508" s="11">
+        <v>10</v>
+      </c>
       <c r="F508" s="11">
         <v>10</v>
       </c>
     </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A509" s="13" t="s">
         <v>240</v>
       </c>
@@ -7781,120 +7807,160 @@
       </c>
       <c r="C509" s="11"/>
       <c r="D509" s="11"/>
-      <c r="E509" s="11"/>
+      <c r="E509" s="11">
+        <v>2</v>
+      </c>
       <c r="F509" s="11">
         <v>5</v>
       </c>
-    </row>
-    <row r="510" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A510" s="11"/>
+      <c r="H509" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A510" s="11" t="s">
+        <v>380</v>
+      </c>
       <c r="B510" s="11" t="s">
         <v>238</v>
       </c>
       <c r="C510" s="11"/>
       <c r="D510" s="11"/>
-      <c r="E510" s="11"/>
+      <c r="E510" s="11">
+        <v>2</v>
+      </c>
       <c r="F510" s="11">
         <v>5</v>
       </c>
     </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A511" s="11"/>
       <c r="B511" s="11" t="s">
         <v>237</v>
       </c>
       <c r="C511" s="11"/>
       <c r="D511" s="11"/>
-      <c r="E511" s="11"/>
+      <c r="E511" s="11">
+        <v>3</v>
+      </c>
       <c r="F511" s="11">
         <v>5</v>
       </c>
-    </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H511" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A512" s="11"/>
       <c r="B512" s="11" t="s">
         <v>239</v>
       </c>
       <c r="C512" s="11"/>
       <c r="D512" s="11"/>
-      <c r="E512" s="11"/>
+      <c r="E512" s="11">
+        <v>4</v>
+      </c>
       <c r="F512" s="11">
         <v>5</v>
       </c>
     </row>
-    <row r="513" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A513" s="11"/>
       <c r="B513" s="11" t="s">
         <v>241</v>
       </c>
       <c r="C513" s="11"/>
       <c r="D513" s="11"/>
-      <c r="E513" s="11"/>
+      <c r="E513" s="11">
+        <v>4</v>
+      </c>
       <c r="F513" s="11">
         <v>5</v>
       </c>
-    </row>
-    <row r="514" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H513" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="514" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A514" s="11"/>
       <c r="B514" s="11" t="s">
         <v>242</v>
       </c>
       <c r="C514" s="11"/>
       <c r="D514" s="11"/>
-      <c r="E514" s="11"/>
+      <c r="E514" s="11">
+        <v>0</v>
+      </c>
       <c r="F514" s="11">
         <v>5</v>
       </c>
     </row>
-    <row r="515" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A515" s="11"/>
       <c r="B515" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C515" s="11"/>
       <c r="D515" s="11"/>
-      <c r="E515" s="11"/>
+      <c r="E515" s="11">
+        <v>1</v>
+      </c>
       <c r="F515" s="11">
         <v>5</v>
       </c>
-    </row>
-    <row r="516" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H515" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="516" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A516" s="11"/>
       <c r="B516" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C516" s="11"/>
       <c r="D516" s="11"/>
-      <c r="E516" s="11"/>
+      <c r="E516" s="11">
+        <v>1</v>
+      </c>
       <c r="F516" s="11">
         <v>5</v>
       </c>
-    </row>
-    <row r="517" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H516" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="517" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A517" s="11"/>
       <c r="B517" s="11" t="s">
         <v>243</v>
       </c>
       <c r="C517" s="11"/>
       <c r="D517" s="11"/>
-      <c r="E517" s="11"/>
+      <c r="E517" s="11">
+        <v>3</v>
+      </c>
       <c r="F517" s="11">
         <v>5</v>
       </c>
-    </row>
-    <row r="518" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H517" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="518" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A518" s="11"/>
       <c r="B518" s="11" t="s">
         <v>244</v>
       </c>
       <c r="C518" s="11"/>
       <c r="D518" s="11"/>
-      <c r="E518" s="11"/>
+      <c r="E518" s="11">
+        <v>5</v>
+      </c>
       <c r="F518" s="11">
         <v>5</v>
       </c>
     </row>
-    <row r="519" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A519" s="11"/>
       <c r="B519" s="11"/>
       <c r="C519" s="11"/>
@@ -7902,22 +7968,28 @@
         <v>206</v>
       </c>
       <c r="E519" s="20">
-        <f>-SUM(E512:E518)</f>
-        <v>0</v>
+        <f>-SUM(E508:E518)*0.3</f>
+        <v>-10.5</v>
       </c>
       <c r="F519" s="11"/>
-    </row>
-    <row r="520" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H519" t="s">
+        <v>385</v>
+      </c>
+      <c r="J519" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="520" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E520">
         <f>SUM(E508:E519)</f>
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="F520">
         <f>SUM(F508:F519)</f>
         <v>60</v>
       </c>
     </row>
-    <row r="524" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A524" s="7"/>
       <c r="B524" t="s">
         <v>183</v>
@@ -7935,7 +8007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A525" s="9" t="s">
         <v>364</v>
       </c>
@@ -7955,7 +8027,7 @@
         <v>-0.12820512820512819</v>
       </c>
     </row>
-    <row r="526" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A526" s="13" t="s">
         <v>365</v>
       </c>
@@ -7964,7 +8036,7 @@
       </c>
       <c r="E526">
         <f>E50+E28+E33+E87+E124+E159+E381+E186+E333+E343+E356+E520</f>
-        <v>-200</v>
+        <v>-175.5</v>
       </c>
       <c r="F526">
         <f>F50+F28+F33+F87+F124+F159+F381+F186+F219+F333+F343+F356+F520</f>
@@ -7972,10 +8044,10 @@
       </c>
       <c r="H526" s="18">
         <f>(E526+E524)/(F526+F524)</f>
-        <v>-0.1762114537444934</v>
-      </c>
-    </row>
-    <row r="527" spans="1:8" x14ac:dyDescent="0.3">
+        <v>-0.15462555066079295</v>
+      </c>
+    </row>
+    <row r="527" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A527" s="14" t="s">
         <v>363</v>
       </c>
@@ -7995,7 +8067,7 @@
         <v>-0.17699115044247787</v>
       </c>
     </row>
-    <row r="531" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="531" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F531" t="s">
         <v>230</v>
       </c>
@@ -8003,7 +8075,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="532" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="532" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D532" t="s">
         <v>232</v>
       </c>
@@ -8011,7 +8083,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="533" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="533" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F533" s="23">
         <v>0.45</v>
       </c>
@@ -8019,7 +8091,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="534" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="534" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F534" s="23">
         <f>F533+(F542-F533)/9</f>
         <v>0.5</v>
@@ -8028,7 +8100,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="535" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="535" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F535" s="23">
         <f>F534+(F542-F533)/9</f>
         <v>0.55000000000000004</v>
@@ -8037,7 +8109,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="536" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="536" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F536" s="23">
         <f>F535+(F542-F533)/9</f>
         <v>0.60000000000000009</v>
@@ -8046,7 +8118,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="537" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="537" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F537" s="23">
         <f>F536+(F542-F533)/9</f>
         <v>0.65000000000000013</v>
@@ -8055,7 +8127,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="538" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="538" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F538" s="23">
         <f>F537+(F542-F533)/9</f>
         <v>0.70000000000000018</v>
@@ -8064,7 +8136,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="539" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="539" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F539" s="23">
         <f>F538+(F542-F533)/9</f>
         <v>0.75000000000000022</v>
@@ -8073,7 +8145,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="540" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="540" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F540" s="23">
         <f>F539+(F542-F533)/9</f>
         <v>0.80000000000000027</v>
@@ -8082,7 +8154,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="541" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="541" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F541" s="23">
         <f>F540+(F542-F533)/9</f>
         <v>0.85000000000000031</v>
@@ -8091,7 +8163,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="542" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="542" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F542" s="23">
         <v>0.9</v>
       </c>
@@ -8099,7 +8171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="543" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="543" spans="4:7" x14ac:dyDescent="0.25">
       <c r="E543" t="s">
         <v>234</v>
       </c>
@@ -8126,14 +8198,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="19"/>
+    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.8" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="29" t="s">
         <v>223</v>
       </c>
@@ -8141,10 +8213,10 @@
       <c r="C1" s="29"/>
       <c r="D1" s="29"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>207</v>
       </c>
@@ -8152,7 +8224,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>38</v>
       </c>
@@ -8160,7 +8232,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>209</v>
       </c>
@@ -8168,7 +8240,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>210</v>
       </c>
@@ -8176,7 +8248,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>211</v>
       </c>
@@ -8184,7 +8256,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>212</v>
       </c>
@@ -8192,7 +8264,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>174</v>
       </c>
@@ -8200,7 +8272,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>208</v>
       </c>
@@ -8208,7 +8280,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>214</v>
       </c>
@@ -8216,7 +8288,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>213</v>
       </c>
@@ -8224,7 +8296,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>215</v>
       </c>
@@ -8232,7 +8304,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>216</v>
       </c>
@@ -8240,7 +8312,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>222</v>
       </c>
@@ -8248,7 +8320,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>224</v>
       </c>
@@ -8256,7 +8328,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>225</v>
       </c>
@@ -8264,7 +8336,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -8278,7 +8350,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
         <v>143</v>
       </c>
@@ -8286,7 +8358,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
         <v>144</v>
       </c>
@@ -8294,7 +8366,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>145</v>
       </c>
@@ -8305,7 +8377,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
         <v>147</v>
       </c>
@@ -8313,7 +8385,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>148</v>
       </c>
@@ -8321,7 +8393,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>149</v>
       </c>
@@ -8329,12 +8401,12 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>162</v>
       </c>
@@ -8345,7 +8417,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
         <v>166</v>
       </c>
@@ -8353,7 +8425,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
         <v>148</v>
       </c>
@@ -8361,7 +8433,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>220</v>
       </c>
@@ -8369,7 +8441,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>167</v>
       </c>
@@ -8380,7 +8452,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
         <v>169</v>
       </c>
@@ -8388,7 +8460,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
         <v>170</v>
       </c>

--- a/ProjectManagement/EvaluationHW.xlsx
+++ b/ProjectManagement/EvaluationHW.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Wings_Hub\Wings-Hub\ML2425\ML24-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Wings-Hub\ML24\ML24-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4B475B-C655-4B92-8C52-913CE8828D79}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="2" r:id="rId1"/>
     <sheet name="Formalities" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,12 +25,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Elmar Wings</author>
   </authors>
   <commentList>
-    <comment ref="K359" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="K359" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -68,12 +67,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Elmar Wings</author>
   </authors>
   <commentList>
-    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="B14" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -100,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="B15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -128,7 +127,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
+    <comment ref="B34" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -165,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="391">
   <si>
     <t>Literature</t>
   </si>
@@ -1326,16 +1325,28 @@
   </si>
   <si>
     <t>no code files, no doxygen</t>
+  </si>
+  <si>
+    <t>Clustering</t>
+  </si>
+  <si>
+    <t>Visualizing K-Means Clustering</t>
+  </si>
+  <si>
+    <t>not a summary, new examples</t>
+  </si>
+  <si>
+    <t>no summary</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1453,6 +1464,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1516,10 +1535,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1568,8 +1588,10 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1847,42 +1869,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:M543"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.73046875" customWidth="1"/>
+    <col min="2" max="2" width="28.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="33.75" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:6" ht="33.4" x14ac:dyDescent="1">
       <c r="A2" s="22" t="s">
         <v>367</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="25" t="s">
         <v>372</v>
       </c>
       <c r="B6" s="25"/>
       <c r="C6" s="25"/>
     </row>
-    <row r="9" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" ht="28.5" x14ac:dyDescent="0.85">
       <c r="A9" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>71</v>
       </c>
@@ -1899,7 +1921,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>369</v>
       </c>
@@ -1916,7 +1938,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>373</v>
       </c>
@@ -1930,7 +1952,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>375</v>
       </c>
@@ -1944,7 +1966,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>75</v>
       </c>
@@ -1952,7 +1974,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>76</v>
       </c>
@@ -1960,7 +1982,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>77</v>
       </c>
@@ -1968,7 +1990,7 @@
         <v>45565</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>78</v>
       </c>
@@ -1976,7 +1998,7 @@
         <v>45688</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>79</v>
       </c>
@@ -1984,7 +2006,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>80</v>
       </c>
@@ -1992,12 +2014,12 @@
         <v>189</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
       <c r="A25" s="6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="5" t="s">
         <v>82</v>
       </c>
@@ -2005,7 +2027,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" s="11"/>
       <c r="B28" s="11" t="s">
         <v>138</v>
@@ -2022,7 +2044,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" s="12"/>
       <c r="B29" s="12" t="s">
         <v>138</v>
@@ -2039,7 +2061,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
         <v>138</v>
@@ -2056,7 +2078,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" s="10"/>
       <c r="B31" s="10" t="s">
         <v>139</v>
@@ -2073,7 +2095,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" s="12"/>
       <c r="B32" s="12" t="s">
         <v>139</v>
@@ -2090,7 +2112,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" s="11"/>
       <c r="B33" s="11" t="s">
         <v>139</v>
@@ -2107,12 +2129,12 @@
         <v>336</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="5" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" s="13" t="s">
         <v>0</v>
       </c>
@@ -2126,7 +2148,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" s="13"/>
       <c r="B37" s="11" t="s">
         <v>27</v>
@@ -2138,7 +2160,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" s="11"/>
       <c r="B38" s="11" t="s">
         <v>3</v>
@@ -2150,7 +2172,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" s="11"/>
       <c r="B39" s="11" t="s">
         <v>4</v>
@@ -2162,7 +2184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" s="11"/>
       <c r="B40" s="11" t="s">
         <v>5</v>
@@ -2174,7 +2196,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" s="11"/>
       <c r="B41" s="11" t="s">
         <v>337</v>
@@ -2186,7 +2208,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" s="13"/>
       <c r="B42" s="11" t="s">
         <v>1</v>
@@ -2200,7 +2222,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" s="13"/>
       <c r="B43" s="11"/>
       <c r="C43" s="11" t="s">
@@ -2212,7 +2234,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" s="11"/>
       <c r="B44" s="11"/>
       <c r="C44" s="11" t="s">
@@ -2224,7 +2246,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" s="11"/>
       <c r="B45" s="11"/>
       <c r="C45" s="11" t="s">
@@ -2236,7 +2258,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46" s="11"/>
       <c r="B46" s="11"/>
       <c r="C46" s="11" t="s">
@@ -2248,7 +2270,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A47" s="11"/>
       <c r="B47" s="11"/>
       <c r="C47" s="11" t="s">
@@ -2260,7 +2282,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A48" s="11"/>
       <c r="B48" s="11"/>
       <c r="C48" s="11" t="s">
@@ -2272,7 +2294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A49" s="11"/>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
@@ -2285,7 +2307,7 @@
       </c>
       <c r="F49" s="11"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A50" s="11"/>
       <c r="E50">
         <f>SUM(E36:E49)</f>
@@ -2296,14 +2318,14 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:12" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="5" t="s">
         <v>339</v>
       </c>
       <c r="K52"/>
       <c r="L52"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A53" s="14" t="s">
         <v>111</v>
       </c>
@@ -2322,7 +2344,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A54" s="14"/>
       <c r="B54" s="14" t="s">
         <v>236</v>
@@ -2337,7 +2359,7 @@
       </c>
       <c r="G54" s="26"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A55" s="14"/>
       <c r="B55" s="14"/>
       <c r="C55" s="12" t="s">
@@ -2350,7 +2372,7 @@
       </c>
       <c r="G55" s="26"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A56" s="14"/>
       <c r="B56" s="12"/>
       <c r="C56" s="12" t="s">
@@ -2363,7 +2385,7 @@
       </c>
       <c r="G56" s="26"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A57" s="14"/>
       <c r="B57" s="14"/>
       <c r="C57" s="12" t="s">
@@ -2376,7 +2398,7 @@
       </c>
       <c r="G57" s="26"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A58" s="14"/>
       <c r="B58" s="14"/>
       <c r="C58" s="12" t="s">
@@ -2389,7 +2411,7 @@
       </c>
       <c r="G58" s="26"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A59" s="14"/>
       <c r="B59" s="14"/>
       <c r="C59" s="12" t="s">
@@ -2402,7 +2424,7 @@
       </c>
       <c r="G59" s="26"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A60" s="14"/>
       <c r="B60" s="14"/>
       <c r="C60" s="12" t="s">
@@ -2415,7 +2437,7 @@
       </c>
       <c r="G60" s="26"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A61" s="14"/>
       <c r="B61" s="14"/>
       <c r="C61" s="12" t="s">
@@ -2428,7 +2450,7 @@
       </c>
       <c r="G61" s="26"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A62" s="14"/>
       <c r="B62" s="14"/>
       <c r="C62" s="12" t="s">
@@ -2441,7 +2463,7 @@
       </c>
       <c r="G62" s="26"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A63" s="14"/>
       <c r="B63" s="14" t="s">
         <v>223</v>
@@ -2456,7 +2478,7 @@
       </c>
       <c r="G63" s="26"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A64" s="14"/>
       <c r="B64" s="14"/>
       <c r="C64" s="12" t="s">
@@ -2469,7 +2491,7 @@
       </c>
       <c r="G64" s="26"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A65" s="14"/>
       <c r="B65" s="14"/>
       <c r="C65" s="12" t="s">
@@ -2482,7 +2504,7 @@
       </c>
       <c r="G65" s="26"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A66" s="14"/>
       <c r="B66" s="14"/>
       <c r="C66" s="12"/>
@@ -2496,7 +2518,7 @@
       <c r="F66" s="12"/>
       <c r="G66" s="26"/>
     </row>
-    <row r="67" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="E67">
@@ -2510,14 +2532,14 @@
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
     </row>
-    <row r="68" spans="1:13" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="5" t="s">
         <v>340</v>
       </c>
       <c r="K68"/>
       <c r="L68"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A69" s="9" t="str">
         <f>$A$68</f>
         <v>Document Manufacturing and Assembly</v>
@@ -2534,7 +2556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A70" s="9"/>
       <c r="B70" s="9" t="s">
         <v>236</v>
@@ -2548,7 +2570,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A71" s="9"/>
       <c r="B71" s="9"/>
       <c r="C71" s="10" t="s">
@@ -2560,7 +2582,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A72" s="9"/>
       <c r="B72" s="9"/>
       <c r="C72" s="10" t="s">
@@ -2572,7 +2594,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A73" s="9"/>
       <c r="B73" s="9"/>
       <c r="C73" s="10" t="s">
@@ -2584,7 +2606,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A74" s="9"/>
       <c r="B74" s="9"/>
       <c r="C74" s="10" t="s">
@@ -2596,7 +2618,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A75" s="9"/>
       <c r="B75" s="9"/>
       <c r="C75" s="10"/>
@@ -2609,7 +2631,7 @@
       </c>
       <c r="F75" s="10"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="E76">
@@ -2621,15 +2643,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A77" s="1"/>
     </row>
-    <row r="78" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="5" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A79" s="13" t="s">
         <v>283</v>
       </c>
@@ -2645,7 +2667,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A80" s="13"/>
       <c r="B80" s="11"/>
       <c r="C80" s="11" t="s">
@@ -2657,7 +2679,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A81" s="13"/>
       <c r="B81" s="11"/>
       <c r="C81" s="11" t="s">
@@ -2669,7 +2691,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A82" s="13"/>
       <c r="B82" s="13" t="s">
         <v>236</v>
@@ -2683,7 +2705,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A83" s="13"/>
       <c r="B83" s="13"/>
       <c r="C83" s="11" t="s">
@@ -2695,7 +2717,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A84" s="13"/>
       <c r="B84" s="13"/>
       <c r="C84" s="11" t="s">
@@ -2707,7 +2729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A85" s="13"/>
       <c r="B85" s="13"/>
       <c r="C85" s="11" t="s">
@@ -2719,7 +2741,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A86" s="13"/>
       <c r="B86" s="13"/>
       <c r="C86" s="13"/>
@@ -2732,7 +2754,7 @@
       </c>
       <c r="F86" s="13"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="E87">
@@ -2744,18 +2766,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="89" spans="1:6" ht="21" x14ac:dyDescent="0.65">
       <c r="A89" s="21" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A91" s="14" t="s">
         <v>6</v>
       </c>
@@ -2769,7 +2791,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A92" s="12"/>
       <c r="B92" s="12"/>
       <c r="C92" s="12" t="s">
@@ -2781,7 +2803,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A93" s="12"/>
       <c r="B93" s="12"/>
       <c r="C93" s="12" t="s">
@@ -2793,7 +2815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A94" s="12"/>
       <c r="B94" s="12"/>
       <c r="C94" s="12" t="s">
@@ -2805,7 +2827,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A95" s="12"/>
       <c r="B95" s="12"/>
       <c r="C95" s="12" t="s">
@@ -2817,7 +2839,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A96" s="12"/>
       <c r="B96" s="12"/>
       <c r="C96" s="12" t="s">
@@ -2829,7 +2851,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A97" s="12"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
@@ -2842,7 +2864,7 @@
       </c>
       <c r="F97" s="12"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E98">
         <f>SUM(E91:E97)</f>
         <v>0</v>
@@ -2852,12 +2874,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="5" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A100" s="9" t="s">
         <v>273</v>
       </c>
@@ -2871,7 +2893,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A101" s="9"/>
       <c r="B101" s="10" t="s">
         <v>13</v>
@@ -2883,7 +2905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A102" s="10"/>
       <c r="B102" s="10" t="s">
         <v>14</v>
@@ -2895,7 +2917,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A103" s="10"/>
       <c r="B103" s="10" t="s">
         <v>15</v>
@@ -2907,7 +2929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A104" s="10"/>
       <c r="B104" s="10" t="s">
         <v>16</v>
@@ -2919,7 +2941,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A105" s="10"/>
       <c r="B105" s="10" t="s">
         <v>17</v>
@@ -2931,7 +2953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A106" s="10"/>
       <c r="B106" s="10" t="s">
         <v>19</v>
@@ -2943,7 +2965,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A107" s="10"/>
       <c r="B107" s="16" t="s">
         <v>18</v>
@@ -2955,7 +2977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A108" s="10"/>
       <c r="B108" s="16"/>
       <c r="C108" s="10"/>
@@ -2967,7 +2989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E109">
         <f>SUM(E100:E108)</f>
         <v>0</v>
@@ -2977,7 +2999,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A113" s="13" t="s">
         <v>299</v>
       </c>
@@ -3000,7 +3022,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A114" s="13" t="s">
         <v>295</v>
       </c>
@@ -3017,7 +3039,7 @@
       </c>
       <c r="G114" s="27"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A115" s="11"/>
       <c r="B115" s="11"/>
       <c r="C115" s="11" t="s">
@@ -3032,7 +3054,7 @@
       </c>
       <c r="G115" s="27"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A116" s="11"/>
       <c r="B116" s="11"/>
       <c r="C116" s="11" t="s">
@@ -3047,7 +3069,7 @@
       </c>
       <c r="G116" s="27"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A117" s="13"/>
       <c r="B117" s="11"/>
       <c r="C117" s="11" t="s">
@@ -3062,7 +3084,7 @@
       </c>
       <c r="G117" s="27"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A118" s="11"/>
       <c r="B118" s="11"/>
       <c r="C118" s="11" t="s">
@@ -3079,7 +3101,7 @@
       </c>
       <c r="G118" s="27"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A119" s="11"/>
       <c r="B119" s="11"/>
       <c r="C119" s="11"/>
@@ -3094,7 +3116,7 @@
       </c>
       <c r="G119" s="27"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A120" s="13"/>
       <c r="B120" s="11"/>
       <c r="C120" s="11"/>
@@ -3109,7 +3131,7 @@
       </c>
       <c r="G120" s="27"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A121" s="13"/>
       <c r="B121" s="11"/>
       <c r="C121" s="11"/>
@@ -3124,7 +3146,7 @@
       </c>
       <c r="G121" s="27"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A122" s="13"/>
       <c r="B122" s="11"/>
       <c r="C122" s="11" t="s">
@@ -3139,7 +3161,7 @@
       </c>
       <c r="G122" s="27"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A123" s="11"/>
       <c r="B123" s="11"/>
       <c r="C123" s="11"/>
@@ -3152,7 +3174,7 @@
       </c>
       <c r="G123" s="27"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
       <c r="E124">
         <f>SUM(E117:E123)</f>
         <v>0</v>
@@ -3163,10 +3185,10 @@
       </c>
       <c r="G124" s="27"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="G125" s="27"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A126" s="14" t="s">
         <v>298</v>
       </c>
@@ -3185,7 +3207,7 @@
       </c>
       <c r="G126" s="27"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A127" s="14" t="s">
         <v>352</v>
       </c>
@@ -3200,7 +3222,7 @@
       </c>
       <c r="G127" s="27"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A128" s="14"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12" t="s">
@@ -3213,7 +3235,7 @@
       </c>
       <c r="G128" s="27"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A129" s="14"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12" t="s">
@@ -3228,7 +3250,7 @@
       </c>
       <c r="G129" s="27"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12" t="s">
@@ -3243,7 +3265,7 @@
       </c>
       <c r="G130" s="27"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A131" s="12"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12" t="s">
@@ -3258,7 +3280,7 @@
       </c>
       <c r="G131" s="27"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A132" s="12"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12" t="s">
@@ -3273,7 +3295,7 @@
       </c>
       <c r="G132" s="27"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12" t="s">
@@ -3286,7 +3308,7 @@
       </c>
       <c r="G133" s="27"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12" t="s">
@@ -3301,7 +3323,7 @@
       </c>
       <c r="G134" s="27"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A135" s="12"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
@@ -3314,7 +3336,7 @@
       </c>
       <c r="G135" s="27"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
       <c r="E136">
         <f>SUM(E126:E135)</f>
         <v>0</v>
@@ -3325,10 +3347,10 @@
       </c>
       <c r="G136" s="27"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
       <c r="G137" s="27"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A138" s="9" t="s">
         <v>351</v>
       </c>
@@ -3349,7 +3371,7 @@
       </c>
       <c r="G138" s="27"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A139" s="10" t="str">
         <f>$A$127</f>
         <v>e.g. camera, IMU, SPI</v>
@@ -3369,7 +3391,7 @@
       </c>
       <c r="G139" s="27"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A140" s="10"/>
       <c r="B140" s="10"/>
       <c r="C140" s="10" t="str">
@@ -3386,7 +3408,7 @@
       </c>
       <c r="G140" s="27"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A141" s="9"/>
       <c r="B141" s="10"/>
       <c r="C141" s="10" t="str">
@@ -3403,7 +3425,7 @@
       </c>
       <c r="G141" s="27"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A142" s="9"/>
       <c r="B142" s="10"/>
       <c r="C142" s="10" t="str">
@@ -3420,7 +3442,7 @@
       </c>
       <c r="G142" s="27"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A143" s="9"/>
       <c r="B143" s="10"/>
       <c r="C143" s="10" t="str">
@@ -3435,7 +3457,7 @@
       </c>
       <c r="G143" s="27"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A144" s="9"/>
       <c r="B144" s="10"/>
       <c r="C144" s="10" t="str">
@@ -3452,7 +3474,7 @@
       </c>
       <c r="G144" s="27"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A145" s="10"/>
       <c r="B145" s="10"/>
       <c r="C145" s="10" t="str">
@@ -3469,7 +3491,7 @@
       </c>
       <c r="G145" s="27"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A146" s="10"/>
       <c r="B146" s="10"/>
       <c r="C146" s="10" t="str">
@@ -3486,7 +3508,7 @@
       </c>
       <c r="G146" s="27"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A147" s="10"/>
       <c r="B147" s="10"/>
       <c r="C147" s="10"/>
@@ -3499,7 +3521,7 @@
       </c>
       <c r="G147" s="27"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
       <c r="E148">
         <f>SUM(E138:E147)</f>
         <v>0</v>
@@ -3510,7 +3532,7 @@
       </c>
       <c r="G148" s="27"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A149" s="13" t="str">
         <f t="shared" ref="A149:A150" si="2">A138</f>
         <v>domain sensor/actor</v>
@@ -3531,7 +3553,7 @@
       </c>
       <c r="G149" s="27"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A150" s="13" t="str">
         <f t="shared" si="2"/>
         <v>e.g. camera, IMU, SPI</v>
@@ -3549,7 +3571,7 @@
       </c>
       <c r="G150" s="27"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A151" s="13"/>
       <c r="B151" s="13"/>
       <c r="C151" s="11" t="str">
@@ -3564,7 +3586,7 @@
       </c>
       <c r="G151" s="27"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A152" s="13"/>
       <c r="B152" s="13"/>
       <c r="C152" s="11" t="str">
@@ -3579,7 +3601,7 @@
       </c>
       <c r="G152" s="27"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A153" s="13"/>
       <c r="B153" s="13"/>
       <c r="C153" s="11" t="str">
@@ -3594,7 +3616,7 @@
       </c>
       <c r="G153" s="27"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A154" s="13"/>
       <c r="B154" s="13"/>
       <c r="C154" s="11" t="str">
@@ -3609,7 +3631,7 @@
       </c>
       <c r="G154" s="27"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A155" s="13"/>
       <c r="B155" s="13"/>
       <c r="C155" s="11" t="str">
@@ -3624,7 +3646,7 @@
       </c>
       <c r="G155" s="27"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A156" s="13"/>
       <c r="B156" s="13"/>
       <c r="C156" s="11" t="str">
@@ -3639,7 +3661,7 @@
       </c>
       <c r="G156" s="27"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A157" s="13"/>
       <c r="B157" s="13"/>
       <c r="C157" s="11" t="str">
@@ -3654,7 +3676,7 @@
       </c>
       <c r="G157" s="27"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A158" s="13"/>
       <c r="B158" s="13"/>
       <c r="C158" s="11"/>
@@ -3668,7 +3690,7 @@
       <c r="F158" s="11"/>
       <c r="G158" s="27"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="E159">
@@ -3681,7 +3703,7 @@
       </c>
       <c r="G159" s="27"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A160" s="14" t="s">
         <v>301</v>
       </c>
@@ -3698,7 +3720,7 @@
       </c>
       <c r="G160" s="27"/>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A161" s="14" t="s">
         <v>302</v>
       </c>
@@ -3713,7 +3735,7 @@
       </c>
       <c r="G161" s="27"/>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A162" s="14"/>
       <c r="B162" s="12"/>
       <c r="C162" s="12" t="s">
@@ -3726,7 +3748,7 @@
       </c>
       <c r="G162" s="27"/>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A163" s="14"/>
       <c r="B163" s="12"/>
       <c r="C163" s="12" t="s">
@@ -3739,7 +3761,7 @@
       </c>
       <c r="G163" s="27"/>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A164" s="14"/>
       <c r="B164" s="12"/>
       <c r="C164" s="12" t="s">
@@ -3752,7 +3774,7 @@
       </c>
       <c r="G164" s="27"/>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A165" s="14"/>
       <c r="B165" s="12"/>
       <c r="C165" s="12" t="s">
@@ -3765,7 +3787,7 @@
       </c>
       <c r="G165" s="27"/>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A166" s="14"/>
       <c r="B166" s="12"/>
       <c r="C166" s="12" t="s">
@@ -3778,7 +3800,7 @@
       </c>
       <c r="G166" s="27"/>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A167" s="14"/>
       <c r="B167" s="12"/>
       <c r="C167" s="12" t="s">
@@ -3795,7 +3817,7 @@
       </c>
       <c r="G167" s="27"/>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A168" s="12"/>
       <c r="B168" s="12"/>
       <c r="C168" s="12"/>
@@ -3810,7 +3832,7 @@
       </c>
       <c r="G168" s="27"/>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A169" s="12"/>
       <c r="B169" s="12"/>
       <c r="C169" s="12" t="s">
@@ -3825,7 +3847,7 @@
       </c>
       <c r="G169" s="27"/>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A170" s="12"/>
       <c r="B170" s="12"/>
       <c r="C170" s="12" t="s">
@@ -3840,7 +3862,7 @@
       </c>
       <c r="G170" s="27"/>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A171" s="12"/>
       <c r="B171" s="12"/>
       <c r="C171" s="12" t="s">
@@ -3855,7 +3877,7 @@
       </c>
       <c r="G171" s="27"/>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A172" s="12"/>
       <c r="B172" s="12"/>
       <c r="C172" s="12"/>
@@ -3868,7 +3890,7 @@
       </c>
       <c r="G172" s="27"/>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.45">
       <c r="E173">
         <f>SUM(E160:E172)</f>
         <v>0</v>
@@ -3879,20 +3901,20 @@
       </c>
       <c r="G173" s="27"/>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.45">
       <c r="G174" s="27"/>
     </row>
-    <row r="175" spans="1:12" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="5" t="s">
         <v>307</v>
       </c>
       <c r="K175"/>
       <c r="L175"/>
     </row>
-    <row r="176" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A177" s="13" t="s">
         <v>21</v>
       </c>
@@ -3906,7 +3928,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A178" s="11"/>
       <c r="B178" s="11"/>
       <c r="C178" s="11" t="s">
@@ -3918,7 +3940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A179" s="11"/>
       <c r="B179" s="11"/>
       <c r="C179" s="11" t="s">
@@ -3930,7 +3952,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A180" s="11"/>
       <c r="B180" s="11"/>
       <c r="C180" s="11" t="s">
@@ -3942,7 +3964,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A181" s="11"/>
       <c r="B181" s="11"/>
       <c r="C181" s="11" t="s">
@@ -3954,7 +3976,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A182" s="11"/>
       <c r="B182" s="11"/>
       <c r="C182" s="11" t="s">
@@ -3966,7 +3988,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A183" s="11"/>
       <c r="B183" s="11"/>
       <c r="C183" s="11" t="s">
@@ -3978,7 +4000,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A184" s="11"/>
       <c r="B184" s="11"/>
       <c r="C184" s="11" t="s">
@@ -3990,7 +4012,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A185" s="11"/>
       <c r="B185" s="11"/>
       <c r="C185" s="11"/>
@@ -4002,7 +4024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.45">
       <c r="E186">
         <f>SUM(E177:E185)</f>
         <v>0</v>
@@ -4012,12 +4034,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" s="5" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A189" s="9" t="s">
         <v>176</v>
       </c>
@@ -4034,7 +4056,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A190" s="9" t="s">
         <v>290</v>
       </c>
@@ -4049,7 +4071,7 @@
       </c>
       <c r="G190" s="28"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A191" s="9"/>
       <c r="B191" s="9"/>
       <c r="C191" s="10" t="s">
@@ -4062,7 +4084,7 @@
       </c>
       <c r="G191" s="28"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A192" s="9"/>
       <c r="B192" s="9"/>
       <c r="C192" s="10" t="s">
@@ -4075,7 +4097,7 @@
       </c>
       <c r="G192" s="28"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A193" s="9"/>
       <c r="B193" s="9"/>
       <c r="C193" s="10" t="s">
@@ -4088,7 +4110,7 @@
       </c>
       <c r="G193" s="28"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A194" s="9"/>
       <c r="B194" s="9"/>
       <c r="C194" s="10" t="s">
@@ -4101,7 +4123,7 @@
       </c>
       <c r="G194" s="28"/>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A195" s="9"/>
       <c r="B195" s="9"/>
       <c r="C195" s="10"/>
@@ -4115,7 +4137,7 @@
       <c r="F195" s="10"/>
       <c r="G195" s="28"/>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="E196">
@@ -4128,7 +4150,7 @@
       </c>
       <c r="G196" s="28"/>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A197" s="9" t="s">
         <v>176</v>
       </c>
@@ -4143,7 +4165,7 @@
       </c>
       <c r="G197" s="28"/>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A198" s="9" t="s">
         <v>292</v>
       </c>
@@ -4158,7 +4180,7 @@
       </c>
       <c r="G198" s="28"/>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A199" s="9" t="s">
         <v>291</v>
       </c>
@@ -4173,7 +4195,7 @@
       </c>
       <c r="G199" s="28"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A200" s="9"/>
       <c r="B200" s="9"/>
       <c r="C200" s="10" t="s">
@@ -4186,7 +4208,7 @@
       </c>
       <c r="G200" s="28"/>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A201" s="9"/>
       <c r="B201" s="9"/>
       <c r="C201" s="10" t="s">
@@ -4199,7 +4221,7 @@
       </c>
       <c r="G201" s="28"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A202" s="9"/>
       <c r="B202" s="9"/>
       <c r="C202" s="10" t="s">
@@ -4212,7 +4234,7 @@
       </c>
       <c r="G202" s="28"/>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A203" s="9"/>
       <c r="B203" s="9"/>
       <c r="C203" s="10"/>
@@ -4226,7 +4248,7 @@
       <c r="F203" s="10"/>
       <c r="G203" s="28"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="E204">
@@ -4239,12 +4261,12 @@
       </c>
       <c r="G204" s="28"/>
     </row>
-    <row r="205" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" s="5" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A206" s="7" t="s">
         <v>28</v>
       </c>
@@ -4256,7 +4278,7 @@
       <c r="E206" s="8"/>
       <c r="F206" s="8"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A207" s="8"/>
       <c r="B207" s="8"/>
       <c r="C207" s="8" t="s">
@@ -4268,7 +4290,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A208" s="8"/>
       <c r="B208" s="8"/>
       <c r="C208" s="8" t="s">
@@ -4278,7 +4300,7 @@
       <c r="E208" s="8"/>
       <c r="F208" s="8"/>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A209" s="8"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8" t="s">
@@ -4288,7 +4310,7 @@
       <c r="E209" s="8"/>
       <c r="F209" s="8"/>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A210" s="8"/>
       <c r="B210" s="8"/>
       <c r="C210" s="8" t="s">
@@ -4300,18 +4322,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.45">
       <c r="F211">
         <f>SUM(F206:F210)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="212" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:13" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" s="5" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A213" s="13" t="s">
         <v>325</v>
       </c>
@@ -4325,7 +4347,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A214" s="13"/>
       <c r="B214" s="11"/>
       <c r="C214" s="11"/>
@@ -4337,7 +4359,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A215" s="13"/>
       <c r="B215" s="11"/>
       <c r="C215" s="11"/>
@@ -4349,7 +4371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A216" s="13"/>
       <c r="B216" s="11"/>
       <c r="C216" s="11"/>
@@ -4361,7 +4383,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A217" s="13"/>
       <c r="B217" s="11"/>
       <c r="C217" s="11"/>
@@ -4373,7 +4395,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A218" s="13"/>
       <c r="B218" s="11"/>
       <c r="C218" s="11"/>
@@ -4386,7 +4408,7 @@
       </c>
       <c r="F218" s="11"/>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A219" s="1"/>
       <c r="E219">
         <f>-SUM(E213:E218)</f>
@@ -4398,7 +4420,7 @@
       </c>
       <c r="M219" s="19"/>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A221" s="9" t="s">
         <v>66</v>
       </c>
@@ -4412,7 +4434,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A222" s="9"/>
       <c r="B222" s="10" t="s">
         <v>42</v>
@@ -4424,7 +4446,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A223" s="9"/>
       <c r="B223" s="10" t="s">
         <v>328</v>
@@ -4436,7 +4458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A224" s="9"/>
       <c r="B224" s="10" t="s">
         <v>67</v>
@@ -4448,7 +4470,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A225" s="9"/>
       <c r="B225" s="10"/>
       <c r="C225" s="10"/>
@@ -4461,7 +4483,7 @@
       </c>
       <c r="F225" s="10"/>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A226" s="1"/>
       <c r="E226">
         <f>-SUM(E221:E225)</f>
@@ -4472,7 +4494,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A227" s="9" t="s">
         <v>261</v>
       </c>
@@ -4490,7 +4512,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A228" s="10"/>
       <c r="B228" s="10"/>
       <c r="C228" s="10"/>
@@ -4502,7 +4524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A229" s="10"/>
       <c r="B229" s="10"/>
       <c r="C229" s="10"/>
@@ -4514,7 +4536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A230" s="10"/>
       <c r="B230" s="10"/>
       <c r="C230" s="10"/>
@@ -4526,7 +4548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A231" s="10"/>
       <c r="B231" s="10"/>
       <c r="C231" s="10"/>
@@ -4538,7 +4560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A232" s="10"/>
       <c r="B232" s="10"/>
       <c r="C232" s="10"/>
@@ -4550,7 +4572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A233" s="10"/>
       <c r="B233" s="10"/>
       <c r="C233" s="10" t="s">
@@ -4564,7 +4586,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A234" s="10"/>
       <c r="B234" s="10"/>
       <c r="C234" s="10"/>
@@ -4576,7 +4598,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A235" s="10"/>
       <c r="B235" s="10"/>
       <c r="C235" s="10"/>
@@ -4588,7 +4610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A236" s="10"/>
       <c r="B236" s="10"/>
       <c r="C236" s="10"/>
@@ -4600,7 +4622,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A237" s="10"/>
       <c r="B237" s="10"/>
       <c r="C237" s="10"/>
@@ -4612,7 +4634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A238" s="10"/>
       <c r="B238" s="10"/>
       <c r="C238" s="10"/>
@@ -4625,7 +4647,7 @@
       </c>
       <c r="F238" s="10"/>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E239">
         <f>SUM(E227:E232)</f>
         <v>0</v>
@@ -4635,7 +4657,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A240" s="7" t="s">
         <v>261</v>
       </c>
@@ -4649,7 +4671,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A241" s="8"/>
       <c r="B241" s="7" t="s">
         <v>20</v>
@@ -4663,7 +4685,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A242" s="8"/>
       <c r="B242" s="8"/>
       <c r="C242" s="8" t="s">
@@ -4675,7 +4697,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A243" s="8"/>
       <c r="B243" s="8"/>
       <c r="C243" s="8" t="s">
@@ -4687,7 +4709,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A244" s="8"/>
       <c r="B244" s="8"/>
       <c r="C244" s="8" t="s">
@@ -4699,7 +4721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A245" s="8"/>
       <c r="B245" s="8"/>
       <c r="C245" s="8" t="s">
@@ -4711,7 +4733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A246" s="8"/>
       <c r="B246" s="8"/>
       <c r="C246" s="8" t="s">
@@ -4723,7 +4745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A247" s="8"/>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4736,7 +4758,7 @@
       </c>
       <c r="F247" s="8"/>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E248">
         <f>SUM(E240:E246)</f>
         <v>0</v>
@@ -4746,7 +4768,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A249" s="7" t="s">
         <v>66</v>
       </c>
@@ -4760,7 +4782,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A250" s="7"/>
       <c r="B250" s="8" t="s">
         <v>42</v>
@@ -4772,7 +4794,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A251" s="7"/>
       <c r="B251" s="8" t="s">
         <v>217</v>
@@ -4784,7 +4806,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A252" s="7"/>
       <c r="B252" s="8" t="s">
         <v>140</v>
@@ -4796,7 +4818,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A253" s="7"/>
       <c r="B253" s="8" t="s">
         <v>65</v>
@@ -4808,7 +4830,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A254" s="7"/>
       <c r="B254" s="8" t="s">
         <v>67</v>
@@ -4820,7 +4842,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A255" s="7"/>
       <c r="B255" s="7" t="s">
         <v>49</v>
@@ -4834,7 +4856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A256" s="7"/>
       <c r="B256" s="7"/>
       <c r="C256" s="8" t="s">
@@ -4846,7 +4868,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A257" s="7"/>
       <c r="B257" s="7"/>
       <c r="C257" s="8" t="s">
@@ -4858,7 +4880,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A258" s="7"/>
       <c r="B258" s="7"/>
       <c r="C258" s="8" t="s">
@@ -4870,7 +4892,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A259" s="7"/>
       <c r="B259" s="7"/>
       <c r="C259" s="8" t="s">
@@ -4882,7 +4904,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A260" s="7"/>
       <c r="B260" s="7"/>
       <c r="C260" s="8" t="s">
@@ -4896,7 +4918,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A261" s="7"/>
       <c r="B261" s="7"/>
       <c r="C261" s="8"/>
@@ -4908,7 +4930,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A262" s="7"/>
       <c r="B262" s="7"/>
       <c r="C262" s="8"/>
@@ -4920,7 +4942,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A263" s="7"/>
       <c r="B263" s="7"/>
       <c r="C263" s="8"/>
@@ -4932,7 +4954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A264" s="7"/>
       <c r="B264" s="7"/>
       <c r="C264" s="8"/>
@@ -4944,7 +4966,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A265" s="7"/>
       <c r="B265" s="7"/>
       <c r="C265" s="8"/>
@@ -4957,7 +4979,7 @@
       </c>
       <c r="F265" s="8"/>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E266">
         <f>SUM(E249:E265)</f>
         <v>0</v>
@@ -4967,7 +4989,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A268" s="7" t="s">
         <v>267</v>
       </c>
@@ -4981,7 +5003,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A269" s="7" t="s">
         <v>269</v>
       </c>
@@ -4995,7 +5017,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A270" s="7"/>
       <c r="B270" s="8" t="s">
         <v>318</v>
@@ -5007,7 +5029,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A271" s="8"/>
       <c r="B271" s="8" t="s">
         <v>316</v>
@@ -5019,7 +5041,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A272" s="8"/>
       <c r="B272" s="8" t="s">
         <v>317</v>
@@ -5031,7 +5053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A273" s="8"/>
       <c r="B273" s="8"/>
       <c r="C273" s="8"/>
@@ -5044,7 +5066,7 @@
       </c>
       <c r="F273" s="8"/>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E274">
         <f>SUM(E268:E272)</f>
         <v>0</v>
@@ -5054,7 +5076,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A275" s="9" t="s">
         <v>34</v>
       </c>
@@ -5068,7 +5090,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A276" s="10"/>
       <c r="B276" s="10" t="s">
         <v>221</v>
@@ -5080,7 +5102,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A277" s="9"/>
       <c r="B277" s="10" t="s">
         <v>285</v>
@@ -5094,7 +5116,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A278" s="10"/>
       <c r="B278" s="10" t="s">
         <v>278</v>
@@ -5108,7 +5130,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A279" s="9"/>
       <c r="B279" s="10" t="s">
         <v>200</v>
@@ -5122,7 +5144,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A280" s="9"/>
       <c r="B280" s="10" t="s">
         <v>286</v>
@@ -5136,7 +5158,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A281" s="9"/>
       <c r="B281" s="10" t="s">
         <v>287</v>
@@ -5148,7 +5170,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A282" s="10"/>
       <c r="B282" s="10" t="s">
         <v>279</v>
@@ -5160,7 +5182,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A283" s="10"/>
       <c r="B283" s="10" t="s">
         <v>280</v>
@@ -5172,7 +5194,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A284" s="10"/>
       <c r="B284" s="10" t="s">
         <v>36</v>
@@ -5184,7 +5206,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A285" s="10"/>
       <c r="B285" s="10"/>
       <c r="C285" s="10"/>
@@ -5197,7 +5219,7 @@
       </c>
       <c r="F285" s="10"/>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E286">
         <f>SUM(E275:E284)</f>
         <v>0</v>
@@ -5207,12 +5229,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="289" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A289" s="5" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A290" s="12" t="s">
         <v>191</v>
       </c>
@@ -5226,7 +5248,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A291" s="14"/>
       <c r="B291" s="14"/>
       <c r="C291" s="12" t="s">
@@ -5238,7 +5260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A292" s="14"/>
       <c r="B292" s="14"/>
       <c r="C292" s="12" t="s">
@@ -5250,7 +5272,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A293" s="14"/>
       <c r="B293" s="14"/>
       <c r="C293" s="12" t="s">
@@ -5262,7 +5284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A294" s="14"/>
       <c r="B294" s="14"/>
       <c r="C294" s="12" t="s">
@@ -5274,7 +5296,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A295" s="12"/>
       <c r="B295" s="12" t="s">
         <v>192</v>
@@ -5288,7 +5310,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A296" s="12"/>
       <c r="B296" s="12"/>
       <c r="C296" s="12" t="s">
@@ -5300,7 +5322,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A297" s="12"/>
       <c r="B297" s="12"/>
       <c r="C297" s="12" t="s">
@@ -5312,7 +5334,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A298" s="12"/>
       <c r="B298" s="12" t="s">
         <v>194</v>
@@ -5326,7 +5348,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A299" s="12"/>
       <c r="B299" s="12"/>
       <c r="C299" s="12" t="s">
@@ -5338,7 +5360,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A300" s="12"/>
       <c r="B300" s="12"/>
       <c r="C300" s="12" t="s">
@@ -5350,7 +5372,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A301" s="14" t="s">
         <v>49</v>
       </c>
@@ -5364,7 +5386,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A302" s="14"/>
       <c r="B302" s="14"/>
       <c r="C302" s="12" t="s">
@@ -5376,7 +5398,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A303" s="14"/>
       <c r="B303" s="14"/>
       <c r="C303" s="12" t="s">
@@ -5388,7 +5410,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A304" s="14"/>
       <c r="B304" s="14"/>
       <c r="C304" s="12" t="s">
@@ -5400,7 +5422,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A305" s="14"/>
       <c r="B305" s="14"/>
       <c r="C305" s="12" t="s">
@@ -5412,7 +5434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A306" s="14"/>
       <c r="B306" s="14"/>
       <c r="C306" s="12" t="s">
@@ -5426,7 +5448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A307" s="14"/>
       <c r="B307" s="14"/>
       <c r="C307" s="12"/>
@@ -5438,7 +5460,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A308" s="14"/>
       <c r="B308" s="14"/>
       <c r="C308" s="12"/>
@@ -5450,7 +5472,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A309" s="14"/>
       <c r="B309" s="14"/>
       <c r="C309" s="12"/>
@@ -5462,7 +5484,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A310" s="14"/>
       <c r="B310" s="14"/>
       <c r="C310" s="12"/>
@@ -5474,7 +5496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A311" s="12"/>
       <c r="B311" s="12"/>
       <c r="C311" s="12"/>
@@ -5487,7 +5509,7 @@
       </c>
       <c r="F311" s="12"/>
     </row>
-    <row r="312" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" ht="15" x14ac:dyDescent="0.45">
       <c r="E312">
         <f>SUM(E290:E311)</f>
         <v>0</v>
@@ -5499,7 +5521,7 @@
       <c r="K312" s="17"/>
       <c r="L312" s="17"/>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A313" s="9" t="s">
         <v>355</v>
       </c>
@@ -5515,7 +5537,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A314" s="10" t="s">
         <v>302</v>
       </c>
@@ -5529,7 +5551,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A315" s="9"/>
       <c r="B315" s="10"/>
       <c r="C315" s="10" t="s">
@@ -5541,7 +5563,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A316" s="10"/>
       <c r="B316" s="10"/>
       <c r="C316" s="10" t="s">
@@ -5555,7 +5577,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A317" s="10"/>
       <c r="B317" s="10"/>
       <c r="C317" s="10" t="s">
@@ -5569,7 +5591,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A318" s="9"/>
       <c r="B318" s="10"/>
       <c r="C318" s="10" t="s">
@@ -5583,7 +5605,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A319" s="9"/>
       <c r="B319" s="10"/>
       <c r="C319" s="10" t="s">
@@ -5597,7 +5619,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A320" s="10"/>
       <c r="B320" s="10"/>
       <c r="C320" s="10"/>
@@ -5609,7 +5631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" ht="15" x14ac:dyDescent="0.45">
       <c r="E321">
         <f>SUM(E313:E320)</f>
         <v>0</v>
@@ -5621,15 +5643,15 @@
       <c r="K321" s="17"/>
       <c r="L321" s="17"/>
     </row>
-    <row r="322" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12" ht="15" x14ac:dyDescent="0.45">
       <c r="K322" s="17"/>
       <c r="L322" s="17"/>
     </row>
-    <row r="323" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12" ht="15" x14ac:dyDescent="0.45">
       <c r="K323" s="17"/>
       <c r="L323" s="17"/>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A324" s="13" t="s">
         <v>271</v>
       </c>
@@ -5643,7 +5665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A325" s="11"/>
       <c r="B325" s="11" t="s">
         <v>273</v>
@@ -5655,7 +5677,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A326" s="11"/>
       <c r="B326" s="11" t="s">
         <v>110</v>
@@ -5667,7 +5689,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A327" s="13" t="s">
         <v>274</v>
       </c>
@@ -5681,7 +5703,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A328" s="11"/>
       <c r="B328" s="11" t="s">
         <v>276</v>
@@ -5693,7 +5715,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A329" s="13" t="s">
         <v>319</v>
       </c>
@@ -5707,7 +5729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A330" s="11"/>
       <c r="B330" s="11"/>
       <c r="C330" s="11" t="s">
@@ -5719,7 +5741,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A331" s="11"/>
       <c r="B331" s="11"/>
       <c r="C331" s="11" t="s">
@@ -5731,7 +5753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A332" s="11"/>
       <c r="B332" s="11"/>
       <c r="C332" s="11"/>
@@ -5744,7 +5766,7 @@
       </c>
       <c r="F332" s="11"/>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.45">
       <c r="E333">
         <f>SUM(E324:E328)</f>
         <v>0</v>
@@ -5754,14 +5776,14 @@
         <v>60</v>
       </c>
     </row>
-    <row r="335" spans="1:12" s="17" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:12" s="17" customFormat="1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A335" s="5" t="s">
         <v>251</v>
       </c>
       <c r="K335"/>
       <c r="L335"/>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A336" s="11" t="s">
         <v>153</v>
       </c>
@@ -5779,7 +5801,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A337" s="11"/>
       <c r="B337" s="11"/>
       <c r="C337" s="11" t="s">
@@ -5793,7 +5815,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A338" s="11"/>
       <c r="B338" s="11"/>
       <c r="C338" s="11" t="s">
@@ -5807,7 +5829,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A339" s="11"/>
       <c r="B339" s="11"/>
       <c r="C339" s="11" t="s">
@@ -5821,7 +5843,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A340" s="11"/>
       <c r="B340" s="11"/>
       <c r="C340" s="11" t="s">
@@ -5835,7 +5857,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A341" s="11"/>
       <c r="B341" s="11"/>
       <c r="C341" s="11" t="s">
@@ -5849,7 +5871,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A342" s="11"/>
       <c r="B342" s="11"/>
       <c r="C342" s="11"/>
@@ -5861,7 +5883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E343">
         <f>SUM(E336:E342)</f>
         <v>0</v>
@@ -5871,7 +5893,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A344" s="13" t="s">
         <v>40</v>
       </c>
@@ -5885,7 +5907,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A345" s="13"/>
       <c r="B345" s="13"/>
       <c r="C345" s="15" t="s">
@@ -5897,7 +5919,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A346" s="13"/>
       <c r="B346" s="13"/>
       <c r="C346" s="15" t="s">
@@ -5909,7 +5931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A347" s="13"/>
       <c r="B347" s="13"/>
       <c r="C347" s="11"/>
@@ -5917,7 +5939,7 @@
       <c r="E347" s="11"/>
       <c r="F347" s="11"/>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A348" s="13" t="s">
         <v>103</v>
       </c>
@@ -5931,7 +5953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A349" s="13"/>
       <c r="B349" s="13"/>
       <c r="C349" s="11" t="s">
@@ -5943,7 +5965,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A350" s="13"/>
       <c r="B350" s="13"/>
       <c r="C350" s="11" t="s">
@@ -5955,7 +5977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A351" s="13"/>
       <c r="B351" s="13"/>
       <c r="C351" s="11"/>
@@ -5963,7 +5985,7 @@
       <c r="E351" s="11"/>
       <c r="F351" s="11"/>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A352" s="13" t="s">
         <v>199</v>
       </c>
@@ -5977,7 +5999,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A353" s="13"/>
       <c r="B353" s="13"/>
       <c r="C353" s="11" t="s">
@@ -5989,7 +6011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A354" s="13"/>
       <c r="B354" s="13"/>
       <c r="C354" s="11" t="s">
@@ -6001,7 +6023,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A355" s="13"/>
       <c r="B355" s="13"/>
       <c r="C355" s="11"/>
@@ -6014,7 +6036,7 @@
       </c>
       <c r="F355" s="11"/>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="E356">
@@ -6027,7 +6049,7 @@
       </c>
       <c r="M356" s="19"/>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A357" s="14" t="s">
         <v>41</v>
       </c>
@@ -6042,7 +6064,7 @@
       </c>
       <c r="M357" s="19"/>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A358" s="14"/>
       <c r="B358" s="14"/>
       <c r="C358" s="12" t="s">
@@ -6055,7 +6077,7 @@
       </c>
       <c r="M358" s="19"/>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A359" s="14"/>
       <c r="B359" s="14"/>
       <c r="C359" s="12"/>
@@ -6069,7 +6091,7 @@
       <c r="F359" s="12"/>
       <c r="M359" s="19"/>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="E360">
@@ -6081,7 +6103,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A362" s="1" t="s">
         <v>5</v>
       </c>
@@ -6097,7 +6119,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A363" s="1" t="s">
         <v>314</v>
       </c>
@@ -6111,7 +6133,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A364" s="1"/>
       <c r="B364" s="10"/>
       <c r="C364" s="10" t="s">
@@ -6123,7 +6145,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A365" s="1"/>
       <c r="B365" s="10"/>
       <c r="C365" s="10" t="s">
@@ -6135,7 +6157,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A366" s="1"/>
       <c r="B366" s="10"/>
       <c r="C366" s="10" t="s">
@@ -6147,7 +6169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A367" s="1"/>
       <c r="B367" s="10"/>
       <c r="C367" s="10" t="s">
@@ -6159,7 +6181,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A368" s="1"/>
       <c r="B368" s="10"/>
       <c r="C368" s="10" t="s">
@@ -6171,7 +6193,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A369" s="1"/>
       <c r="B369" s="10"/>
       <c r="C369" s="10" t="s">
@@ -6183,7 +6205,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A370" s="1"/>
       <c r="B370" s="10"/>
       <c r="C370" s="10"/>
@@ -6196,7 +6218,7 @@
       </c>
       <c r="F370" s="10"/>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="E371">
@@ -6208,7 +6230,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A372" s="1"/>
       <c r="B372" s="13" t="s">
         <v>54</v>
@@ -6222,7 +6244,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A373" s="1"/>
       <c r="B373" s="11"/>
       <c r="C373" s="11" t="s">
@@ -6234,7 +6256,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A374" s="1"/>
       <c r="B374" s="11"/>
       <c r="C374" s="11" t="s">
@@ -6246,7 +6268,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A375" s="1"/>
       <c r="B375" s="11"/>
       <c r="C375" s="11" t="s">
@@ -6258,7 +6280,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A376" s="1"/>
       <c r="B376" s="11"/>
       <c r="C376" s="11" t="s">
@@ -6270,7 +6292,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A377" s="1"/>
       <c r="B377" s="11"/>
       <c r="C377" s="11" t="s">
@@ -6282,7 +6304,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A378" s="1"/>
       <c r="B378" s="11"/>
       <c r="C378" s="11" t="s">
@@ -6294,7 +6316,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A379" s="1"/>
       <c r="B379" s="11"/>
       <c r="C379" s="11" t="s">
@@ -6306,7 +6328,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A380" s="1"/>
       <c r="B380" s="11"/>
       <c r="C380" s="11"/>
@@ -6319,7 +6341,7 @@
       </c>
       <c r="F380" s="11"/>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="E381">
@@ -6331,7 +6353,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A382" s="1"/>
       <c r="B382" s="14" t="s">
         <v>54</v>
@@ -6345,7 +6367,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A383" s="1"/>
       <c r="B383" s="12"/>
       <c r="C383" s="12" t="s">
@@ -6357,7 +6379,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A384" s="1"/>
       <c r="B384" s="12"/>
       <c r="C384" s="12" t="s">
@@ -6369,7 +6391,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A385" s="1"/>
       <c r="B385" s="12"/>
       <c r="C385" s="12" t="str">
@@ -6382,7 +6404,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A386" s="1"/>
       <c r="B386" s="12"/>
       <c r="C386" s="12" t="str">
@@ -6395,7 +6417,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A387" s="1"/>
       <c r="B387" s="12"/>
       <c r="C387" s="12" t="str">
@@ -6408,7 +6430,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A388" s="1"/>
       <c r="B388" s="12"/>
       <c r="C388" s="12" t="str">
@@ -6421,7 +6443,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A389" s="1"/>
       <c r="B389" s="12"/>
       <c r="C389" s="12" t="s">
@@ -6433,7 +6455,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A390" s="1"/>
       <c r="B390" s="12"/>
       <c r="C390" s="12"/>
@@ -6446,7 +6468,7 @@
       </c>
       <c r="F390" s="12"/>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="E391">
@@ -6458,12 +6480,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="393" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A393" s="5" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A394" s="7" t="s">
         <v>309</v>
       </c>
@@ -6473,7 +6495,7 @@
       <c r="E394" s="8"/>
       <c r="F394" s="8"/>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A395" s="7"/>
       <c r="B395" s="8"/>
       <c r="C395" s="8"/>
@@ -6481,7 +6503,7 @@
       <c r="E395" s="8"/>
       <c r="F395" s="8"/>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A396" s="7"/>
       <c r="B396" s="8" t="s">
         <v>157</v>
@@ -6491,7 +6513,7 @@
       <c r="E396" s="8"/>
       <c r="F396" s="8"/>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A397" s="7"/>
       <c r="B397" s="8" t="s">
         <v>158</v>
@@ -6503,7 +6525,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A398" s="7"/>
       <c r="B398" s="8" t="s">
         <v>159</v>
@@ -6515,7 +6537,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A399" s="7"/>
       <c r="B399" s="8" t="s">
         <v>160</v>
@@ -6529,7 +6551,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A400" s="7"/>
       <c r="B400" s="8"/>
       <c r="C400" s="8" t="s">
@@ -6541,7 +6563,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A401" s="7"/>
       <c r="B401" s="8" t="s">
         <v>162</v>
@@ -6555,7 +6577,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A402" s="7"/>
       <c r="B402" s="8"/>
       <c r="C402" s="8" t="s">
@@ -6567,7 +6589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A403" s="7"/>
       <c r="B403" s="8"/>
       <c r="C403" s="8" t="s">
@@ -6579,7 +6601,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A404" s="7"/>
       <c r="B404" s="8"/>
       <c r="C404" s="8" t="s">
@@ -6591,7 +6613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A405" s="7"/>
       <c r="B405" s="8"/>
       <c r="C405" s="8" t="s">
@@ -6603,7 +6625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A406" s="7"/>
       <c r="B406" s="8"/>
       <c r="C406" s="8"/>
@@ -6616,7 +6638,7 @@
       </c>
       <c r="F406" s="8"/>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A407" s="1"/>
       <c r="E407">
         <f>SUM(E394:E406)</f>
@@ -6627,10 +6649,10 @@
         <v>65</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A408" s="1"/>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A409" s="9" t="s">
         <v>90</v>
       </c>
@@ -6644,7 +6666,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A410" s="10"/>
       <c r="B410" s="10" t="s">
         <v>92</v>
@@ -6656,7 +6678,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A411" s="10"/>
       <c r="B411" s="10" t="s">
         <v>93</v>
@@ -6668,7 +6690,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A412" s="10"/>
       <c r="B412" s="10" t="s">
         <v>94</v>
@@ -6680,7 +6702,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A413" s="9" t="s">
         <v>102</v>
       </c>
@@ -6690,7 +6712,7 @@
       <c r="E413" s="10"/>
       <c r="F413" s="10"/>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A414" s="9"/>
       <c r="B414" s="10" t="s">
         <v>118</v>
@@ -6702,7 +6724,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A415" s="10"/>
       <c r="B415" s="10" t="s">
         <v>119</v>
@@ -6716,7 +6738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A416" s="10"/>
       <c r="B416" s="10" t="s">
         <v>120</v>
@@ -6730,7 +6752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A417" s="10"/>
       <c r="B417" s="10" t="s">
         <v>121</v>
@@ -6742,7 +6764,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A418" s="10"/>
       <c r="B418" s="10"/>
       <c r="C418" s="10"/>
@@ -6750,7 +6772,7 @@
       <c r="E418" s="10"/>
       <c r="F418" s="10"/>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A419" s="10"/>
       <c r="B419" s="10"/>
       <c r="C419" s="10"/>
@@ -6763,7 +6785,7 @@
       </c>
       <c r="F419" s="10"/>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E420">
         <f>SUM(E409:E419)</f>
         <v>0</v>
@@ -6773,12 +6795,12 @@
         <v>550</v>
       </c>
     </row>
-    <row r="421" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A421" s="5" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A422" s="7" t="s">
         <v>36</v>
       </c>
@@ -6794,7 +6816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A423" s="7"/>
       <c r="B423" s="8"/>
       <c r="C423" s="8" t="s">
@@ -6806,7 +6828,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A424" s="7"/>
       <c r="B424" s="8"/>
       <c r="C424" s="8" t="s">
@@ -6818,7 +6840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A425" s="7"/>
       <c r="B425" s="8"/>
       <c r="C425" s="8" t="s">
@@ -6830,7 +6852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A426" s="7"/>
       <c r="B426" s="8"/>
       <c r="C426" s="8" t="s">
@@ -6842,7 +6864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A427" s="8"/>
       <c r="B427" s="8" t="s">
         <v>12</v>
@@ -6854,7 +6876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A428" s="8"/>
       <c r="B428" s="8" t="s">
         <v>39</v>
@@ -6866,7 +6888,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A429" s="8"/>
       <c r="B429" s="8" t="s">
         <v>68</v>
@@ -6878,7 +6900,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A430" s="8"/>
       <c r="B430" s="8" t="s">
         <v>85</v>
@@ -6890,7 +6912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A431" s="8"/>
       <c r="B431" s="8"/>
       <c r="C431" s="8"/>
@@ -6903,7 +6925,7 @@
       </c>
       <c r="F431" s="8"/>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E432">
         <f>SUM(E422:E431)</f>
         <v>0</v>
@@ -6913,7 +6935,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A433" s="8" t="s">
         <v>122</v>
       </c>
@@ -6927,7 +6949,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A434" s="8"/>
       <c r="B434" s="8" t="s">
         <v>124</v>
@@ -6939,7 +6961,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A435" s="8"/>
       <c r="B435" s="8" t="s">
         <v>125</v>
@@ -6951,7 +6973,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A436" s="8"/>
       <c r="B436" s="8" t="s">
         <v>126</v>
@@ -6963,7 +6985,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A437" s="8"/>
       <c r="B437" s="8" t="s">
         <v>127</v>
@@ -6975,7 +6997,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A438" s="8"/>
       <c r="B438" s="8" t="s">
         <v>228</v>
@@ -6987,7 +7009,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A439" s="8"/>
       <c r="B439" s="8" t="s">
         <v>128</v>
@@ -6999,7 +7021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A440" s="8"/>
       <c r="B440" s="8" t="s">
         <v>229</v>
@@ -7011,7 +7033,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A441" s="8"/>
       <c r="B441" s="8" t="s">
         <v>129</v>
@@ -7023,7 +7045,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A442" s="8"/>
       <c r="B442" s="8"/>
       <c r="C442" s="8"/>
@@ -7036,7 +7058,7 @@
       </c>
       <c r="F442" s="8"/>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E443">
         <f>SUM(E433:E442)</f>
         <v>0</v>
@@ -7046,7 +7068,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A444" s="8" t="s">
         <v>130</v>
       </c>
@@ -7060,7 +7082,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A445" s="8"/>
       <c r="B445" s="8" t="s">
         <v>132</v>
@@ -7072,7 +7094,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A446" s="8"/>
       <c r="B446" s="8" t="s">
         <v>7</v>
@@ -7084,7 +7106,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A447" s="8"/>
       <c r="B447" s="8" t="s">
         <v>133</v>
@@ -7096,7 +7118,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A448" s="8"/>
       <c r="B448" s="8" t="s">
         <v>134</v>
@@ -7108,7 +7130,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A449" s="8"/>
       <c r="B449" s="8" t="s">
         <v>135</v>
@@ -7120,7 +7142,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A450" s="8"/>
       <c r="B450" s="8" t="s">
         <v>136</v>
@@ -7132,7 +7154,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A451" s="8"/>
       <c r="B451" s="8"/>
       <c r="C451" s="8"/>
@@ -7145,7 +7167,7 @@
       </c>
       <c r="F451" s="8"/>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E452">
         <f>SUM(E444:E451)</f>
         <v>0</v>
@@ -7155,7 +7177,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A453" s="7" t="s">
         <v>312</v>
       </c>
@@ -7171,7 +7193,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A454" s="7"/>
       <c r="B454" s="7"/>
       <c r="C454" s="8"/>
@@ -7183,7 +7205,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A455" s="7"/>
       <c r="B455" s="7"/>
       <c r="C455" s="8"/>
@@ -7195,7 +7217,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A456" s="7"/>
       <c r="B456" s="7"/>
       <c r="C456" s="8" t="s">
@@ -7209,7 +7231,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A457" s="7"/>
       <c r="B457" s="7"/>
       <c r="C457" s="8"/>
@@ -7221,7 +7243,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A458" s="7"/>
       <c r="B458" s="7"/>
       <c r="C458" s="8"/>
@@ -7233,7 +7255,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A459" s="7"/>
       <c r="B459" s="7"/>
       <c r="C459" s="8"/>
@@ -7245,7 +7267,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A460" s="7"/>
       <c r="B460" s="7"/>
       <c r="C460" s="8"/>
@@ -7257,7 +7279,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E461">
         <f>SUM(E453:E460)</f>
         <v>0</v>
@@ -7267,12 +7289,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="462" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A462" s="5" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A463" s="7" t="s">
         <v>235</v>
       </c>
@@ -7288,7 +7310,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A464" s="7"/>
       <c r="B464" s="8"/>
       <c r="C464" s="8" t="s">
@@ -7300,7 +7322,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A465" s="8"/>
       <c r="B465" s="7" t="s">
         <v>236</v>
@@ -7314,7 +7336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A466" s="8"/>
       <c r="B466" s="8"/>
       <c r="C466" s="8" t="s">
@@ -7326,7 +7348,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A467" s="8"/>
       <c r="B467" s="8"/>
       <c r="C467" s="8" t="s">
@@ -7338,7 +7360,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A468" s="8"/>
       <c r="B468" s="8"/>
       <c r="C468" s="8" t="s">
@@ -7350,7 +7372,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A469" s="8"/>
       <c r="B469" s="8"/>
       <c r="C469" s="8" t="s">
@@ -7362,7 +7384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A470" s="8"/>
       <c r="B470" s="8"/>
       <c r="C470" s="8"/>
@@ -7374,7 +7396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E471">
         <f>SUM(E463:E470)</f>
         <v>0</v>
@@ -7384,12 +7406,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A472" s="1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A473" s="14" t="s">
         <v>330</v>
       </c>
@@ -7405,7 +7427,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A474" s="14" t="s">
         <v>332</v>
       </c>
@@ -7423,7 +7445,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A475" s="14"/>
       <c r="B475" s="12"/>
       <c r="C475" s="12" t="s">
@@ -7437,7 +7459,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A476" s="1"/>
       <c r="D476" s="20" t="s">
         <v>206</v>
@@ -7447,7 +7469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.45">
       <c r="E477">
         <f>SUM(E473:E476)</f>
         <v>0</v>
@@ -7457,12 +7479,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="479" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A479" s="5" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A480" s="14" t="s">
         <v>235</v>
       </c>
@@ -7476,7 +7498,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A481" s="14" t="s">
         <v>240</v>
       </c>
@@ -7490,7 +7512,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A482" s="12"/>
       <c r="B482" s="12" t="s">
         <v>238</v>
@@ -7502,7 +7524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A483" s="12"/>
       <c r="B483" s="12" t="s">
         <v>237</v>
@@ -7514,7 +7536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A484" s="12"/>
       <c r="B484" s="12" t="s">
         <v>239</v>
@@ -7526,7 +7548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A485" s="12"/>
       <c r="B485" s="12" t="s">
         <v>241</v>
@@ -7538,7 +7560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A486" s="12"/>
       <c r="B486" s="12" t="s">
         <v>242</v>
@@ -7550,7 +7572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A487" s="12"/>
       <c r="B487" s="12" t="s">
         <v>25</v>
@@ -7562,7 +7584,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A488" s="12"/>
       <c r="B488" s="12" t="s">
         <v>26</v>
@@ -7574,7 +7596,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A489" s="12"/>
       <c r="B489" s="12" t="s">
         <v>243</v>
@@ -7586,7 +7608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A490" s="12"/>
       <c r="B490" s="12" t="s">
         <v>244</v>
@@ -7598,7 +7620,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A491" s="12"/>
       <c r="B491" s="12"/>
       <c r="C491" s="12"/>
@@ -7610,7 +7632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.45">
       <c r="E492">
         <f>SUM(E480:E491)</f>
         <v>0</v>
@@ -7620,7 +7642,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A494" s="9" t="s">
         <v>235</v>
       </c>
@@ -7629,13 +7651,15 @@
       </c>
       <c r="C494" s="10"/>
       <c r="D494" s="10"/>
-      <c r="E494" s="10"/>
+      <c r="E494" s="10">
+        <v>10</v>
+      </c>
       <c r="F494" s="10">
         <v>10</v>
       </c>
       <c r="H494" s="18"/>
     </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A495" s="9" t="s">
         <v>240</v>
       </c>
@@ -7644,123 +7668,148 @@
       </c>
       <c r="C495" s="10"/>
       <c r="D495" s="10"/>
-      <c r="E495" s="10"/>
+      <c r="E495" s="10">
+        <v>5</v>
+      </c>
       <c r="F495" s="10">
         <v>5</v>
       </c>
       <c r="H495" s="18"/>
     </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A496" s="10"/>
+    <row r="496" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A496" s="10" t="s">
+        <v>387</v>
+      </c>
       <c r="B496" s="10" t="s">
         <v>238</v>
       </c>
       <c r="C496" s="10"/>
       <c r="D496" s="10"/>
-      <c r="E496" s="10"/>
+      <c r="E496" s="10">
+        <v>0</v>
+      </c>
       <c r="F496" s="10">
         <v>5</v>
       </c>
       <c r="H496" s="18"/>
     </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A497" s="10"/>
       <c r="B497" s="10" t="s">
         <v>237</v>
       </c>
       <c r="C497" s="10"/>
       <c r="D497" s="10"/>
-      <c r="E497" s="10"/>
+      <c r="E497" s="10">
+        <v>4</v>
+      </c>
       <c r="F497" s="10">
         <v>5</v>
       </c>
       <c r="H497" s="18"/>
     </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A498" s="10"/>
       <c r="B498" s="10" t="s">
         <v>239</v>
       </c>
       <c r="C498" s="10"/>
       <c r="D498" s="10"/>
-      <c r="E498" s="10"/>
+      <c r="E498" s="10">
+        <v>0</v>
+      </c>
       <c r="F498" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A499" s="10"/>
       <c r="B499" s="10" t="s">
         <v>241</v>
       </c>
       <c r="C499" s="10"/>
       <c r="D499" s="10"/>
-      <c r="E499" s="10"/>
+      <c r="E499" s="10">
+        <v>3</v>
+      </c>
       <c r="F499" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A500" s="10"/>
       <c r="B500" s="10" t="s">
         <v>242</v>
       </c>
       <c r="C500" s="10"/>
       <c r="D500" s="10"/>
-      <c r="E500" s="10"/>
+      <c r="E500" s="10">
+        <v>0</v>
+      </c>
       <c r="F500" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A501" s="10"/>
       <c r="B501" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C501" s="10"/>
       <c r="D501" s="10"/>
-      <c r="E501" s="10"/>
+      <c r="E501" s="10">
+        <v>3</v>
+      </c>
       <c r="F501" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A502" s="10"/>
       <c r="B502" s="10" t="s">
         <v>26</v>
       </c>
       <c r="C502" s="10"/>
       <c r="D502" s="10"/>
-      <c r="E502" s="10"/>
+      <c r="E502" s="10">
+        <v>3</v>
+      </c>
       <c r="F502" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A503" s="10"/>
       <c r="B503" s="10" t="s">
         <v>243</v>
       </c>
       <c r="C503" s="10"/>
       <c r="D503" s="10"/>
-      <c r="E503" s="10"/>
+      <c r="E503" s="10">
+        <v>0</v>
+      </c>
       <c r="F503" s="10">
         <v>5</v>
       </c>
-    </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H503" s="30" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="504" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A504" s="10"/>
       <c r="B504" s="10" t="s">
         <v>244</v>
       </c>
       <c r="C504" s="10"/>
       <c r="D504" s="10"/>
-      <c r="E504" s="10"/>
+      <c r="E504" s="10">
+        <v>5</v>
+      </c>
       <c r="F504" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A505" s="10"/>
       <c r="B505" s="10"/>
       <c r="C505" s="10"/>
@@ -7768,21 +7817,30 @@
         <v>206</v>
       </c>
       <c r="E505" s="20">
-        <f>-SUM(E498:E504)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
+        <f>-SUM(E494:E504)*0.5</f>
+        <v>-16.5</v>
+      </c>
+      <c r="G505" t="s">
+        <v>215</v>
+      </c>
+      <c r="H505" t="s">
+        <v>389</v>
+      </c>
+      <c r="K505" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="506" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E506">
         <f>SUM(E494:E505)</f>
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="F506">
         <f>SUM(F494:F505)</f>
         <v>60</v>
       </c>
     </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A508" s="13" t="s">
         <v>235</v>
       </c>
@@ -7798,7 +7856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A509" s="13" t="s">
         <v>240</v>
       </c>
@@ -7817,7 +7875,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A510" s="11" t="s">
         <v>380</v>
       </c>
@@ -7833,7 +7891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A511" s="11"/>
       <c r="B511" s="11" t="s">
         <v>237</v>
@@ -7850,7 +7908,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A512" s="11"/>
       <c r="B512" s="11" t="s">
         <v>239</v>
@@ -7864,7 +7922,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="513" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A513" s="11"/>
       <c r="B513" s="11" t="s">
         <v>241</v>
@@ -7881,7 +7939,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="514" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A514" s="11"/>
       <c r="B514" s="11" t="s">
         <v>242</v>
@@ -7895,7 +7953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="515" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A515" s="11"/>
       <c r="B515" s="11" t="s">
         <v>25</v>
@@ -7912,7 +7970,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="516" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A516" s="11"/>
       <c r="B516" s="11" t="s">
         <v>26</v>
@@ -7929,7 +7987,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="517" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A517" s="11"/>
       <c r="B517" s="11" t="s">
         <v>243</v>
@@ -7946,7 +8004,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="518" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A518" s="11"/>
       <c r="B518" s="11" t="s">
         <v>244</v>
@@ -7960,7 +8018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="519" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A519" s="11"/>
       <c r="B519" s="11"/>
       <c r="C519" s="11"/>
@@ -7979,7 +8037,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="520" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:10" x14ac:dyDescent="0.45">
       <c r="E520">
         <f>SUM(E508:E519)</f>
         <v>24.5</v>
@@ -7989,7 +8047,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="524" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A524" s="7"/>
       <c r="B524" t="s">
         <v>183</v>
@@ -8007,7 +8065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A525" s="9" t="s">
         <v>364</v>
       </c>
@@ -8016,7 +8074,7 @@
       </c>
       <c r="E525">
         <f>E76+E30+E31+E109+E148+E174+E371+E196+E204+E239+E286+E420+E506+E321</f>
-        <v>-200</v>
+        <v>-183.5</v>
       </c>
       <c r="F525">
         <f>F76+F30+F31+F109+F148+F174+F371+F196+F204+F226+F239+F286+F420+F506+F321</f>
@@ -8024,10 +8082,10 @@
       </c>
       <c r="H525" s="18">
         <f>(E525+E524)/(F525+F524)</f>
-        <v>-0.12820512820512819</v>
-      </c>
-    </row>
-    <row r="526" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.11762820512820513</v>
+      </c>
+    </row>
+    <row r="526" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A526" s="13" t="s">
         <v>365</v>
       </c>
@@ -8047,7 +8105,7 @@
         <v>-0.15462555066079295</v>
       </c>
     </row>
-    <row r="527" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A527" s="14" t="s">
         <v>363</v>
       </c>
@@ -8067,7 +8125,7 @@
         <v>-0.17699115044247787</v>
       </c>
     </row>
-    <row r="531" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="531" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F531" t="s">
         <v>230</v>
       </c>
@@ -8075,7 +8133,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="532" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="532" spans="4:7" x14ac:dyDescent="0.45">
       <c r="D532" t="s">
         <v>232</v>
       </c>
@@ -8083,7 +8141,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="533" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="533" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F533" s="23">
         <v>0.45</v>
       </c>
@@ -8091,7 +8149,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="534" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="534" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F534" s="23">
         <f>F533+(F542-F533)/9</f>
         <v>0.5</v>
@@ -8100,7 +8158,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="535" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="535" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F535" s="23">
         <f>F534+(F542-F533)/9</f>
         <v>0.55000000000000004</v>
@@ -8109,7 +8167,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="536" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="536" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F536" s="23">
         <f>F535+(F542-F533)/9</f>
         <v>0.60000000000000009</v>
@@ -8118,7 +8176,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="537" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="537" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F537" s="23">
         <f>F536+(F542-F533)/9</f>
         <v>0.65000000000000013</v>
@@ -8127,7 +8185,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="538" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="538" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F538" s="23">
         <f>F537+(F542-F533)/9</f>
         <v>0.70000000000000018</v>
@@ -8136,7 +8194,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="539" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="539" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F539" s="23">
         <f>F538+(F542-F533)/9</f>
         <v>0.75000000000000022</v>
@@ -8145,7 +8203,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="540" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="540" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F540" s="23">
         <f>F539+(F542-F533)/9</f>
         <v>0.80000000000000027</v>
@@ -8154,7 +8212,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="541" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="541" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F541" s="23">
         <f>F540+(F542-F533)/9</f>
         <v>0.85000000000000031</v>
@@ -8163,7 +8221,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="542" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="542" spans="4:7" x14ac:dyDescent="0.45">
       <c r="F542" s="23">
         <v>0.9</v>
       </c>
@@ -8171,7 +8229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="543" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="543" spans="4:7" x14ac:dyDescent="0.45">
       <c r="E543" t="s">
         <v>234</v>
       </c>
@@ -8184,28 +8242,31 @@
     <mergeCell ref="G189:G204"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B21" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B14" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B21"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B14">
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H503" r:id="rId1" display="https://www.naftaliharris.com/blog/visualizing-k-means-clustering/"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="19"/>
+    <col min="2" max="2" width="35.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.86328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.3984375" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="25.5" x14ac:dyDescent="0.75">
       <c r="A1" s="29" t="s">
         <v>223</v>
       </c>
@@ -8213,10 +8274,10 @@
       <c r="C1" s="29"/>
       <c r="D1" s="29"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>207</v>
       </c>
@@ -8224,7 +8285,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>38</v>
       </c>
@@ -8232,7 +8293,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>209</v>
       </c>
@@ -8240,7 +8301,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>210</v>
       </c>
@@ -8248,7 +8309,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>211</v>
       </c>
@@ -8256,7 +8317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>212</v>
       </c>
@@ -8264,7 +8325,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>174</v>
       </c>
@@ -8272,7 +8333,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>208</v>
       </c>
@@ -8280,7 +8341,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>214</v>
       </c>
@@ -8288,7 +8349,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>213</v>
       </c>
@@ -8296,7 +8357,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>215</v>
       </c>
@@ -8304,7 +8365,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>216</v>
       </c>
@@ -8312,7 +8373,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>222</v>
       </c>
@@ -8320,7 +8381,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
         <v>224</v>
       </c>
@@ -8328,7 +8389,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
         <v>225</v>
       </c>
@@ -8336,7 +8397,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -8350,7 +8411,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C23" t="s">
         <v>143</v>
       </c>
@@ -8358,7 +8419,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C24" t="s">
         <v>144</v>
       </c>
@@ -8366,7 +8427,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
         <v>145</v>
       </c>
@@ -8377,7 +8438,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C26" t="s">
         <v>147</v>
       </c>
@@ -8385,7 +8446,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C27" t="s">
         <v>148</v>
       </c>
@@ -8393,7 +8454,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C28" t="s">
         <v>149</v>
       </c>
@@ -8401,12 +8462,12 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
         <v>162</v>
       </c>
@@ -8417,7 +8478,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C32" t="s">
         <v>166</v>
       </c>
@@ -8425,7 +8486,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C33" t="s">
         <v>148</v>
       </c>
@@ -8433,7 +8494,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
         <v>220</v>
       </c>
@@ -8441,7 +8502,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
         <v>167</v>
       </c>
@@ -8452,7 +8513,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C36" t="s">
         <v>169</v>
       </c>
@@ -8460,7 +8521,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C37" t="s">
         <v>170</v>
       </c>

--- a/ProjectManagement/EvaluationHW.xlsx
+++ b/ProjectManagement/EvaluationHW.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Wings-Hub\ML24\ML24-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\Winter 2024-25\ML project\ML24-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14FFAB34-2F15-44C0-99B8-E51D23FF77A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="2" r:id="rId1"/>
     <sheet name="Formalities" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,12 +26,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Elmar Wings</author>
   </authors>
   <commentList>
-    <comment ref="K359" authorId="0" shapeId="0">
+    <comment ref="K359" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -67,12 +68,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Elmar Wings</author>
   </authors>
   <commentList>
-    <comment ref="B14" authorId="0" shapeId="0">
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -99,7 +100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B15" authorId="0" shapeId="0">
+    <comment ref="B15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -127,7 +128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B34" authorId="0" shapeId="0">
+    <comment ref="B34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
@@ -164,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="392">
   <si>
     <t>Literature</t>
   </si>
@@ -1337,12 +1338,15 @@
   </si>
   <si>
     <t>no summary</t>
+  </si>
+  <si>
+    <t>Logitech C270 HD Webcam</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
@@ -1573,6 +1577,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1588,11 +1593,10 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Link" xfId="1" builtinId="8"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1869,42 +1873,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M543"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.73046875" customWidth="1"/>
-    <col min="2" max="2" width="28.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.77734375" customWidth="1"/>
+    <col min="2" max="2" width="28.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="33.4" x14ac:dyDescent="1">
+    <row r="2" spans="1:6" ht="33.6" x14ac:dyDescent="0.65">
       <c r="A2" s="22" t="s">
         <v>367</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" s="25" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="26" t="s">
         <v>372</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-    </row>
-    <row r="9" spans="1:6" ht="28.5" x14ac:dyDescent="0.85">
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+    </row>
+    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>71</v>
       </c>
@@ -1921,7 +1925,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>369</v>
       </c>
@@ -1938,7 +1942,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>373</v>
       </c>
@@ -1952,7 +1956,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>375</v>
       </c>
@@ -1966,7 +1970,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>75</v>
       </c>
@@ -1974,7 +1978,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>76</v>
       </c>
@@ -1982,7 +1986,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>77</v>
       </c>
@@ -1990,7 +1994,7 @@
         <v>45565</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>78</v>
       </c>
@@ -1998,7 +2002,7 @@
         <v>45688</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>79</v>
       </c>
@@ -2006,7 +2010,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>80</v>
       </c>
@@ -2014,12 +2018,12 @@
         <v>189</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="25" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A25" s="6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>82</v>
       </c>
@@ -2027,7 +2031,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
       <c r="B28" s="11" t="s">
         <v>138</v>
@@ -2044,7 +2048,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="12"/>
       <c r="B29" s="12" t="s">
         <v>138</v>
@@ -2061,7 +2065,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
         <v>138</v>
@@ -2078,7 +2082,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="10"/>
       <c r="B31" s="10" t="s">
         <v>139</v>
@@ -2095,7 +2099,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="12"/>
       <c r="B32" s="12" t="s">
         <v>139</v>
@@ -2112,7 +2116,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="11"/>
       <c r="B33" s="11" t="s">
         <v>139</v>
@@ -2129,12 +2133,12 @@
         <v>336</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>0</v>
       </c>
@@ -2148,7 +2152,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>
       <c r="B37" s="11" t="s">
         <v>27</v>
@@ -2160,7 +2164,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="11"/>
       <c r="B38" s="11" t="s">
         <v>3</v>
@@ -2172,7 +2176,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="11"/>
       <c r="B39" s="11" t="s">
         <v>4</v>
@@ -2184,7 +2188,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="11"/>
       <c r="B40" s="11" t="s">
         <v>5</v>
@@ -2196,7 +2200,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="11"/>
       <c r="B41" s="11" t="s">
         <v>337</v>
@@ -2208,7 +2212,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>
       <c r="B42" s="11" t="s">
         <v>1</v>
@@ -2222,7 +2226,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>
       <c r="B43" s="11"/>
       <c r="C43" s="11" t="s">
@@ -2234,7 +2238,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="11"/>
       <c r="B44" s="11"/>
       <c r="C44" s="11" t="s">
@@ -2246,7 +2250,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="11"/>
       <c r="B45" s="11"/>
       <c r="C45" s="11" t="s">
@@ -2258,7 +2262,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="11"/>
       <c r="B46" s="11"/>
       <c r="C46" s="11" t="s">
@@ -2270,7 +2274,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="11"/>
       <c r="B47" s="11"/>
       <c r="C47" s="11" t="s">
@@ -2282,7 +2286,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="11"/>
       <c r="B48" s="11"/>
       <c r="C48" s="11" t="s">
@@ -2294,7 +2298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="11"/>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
@@ -2307,7 +2311,7 @@
       </c>
       <c r="F49" s="11"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="11"/>
       <c r="E50">
         <f>SUM(E36:E49)</f>
@@ -2318,14 +2322,14 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:12" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:12" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>339</v>
       </c>
       <c r="K52"/>
       <c r="L52"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
         <v>111</v>
       </c>
@@ -2340,11 +2344,11 @@
       <c r="F53" s="12">
         <v>10</v>
       </c>
-      <c r="G53" s="26" t="s">
+      <c r="G53" s="27" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="14"/>
       <c r="B54" s="14" t="s">
         <v>236</v>
@@ -2357,9 +2361,9 @@
       <c r="F54" s="12">
         <v>5</v>
       </c>
-      <c r="G54" s="26"/>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G54" s="27"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="14"/>
       <c r="B55" s="14"/>
       <c r="C55" s="12" t="s">
@@ -2370,9 +2374,9 @@
       <c r="F55" s="12">
         <v>5</v>
       </c>
-      <c r="G55" s="26"/>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G55" s="27"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="14"/>
       <c r="B56" s="12"/>
       <c r="C56" s="12" t="s">
@@ -2383,9 +2387,9 @@
       <c r="F56" s="12">
         <v>5</v>
       </c>
-      <c r="G56" s="26"/>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G56" s="27"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="14"/>
       <c r="B57" s="14"/>
       <c r="C57" s="12" t="s">
@@ -2396,9 +2400,9 @@
       <c r="F57" s="12">
         <v>10</v>
       </c>
-      <c r="G57" s="26"/>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G57" s="27"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="14"/>
       <c r="B58" s="14"/>
       <c r="C58" s="12" t="s">
@@ -2409,9 +2413,9 @@
       <c r="F58" s="12">
         <v>5</v>
       </c>
-      <c r="G58" s="26"/>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G58" s="27"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="14"/>
       <c r="B59" s="14"/>
       <c r="C59" s="12" t="s">
@@ -2422,9 +2426,9 @@
       <c r="F59" s="12">
         <v>15</v>
       </c>
-      <c r="G59" s="26"/>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G59" s="27"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="14"/>
       <c r="B60" s="14"/>
       <c r="C60" s="12" t="s">
@@ -2435,9 +2439,9 @@
       <c r="F60" s="12">
         <v>5</v>
       </c>
-      <c r="G60" s="26"/>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G60" s="27"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="14"/>
       <c r="B61" s="14"/>
       <c r="C61" s="12" t="s">
@@ -2448,9 +2452,9 @@
       <c r="F61" s="12">
         <v>10</v>
       </c>
-      <c r="G61" s="26"/>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G61" s="27"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="14"/>
       <c r="B62" s="14"/>
       <c r="C62" s="12" t="s">
@@ -2461,9 +2465,9 @@
       <c r="F62" s="12">
         <v>5</v>
       </c>
-      <c r="G62" s="26"/>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G62" s="27"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="14"/>
       <c r="B63" s="14" t="s">
         <v>223</v>
@@ -2476,9 +2480,9 @@
       <c r="F63" s="12">
         <v>5</v>
       </c>
-      <c r="G63" s="26"/>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G63" s="27"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="14"/>
       <c r="B64" s="14"/>
       <c r="C64" s="12" t="s">
@@ -2489,9 +2493,9 @@
       <c r="F64" s="12">
         <v>20</v>
       </c>
-      <c r="G64" s="26"/>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="G64" s="27"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="14"/>
       <c r="B65" s="14"/>
       <c r="C65" s="12" t="s">
@@ -2502,9 +2506,9 @@
       <c r="F65" s="12">
         <v>10</v>
       </c>
-      <c r="G65" s="26"/>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="G65" s="27"/>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="14"/>
       <c r="B66" s="14"/>
       <c r="C66" s="12"/>
@@ -2516,9 +2520,9 @@
         <v>0</v>
       </c>
       <c r="F66" s="12"/>
-      <c r="G66" s="26"/>
-    </row>
-    <row r="67" spans="1:13" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="G66" s="27"/>
+    </row>
+    <row r="67" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="E67">
@@ -2532,14 +2536,14 @@
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
     </row>
-    <row r="68" spans="1:13" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:13" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
         <v>340</v>
       </c>
       <c r="K68"/>
       <c r="L68"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="str">
         <f>$A$68</f>
         <v>Document Manufacturing and Assembly</v>
@@ -2556,7 +2560,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="9"/>
       <c r="B70" s="9" t="s">
         <v>236</v>
@@ -2570,7 +2574,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="9"/>
       <c r="B71" s="9"/>
       <c r="C71" s="10" t="s">
@@ -2582,7 +2586,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="9"/>
       <c r="B72" s="9"/>
       <c r="C72" s="10" t="s">
@@ -2594,7 +2598,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="9"/>
       <c r="B73" s="9"/>
       <c r="C73" s="10" t="s">
@@ -2606,7 +2610,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="9"/>
       <c r="B74" s="9"/>
       <c r="C74" s="10" t="s">
@@ -2618,7 +2622,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="9"/>
       <c r="B75" s="9"/>
       <c r="C75" s="10"/>
@@ -2631,7 +2635,7 @@
       </c>
       <c r="F75" s="10"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="E76">
@@ -2643,15 +2647,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
     </row>
-    <row r="78" spans="1:13" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="13" t="s">
         <v>283</v>
       </c>
@@ -2667,7 +2671,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="13"/>
       <c r="B80" s="11"/>
       <c r="C80" s="11" t="s">
@@ -2679,7 +2683,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="13"/>
       <c r="B81" s="11"/>
       <c r="C81" s="11" t="s">
@@ -2691,7 +2695,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="13"/>
       <c r="B82" s="13" t="s">
         <v>236</v>
@@ -2705,7 +2709,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="13"/>
       <c r="B83" s="13"/>
       <c r="C83" s="11" t="s">
@@ -2717,7 +2721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="13"/>
       <c r="B84" s="13"/>
       <c r="C84" s="11" t="s">
@@ -2729,7 +2733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="13"/>
       <c r="B85" s="13"/>
       <c r="C85" s="11" t="s">
@@ -2741,7 +2745,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="13"/>
       <c r="B86" s="13"/>
       <c r="C86" s="13"/>
@@ -2754,7 +2758,7 @@
       </c>
       <c r="F86" s="13"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="E87">
@@ -2766,18 +2770,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="89" spans="1:6" ht="21" x14ac:dyDescent="0.65">
+    <row r="88" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="1:6" ht="21" x14ac:dyDescent="0.4">
       <c r="A89" s="21" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="14" t="s">
         <v>6</v>
       </c>
@@ -2791,7 +2795,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="12"/>
       <c r="B92" s="12"/>
       <c r="C92" s="12" t="s">
@@ -2803,7 +2807,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="12"/>
       <c r="B93" s="12"/>
       <c r="C93" s="12" t="s">
@@ -2815,7 +2819,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="12"/>
       <c r="B94" s="12"/>
       <c r="C94" s="12" t="s">
@@ -2827,7 +2831,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="12"/>
       <c r="B95" s="12"/>
       <c r="C95" s="12" t="s">
@@ -2839,7 +2843,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="12"/>
       <c r="B96" s="12"/>
       <c r="C96" s="12" t="s">
@@ -2851,7 +2855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="12"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
@@ -2864,7 +2868,7 @@
       </c>
       <c r="F97" s="12"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E98">
         <f>SUM(E91:E97)</f>
         <v>0</v>
@@ -2874,12 +2878,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="9" t="s">
         <v>273</v>
       </c>
@@ -2893,7 +2897,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="9"/>
       <c r="B101" s="10" t="s">
         <v>13</v>
@@ -2905,7 +2909,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="10"/>
       <c r="B102" s="10" t="s">
         <v>14</v>
@@ -2917,7 +2921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="10"/>
       <c r="B103" s="10" t="s">
         <v>15</v>
@@ -2929,7 +2933,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="10"/>
       <c r="B104" s="10" t="s">
         <v>16</v>
@@ -2941,7 +2945,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="10"/>
       <c r="B105" s="10" t="s">
         <v>17</v>
@@ -2953,7 +2957,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="10"/>
       <c r="B106" s="10" t="s">
         <v>19</v>
@@ -2965,7 +2969,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="10"/>
       <c r="B107" s="16" t="s">
         <v>18</v>
@@ -2977,7 +2981,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="10"/>
       <c r="B108" s="16"/>
       <c r="C108" s="10"/>
@@ -2989,7 +2993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E109">
         <f>SUM(E100:E108)</f>
         <v>0</v>
@@ -2999,7 +3003,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="13" t="s">
         <v>299</v>
       </c>
@@ -3018,11 +3022,11 @@
       <c r="F113" s="11">
         <v>20</v>
       </c>
-      <c r="G113" s="27" t="s">
+      <c r="G113" s="28" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="13" t="s">
         <v>295</v>
       </c>
@@ -3037,9 +3041,9 @@
       <c r="F114" s="11">
         <v>10</v>
       </c>
-      <c r="G114" s="27"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G114" s="28"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="11"/>
       <c r="B115" s="11"/>
       <c r="C115" s="11" t="s">
@@ -3052,9 +3056,9 @@
       <c r="F115" s="11">
         <v>10</v>
       </c>
-      <c r="G115" s="27"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G115" s="28"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="11"/>
       <c r="B116" s="11"/>
       <c r="C116" s="11" t="s">
@@ -3067,9 +3071,9 @@
       <c r="F116" s="11">
         <v>10</v>
       </c>
-      <c r="G116" s="27"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G116" s="28"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="13"/>
       <c r="B117" s="11"/>
       <c r="C117" s="11" t="s">
@@ -3082,9 +3086,9 @@
       <c r="F117" s="11">
         <v>10</v>
       </c>
-      <c r="G117" s="27"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G117" s="28"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="11"/>
       <c r="B118" s="11"/>
       <c r="C118" s="11" t="s">
@@ -3099,9 +3103,9 @@
       <c r="F118" s="11">
         <v>10</v>
       </c>
-      <c r="G118" s="27"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G118" s="28"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="11"/>
       <c r="B119" s="11"/>
       <c r="C119" s="11"/>
@@ -3114,9 +3118,9 @@
       <c r="F119" s="11">
         <v>10</v>
       </c>
-      <c r="G119" s="27"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G119" s="28"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="13"/>
       <c r="B120" s="11"/>
       <c r="C120" s="11"/>
@@ -3129,9 +3133,9 @@
       <c r="F120" s="11">
         <v>10</v>
       </c>
-      <c r="G120" s="27"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G120" s="28"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="13"/>
       <c r="B121" s="11"/>
       <c r="C121" s="11"/>
@@ -3144,9 +3148,9 @@
       <c r="F121" s="11">
         <v>10</v>
       </c>
-      <c r="G121" s="27"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G121" s="28"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="13"/>
       <c r="B122" s="11"/>
       <c r="C122" s="11" t="s">
@@ -3159,9 +3163,9 @@
       <c r="F122" s="11">
         <v>20</v>
       </c>
-      <c r="G122" s="27"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G122" s="28"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="11"/>
       <c r="B123" s="11"/>
       <c r="C123" s="11"/>
@@ -3172,9 +3176,9 @@
         <f>-SUM(E113:E122)</f>
         <v>0</v>
       </c>
-      <c r="G123" s="27"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G123" s="28"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E124">
         <f>SUM(E117:E123)</f>
         <v>0</v>
@@ -3183,12 +3187,12 @@
         <f>SUM(F113:F122)</f>
         <v>120</v>
       </c>
-      <c r="G124" s="27"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="G125" s="27"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G124" s="28"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G125" s="28"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="14" t="s">
         <v>298</v>
       </c>
@@ -3205,9 +3209,9 @@
       <c r="F126" s="12">
         <v>10</v>
       </c>
-      <c r="G126" s="27"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G126" s="28"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="14" t="s">
         <v>352</v>
       </c>
@@ -3220,9 +3224,9 @@
       <c r="F127" s="12">
         <v>7</v>
       </c>
-      <c r="G127" s="27"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G127" s="28"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="14"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12" t="s">
@@ -3233,9 +3237,9 @@
       <c r="F128" s="12">
         <v>10</v>
       </c>
-      <c r="G128" s="27"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G128" s="28"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="14"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12" t="s">
@@ -3248,9 +3252,9 @@
       <c r="F129" s="12">
         <v>10</v>
       </c>
-      <c r="G129" s="27"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G129" s="28"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12" t="s">
@@ -3263,9 +3267,9 @@
       <c r="F130" s="12">
         <v>10</v>
       </c>
-      <c r="G130" s="27"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G130" s="28"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="12"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12" t="s">
@@ -3278,9 +3282,9 @@
       <c r="F131" s="12">
         <v>8</v>
       </c>
-      <c r="G131" s="27"/>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G131" s="28"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="12"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12" t="s">
@@ -3293,9 +3297,9 @@
       <c r="F132" s="12">
         <v>8</v>
       </c>
-      <c r="G132" s="27"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G132" s="28"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12" t="s">
@@ -3306,9 +3310,9 @@
       <c r="F133" s="12">
         <v>7</v>
       </c>
-      <c r="G133" s="27"/>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G133" s="28"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12" t="s">
@@ -3321,9 +3325,9 @@
       <c r="F134" s="12">
         <v>5</v>
       </c>
-      <c r="G134" s="27"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G134" s="28"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="12"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
@@ -3334,9 +3338,9 @@
         <f>-SUM(E126:E134)</f>
         <v>0</v>
       </c>
-      <c r="G135" s="27"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G135" s="28"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E136">
         <f>SUM(E126:E135)</f>
         <v>0</v>
@@ -3345,12 +3349,12 @@
         <f>SUM(F126:F134)</f>
         <v>75</v>
       </c>
-      <c r="G136" s="27"/>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="G137" s="27"/>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G136" s="28"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G137" s="28"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="9" t="s">
         <v>351</v>
       </c>
@@ -3369,9 +3373,9 @@
         <f t="shared" ref="F138:F146" si="1">F126</f>
         <v>10</v>
       </c>
-      <c r="G138" s="27"/>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G138" s="28"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="10" t="str">
         <f>$A$127</f>
         <v>e.g. camera, IMU, SPI</v>
@@ -3389,9 +3393,9 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="G139" s="27"/>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G139" s="28"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="10"/>
       <c r="B140" s="10"/>
       <c r="C140" s="10" t="str">
@@ -3406,9 +3410,9 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G140" s="27"/>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G140" s="28"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="9"/>
       <c r="B141" s="10"/>
       <c r="C141" s="10" t="str">
@@ -3423,9 +3427,9 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G141" s="27"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G141" s="28"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="9"/>
       <c r="B142" s="10"/>
       <c r="C142" s="10" t="str">
@@ -3440,9 +3444,9 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="G142" s="27"/>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G142" s="28"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="9"/>
       <c r="B143" s="10"/>
       <c r="C143" s="10" t="str">
@@ -3455,9 +3459,9 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G143" s="27"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G143" s="28"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="9"/>
       <c r="B144" s="10"/>
       <c r="C144" s="10" t="str">
@@ -3472,9 +3476,9 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G144" s="27"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G144" s="28"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="10"/>
       <c r="B145" s="10"/>
       <c r="C145" s="10" t="str">
@@ -3489,9 +3493,9 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="G145" s="27"/>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G145" s="28"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="10"/>
       <c r="B146" s="10"/>
       <c r="C146" s="10" t="str">
@@ -3506,9 +3510,9 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="G146" s="27"/>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G146" s="28"/>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="10"/>
       <c r="B147" s="10"/>
       <c r="C147" s="10"/>
@@ -3519,9 +3523,9 @@
         <f>-SUM(E138:E146)</f>
         <v>0</v>
       </c>
-      <c r="G147" s="27"/>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G147" s="28"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E148">
         <f>SUM(E138:E147)</f>
         <v>0</v>
@@ -3530,9 +3534,9 @@
         <f>SUM(F138:F146)</f>
         <v>75</v>
       </c>
-      <c r="G148" s="27"/>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G148" s="28"/>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="13" t="str">
         <f t="shared" ref="A149:A150" si="2">A138</f>
         <v>domain sensor/actor</v>
@@ -3551,12 +3555,11 @@
         <f t="shared" ref="F149:F157" si="4">F138</f>
         <v>10</v>
       </c>
-      <c r="G149" s="27"/>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A150" s="13" t="str">
-        <f t="shared" si="2"/>
-        <v>e.g. camera, IMU, SPI</v>
+      <c r="G149" s="28"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A150" s="13" t="s">
+        <v>391</v>
       </c>
       <c r="B150" s="13"/>
       <c r="C150" s="11" t="str">
@@ -3569,9 +3572,9 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="G150" s="27"/>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G150" s="28"/>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="13"/>
       <c r="B151" s="13"/>
       <c r="C151" s="11" t="str">
@@ -3584,9 +3587,9 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="G151" s="27"/>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G151" s="28"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="13"/>
       <c r="B152" s="13"/>
       <c r="C152" s="11" t="str">
@@ -3599,9 +3602,9 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="G152" s="27"/>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G152" s="28"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="13"/>
       <c r="B153" s="13"/>
       <c r="C153" s="11" t="str">
@@ -3614,9 +3617,9 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="G153" s="27"/>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G153" s="28"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="13"/>
       <c r="B154" s="13"/>
       <c r="C154" s="11" t="str">
@@ -3629,9 +3632,9 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="G154" s="27"/>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G154" s="28"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="13"/>
       <c r="B155" s="13"/>
       <c r="C155" s="11" t="str">
@@ -3644,9 +3647,9 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="G155" s="27"/>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G155" s="28"/>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="13"/>
       <c r="B156" s="13"/>
       <c r="C156" s="11" t="str">
@@ -3659,9 +3662,9 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="G156" s="27"/>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G156" s="28"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="13"/>
       <c r="B157" s="13"/>
       <c r="C157" s="11" t="str">
@@ -3674,9 +3677,9 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="G157" s="27"/>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G157" s="28"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="13"/>
       <c r="B158" s="13"/>
       <c r="C158" s="11"/>
@@ -3688,9 +3691,9 @@
         <v>0</v>
       </c>
       <c r="F158" s="11"/>
-      <c r="G158" s="27"/>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G158" s="28"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="E159">
@@ -3701,9 +3704,9 @@
         <f>SUM(F149:F157)</f>
         <v>75</v>
       </c>
-      <c r="G159" s="27"/>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G159" s="28"/>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="14" t="s">
         <v>301</v>
       </c>
@@ -3718,9 +3721,9 @@
       <c r="F160" s="12">
         <v>10</v>
       </c>
-      <c r="G160" s="27"/>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G160" s="28"/>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="14" t="s">
         <v>302</v>
       </c>
@@ -3733,9 +3736,9 @@
       <c r="F161" s="12">
         <v>10</v>
       </c>
-      <c r="G161" s="27"/>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G161" s="28"/>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="14"/>
       <c r="B162" s="12"/>
       <c r="C162" s="12" t="s">
@@ -3746,9 +3749,9 @@
       <c r="F162" s="12">
         <v>10</v>
       </c>
-      <c r="G162" s="27"/>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G162" s="28"/>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="14"/>
       <c r="B163" s="12"/>
       <c r="C163" s="12" t="s">
@@ -3759,9 +3762,9 @@
       <c r="F163" s="12">
         <v>10</v>
       </c>
-      <c r="G163" s="27"/>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G163" s="28"/>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="14"/>
       <c r="B164" s="12"/>
       <c r="C164" s="12" t="s">
@@ -3772,9 +3775,9 @@
       <c r="F164" s="12">
         <v>10</v>
       </c>
-      <c r="G164" s="27"/>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G164" s="28"/>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="14"/>
       <c r="B165" s="12"/>
       <c r="C165" s="12" t="s">
@@ -3785,9 +3788,9 @@
       <c r="F165" s="12">
         <v>6</v>
       </c>
-      <c r="G165" s="27"/>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G165" s="28"/>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="14"/>
       <c r="B166" s="12"/>
       <c r="C166" s="12" t="s">
@@ -3798,9 +3801,9 @@
       <c r="F166" s="12">
         <v>6</v>
       </c>
-      <c r="G166" s="27"/>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G166" s="28"/>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="14"/>
       <c r="B167" s="12"/>
       <c r="C167" s="12" t="s">
@@ -3815,9 +3818,9 @@
       <c r="F167" s="12">
         <v>6</v>
       </c>
-      <c r="G167" s="27"/>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G167" s="28"/>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="12"/>
       <c r="B168" s="12"/>
       <c r="C168" s="12"/>
@@ -3830,9 +3833,9 @@
       <c r="F168" s="12">
         <v>6</v>
       </c>
-      <c r="G168" s="27"/>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G168" s="28"/>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="12"/>
       <c r="B169" s="12"/>
       <c r="C169" s="12" t="s">
@@ -3845,9 +3848,9 @@
       <c r="F169" s="12">
         <v>6</v>
       </c>
-      <c r="G169" s="27"/>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G169" s="28"/>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="12"/>
       <c r="B170" s="12"/>
       <c r="C170" s="12" t="s">
@@ -3860,9 +3863,9 @@
       <c r="F170" s="12">
         <v>5</v>
       </c>
-      <c r="G170" s="27"/>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G170" s="28"/>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="12"/>
       <c r="B171" s="12"/>
       <c r="C171" s="12" t="s">
@@ -3875,9 +3878,9 @@
       <c r="F171" s="12">
         <v>5</v>
       </c>
-      <c r="G171" s="27"/>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G171" s="28"/>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="12"/>
       <c r="B172" s="12"/>
       <c r="C172" s="12"/>
@@ -3888,9 +3891,9 @@
         <f>-SUM(E160:E171)</f>
         <v>0</v>
       </c>
-      <c r="G172" s="27"/>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="G172" s="28"/>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E173">
         <f>SUM(E160:E172)</f>
         <v>0</v>
@@ -3899,22 +3902,22 @@
         <f>SUM(F160:F171)</f>
         <v>90</v>
       </c>
-      <c r="G173" s="27"/>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="G174" s="27"/>
-    </row>
-    <row r="175" spans="1:12" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="G173" s="28"/>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="G174" s="28"/>
+    </row>
+    <row r="175" spans="1:12" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A175" s="5" t="s">
         <v>307</v>
       </c>
       <c r="K175"/>
       <c r="L175"/>
     </row>
-    <row r="176" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" s="13" t="s">
         <v>21</v>
       </c>
@@ -3928,7 +3931,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" s="11"/>
       <c r="B178" s="11"/>
       <c r="C178" s="11" t="s">
@@ -3940,7 +3943,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" s="11"/>
       <c r="B179" s="11"/>
       <c r="C179" s="11" t="s">
@@ -3952,7 +3955,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" s="11"/>
       <c r="B180" s="11"/>
       <c r="C180" s="11" t="s">
@@ -3964,7 +3967,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" s="11"/>
       <c r="B181" s="11"/>
       <c r="C181" s="11" t="s">
@@ -3976,7 +3979,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" s="11"/>
       <c r="B182" s="11"/>
       <c r="C182" s="11" t="s">
@@ -3988,7 +3991,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" s="11"/>
       <c r="B183" s="11"/>
       <c r="C183" s="11" t="s">
@@ -4000,7 +4003,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" s="11"/>
       <c r="B184" s="11"/>
       <c r="C184" s="11" t="s">
@@ -4012,7 +4015,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" s="11"/>
       <c r="B185" s="11"/>
       <c r="C185" s="11"/>
@@ -4024,7 +4027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E186">
         <f>SUM(E177:E185)</f>
         <v>0</v>
@@ -4034,12 +4037,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A188" s="5" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" s="9" t="s">
         <v>176</v>
       </c>
@@ -4052,11 +4055,11 @@
       <c r="F189" s="10">
         <v>5</v>
       </c>
-      <c r="G189" s="28" t="s">
+      <c r="G189" s="29" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" s="9" t="s">
         <v>290</v>
       </c>
@@ -4069,9 +4072,9 @@
       <c r="F190" s="10">
         <v>10</v>
       </c>
-      <c r="G190" s="28"/>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G190" s="29"/>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="9"/>
       <c r="B191" s="9"/>
       <c r="C191" s="10" t="s">
@@ -4082,9 +4085,9 @@
       <c r="F191" s="10">
         <v>10</v>
       </c>
-      <c r="G191" s="28"/>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G191" s="29"/>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="9"/>
       <c r="B192" s="9"/>
       <c r="C192" s="10" t="s">
@@ -4095,9 +4098,9 @@
       <c r="F192" s="10">
         <v>5</v>
       </c>
-      <c r="G192" s="28"/>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G192" s="29"/>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" s="9"/>
       <c r="B193" s="9"/>
       <c r="C193" s="10" t="s">
@@ -4108,9 +4111,9 @@
       <c r="F193" s="10">
         <v>5</v>
       </c>
-      <c r="G193" s="28"/>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G193" s="29"/>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" s="9"/>
       <c r="B194" s="9"/>
       <c r="C194" s="10" t="s">
@@ -4121,9 +4124,9 @@
       <c r="F194" s="10">
         <v>5</v>
       </c>
-      <c r="G194" s="28"/>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G194" s="29"/>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" s="9"/>
       <c r="B195" s="9"/>
       <c r="C195" s="10"/>
@@ -4135,9 +4138,9 @@
         <v>0</v>
       </c>
       <c r="F195" s="10"/>
-      <c r="G195" s="28"/>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G195" s="29"/>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="E196">
@@ -4148,9 +4151,9 @@
         <f>SUM(F189:F194)</f>
         <v>40</v>
       </c>
-      <c r="G196" s="28"/>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G196" s="29"/>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" s="9" t="s">
         <v>176</v>
       </c>
@@ -4163,9 +4166,9 @@
       <c r="F197" s="10">
         <v>5</v>
       </c>
-      <c r="G197" s="28"/>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G197" s="29"/>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" s="9" t="s">
         <v>292</v>
       </c>
@@ -4178,9 +4181,9 @@
       <c r="F198" s="10">
         <v>10</v>
       </c>
-      <c r="G198" s="28"/>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G198" s="29"/>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="9" t="s">
         <v>291</v>
       </c>
@@ -4193,9 +4196,9 @@
       <c r="F199" s="10">
         <v>10</v>
       </c>
-      <c r="G199" s="28"/>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G199" s="29"/>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="9"/>
       <c r="B200" s="9"/>
       <c r="C200" s="10" t="s">
@@ -4206,9 +4209,9 @@
       <c r="F200" s="10">
         <v>5</v>
       </c>
-      <c r="G200" s="28"/>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G200" s="29"/>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" s="9"/>
       <c r="B201" s="9"/>
       <c r="C201" s="10" t="s">
@@ -4219,9 +4222,9 @@
       <c r="F201" s="10">
         <v>5</v>
       </c>
-      <c r="G201" s="28"/>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G201" s="29"/>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" s="9"/>
       <c r="B202" s="9"/>
       <c r="C202" s="10" t="s">
@@ -4232,9 +4235,9 @@
       <c r="F202" s="10">
         <v>5</v>
       </c>
-      <c r="G202" s="28"/>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G202" s="29"/>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="9"/>
       <c r="B203" s="9"/>
       <c r="C203" s="10"/>
@@ -4246,9 +4249,9 @@
         <v>0</v>
       </c>
       <c r="F203" s="10"/>
-      <c r="G203" s="28"/>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G203" s="29"/>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="E204">
@@ -4259,14 +4262,14 @@
         <f>SUM(F197:F202)</f>
         <v>40</v>
       </c>
-      <c r="G204" s="28"/>
-    </row>
-    <row r="205" spans="1:7" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="G204" s="29"/>
+    </row>
+    <row r="205" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A205" s="5" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" s="7" t="s">
         <v>28</v>
       </c>
@@ -4278,7 +4281,7 @@
       <c r="E206" s="8"/>
       <c r="F206" s="8"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" s="8"/>
       <c r="B207" s="8"/>
       <c r="C207" s="8" t="s">
@@ -4290,7 +4293,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" s="8"/>
       <c r="B208" s="8"/>
       <c r="C208" s="8" t="s">
@@ -4300,7 +4303,7 @@
       <c r="E208" s="8"/>
       <c r="F208" s="8"/>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A209" s="8"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8" t="s">
@@ -4310,7 +4313,7 @@
       <c r="E209" s="8"/>
       <c r="F209" s="8"/>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A210" s="8"/>
       <c r="B210" s="8"/>
       <c r="C210" s="8" t="s">
@@ -4322,18 +4325,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F211">
         <f>SUM(F206:F210)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="212" spans="1:13" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="212" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A212" s="5" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A213" s="13" t="s">
         <v>325</v>
       </c>
@@ -4347,7 +4350,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A214" s="13"/>
       <c r="B214" s="11"/>
       <c r="C214" s="11"/>
@@ -4359,7 +4362,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A215" s="13"/>
       <c r="B215" s="11"/>
       <c r="C215" s="11"/>
@@ -4371,7 +4374,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A216" s="13"/>
       <c r="B216" s="11"/>
       <c r="C216" s="11"/>
@@ -4383,7 +4386,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A217" s="13"/>
       <c r="B217" s="11"/>
       <c r="C217" s="11"/>
@@ -4395,7 +4398,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A218" s="13"/>
       <c r="B218" s="11"/>
       <c r="C218" s="11"/>
@@ -4408,7 +4411,7 @@
       </c>
       <c r="F218" s="11"/>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A219" s="1"/>
       <c r="E219">
         <f>-SUM(E213:E218)</f>
@@ -4420,7 +4423,7 @@
       </c>
       <c r="M219" s="19"/>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A221" s="9" t="s">
         <v>66</v>
       </c>
@@ -4434,7 +4437,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A222" s="9"/>
       <c r="B222" s="10" t="s">
         <v>42</v>
@@ -4446,7 +4449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A223" s="9"/>
       <c r="B223" s="10" t="s">
         <v>328</v>
@@ -4458,7 +4461,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A224" s="9"/>
       <c r="B224" s="10" t="s">
         <v>67</v>
@@ -4470,7 +4473,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="9"/>
       <c r="B225" s="10"/>
       <c r="C225" s="10"/>
@@ -4483,7 +4486,7 @@
       </c>
       <c r="F225" s="10"/>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="1"/>
       <c r="E226">
         <f>-SUM(E221:E225)</f>
@@ -4494,7 +4497,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="9" t="s">
         <v>261</v>
       </c>
@@ -4512,7 +4515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="10"/>
       <c r="B228" s="10"/>
       <c r="C228" s="10"/>
@@ -4524,7 +4527,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="10"/>
       <c r="B229" s="10"/>
       <c r="C229" s="10"/>
@@ -4536,7 +4539,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="10"/>
       <c r="B230" s="10"/>
       <c r="C230" s="10"/>
@@ -4548,7 +4551,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="10"/>
       <c r="B231" s="10"/>
       <c r="C231" s="10"/>
@@ -4560,7 +4563,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="10"/>
       <c r="B232" s="10"/>
       <c r="C232" s="10"/>
@@ -4572,7 +4575,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="10"/>
       <c r="B233" s="10"/>
       <c r="C233" s="10" t="s">
@@ -4586,7 +4589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="10"/>
       <c r="B234" s="10"/>
       <c r="C234" s="10"/>
@@ -4598,7 +4601,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="10"/>
       <c r="B235" s="10"/>
       <c r="C235" s="10"/>
@@ -4610,7 +4613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="10"/>
       <c r="B236" s="10"/>
       <c r="C236" s="10"/>
@@ -4622,7 +4625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="10"/>
       <c r="B237" s="10"/>
       <c r="C237" s="10"/>
@@ -4634,7 +4637,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="10"/>
       <c r="B238" s="10"/>
       <c r="C238" s="10"/>
@@ -4647,7 +4650,7 @@
       </c>
       <c r="F238" s="10"/>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E239">
         <f>SUM(E227:E232)</f>
         <v>0</v>
@@ -4657,7 +4660,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="7" t="s">
         <v>261</v>
       </c>
@@ -4671,7 +4674,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="8"/>
       <c r="B241" s="7" t="s">
         <v>20</v>
@@ -4685,7 +4688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="8"/>
       <c r="B242" s="8"/>
       <c r="C242" s="8" t="s">
@@ -4697,7 +4700,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="8"/>
       <c r="B243" s="8"/>
       <c r="C243" s="8" t="s">
@@ -4709,7 +4712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="8"/>
       <c r="B244" s="8"/>
       <c r="C244" s="8" t="s">
@@ -4721,7 +4724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="8"/>
       <c r="B245" s="8"/>
       <c r="C245" s="8" t="s">
@@ -4733,7 +4736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="8"/>
       <c r="B246" s="8"/>
       <c r="C246" s="8" t="s">
@@ -4745,7 +4748,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="8"/>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4758,7 +4761,7 @@
       </c>
       <c r="F247" s="8"/>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E248">
         <f>SUM(E240:E246)</f>
         <v>0</v>
@@ -4768,7 +4771,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="7" t="s">
         <v>66</v>
       </c>
@@ -4782,7 +4785,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="7"/>
       <c r="B250" s="8" t="s">
         <v>42</v>
@@ -4794,7 +4797,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="7"/>
       <c r="B251" s="8" t="s">
         <v>217</v>
@@ -4806,7 +4809,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="7"/>
       <c r="B252" s="8" t="s">
         <v>140</v>
@@ -4818,7 +4821,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="7"/>
       <c r="B253" s="8" t="s">
         <v>65</v>
@@ -4830,7 +4833,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="7"/>
       <c r="B254" s="8" t="s">
         <v>67</v>
@@ -4842,7 +4845,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="7"/>
       <c r="B255" s="7" t="s">
         <v>49</v>
@@ -4856,7 +4859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="7"/>
       <c r="B256" s="7"/>
       <c r="C256" s="8" t="s">
@@ -4868,7 +4871,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="7"/>
       <c r="B257" s="7"/>
       <c r="C257" s="8" t="s">
@@ -4880,7 +4883,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="7"/>
       <c r="B258" s="7"/>
       <c r="C258" s="8" t="s">
@@ -4892,7 +4895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="7"/>
       <c r="B259" s="7"/>
       <c r="C259" s="8" t="s">
@@ -4904,7 +4907,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="7"/>
       <c r="B260" s="7"/>
       <c r="C260" s="8" t="s">
@@ -4918,7 +4921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="7"/>
       <c r="B261" s="7"/>
       <c r="C261" s="8"/>
@@ -4930,7 +4933,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="7"/>
       <c r="B262" s="7"/>
       <c r="C262" s="8"/>
@@ -4942,7 +4945,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="7"/>
       <c r="B263" s="7"/>
       <c r="C263" s="8"/>
@@ -4954,7 +4957,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="7"/>
       <c r="B264" s="7"/>
       <c r="C264" s="8"/>
@@ -4966,7 +4969,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="7"/>
       <c r="B265" s="7"/>
       <c r="C265" s="8"/>
@@ -4979,7 +4982,7 @@
       </c>
       <c r="F265" s="8"/>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E266">
         <f>SUM(E249:E265)</f>
         <v>0</v>
@@ -4989,7 +4992,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" s="7" t="s">
         <v>267</v>
       </c>
@@ -5003,7 +5006,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="7" t="s">
         <v>269</v>
       </c>
@@ -5017,7 +5020,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="7"/>
       <c r="B270" s="8" t="s">
         <v>318</v>
@@ -5029,7 +5032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="8"/>
       <c r="B271" s="8" t="s">
         <v>316</v>
@@ -5041,7 +5044,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="8"/>
       <c r="B272" s="8" t="s">
         <v>317</v>
@@ -5053,7 +5056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="8"/>
       <c r="B273" s="8"/>
       <c r="C273" s="8"/>
@@ -5066,7 +5069,7 @@
       </c>
       <c r="F273" s="8"/>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E274">
         <f>SUM(E268:E272)</f>
         <v>0</v>
@@ -5076,7 +5079,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="9" t="s">
         <v>34</v>
       </c>
@@ -5090,7 +5093,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="10"/>
       <c r="B276" s="10" t="s">
         <v>221</v>
@@ -5102,7 +5105,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="9"/>
       <c r="B277" s="10" t="s">
         <v>285</v>
@@ -5116,7 +5119,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="10"/>
       <c r="B278" s="10" t="s">
         <v>278</v>
@@ -5130,7 +5133,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="9"/>
       <c r="B279" s="10" t="s">
         <v>200</v>
@@ -5144,7 +5147,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="9"/>
       <c r="B280" s="10" t="s">
         <v>286</v>
@@ -5158,7 +5161,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="9"/>
       <c r="B281" s="10" t="s">
         <v>287</v>
@@ -5170,7 +5173,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="10"/>
       <c r="B282" s="10" t="s">
         <v>279</v>
@@ -5182,7 +5185,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="10"/>
       <c r="B283" s="10" t="s">
         <v>280</v>
@@ -5194,7 +5197,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="10"/>
       <c r="B284" s="10" t="s">
         <v>36</v>
@@ -5206,7 +5209,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285" s="10"/>
       <c r="B285" s="10"/>
       <c r="C285" s="10"/>
@@ -5219,7 +5222,7 @@
       </c>
       <c r="F285" s="10"/>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E286">
         <f>SUM(E275:E284)</f>
         <v>0</v>
@@ -5229,12 +5232,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="289" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="289" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A289" s="5" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="12" t="s">
         <v>191</v>
       </c>
@@ -5248,7 +5251,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="14"/>
       <c r="B291" s="14"/>
       <c r="C291" s="12" t="s">
@@ -5260,7 +5263,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" s="14"/>
       <c r="B292" s="14"/>
       <c r="C292" s="12" t="s">
@@ -5272,7 +5275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" s="14"/>
       <c r="B293" s="14"/>
       <c r="C293" s="12" t="s">
@@ -5284,7 +5287,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" s="14"/>
       <c r="B294" s="14"/>
       <c r="C294" s="12" t="s">
@@ -5296,7 +5299,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" s="12"/>
       <c r="B295" s="12" t="s">
         <v>192</v>
@@ -5310,7 +5313,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="12"/>
       <c r="B296" s="12"/>
       <c r="C296" s="12" t="s">
@@ -5322,7 +5325,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="12"/>
       <c r="B297" s="12"/>
       <c r="C297" s="12" t="s">
@@ -5334,7 +5337,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" s="12"/>
       <c r="B298" s="12" t="s">
         <v>194</v>
@@ -5348,7 +5351,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" s="12"/>
       <c r="B299" s="12"/>
       <c r="C299" s="12" t="s">
@@ -5360,7 +5363,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="12"/>
       <c r="B300" s="12"/>
       <c r="C300" s="12" t="s">
@@ -5372,7 +5375,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" s="14" t="s">
         <v>49</v>
       </c>
@@ -5386,7 +5389,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" s="14"/>
       <c r="B302" s="14"/>
       <c r="C302" s="12" t="s">
@@ -5398,7 +5401,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" s="14"/>
       <c r="B303" s="14"/>
       <c r="C303" s="12" t="s">
@@ -5410,7 +5413,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" s="14"/>
       <c r="B304" s="14"/>
       <c r="C304" s="12" t="s">
@@ -5422,7 +5425,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" s="14"/>
       <c r="B305" s="14"/>
       <c r="C305" s="12" t="s">
@@ -5434,7 +5437,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" s="14"/>
       <c r="B306" s="14"/>
       <c r="C306" s="12" t="s">
@@ -5448,7 +5451,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" s="14"/>
       <c r="B307" s="14"/>
       <c r="C307" s="12"/>
@@ -5460,7 +5463,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308" s="14"/>
       <c r="B308" s="14"/>
       <c r="C308" s="12"/>
@@ -5472,7 +5475,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309" s="14"/>
       <c r="B309" s="14"/>
       <c r="C309" s="12"/>
@@ -5484,7 +5487,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310" s="14"/>
       <c r="B310" s="14"/>
       <c r="C310" s="12"/>
@@ -5496,7 +5499,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311" s="12"/>
       <c r="B311" s="12"/>
       <c r="C311" s="12"/>
@@ -5509,7 +5512,7 @@
       </c>
       <c r="F311" s="12"/>
     </row>
-    <row r="312" spans="1:12" ht="15" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E312">
         <f>SUM(E290:E311)</f>
         <v>0</v>
@@ -5521,7 +5524,7 @@
       <c r="K312" s="17"/>
       <c r="L312" s="17"/>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" s="9" t="s">
         <v>355</v>
       </c>
@@ -5537,7 +5540,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A314" s="10" t="s">
         <v>302</v>
       </c>
@@ -5551,7 +5554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315" s="9"/>
       <c r="B315" s="10"/>
       <c r="C315" s="10" t="s">
@@ -5563,7 +5566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316" s="10"/>
       <c r="B316" s="10"/>
       <c r="C316" s="10" t="s">
@@ -5577,7 +5580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317" s="10"/>
       <c r="B317" s="10"/>
       <c r="C317" s="10" t="s">
@@ -5591,7 +5594,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" s="9"/>
       <c r="B318" s="10"/>
       <c r="C318" s="10" t="s">
@@ -5605,7 +5608,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A319" s="9"/>
       <c r="B319" s="10"/>
       <c r="C319" s="10" t="s">
@@ -5619,7 +5622,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A320" s="10"/>
       <c r="B320" s="10"/>
       <c r="C320" s="10"/>
@@ -5631,7 +5634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:12" ht="15" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E321">
         <f>SUM(E313:E320)</f>
         <v>0</v>
@@ -5643,15 +5646,15 @@
       <c r="K321" s="17"/>
       <c r="L321" s="17"/>
     </row>
-    <row r="322" spans="1:12" ht="15" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K322" s="17"/>
       <c r="L322" s="17"/>
     </row>
-    <row r="323" spans="1:12" ht="15" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K323" s="17"/>
       <c r="L323" s="17"/>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A324" s="13" t="s">
         <v>271</v>
       </c>
@@ -5665,7 +5668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A325" s="11"/>
       <c r="B325" s="11" t="s">
         <v>273</v>
@@ -5677,7 +5680,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A326" s="11"/>
       <c r="B326" s="11" t="s">
         <v>110</v>
@@ -5689,7 +5692,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A327" s="13" t="s">
         <v>274</v>
       </c>
@@ -5703,7 +5706,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A328" s="11"/>
       <c r="B328" s="11" t="s">
         <v>276</v>
@@ -5715,7 +5718,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329" s="13" t="s">
         <v>319</v>
       </c>
@@ -5729,7 +5732,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A330" s="11"/>
       <c r="B330" s="11"/>
       <c r="C330" s="11" t="s">
@@ -5741,7 +5744,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" s="11"/>
       <c r="B331" s="11"/>
       <c r="C331" s="11" t="s">
@@ -5753,7 +5756,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A332" s="11"/>
       <c r="B332" s="11"/>
       <c r="C332" s="11"/>
@@ -5766,7 +5769,7 @@
       </c>
       <c r="F332" s="11"/>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E333">
         <f>SUM(E324:E328)</f>
         <v>0</v>
@@ -5776,14 +5779,14 @@
         <v>60</v>
       </c>
     </row>
-    <row r="335" spans="1:12" s="17" customFormat="1" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="335" spans="1:12" s="17" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A335" s="5" t="s">
         <v>251</v>
       </c>
       <c r="K335"/>
       <c r="L335"/>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A336" s="11" t="s">
         <v>153</v>
       </c>
@@ -5801,7 +5804,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337" s="11"/>
       <c r="B337" s="11"/>
       <c r="C337" s="11" t="s">
@@ -5815,7 +5818,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A338" s="11"/>
       <c r="B338" s="11"/>
       <c r="C338" s="11" t="s">
@@ -5829,7 +5832,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A339" s="11"/>
       <c r="B339" s="11"/>
       <c r="C339" s="11" t="s">
@@ -5843,7 +5846,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A340" s="11"/>
       <c r="B340" s="11"/>
       <c r="C340" s="11" t="s">
@@ -5857,7 +5860,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A341" s="11"/>
       <c r="B341" s="11"/>
       <c r="C341" s="11" t="s">
@@ -5871,7 +5874,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A342" s="11"/>
       <c r="B342" s="11"/>
       <c r="C342" s="11"/>
@@ -5883,7 +5886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E343">
         <f>SUM(E336:E342)</f>
         <v>0</v>
@@ -5893,7 +5896,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344" s="13" t="s">
         <v>40</v>
       </c>
@@ -5907,7 +5910,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A345" s="13"/>
       <c r="B345" s="13"/>
       <c r="C345" s="15" t="s">
@@ -5919,7 +5922,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A346" s="13"/>
       <c r="B346" s="13"/>
       <c r="C346" s="15" t="s">
@@ -5931,7 +5934,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A347" s="13"/>
       <c r="B347" s="13"/>
       <c r="C347" s="11"/>
@@ -5939,7 +5942,7 @@
       <c r="E347" s="11"/>
       <c r="F347" s="11"/>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A348" s="13" t="s">
         <v>103</v>
       </c>
@@ -5953,7 +5956,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A349" s="13"/>
       <c r="B349" s="13"/>
       <c r="C349" s="11" t="s">
@@ -5965,7 +5968,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A350" s="13"/>
       <c r="B350" s="13"/>
       <c r="C350" s="11" t="s">
@@ -5977,7 +5980,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A351" s="13"/>
       <c r="B351" s="13"/>
       <c r="C351" s="11"/>
@@ -5985,7 +5988,7 @@
       <c r="E351" s="11"/>
       <c r="F351" s="11"/>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A352" s="13" t="s">
         <v>199</v>
       </c>
@@ -5999,7 +6002,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A353" s="13"/>
       <c r="B353" s="13"/>
       <c r="C353" s="11" t="s">
@@ -6011,7 +6014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A354" s="13"/>
       <c r="B354" s="13"/>
       <c r="C354" s="11" t="s">
@@ -6023,7 +6026,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A355" s="13"/>
       <c r="B355" s="13"/>
       <c r="C355" s="11"/>
@@ -6036,7 +6039,7 @@
       </c>
       <c r="F355" s="11"/>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="E356">
@@ -6049,7 +6052,7 @@
       </c>
       <c r="M356" s="19"/>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A357" s="14" t="s">
         <v>41</v>
       </c>
@@ -6064,7 +6067,7 @@
       </c>
       <c r="M357" s="19"/>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A358" s="14"/>
       <c r="B358" s="14"/>
       <c r="C358" s="12" t="s">
@@ -6077,7 +6080,7 @@
       </c>
       <c r="M358" s="19"/>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A359" s="14"/>
       <c r="B359" s="14"/>
       <c r="C359" s="12"/>
@@ -6091,7 +6094,7 @@
       <c r="F359" s="12"/>
       <c r="M359" s="19"/>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="E360">
@@ -6103,7 +6106,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>5</v>
       </c>
@@ -6119,7 +6122,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
         <v>314</v>
       </c>
@@ -6133,7 +6136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A364" s="1"/>
       <c r="B364" s="10"/>
       <c r="C364" s="10" t="s">
@@ -6145,7 +6148,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A365" s="1"/>
       <c r="B365" s="10"/>
       <c r="C365" s="10" t="s">
@@ -6157,7 +6160,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A366" s="1"/>
       <c r="B366" s="10"/>
       <c r="C366" s="10" t="s">
@@ -6169,7 +6172,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A367" s="1"/>
       <c r="B367" s="10"/>
       <c r="C367" s="10" t="s">
@@ -6181,7 +6184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A368" s="1"/>
       <c r="B368" s="10"/>
       <c r="C368" s="10" t="s">
@@ -6193,7 +6196,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A369" s="1"/>
       <c r="B369" s="10"/>
       <c r="C369" s="10" t="s">
@@ -6205,7 +6208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A370" s="1"/>
       <c r="B370" s="10"/>
       <c r="C370" s="10"/>
@@ -6218,7 +6221,7 @@
       </c>
       <c r="F370" s="10"/>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="E371">
@@ -6230,7 +6233,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A372" s="1"/>
       <c r="B372" s="13" t="s">
         <v>54</v>
@@ -6244,7 +6247,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A373" s="1"/>
       <c r="B373" s="11"/>
       <c r="C373" s="11" t="s">
@@ -6256,7 +6259,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A374" s="1"/>
       <c r="B374" s="11"/>
       <c r="C374" s="11" t="s">
@@ -6268,7 +6271,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A375" s="1"/>
       <c r="B375" s="11"/>
       <c r="C375" s="11" t="s">
@@ -6280,7 +6283,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A376" s="1"/>
       <c r="B376" s="11"/>
       <c r="C376" s="11" t="s">
@@ -6292,7 +6295,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A377" s="1"/>
       <c r="B377" s="11"/>
       <c r="C377" s="11" t="s">
@@ -6304,7 +6307,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A378" s="1"/>
       <c r="B378" s="11"/>
       <c r="C378" s="11" t="s">
@@ -6316,7 +6319,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A379" s="1"/>
       <c r="B379" s="11"/>
       <c r="C379" s="11" t="s">
@@ -6328,7 +6331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A380" s="1"/>
       <c r="B380" s="11"/>
       <c r="C380" s="11"/>
@@ -6341,7 +6344,7 @@
       </c>
       <c r="F380" s="11"/>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="E381">
@@ -6353,7 +6356,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A382" s="1"/>
       <c r="B382" s="14" t="s">
         <v>54</v>
@@ -6367,7 +6370,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A383" s="1"/>
       <c r="B383" s="12"/>
       <c r="C383" s="12" t="s">
@@ -6379,7 +6382,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A384" s="1"/>
       <c r="B384" s="12"/>
       <c r="C384" s="12" t="s">
@@ -6391,7 +6394,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A385" s="1"/>
       <c r="B385" s="12"/>
       <c r="C385" s="12" t="str">
@@ -6404,7 +6407,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A386" s="1"/>
       <c r="B386" s="12"/>
       <c r="C386" s="12" t="str">
@@ -6417,7 +6420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A387" s="1"/>
       <c r="B387" s="12"/>
       <c r="C387" s="12" t="str">
@@ -6430,7 +6433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A388" s="1"/>
       <c r="B388" s="12"/>
       <c r="C388" s="12" t="str">
@@ -6443,7 +6446,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A389" s="1"/>
       <c r="B389" s="12"/>
       <c r="C389" s="12" t="s">
@@ -6455,7 +6458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A390" s="1"/>
       <c r="B390" s="12"/>
       <c r="C390" s="12"/>
@@ -6468,7 +6471,7 @@
       </c>
       <c r="F390" s="12"/>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="E391">
@@ -6480,12 +6483,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="393" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="393" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A393" s="5" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A394" s="7" t="s">
         <v>309</v>
       </c>
@@ -6495,7 +6498,7 @@
       <c r="E394" s="8"/>
       <c r="F394" s="8"/>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A395" s="7"/>
       <c r="B395" s="8"/>
       <c r="C395" s="8"/>
@@ -6503,7 +6506,7 @@
       <c r="E395" s="8"/>
       <c r="F395" s="8"/>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A396" s="7"/>
       <c r="B396" s="8" t="s">
         <v>157</v>
@@ -6513,7 +6516,7 @@
       <c r="E396" s="8"/>
       <c r="F396" s="8"/>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A397" s="7"/>
       <c r="B397" s="8" t="s">
         <v>158</v>
@@ -6525,7 +6528,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A398" s="7"/>
       <c r="B398" s="8" t="s">
         <v>159</v>
@@ -6537,7 +6540,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A399" s="7"/>
       <c r="B399" s="8" t="s">
         <v>160</v>
@@ -6551,7 +6554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A400" s="7"/>
       <c r="B400" s="8"/>
       <c r="C400" s="8" t="s">
@@ -6563,7 +6566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A401" s="7"/>
       <c r="B401" s="8" t="s">
         <v>162</v>
@@ -6577,7 +6580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A402" s="7"/>
       <c r="B402" s="8"/>
       <c r="C402" s="8" t="s">
@@ -6589,7 +6592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A403" s="7"/>
       <c r="B403" s="8"/>
       <c r="C403" s="8" t="s">
@@ -6601,7 +6604,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A404" s="7"/>
       <c r="B404" s="8"/>
       <c r="C404" s="8" t="s">
@@ -6613,7 +6616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A405" s="7"/>
       <c r="B405" s="8"/>
       <c r="C405" s="8" t="s">
@@ -6625,7 +6628,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A406" s="7"/>
       <c r="B406" s="8"/>
       <c r="C406" s="8"/>
@@ -6638,7 +6641,7 @@
       </c>
       <c r="F406" s="8"/>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A407" s="1"/>
       <c r="E407">
         <f>SUM(E394:E406)</f>
@@ -6649,10 +6652,10 @@
         <v>65</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A408" s="1"/>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A409" s="9" t="s">
         <v>90</v>
       </c>
@@ -6666,7 +6669,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A410" s="10"/>
       <c r="B410" s="10" t="s">
         <v>92</v>
@@ -6678,7 +6681,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A411" s="10"/>
       <c r="B411" s="10" t="s">
         <v>93</v>
@@ -6690,7 +6693,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A412" s="10"/>
       <c r="B412" s="10" t="s">
         <v>94</v>
@@ -6702,7 +6705,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A413" s="9" t="s">
         <v>102</v>
       </c>
@@ -6712,7 +6715,7 @@
       <c r="E413" s="10"/>
       <c r="F413" s="10"/>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A414" s="9"/>
       <c r="B414" s="10" t="s">
         <v>118</v>
@@ -6724,7 +6727,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A415" s="10"/>
       <c r="B415" s="10" t="s">
         <v>119</v>
@@ -6738,7 +6741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A416" s="10"/>
       <c r="B416" s="10" t="s">
         <v>120</v>
@@ -6752,7 +6755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A417" s="10"/>
       <c r="B417" s="10" t="s">
         <v>121</v>
@@ -6764,7 +6767,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A418" s="10"/>
       <c r="B418" s="10"/>
       <c r="C418" s="10"/>
@@ -6772,7 +6775,7 @@
       <c r="E418" s="10"/>
       <c r="F418" s="10"/>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A419" s="10"/>
       <c r="B419" s="10"/>
       <c r="C419" s="10"/>
@@ -6785,7 +6788,7 @@
       </c>
       <c r="F419" s="10"/>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E420">
         <f>SUM(E409:E419)</f>
         <v>0</v>
@@ -6795,12 +6798,12 @@
         <v>550</v>
       </c>
     </row>
-    <row r="421" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="421" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A421" s="5" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A422" s="7" t="s">
         <v>36</v>
       </c>
@@ -6816,7 +6819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A423" s="7"/>
       <c r="B423" s="8"/>
       <c r="C423" s="8" t="s">
@@ -6828,7 +6831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A424" s="7"/>
       <c r="B424" s="8"/>
       <c r="C424" s="8" t="s">
@@ -6840,7 +6843,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A425" s="7"/>
       <c r="B425" s="8"/>
       <c r="C425" s="8" t="s">
@@ -6852,7 +6855,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A426" s="7"/>
       <c r="B426" s="8"/>
       <c r="C426" s="8" t="s">
@@ -6864,7 +6867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A427" s="8"/>
       <c r="B427" s="8" t="s">
         <v>12</v>
@@ -6876,7 +6879,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A428" s="8"/>
       <c r="B428" s="8" t="s">
         <v>39</v>
@@ -6888,7 +6891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A429" s="8"/>
       <c r="B429" s="8" t="s">
         <v>68</v>
@@ -6900,7 +6903,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A430" s="8"/>
       <c r="B430" s="8" t="s">
         <v>85</v>
@@ -6912,7 +6915,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A431" s="8"/>
       <c r="B431" s="8"/>
       <c r="C431" s="8"/>
@@ -6925,7 +6928,7 @@
       </c>
       <c r="F431" s="8"/>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E432">
         <f>SUM(E422:E431)</f>
         <v>0</v>
@@ -6935,7 +6938,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A433" s="8" t="s">
         <v>122</v>
       </c>
@@ -6949,7 +6952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A434" s="8"/>
       <c r="B434" s="8" t="s">
         <v>124</v>
@@ -6961,7 +6964,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A435" s="8"/>
       <c r="B435" s="8" t="s">
         <v>125</v>
@@ -6973,7 +6976,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A436" s="8"/>
       <c r="B436" s="8" t="s">
         <v>126</v>
@@ -6985,7 +6988,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A437" s="8"/>
       <c r="B437" s="8" t="s">
         <v>127</v>
@@ -6997,7 +7000,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A438" s="8"/>
       <c r="B438" s="8" t="s">
         <v>228</v>
@@ -7009,7 +7012,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A439" s="8"/>
       <c r="B439" s="8" t="s">
         <v>128</v>
@@ -7021,7 +7024,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A440" s="8"/>
       <c r="B440" s="8" t="s">
         <v>229</v>
@@ -7033,7 +7036,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A441" s="8"/>
       <c r="B441" s="8" t="s">
         <v>129</v>
@@ -7045,7 +7048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A442" s="8"/>
       <c r="B442" s="8"/>
       <c r="C442" s="8"/>
@@ -7058,7 +7061,7 @@
       </c>
       <c r="F442" s="8"/>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E443">
         <f>SUM(E433:E442)</f>
         <v>0</v>
@@ -7068,7 +7071,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A444" s="8" t="s">
         <v>130</v>
       </c>
@@ -7082,7 +7085,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A445" s="8"/>
       <c r="B445" s="8" t="s">
         <v>132</v>
@@ -7094,7 +7097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A446" s="8"/>
       <c r="B446" s="8" t="s">
         <v>7</v>
@@ -7106,7 +7109,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A447" s="8"/>
       <c r="B447" s="8" t="s">
         <v>133</v>
@@ -7118,7 +7121,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A448" s="8"/>
       <c r="B448" s="8" t="s">
         <v>134</v>
@@ -7130,7 +7133,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A449" s="8"/>
       <c r="B449" s="8" t="s">
         <v>135</v>
@@ -7142,7 +7145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A450" s="8"/>
       <c r="B450" s="8" t="s">
         <v>136</v>
@@ -7154,7 +7157,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A451" s="8"/>
       <c r="B451" s="8"/>
       <c r="C451" s="8"/>
@@ -7167,7 +7170,7 @@
       </c>
       <c r="F451" s="8"/>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E452">
         <f>SUM(E444:E451)</f>
         <v>0</v>
@@ -7177,7 +7180,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A453" s="7" t="s">
         <v>312</v>
       </c>
@@ -7193,7 +7196,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A454" s="7"/>
       <c r="B454" s="7"/>
       <c r="C454" s="8"/>
@@ -7205,7 +7208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A455" s="7"/>
       <c r="B455" s="7"/>
       <c r="C455" s="8"/>
@@ -7217,7 +7220,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A456" s="7"/>
       <c r="B456" s="7"/>
       <c r="C456" s="8" t="s">
@@ -7231,7 +7234,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A457" s="7"/>
       <c r="B457" s="7"/>
       <c r="C457" s="8"/>
@@ -7243,7 +7246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A458" s="7"/>
       <c r="B458" s="7"/>
       <c r="C458" s="8"/>
@@ -7255,7 +7258,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A459" s="7"/>
       <c r="B459" s="7"/>
       <c r="C459" s="8"/>
@@ -7267,7 +7270,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A460" s="7"/>
       <c r="B460" s="7"/>
       <c r="C460" s="8"/>
@@ -7279,7 +7282,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E461">
         <f>SUM(E453:E460)</f>
         <v>0</v>
@@ -7289,12 +7292,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="462" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="462" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A462" s="5" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A463" s="7" t="s">
         <v>235</v>
       </c>
@@ -7310,7 +7313,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A464" s="7"/>
       <c r="B464" s="8"/>
       <c r="C464" s="8" t="s">
@@ -7322,7 +7325,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A465" s="8"/>
       <c r="B465" s="7" t="s">
         <v>236</v>
@@ -7336,7 +7339,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A466" s="8"/>
       <c r="B466" s="8"/>
       <c r="C466" s="8" t="s">
@@ -7348,7 +7351,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A467" s="8"/>
       <c r="B467" s="8"/>
       <c r="C467" s="8" t="s">
@@ -7360,7 +7363,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A468" s="8"/>
       <c r="B468" s="8"/>
       <c r="C468" s="8" t="s">
@@ -7372,7 +7375,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A469" s="8"/>
       <c r="B469" s="8"/>
       <c r="C469" s="8" t="s">
@@ -7384,7 +7387,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A470" s="8"/>
       <c r="B470" s="8"/>
       <c r="C470" s="8"/>
@@ -7396,7 +7399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E471">
         <f>SUM(E463:E470)</f>
         <v>0</v>
@@ -7406,12 +7409,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A473" s="14" t="s">
         <v>330</v>
       </c>
@@ -7427,7 +7430,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A474" s="14" t="s">
         <v>332</v>
       </c>
@@ -7445,7 +7448,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A475" s="14"/>
       <c r="B475" s="12"/>
       <c r="C475" s="12" t="s">
@@ -7459,7 +7462,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A476" s="1"/>
       <c r="D476" s="20" t="s">
         <v>206</v>
@@ -7469,7 +7472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E477">
         <f>SUM(E473:E476)</f>
         <v>0</v>
@@ -7479,12 +7482,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="479" spans="1:6" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="479" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A479" s="5" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A480" s="14" t="s">
         <v>235</v>
       </c>
@@ -7498,7 +7501,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A481" s="14" t="s">
         <v>240</v>
       </c>
@@ -7512,7 +7515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A482" s="12"/>
       <c r="B482" s="12" t="s">
         <v>238</v>
@@ -7524,7 +7527,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A483" s="12"/>
       <c r="B483" s="12" t="s">
         <v>237</v>
@@ -7536,7 +7539,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A484" s="12"/>
       <c r="B484" s="12" t="s">
         <v>239</v>
@@ -7548,7 +7551,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A485" s="12"/>
       <c r="B485" s="12" t="s">
         <v>241</v>
@@ -7560,7 +7563,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A486" s="12"/>
       <c r="B486" s="12" t="s">
         <v>242</v>
@@ -7572,7 +7575,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A487" s="12"/>
       <c r="B487" s="12" t="s">
         <v>25</v>
@@ -7584,7 +7587,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A488" s="12"/>
       <c r="B488" s="12" t="s">
         <v>26</v>
@@ -7596,7 +7599,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A489" s="12"/>
       <c r="B489" s="12" t="s">
         <v>243</v>
@@ -7608,7 +7611,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A490" s="12"/>
       <c r="B490" s="12" t="s">
         <v>244</v>
@@ -7620,7 +7623,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A491" s="12"/>
       <c r="B491" s="12"/>
       <c r="C491" s="12"/>
@@ -7632,7 +7635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E492">
         <f>SUM(E480:E491)</f>
         <v>0</v>
@@ -7642,7 +7645,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A494" s="9" t="s">
         <v>235</v>
       </c>
@@ -7659,7 +7662,7 @@
       </c>
       <c r="H494" s="18"/>
     </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A495" s="9" t="s">
         <v>240</v>
       </c>
@@ -7676,7 +7679,7 @@
       </c>
       <c r="H495" s="18"/>
     </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A496" s="10" t="s">
         <v>387</v>
       </c>
@@ -7693,7 +7696,7 @@
       </c>
       <c r="H496" s="18"/>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A497" s="10"/>
       <c r="B497" s="10" t="s">
         <v>237</v>
@@ -7708,7 +7711,7 @@
       </c>
       <c r="H497" s="18"/>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A498" s="10"/>
       <c r="B498" s="10" t="s">
         <v>239</v>
@@ -7722,7 +7725,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A499" s="10"/>
       <c r="B499" s="10" t="s">
         <v>241</v>
@@ -7736,7 +7739,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A500" s="10"/>
       <c r="B500" s="10" t="s">
         <v>242</v>
@@ -7750,7 +7753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="501" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A501" s="10"/>
       <c r="B501" s="10" t="s">
         <v>25</v>
@@ -7764,7 +7767,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A502" s="10"/>
       <c r="B502" s="10" t="s">
         <v>26</v>
@@ -7778,7 +7781,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="503" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A503" s="10"/>
       <c r="B503" s="10" t="s">
         <v>243</v>
@@ -7791,11 +7794,11 @@
       <c r="F503" s="10">
         <v>5</v>
       </c>
-      <c r="H503" s="30" t="s">
+      <c r="H503" s="25" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A504" s="10"/>
       <c r="B504" s="10" t="s">
         <v>244</v>
@@ -7809,7 +7812,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A505" s="10"/>
       <c r="B505" s="10"/>
       <c r="C505" s="10"/>
@@ -7830,7 +7833,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E506">
         <f>SUM(E494:E505)</f>
         <v>16.5</v>
@@ -7840,7 +7843,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A508" s="13" t="s">
         <v>235</v>
       </c>
@@ -7856,7 +7859,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="509" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A509" s="13" t="s">
         <v>240</v>
       </c>
@@ -7875,7 +7878,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="510" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A510" s="11" t="s">
         <v>380</v>
       </c>
@@ -7891,7 +7894,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="511" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A511" s="11"/>
       <c r="B511" s="11" t="s">
         <v>237</v>
@@ -7908,7 +7911,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="512" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A512" s="11"/>
       <c r="B512" s="11" t="s">
         <v>239</v>
@@ -7922,7 +7925,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="513" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A513" s="11"/>
       <c r="B513" s="11" t="s">
         <v>241</v>
@@ -7939,7 +7942,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="514" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A514" s="11"/>
       <c r="B514" s="11" t="s">
         <v>242</v>
@@ -7953,7 +7956,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="515" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A515" s="11"/>
       <c r="B515" s="11" t="s">
         <v>25</v>
@@ -7970,7 +7973,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="516" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A516" s="11"/>
       <c r="B516" s="11" t="s">
         <v>26</v>
@@ -7987,7 +7990,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="517" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A517" s="11"/>
       <c r="B517" s="11" t="s">
         <v>243</v>
@@ -8004,7 +8007,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="518" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A518" s="11"/>
       <c r="B518" s="11" t="s">
         <v>244</v>
@@ -8018,7 +8021,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="519" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A519" s="11"/>
       <c r="B519" s="11"/>
       <c r="C519" s="11"/>
@@ -8037,7 +8040,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="520" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E520">
         <f>SUM(E508:E519)</f>
         <v>24.5</v>
@@ -8047,7 +8050,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="524" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A524" s="7"/>
       <c r="B524" t="s">
         <v>183</v>
@@ -8065,7 +8068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A525" s="9" t="s">
         <v>364</v>
       </c>
@@ -8085,7 +8088,7 @@
         <v>-0.11762820512820513</v>
       </c>
     </row>
-    <row r="526" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A526" s="13" t="s">
         <v>365</v>
       </c>
@@ -8105,7 +8108,7 @@
         <v>-0.15462555066079295</v>
       </c>
     </row>
-    <row r="527" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A527" s="14" t="s">
         <v>363</v>
       </c>
@@ -8125,7 +8128,7 @@
         <v>-0.17699115044247787</v>
       </c>
     </row>
-    <row r="531" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="531" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F531" t="s">
         <v>230</v>
       </c>
@@ -8133,7 +8136,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="532" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="532" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D532" t="s">
         <v>232</v>
       </c>
@@ -8141,7 +8144,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="533" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="533" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F533" s="23">
         <v>0.45</v>
       </c>
@@ -8149,7 +8152,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="534" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="534" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F534" s="23">
         <f>F533+(F542-F533)/9</f>
         <v>0.5</v>
@@ -8158,7 +8161,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="535" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="535" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F535" s="23">
         <f>F534+(F542-F533)/9</f>
         <v>0.55000000000000004</v>
@@ -8167,7 +8170,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="536" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="536" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F536" s="23">
         <f>F535+(F542-F533)/9</f>
         <v>0.60000000000000009</v>
@@ -8176,7 +8179,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="537" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="537" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F537" s="23">
         <f>F536+(F542-F533)/9</f>
         <v>0.65000000000000013</v>
@@ -8185,7 +8188,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="538" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="538" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F538" s="23">
         <f>F537+(F542-F533)/9</f>
         <v>0.70000000000000018</v>
@@ -8194,7 +8197,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="539" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="539" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F539" s="23">
         <f>F538+(F542-F533)/9</f>
         <v>0.75000000000000022</v>
@@ -8203,7 +8206,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="540" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="540" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F540" s="23">
         <f>F539+(F542-F533)/9</f>
         <v>0.80000000000000027</v>
@@ -8212,7 +8215,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="541" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="541" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F541" s="23">
         <f>F540+(F542-F533)/9</f>
         <v>0.85000000000000031</v>
@@ -8221,7 +8224,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="542" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="542" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F542" s="23">
         <v>0.9</v>
       </c>
@@ -8229,7 +8232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="543" spans="4:7" x14ac:dyDescent="0.45">
+    <row r="543" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E543" t="s">
         <v>234</v>
       </c>
@@ -8242,13 +8245,13 @@
     <mergeCell ref="G189:G204"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B21"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B14">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Name of the module" prompt="e.g. _x000a_Master Thesis_x000a_Bachelor Thesis _x000a_Mathematics and Analytics_x000a_Projekt 1_x000a_Project T_x000a_Technisches Projekt" sqref="B21" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Study Course" prompt="Choose your Study Course" sqref="B14" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Technical Management, Business Intelligen ans Data Analytics,Maschinenbau,Indin,IBS,Maschinenbau und Design,Maschinenbau und Design im Praxisverbund,Engineering Physics,other"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="H503" r:id="rId1" display="https://www.naftaliharris.com/blog/visualizing-k-means-clustering/"/>
+    <hyperlink ref="H503" r:id="rId1" display="https://www.naftaliharris.com/blog/visualizing-k-means-clustering/" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
@@ -8257,27 +8260,27 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.86328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.3984375" style="19"/>
+    <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.5" x14ac:dyDescent="0.75">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:4" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A1" s="30" t="s">
         <v>223</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>207</v>
       </c>
@@ -8285,7 +8288,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>38</v>
       </c>
@@ -8293,7 +8296,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>209</v>
       </c>
@@ -8301,7 +8304,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>210</v>
       </c>
@@ -8309,7 +8312,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>211</v>
       </c>
@@ -8317,7 +8320,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>212</v>
       </c>
@@ -8325,7 +8328,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>174</v>
       </c>
@@ -8333,7 +8336,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>208</v>
       </c>
@@ -8341,7 +8344,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>214</v>
       </c>
@@ -8349,7 +8352,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>213</v>
       </c>
@@ -8357,7 +8360,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>215</v>
       </c>
@@ -8365,7 +8368,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>216</v>
       </c>
@@ -8373,7 +8376,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>222</v>
       </c>
@@ -8381,7 +8384,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>224</v>
       </c>
@@ -8389,7 +8392,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>225</v>
       </c>
@@ -8397,7 +8400,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -8411,7 +8414,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
         <v>143</v>
       </c>
@@ -8419,7 +8422,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>144</v>
       </c>
@@ -8427,7 +8430,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>145</v>
       </c>
@@ -8438,7 +8441,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
         <v>147</v>
       </c>
@@ -8446,7 +8449,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
         <v>148</v>
       </c>
@@ -8454,7 +8457,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
         <v>149</v>
       </c>
@@ -8462,12 +8465,12 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>162</v>
       </c>
@@ -8478,7 +8481,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
         <v>166</v>
       </c>
@@ -8486,7 +8489,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>148</v>
       </c>
@@ -8494,7 +8497,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>220</v>
       </c>
@@ -8502,7 +8505,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>167</v>
       </c>
@@ -8513,7 +8516,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
         <v>169</v>
       </c>
@@ -8521,7 +8524,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C37" t="s">
         <v>170</v>
       </c>

--- a/ProjectManagement/EvaluationHW.xlsx
+++ b/ProjectManagement/EvaluationHW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\Winter 2024-25\ML project\ML24-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Wings_Hub\Wings-Hub\ML2425\ML24-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14FFAB34-2F15-44C0-99B8-E51D23FF77A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E029D6AF-5957-4AE4-9D0E-1807BE7F4E71}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="2" r:id="rId1"/>
@@ -165,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="401">
   <si>
     <t>Literature</t>
   </si>
@@ -1341,6 +1341,33 @@
   </si>
   <si>
     <t>Logitech C270 HD Webcam</t>
+  </si>
+  <si>
+    <t>RANSAC</t>
+  </si>
+  <si>
+    <t>okay</t>
+  </si>
+  <si>
+    <t>not really (pictures, code,…)</t>
+  </si>
+  <si>
+    <t>not external</t>
+  </si>
+  <si>
+    <t>mno details</t>
+  </si>
+  <si>
+    <t>no config</t>
+  </si>
+  <si>
+    <t>no dexcription of the input</t>
+  </si>
+  <si>
+    <t>no description of the output</t>
+  </si>
+  <si>
+    <t>not used</t>
   </si>
 </sst>
 </file>
@@ -1595,8 +1622,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1875,40 +1902,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M543"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.77734375" customWidth="1"/>
-    <col min="2" max="2" width="28.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="33.6" x14ac:dyDescent="0.65">
+    <row r="2" spans="1:6" ht="33.75" x14ac:dyDescent="0.5">
       <c r="A2" s="22" t="s">
         <v>367</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
         <v>372</v>
       </c>
       <c r="B6" s="26"/>
       <c r="C6" s="26"/>
     </row>
-    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>71</v>
       </c>
@@ -1925,7 +1952,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>369</v>
       </c>
@@ -1942,7 +1969,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>373</v>
       </c>
@@ -1956,7 +1983,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>375</v>
       </c>
@@ -1970,7 +1997,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>75</v>
       </c>
@@ -1978,7 +2005,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>76</v>
       </c>
@@ -1986,7 +2013,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>77</v>
       </c>
@@ -1994,7 +2021,7 @@
         <v>45565</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>78</v>
       </c>
@@ -2002,7 +2029,7 @@
         <v>45688</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>79</v>
       </c>
@@ -2010,7 +2037,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>80</v>
       </c>
@@ -2018,12 +2045,12 @@
         <v>189</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>82</v>
       </c>
@@ -2031,7 +2058,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="11"/>
       <c r="B28" s="11" t="s">
         <v>138</v>
@@ -2048,7 +2075,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="12"/>
       <c r="B29" s="12" t="s">
         <v>138</v>
@@ -2065,7 +2092,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
         <v>138</v>
@@ -2082,7 +2109,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="10"/>
       <c r="B31" s="10" t="s">
         <v>139</v>
@@ -2099,7 +2126,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
       <c r="B32" s="12" t="s">
         <v>139</v>
@@ -2116,7 +2143,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="11" t="s">
         <v>139</v>
@@ -2133,12 +2160,12 @@
         <v>336</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>0</v>
       </c>
@@ -2152,7 +2179,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="13"/>
       <c r="B37" s="11" t="s">
         <v>27</v>
@@ -2164,7 +2191,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
       <c r="B38" s="11" t="s">
         <v>3</v>
@@ -2176,7 +2203,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="11"/>
       <c r="B39" s="11" t="s">
         <v>4</v>
@@ -2188,7 +2215,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="11"/>
       <c r="B40" s="11" t="s">
         <v>5</v>
@@ -2200,7 +2227,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
       <c r="B41" s="11" t="s">
         <v>337</v>
@@ -2212,7 +2239,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="13"/>
       <c r="B42" s="11" t="s">
         <v>1</v>
@@ -2226,7 +2253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="13"/>
       <c r="B43" s="11"/>
       <c r="C43" s="11" t="s">
@@ -2238,7 +2265,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="11"/>
       <c r="B44" s="11"/>
       <c r="C44" s="11" t="s">
@@ -2250,7 +2277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="11"/>
       <c r="B45" s="11"/>
       <c r="C45" s="11" t="s">
@@ -2262,7 +2289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="11"/>
       <c r="B46" s="11"/>
       <c r="C46" s="11" t="s">
@@ -2274,7 +2301,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="11"/>
       <c r="B47" s="11"/>
       <c r="C47" s="11" t="s">
@@ -2286,7 +2313,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="11"/>
       <c r="B48" s="11"/>
       <c r="C48" s="11" t="s">
@@ -2298,7 +2325,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="11"/>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
@@ -2311,7 +2338,7 @@
       </c>
       <c r="F49" s="11"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="11"/>
       <c r="E50">
         <f>SUM(E36:E49)</f>
@@ -2322,14 +2349,14 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:12" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>339</v>
       </c>
       <c r="K52"/>
       <c r="L52"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
         <v>111</v>
       </c>
@@ -2348,7 +2375,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="14"/>
       <c r="B54" s="14" t="s">
         <v>236</v>
@@ -2363,7 +2390,7 @@
       </c>
       <c r="G54" s="27"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="14"/>
       <c r="B55" s="14"/>
       <c r="C55" s="12" t="s">
@@ -2376,7 +2403,7 @@
       </c>
       <c r="G55" s="27"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="14"/>
       <c r="B56" s="12"/>
       <c r="C56" s="12" t="s">
@@ -2389,7 +2416,7 @@
       </c>
       <c r="G56" s="27"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="14"/>
       <c r="B57" s="14"/>
       <c r="C57" s="12" t="s">
@@ -2402,7 +2429,7 @@
       </c>
       <c r="G57" s="27"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="14"/>
       <c r="B58" s="14"/>
       <c r="C58" s="12" t="s">
@@ -2415,7 +2442,7 @@
       </c>
       <c r="G58" s="27"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="14"/>
       <c r="B59" s="14"/>
       <c r="C59" s="12" t="s">
@@ -2428,7 +2455,7 @@
       </c>
       <c r="G59" s="27"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="14"/>
       <c r="B60" s="14"/>
       <c r="C60" s="12" t="s">
@@ -2441,7 +2468,7 @@
       </c>
       <c r="G60" s="27"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="14"/>
       <c r="B61" s="14"/>
       <c r="C61" s="12" t="s">
@@ -2454,7 +2481,7 @@
       </c>
       <c r="G61" s="27"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="14"/>
       <c r="B62" s="14"/>
       <c r="C62" s="12" t="s">
@@ -2467,7 +2494,7 @@
       </c>
       <c r="G62" s="27"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="14"/>
       <c r="B63" s="14" t="s">
         <v>223</v>
@@ -2482,7 +2509,7 @@
       </c>
       <c r="G63" s="27"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="14"/>
       <c r="B64" s="14"/>
       <c r="C64" s="12" t="s">
@@ -2495,7 +2522,7 @@
       </c>
       <c r="G64" s="27"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="14"/>
       <c r="B65" s="14"/>
       <c r="C65" s="12" t="s">
@@ -2508,7 +2535,7 @@
       </c>
       <c r="G65" s="27"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="14"/>
       <c r="B66" s="14"/>
       <c r="C66" s="12"/>
@@ -2522,7 +2549,7 @@
       <c r="F66" s="12"/>
       <c r="G66" s="27"/>
     </row>
-    <row r="67" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="E67">
@@ -2536,14 +2563,14 @@
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
     </row>
-    <row r="68" spans="1:13" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:13" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>340</v>
       </c>
       <c r="K68"/>
       <c r="L68"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="str">
         <f>$A$68</f>
         <v>Document Manufacturing and Assembly</v>
@@ -2560,7 +2587,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="9"/>
       <c r="B70" s="9" t="s">
         <v>236</v>
@@ -2574,7 +2601,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="9"/>
       <c r="B71" s="9"/>
       <c r="C71" s="10" t="s">
@@ -2586,7 +2613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="9"/>
       <c r="B72" s="9"/>
       <c r="C72" s="10" t="s">
@@ -2598,7 +2625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="9"/>
       <c r="B73" s="9"/>
       <c r="C73" s="10" t="s">
@@ -2610,7 +2637,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="9"/>
       <c r="B74" s="9"/>
       <c r="C74" s="10" t="s">
@@ -2622,7 +2649,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="9"/>
       <c r="B75" s="9"/>
       <c r="C75" s="10"/>
@@ -2635,7 +2662,7 @@
       </c>
       <c r="F75" s="10"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="E76">
@@ -2647,15 +2674,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
     </row>
-    <row r="78" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="13" t="s">
         <v>283</v>
       </c>
@@ -2671,7 +2698,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="13"/>
       <c r="B80" s="11"/>
       <c r="C80" s="11" t="s">
@@ -2683,7 +2710,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="13"/>
       <c r="B81" s="11"/>
       <c r="C81" s="11" t="s">
@@ -2695,7 +2722,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="13"/>
       <c r="B82" s="13" t="s">
         <v>236</v>
@@ -2709,7 +2736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="13"/>
       <c r="B83" s="13"/>
       <c r="C83" s="11" t="s">
@@ -2721,7 +2748,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="13"/>
       <c r="B84" s="13"/>
       <c r="C84" s="11" t="s">
@@ -2733,7 +2760,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="13"/>
       <c r="B85" s="13"/>
       <c r="C85" s="11" t="s">
@@ -2745,7 +2772,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="13"/>
       <c r="B86" s="13"/>
       <c r="C86" s="13"/>
@@ -2758,7 +2785,7 @@
       </c>
       <c r="F86" s="13"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="E87">
@@ -2770,18 +2797,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A89" s="21" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="14" t="s">
         <v>6</v>
       </c>
@@ -2795,7 +2822,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="12"/>
       <c r="B92" s="12"/>
       <c r="C92" s="12" t="s">
@@ -2807,7 +2834,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="12"/>
       <c r="B93" s="12"/>
       <c r="C93" s="12" t="s">
@@ -2819,7 +2846,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="12"/>
       <c r="B94" s="12"/>
       <c r="C94" s="12" t="s">
@@ -2831,7 +2858,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="12"/>
       <c r="B95" s="12"/>
       <c r="C95" s="12" t="s">
@@ -2843,7 +2870,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="12"/>
       <c r="B96" s="12"/>
       <c r="C96" s="12" t="s">
@@ -2855,7 +2882,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="12"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
@@ -2868,7 +2895,7 @@
       </c>
       <c r="F97" s="12"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E98">
         <f>SUM(E91:E97)</f>
         <v>0</v>
@@ -2878,12 +2905,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="9" t="s">
         <v>273</v>
       </c>
@@ -2897,7 +2924,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="9"/>
       <c r="B101" s="10" t="s">
         <v>13</v>
@@ -2909,7 +2936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="10"/>
       <c r="B102" s="10" t="s">
         <v>14</v>
@@ -2921,7 +2948,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="10"/>
       <c r="B103" s="10" t="s">
         <v>15</v>
@@ -2933,7 +2960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="10"/>
       <c r="B104" s="10" t="s">
         <v>16</v>
@@ -2945,7 +2972,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="10"/>
       <c r="B105" s="10" t="s">
         <v>17</v>
@@ -2957,7 +2984,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="10"/>
       <c r="B106" s="10" t="s">
         <v>19</v>
@@ -2969,7 +2996,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="10"/>
       <c r="B107" s="16" t="s">
         <v>18</v>
@@ -2981,7 +3008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="10"/>
       <c r="B108" s="16"/>
       <c r="C108" s="10"/>
@@ -2993,7 +3020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E109">
         <f>SUM(E100:E108)</f>
         <v>0</v>
@@ -3003,7 +3030,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="13" t="s">
         <v>299</v>
       </c>
@@ -3026,7 +3053,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="13" t="s">
         <v>295</v>
       </c>
@@ -3043,7 +3070,7 @@
       </c>
       <c r="G114" s="28"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="11"/>
       <c r="B115" s="11"/>
       <c r="C115" s="11" t="s">
@@ -3058,7 +3085,7 @@
       </c>
       <c r="G115" s="28"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="11"/>
       <c r="B116" s="11"/>
       <c r="C116" s="11" t="s">
@@ -3073,7 +3100,7 @@
       </c>
       <c r="G116" s="28"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="13"/>
       <c r="B117" s="11"/>
       <c r="C117" s="11" t="s">
@@ -3088,7 +3115,7 @@
       </c>
       <c r="G117" s="28"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="11"/>
       <c r="B118" s="11"/>
       <c r="C118" s="11" t="s">
@@ -3105,7 +3132,7 @@
       </c>
       <c r="G118" s="28"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="11"/>
       <c r="B119" s="11"/>
       <c r="C119" s="11"/>
@@ -3120,7 +3147,7 @@
       </c>
       <c r="G119" s="28"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
       <c r="B120" s="11"/>
       <c r="C120" s="11"/>
@@ -3135,7 +3162,7 @@
       </c>
       <c r="G120" s="28"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="13"/>
       <c r="B121" s="11"/>
       <c r="C121" s="11"/>
@@ -3150,7 +3177,7 @@
       </c>
       <c r="G121" s="28"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="13"/>
       <c r="B122" s="11"/>
       <c r="C122" s="11" t="s">
@@ -3165,7 +3192,7 @@
       </c>
       <c r="G122" s="28"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="11"/>
       <c r="B123" s="11"/>
       <c r="C123" s="11"/>
@@ -3178,7 +3205,7 @@
       </c>
       <c r="G123" s="28"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E124">
         <f>SUM(E117:E123)</f>
         <v>0</v>
@@ -3189,10 +3216,10 @@
       </c>
       <c r="G124" s="28"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G125" s="28"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="14" t="s">
         <v>298</v>
       </c>
@@ -3211,7 +3238,7 @@
       </c>
       <c r="G126" s="28"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="14" t="s">
         <v>352</v>
       </c>
@@ -3226,7 +3253,7 @@
       </c>
       <c r="G127" s="28"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="14"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12" t="s">
@@ -3239,7 +3266,7 @@
       </c>
       <c r="G128" s="28"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="14"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12" t="s">
@@ -3254,7 +3281,7 @@
       </c>
       <c r="G129" s="28"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12" t="s">
@@ -3269,7 +3296,7 @@
       </c>
       <c r="G130" s="28"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="12"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12" t="s">
@@ -3284,7 +3311,7 @@
       </c>
       <c r="G131" s="28"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="12"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12" t="s">
@@ -3299,7 +3326,7 @@
       </c>
       <c r="G132" s="28"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12" t="s">
@@ -3312,7 +3339,7 @@
       </c>
       <c r="G133" s="28"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12" t="s">
@@ -3327,7 +3354,7 @@
       </c>
       <c r="G134" s="28"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="12"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
@@ -3340,7 +3367,7 @@
       </c>
       <c r="G135" s="28"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E136">
         <f>SUM(E126:E135)</f>
         <v>0</v>
@@ -3351,10 +3378,10 @@
       </c>
       <c r="G136" s="28"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G137" s="28"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="9" t="s">
         <v>351</v>
       </c>
@@ -3375,7 +3402,7 @@
       </c>
       <c r="G138" s="28"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="10" t="str">
         <f>$A$127</f>
         <v>e.g. camera, IMU, SPI</v>
@@ -3395,7 +3422,7 @@
       </c>
       <c r="G139" s="28"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="10"/>
       <c r="B140" s="10"/>
       <c r="C140" s="10" t="str">
@@ -3412,7 +3439,7 @@
       </c>
       <c r="G140" s="28"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="9"/>
       <c r="B141" s="10"/>
       <c r="C141" s="10" t="str">
@@ -3429,7 +3456,7 @@
       </c>
       <c r="G141" s="28"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="9"/>
       <c r="B142" s="10"/>
       <c r="C142" s="10" t="str">
@@ -3446,7 +3473,7 @@
       </c>
       <c r="G142" s="28"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="9"/>
       <c r="B143" s="10"/>
       <c r="C143" s="10" t="str">
@@ -3461,7 +3488,7 @@
       </c>
       <c r="G143" s="28"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="9"/>
       <c r="B144" s="10"/>
       <c r="C144" s="10" t="str">
@@ -3478,7 +3505,7 @@
       </c>
       <c r="G144" s="28"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="10"/>
       <c r="B145" s="10"/>
       <c r="C145" s="10" t="str">
@@ -3495,7 +3522,7 @@
       </c>
       <c r="G145" s="28"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="10"/>
       <c r="B146" s="10"/>
       <c r="C146" s="10" t="str">
@@ -3512,7 +3539,7 @@
       </c>
       <c r="G146" s="28"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="10"/>
       <c r="B147" s="10"/>
       <c r="C147" s="10"/>
@@ -3525,7 +3552,7 @@
       </c>
       <c r="G147" s="28"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E148">
         <f>SUM(E138:E147)</f>
         <v>0</v>
@@ -3536,9 +3563,9 @@
       </c>
       <c r="G148" s="28"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="13" t="str">
-        <f t="shared" ref="A149:A150" si="2">A138</f>
+        <f t="shared" ref="A149" si="2">A138</f>
         <v>domain sensor/actor</v>
       </c>
       <c r="B149" s="13" t="str">
@@ -3557,7 +3584,7 @@
       </c>
       <c r="G149" s="28"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="13" t="s">
         <v>391</v>
       </c>
@@ -3574,7 +3601,7 @@
       </c>
       <c r="G150" s="28"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="13"/>
       <c r="B151" s="13"/>
       <c r="C151" s="11" t="str">
@@ -3589,7 +3616,7 @@
       </c>
       <c r="G151" s="28"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="13"/>
       <c r="B152" s="13"/>
       <c r="C152" s="11" t="str">
@@ -3604,7 +3631,7 @@
       </c>
       <c r="G152" s="28"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="13"/>
       <c r="B153" s="13"/>
       <c r="C153" s="11" t="str">
@@ -3619,7 +3646,7 @@
       </c>
       <c r="G153" s="28"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="13"/>
       <c r="B154" s="13"/>
       <c r="C154" s="11" t="str">
@@ -3634,7 +3661,7 @@
       </c>
       <c r="G154" s="28"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="13"/>
       <c r="B155" s="13"/>
       <c r="C155" s="11" t="str">
@@ -3649,7 +3676,7 @@
       </c>
       <c r="G155" s="28"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="13"/>
       <c r="B156" s="13"/>
       <c r="C156" s="11" t="str">
@@ -3664,7 +3691,7 @@
       </c>
       <c r="G156" s="28"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="13"/>
       <c r="B157" s="13"/>
       <c r="C157" s="11" t="str">
@@ -3679,7 +3706,7 @@
       </c>
       <c r="G157" s="28"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="13"/>
       <c r="B158" s="13"/>
       <c r="C158" s="11"/>
@@ -3693,7 +3720,7 @@
       <c r="F158" s="11"/>
       <c r="G158" s="28"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="E159">
@@ -3706,7 +3733,7 @@
       </c>
       <c r="G159" s="28"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="14" t="s">
         <v>301</v>
       </c>
@@ -3723,7 +3750,7 @@
       </c>
       <c r="G160" s="28"/>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="14" t="s">
         <v>302</v>
       </c>
@@ -3738,7 +3765,7 @@
       </c>
       <c r="G161" s="28"/>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="14"/>
       <c r="B162" s="12"/>
       <c r="C162" s="12" t="s">
@@ -3751,7 +3778,7 @@
       </c>
       <c r="G162" s="28"/>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="14"/>
       <c r="B163" s="12"/>
       <c r="C163" s="12" t="s">
@@ -3764,7 +3791,7 @@
       </c>
       <c r="G163" s="28"/>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="14"/>
       <c r="B164" s="12"/>
       <c r="C164" s="12" t="s">
@@ -3777,7 +3804,7 @@
       </c>
       <c r="G164" s="28"/>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="14"/>
       <c r="B165" s="12"/>
       <c r="C165" s="12" t="s">
@@ -3790,7 +3817,7 @@
       </c>
       <c r="G165" s="28"/>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="14"/>
       <c r="B166" s="12"/>
       <c r="C166" s="12" t="s">
@@ -3803,7 +3830,7 @@
       </c>
       <c r="G166" s="28"/>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="14"/>
       <c r="B167" s="12"/>
       <c r="C167" s="12" t="s">
@@ -3820,7 +3847,7 @@
       </c>
       <c r="G167" s="28"/>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="12"/>
       <c r="B168" s="12"/>
       <c r="C168" s="12"/>
@@ -3835,7 +3862,7 @@
       </c>
       <c r="G168" s="28"/>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" s="12"/>
       <c r="B169" s="12"/>
       <c r="C169" s="12" t="s">
@@ -3850,7 +3877,7 @@
       </c>
       <c r="G169" s="28"/>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" s="12"/>
       <c r="B170" s="12"/>
       <c r="C170" s="12" t="s">
@@ -3865,7 +3892,7 @@
       </c>
       <c r="G170" s="28"/>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" s="12"/>
       <c r="B171" s="12"/>
       <c r="C171" s="12" t="s">
@@ -3880,7 +3907,7 @@
       </c>
       <c r="G171" s="28"/>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" s="12"/>
       <c r="B172" s="12"/>
       <c r="C172" s="12"/>
@@ -3893,7 +3920,7 @@
       </c>
       <c r="G172" s="28"/>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E173">
         <f>SUM(E160:E172)</f>
         <v>0</v>
@@ -3904,20 +3931,20 @@
       </c>
       <c r="G173" s="28"/>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G174" s="28"/>
     </row>
-    <row r="175" spans="1:12" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:12" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A175" s="5" t="s">
         <v>307</v>
       </c>
       <c r="K175"/>
       <c r="L175"/>
     </row>
-    <row r="176" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="13" t="s">
         <v>21</v>
       </c>
@@ -3931,7 +3958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="11"/>
       <c r="B178" s="11"/>
       <c r="C178" s="11" t="s">
@@ -3943,7 +3970,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="11"/>
       <c r="B179" s="11"/>
       <c r="C179" s="11" t="s">
@@ -3955,7 +3982,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="11"/>
       <c r="B180" s="11"/>
       <c r="C180" s="11" t="s">
@@ -3967,7 +3994,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="11"/>
       <c r="B181" s="11"/>
       <c r="C181" s="11" t="s">
@@ -3979,7 +4006,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="11"/>
       <c r="B182" s="11"/>
       <c r="C182" s="11" t="s">
@@ -3991,7 +4018,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="11"/>
       <c r="B183" s="11"/>
       <c r="C183" s="11" t="s">
@@ -4003,7 +4030,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="11"/>
       <c r="B184" s="11"/>
       <c r="C184" s="11" t="s">
@@ -4015,7 +4042,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="11"/>
       <c r="B185" s="11"/>
       <c r="C185" s="11"/>
@@ -4027,7 +4054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E186">
         <f>SUM(E177:E185)</f>
         <v>0</v>
@@ -4037,12 +4064,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A188" s="5" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="9" t="s">
         <v>176</v>
       </c>
@@ -4059,7 +4086,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="9" t="s">
         <v>290</v>
       </c>
@@ -4074,7 +4101,7 @@
       </c>
       <c r="G190" s="29"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="9"/>
       <c r="B191" s="9"/>
       <c r="C191" s="10" t="s">
@@ -4087,7 +4114,7 @@
       </c>
       <c r="G191" s="29"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="9"/>
       <c r="B192" s="9"/>
       <c r="C192" s="10" t="s">
@@ -4100,7 +4127,7 @@
       </c>
       <c r="G192" s="29"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="9"/>
       <c r="B193" s="9"/>
       <c r="C193" s="10" t="s">
@@ -4113,7 +4140,7 @@
       </c>
       <c r="G193" s="29"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="9"/>
       <c r="B194" s="9"/>
       <c r="C194" s="10" t="s">
@@ -4126,7 +4153,7 @@
       </c>
       <c r="G194" s="29"/>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="9"/>
       <c r="B195" s="9"/>
       <c r="C195" s="10"/>
@@ -4140,7 +4167,7 @@
       <c r="F195" s="10"/>
       <c r="G195" s="29"/>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="E196">
@@ -4153,7 +4180,7 @@
       </c>
       <c r="G196" s="29"/>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="9" t="s">
         <v>176</v>
       </c>
@@ -4168,7 +4195,7 @@
       </c>
       <c r="G197" s="29"/>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="9" t="s">
         <v>292</v>
       </c>
@@ -4183,7 +4210,7 @@
       </c>
       <c r="G198" s="29"/>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="9" t="s">
         <v>291</v>
       </c>
@@ -4198,7 +4225,7 @@
       </c>
       <c r="G199" s="29"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="9"/>
       <c r="B200" s="9"/>
       <c r="C200" s="10" t="s">
@@ -4211,7 +4238,7 @@
       </c>
       <c r="G200" s="29"/>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" s="9"/>
       <c r="B201" s="9"/>
       <c r="C201" s="10" t="s">
@@ -4224,7 +4251,7 @@
       </c>
       <c r="G201" s="29"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="9"/>
       <c r="B202" s="9"/>
       <c r="C202" s="10" t="s">
@@ -4237,7 +4264,7 @@
       </c>
       <c r="G202" s="29"/>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="9"/>
       <c r="B203" s="9"/>
       <c r="C203" s="10"/>
@@ -4251,7 +4278,7 @@
       <c r="F203" s="10"/>
       <c r="G203" s="29"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="E204">
@@ -4264,12 +4291,12 @@
       </c>
       <c r="G204" s="29"/>
     </row>
-    <row r="205" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A205" s="5" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="7" t="s">
         <v>28</v>
       </c>
@@ -4281,7 +4308,7 @@
       <c r="E206" s="8"/>
       <c r="F206" s="8"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="8"/>
       <c r="B207" s="8"/>
       <c r="C207" s="8" t="s">
@@ -4293,7 +4320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="8"/>
       <c r="B208" s="8"/>
       <c r="C208" s="8" t="s">
@@ -4303,7 +4330,7 @@
       <c r="E208" s="8"/>
       <c r="F208" s="8"/>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A209" s="8"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8" t="s">
@@ -4313,7 +4340,7 @@
       <c r="E209" s="8"/>
       <c r="F209" s="8"/>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A210" s="8"/>
       <c r="B210" s="8"/>
       <c r="C210" s="8" t="s">
@@ -4325,18 +4352,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
       <c r="F211">
         <f>SUM(F206:F210)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="212" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A212" s="5" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A213" s="13" t="s">
         <v>325</v>
       </c>
@@ -4350,7 +4377,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A214" s="13"/>
       <c r="B214" s="11"/>
       <c r="C214" s="11"/>
@@ -4362,7 +4389,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A215" s="13"/>
       <c r="B215" s="11"/>
       <c r="C215" s="11"/>
@@ -4374,7 +4401,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A216" s="13"/>
       <c r="B216" s="11"/>
       <c r="C216" s="11"/>
@@ -4386,7 +4413,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A217" s="13"/>
       <c r="B217" s="11"/>
       <c r="C217" s="11"/>
@@ -4398,7 +4425,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A218" s="13"/>
       <c r="B218" s="11"/>
       <c r="C218" s="11"/>
@@ -4411,7 +4438,7 @@
       </c>
       <c r="F218" s="11"/>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="E219">
         <f>-SUM(E213:E218)</f>
@@ -4423,7 +4450,7 @@
       </c>
       <c r="M219" s="19"/>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A221" s="9" t="s">
         <v>66</v>
       </c>
@@ -4437,7 +4464,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A222" s="9"/>
       <c r="B222" s="10" t="s">
         <v>42</v>
@@ -4449,7 +4476,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A223" s="9"/>
       <c r="B223" s="10" t="s">
         <v>328</v>
@@ -4461,7 +4488,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A224" s="9"/>
       <c r="B224" s="10" t="s">
         <v>67</v>
@@ -4473,7 +4500,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="9"/>
       <c r="B225" s="10"/>
       <c r="C225" s="10"/>
@@ -4486,7 +4513,7 @@
       </c>
       <c r="F225" s="10"/>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="E226">
         <f>-SUM(E221:E225)</f>
@@ -4497,7 +4524,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="9" t="s">
         <v>261</v>
       </c>
@@ -4515,7 +4542,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="10"/>
       <c r="B228" s="10"/>
       <c r="C228" s="10"/>
@@ -4527,7 +4554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="10"/>
       <c r="B229" s="10"/>
       <c r="C229" s="10"/>
@@ -4539,7 +4566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="10"/>
       <c r="B230" s="10"/>
       <c r="C230" s="10"/>
@@ -4551,7 +4578,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="10"/>
       <c r="B231" s="10"/>
       <c r="C231" s="10"/>
@@ -4563,7 +4590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="10"/>
       <c r="B232" s="10"/>
       <c r="C232" s="10"/>
@@ -4575,7 +4602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="10"/>
       <c r="B233" s="10"/>
       <c r="C233" s="10" t="s">
@@ -4589,7 +4616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="10"/>
       <c r="B234" s="10"/>
       <c r="C234" s="10"/>
@@ -4601,7 +4628,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="10"/>
       <c r="B235" s="10"/>
       <c r="C235" s="10"/>
@@ -4613,7 +4640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="10"/>
       <c r="B236" s="10"/>
       <c r="C236" s="10"/>
@@ -4625,7 +4652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="10"/>
       <c r="B237" s="10"/>
       <c r="C237" s="10"/>
@@ -4637,7 +4664,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="10"/>
       <c r="B238" s="10"/>
       <c r="C238" s="10"/>
@@ -4650,7 +4677,7 @@
       </c>
       <c r="F238" s="10"/>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E239">
         <f>SUM(E227:E232)</f>
         <v>0</v>
@@ -4660,7 +4687,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="7" t="s">
         <v>261</v>
       </c>
@@ -4674,7 +4701,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="8"/>
       <c r="B241" s="7" t="s">
         <v>20</v>
@@ -4688,7 +4715,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="8"/>
       <c r="B242" s="8"/>
       <c r="C242" s="8" t="s">
@@ -4700,7 +4727,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="8"/>
       <c r="B243" s="8"/>
       <c r="C243" s="8" t="s">
@@ -4712,7 +4739,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="8"/>
       <c r="B244" s="8"/>
       <c r="C244" s="8" t="s">
@@ -4724,7 +4751,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="8"/>
       <c r="B245" s="8"/>
       <c r="C245" s="8" t="s">
@@ -4736,7 +4763,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="8"/>
       <c r="B246" s="8"/>
       <c r="C246" s="8" t="s">
@@ -4748,7 +4775,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="8"/>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4761,7 +4788,7 @@
       </c>
       <c r="F247" s="8"/>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E248">
         <f>SUM(E240:E246)</f>
         <v>0</v>
@@ -4771,7 +4798,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="7" t="s">
         <v>66</v>
       </c>
@@ -4785,7 +4812,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="7"/>
       <c r="B250" s="8" t="s">
         <v>42</v>
@@ -4797,7 +4824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="7"/>
       <c r="B251" s="8" t="s">
         <v>217</v>
@@ -4809,7 +4836,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="7"/>
       <c r="B252" s="8" t="s">
         <v>140</v>
@@ -4821,7 +4848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="7"/>
       <c r="B253" s="8" t="s">
         <v>65</v>
@@ -4833,7 +4860,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="7"/>
       <c r="B254" s="8" t="s">
         <v>67</v>
@@ -4845,7 +4872,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="7"/>
       <c r="B255" s="7" t="s">
         <v>49</v>
@@ -4859,7 +4886,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="7"/>
       <c r="B256" s="7"/>
       <c r="C256" s="8" t="s">
@@ -4871,7 +4898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="7"/>
       <c r="B257" s="7"/>
       <c r="C257" s="8" t="s">
@@ -4883,7 +4910,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="7"/>
       <c r="B258" s="7"/>
       <c r="C258" s="8" t="s">
@@ -4895,7 +4922,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="7"/>
       <c r="B259" s="7"/>
       <c r="C259" s="8" t="s">
@@ -4907,7 +4934,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="7"/>
       <c r="B260" s="7"/>
       <c r="C260" s="8" t="s">
@@ -4921,7 +4948,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="7"/>
       <c r="B261" s="7"/>
       <c r="C261" s="8"/>
@@ -4933,7 +4960,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="7"/>
       <c r="B262" s="7"/>
       <c r="C262" s="8"/>
@@ -4945,7 +4972,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="7"/>
       <c r="B263" s="7"/>
       <c r="C263" s="8"/>
@@ -4957,7 +4984,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="7"/>
       <c r="B264" s="7"/>
       <c r="C264" s="8"/>
@@ -4969,7 +4996,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="7"/>
       <c r="B265" s="7"/>
       <c r="C265" s="8"/>
@@ -4982,7 +5009,7 @@
       </c>
       <c r="F265" s="8"/>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E266">
         <f>SUM(E249:E265)</f>
         <v>0</v>
@@ -4992,7 +5019,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="7" t="s">
         <v>267</v>
       </c>
@@ -5006,7 +5033,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="7" t="s">
         <v>269</v>
       </c>
@@ -5020,7 +5047,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="7"/>
       <c r="B270" s="8" t="s">
         <v>318</v>
@@ -5032,7 +5059,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="8"/>
       <c r="B271" s="8" t="s">
         <v>316</v>
@@ -5044,7 +5071,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="8"/>
       <c r="B272" s="8" t="s">
         <v>317</v>
@@ -5056,7 +5083,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="8"/>
       <c r="B273" s="8"/>
       <c r="C273" s="8"/>
@@ -5069,7 +5096,7 @@
       </c>
       <c r="F273" s="8"/>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E274">
         <f>SUM(E268:E272)</f>
         <v>0</v>
@@ -5079,7 +5106,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="9" t="s">
         <v>34</v>
       </c>
@@ -5093,7 +5120,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="10"/>
       <c r="B276" s="10" t="s">
         <v>221</v>
@@ -5105,7 +5132,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="9"/>
       <c r="B277" s="10" t="s">
         <v>285</v>
@@ -5119,7 +5146,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="10"/>
       <c r="B278" s="10" t="s">
         <v>278</v>
@@ -5133,7 +5160,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="9"/>
       <c r="B279" s="10" t="s">
         <v>200</v>
@@ -5147,7 +5174,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="9"/>
       <c r="B280" s="10" t="s">
         <v>286</v>
@@ -5161,7 +5188,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="9"/>
       <c r="B281" s="10" t="s">
         <v>287</v>
@@ -5173,7 +5200,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="10"/>
       <c r="B282" s="10" t="s">
         <v>279</v>
@@ -5185,7 +5212,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="10"/>
       <c r="B283" s="10" t="s">
         <v>280</v>
@@ -5197,7 +5224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="10"/>
       <c r="B284" s="10" t="s">
         <v>36</v>
@@ -5209,7 +5236,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="10"/>
       <c r="B285" s="10"/>
       <c r="C285" s="10"/>
@@ -5222,7 +5249,7 @@
       </c>
       <c r="F285" s="10"/>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E286">
         <f>SUM(E275:E284)</f>
         <v>0</v>
@@ -5232,12 +5259,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="289" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A289" s="5" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="12" t="s">
         <v>191</v>
       </c>
@@ -5251,7 +5278,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="14"/>
       <c r="B291" s="14"/>
       <c r="C291" s="12" t="s">
@@ -5263,7 +5290,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="14"/>
       <c r="B292" s="14"/>
       <c r="C292" s="12" t="s">
@@ -5275,7 +5302,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="14"/>
       <c r="B293" s="14"/>
       <c r="C293" s="12" t="s">
@@ -5287,7 +5314,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="14"/>
       <c r="B294" s="14"/>
       <c r="C294" s="12" t="s">
@@ -5299,7 +5326,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="12"/>
       <c r="B295" s="12" t="s">
         <v>192</v>
@@ -5313,7 +5340,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="12"/>
       <c r="B296" s="12"/>
       <c r="C296" s="12" t="s">
@@ -5325,7 +5352,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="12"/>
       <c r="B297" s="12"/>
       <c r="C297" s="12" t="s">
@@ -5337,7 +5364,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="12"/>
       <c r="B298" s="12" t="s">
         <v>194</v>
@@ -5351,7 +5378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="12"/>
       <c r="B299" s="12"/>
       <c r="C299" s="12" t="s">
@@ -5363,7 +5390,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="12"/>
       <c r="B300" s="12"/>
       <c r="C300" s="12" t="s">
@@ -5375,7 +5402,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="14" t="s">
         <v>49</v>
       </c>
@@ -5389,7 +5416,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="14"/>
       <c r="B302" s="14"/>
       <c r="C302" s="12" t="s">
@@ -5401,7 +5428,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="14"/>
       <c r="B303" s="14"/>
       <c r="C303" s="12" t="s">
@@ -5413,7 +5440,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="14"/>
       <c r="B304" s="14"/>
       <c r="C304" s="12" t="s">
@@ -5425,7 +5452,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A305" s="14"/>
       <c r="B305" s="14"/>
       <c r="C305" s="12" t="s">
@@ -5437,7 +5464,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A306" s="14"/>
       <c r="B306" s="14"/>
       <c r="C306" s="12" t="s">
@@ -5451,7 +5478,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A307" s="14"/>
       <c r="B307" s="14"/>
       <c r="C307" s="12"/>
@@ -5463,7 +5490,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A308" s="14"/>
       <c r="B308" s="14"/>
       <c r="C308" s="12"/>
@@ -5475,7 +5502,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A309" s="14"/>
       <c r="B309" s="14"/>
       <c r="C309" s="12"/>
@@ -5487,7 +5514,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A310" s="14"/>
       <c r="B310" s="14"/>
       <c r="C310" s="12"/>
@@ -5499,7 +5526,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A311" s="12"/>
       <c r="B311" s="12"/>
       <c r="C311" s="12"/>
@@ -5512,7 +5539,7 @@
       </c>
       <c r="F311" s="12"/>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="E312">
         <f>SUM(E290:E311)</f>
         <v>0</v>
@@ -5524,7 +5551,7 @@
       <c r="K312" s="17"/>
       <c r="L312" s="17"/>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A313" s="9" t="s">
         <v>355</v>
       </c>
@@ -5540,7 +5567,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A314" s="10" t="s">
         <v>302</v>
       </c>
@@ -5554,7 +5581,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A315" s="9"/>
       <c r="B315" s="10"/>
       <c r="C315" s="10" t="s">
@@ -5566,7 +5593,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A316" s="10"/>
       <c r="B316" s="10"/>
       <c r="C316" s="10" t="s">
@@ -5580,7 +5607,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A317" s="10"/>
       <c r="B317" s="10"/>
       <c r="C317" s="10" t="s">
@@ -5594,7 +5621,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A318" s="9"/>
       <c r="B318" s="10"/>
       <c r="C318" s="10" t="s">
@@ -5608,7 +5635,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A319" s="9"/>
       <c r="B319" s="10"/>
       <c r="C319" s="10" t="s">
@@ -5622,7 +5649,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A320" s="10"/>
       <c r="B320" s="10"/>
       <c r="C320" s="10"/>
@@ -5634,7 +5661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="E321">
         <f>SUM(E313:E320)</f>
         <v>0</v>
@@ -5646,15 +5673,15 @@
       <c r="K321" s="17"/>
       <c r="L321" s="17"/>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="K322" s="17"/>
       <c r="L322" s="17"/>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="K323" s="17"/>
       <c r="L323" s="17"/>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A324" s="13" t="s">
         <v>271</v>
       </c>
@@ -5668,7 +5695,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A325" s="11"/>
       <c r="B325" s="11" t="s">
         <v>273</v>
@@ -5680,7 +5707,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A326" s="11"/>
       <c r="B326" s="11" t="s">
         <v>110</v>
@@ -5692,7 +5719,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A327" s="13" t="s">
         <v>274</v>
       </c>
@@ -5706,7 +5733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A328" s="11"/>
       <c r="B328" s="11" t="s">
         <v>276</v>
@@ -5718,7 +5745,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A329" s="13" t="s">
         <v>319</v>
       </c>
@@ -5732,7 +5759,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A330" s="11"/>
       <c r="B330" s="11"/>
       <c r="C330" s="11" t="s">
@@ -5744,7 +5771,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A331" s="11"/>
       <c r="B331" s="11"/>
       <c r="C331" s="11" t="s">
@@ -5756,7 +5783,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A332" s="11"/>
       <c r="B332" s="11"/>
       <c r="C332" s="11"/>
@@ -5769,7 +5796,7 @@
       </c>
       <c r="F332" s="11"/>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E333">
         <f>SUM(E324:E328)</f>
         <v>0</v>
@@ -5779,14 +5806,14 @@
         <v>60</v>
       </c>
     </row>
-    <row r="335" spans="1:12" s="17" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:12" s="17" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A335" s="5" t="s">
         <v>251</v>
       </c>
       <c r="K335"/>
       <c r="L335"/>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A336" s="11" t="s">
         <v>153</v>
       </c>
@@ -5804,7 +5831,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="11"/>
       <c r="B337" s="11"/>
       <c r="C337" s="11" t="s">
@@ -5818,7 +5845,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="11"/>
       <c r="B338" s="11"/>
       <c r="C338" s="11" t="s">
@@ -5832,7 +5859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="11"/>
       <c r="B339" s="11"/>
       <c r="C339" s="11" t="s">
@@ -5846,7 +5873,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="11"/>
       <c r="B340" s="11"/>
       <c r="C340" s="11" t="s">
@@ -5860,7 +5887,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="11"/>
       <c r="B341" s="11"/>
       <c r="C341" s="11" t="s">
@@ -5874,7 +5901,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="11"/>
       <c r="B342" s="11"/>
       <c r="C342" s="11"/>
@@ -5886,7 +5913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E343">
         <f>SUM(E336:E342)</f>
         <v>0</v>
@@ -5896,7 +5923,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="13" t="s">
         <v>40</v>
       </c>
@@ -5910,7 +5937,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="13"/>
       <c r="B345" s="13"/>
       <c r="C345" s="15" t="s">
@@ -5922,7 +5949,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="13"/>
       <c r="B346" s="13"/>
       <c r="C346" s="15" t="s">
@@ -5934,7 +5961,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="13"/>
       <c r="B347" s="13"/>
       <c r="C347" s="11"/>
@@ -5942,7 +5969,7 @@
       <c r="E347" s="11"/>
       <c r="F347" s="11"/>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="13" t="s">
         <v>103</v>
       </c>
@@ -5956,7 +5983,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="13"/>
       <c r="B349" s="13"/>
       <c r="C349" s="11" t="s">
@@ -5968,7 +5995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="13"/>
       <c r="B350" s="13"/>
       <c r="C350" s="11" t="s">
@@ -5980,7 +6007,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="13"/>
       <c r="B351" s="13"/>
       <c r="C351" s="11"/>
@@ -5988,7 +6015,7 @@
       <c r="E351" s="11"/>
       <c r="F351" s="11"/>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="13" t="s">
         <v>199</v>
       </c>
@@ -6002,7 +6029,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A353" s="13"/>
       <c r="B353" s="13"/>
       <c r="C353" s="11" t="s">
@@ -6014,7 +6041,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A354" s="13"/>
       <c r="B354" s="13"/>
       <c r="C354" s="11" t="s">
@@ -6026,7 +6053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A355" s="13"/>
       <c r="B355" s="13"/>
       <c r="C355" s="11"/>
@@ -6039,7 +6066,7 @@
       </c>
       <c r="F355" s="11"/>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="E356">
@@ -6052,7 +6079,7 @@
       </c>
       <c r="M356" s="19"/>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A357" s="14" t="s">
         <v>41</v>
       </c>
@@ -6067,7 +6094,7 @@
       </c>
       <c r="M357" s="19"/>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A358" s="14"/>
       <c r="B358" s="14"/>
       <c r="C358" s="12" t="s">
@@ -6080,7 +6107,7 @@
       </c>
       <c r="M358" s="19"/>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A359" s="14"/>
       <c r="B359" s="14"/>
       <c r="C359" s="12"/>
@@ -6094,7 +6121,7 @@
       <c r="F359" s="12"/>
       <c r="M359" s="19"/>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="E360">
@@ -6106,7 +6133,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>5</v>
       </c>
@@ -6122,7 +6149,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>314</v>
       </c>
@@ -6136,7 +6163,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="10"/>
       <c r="C364" s="10" t="s">
@@ -6148,7 +6175,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="10"/>
       <c r="C365" s="10" t="s">
@@ -6160,7 +6187,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="10"/>
       <c r="C366" s="10" t="s">
@@ -6172,7 +6199,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="10"/>
       <c r="C367" s="10" t="s">
@@ -6184,7 +6211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="10"/>
       <c r="C368" s="10" t="s">
@@ -6196,7 +6223,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="10"/>
       <c r="C369" s="10" t="s">
@@ -6208,7 +6235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="10"/>
       <c r="C370" s="10"/>
@@ -6221,7 +6248,7 @@
       </c>
       <c r="F370" s="10"/>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="E371">
@@ -6233,7 +6260,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="13" t="s">
         <v>54</v>
@@ -6247,7 +6274,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="11"/>
       <c r="C373" s="11" t="s">
@@ -6259,7 +6286,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="11"/>
       <c r="C374" s="11" t="s">
@@ -6271,7 +6298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="11"/>
       <c r="C375" s="11" t="s">
@@ -6283,7 +6310,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="11"/>
       <c r="C376" s="11" t="s">
@@ -6295,7 +6322,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="11"/>
       <c r="C377" s="11" t="s">
@@ -6307,7 +6334,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="11"/>
       <c r="C378" s="11" t="s">
@@ -6319,7 +6346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="11"/>
       <c r="C379" s="11" t="s">
@@ -6331,7 +6358,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="11"/>
       <c r="C380" s="11"/>
@@ -6344,7 +6371,7 @@
       </c>
       <c r="F380" s="11"/>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="E381">
@@ -6356,7 +6383,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="14" t="s">
         <v>54</v>
@@ -6370,7 +6397,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="12"/>
       <c r="C383" s="12" t="s">
@@ -6382,7 +6409,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="12"/>
       <c r="C384" s="12" t="s">
@@ -6394,7 +6421,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="12"/>
       <c r="C385" s="12" t="str">
@@ -6407,7 +6434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="12"/>
       <c r="C386" s="12" t="str">
@@ -6420,7 +6447,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="12"/>
       <c r="C387" s="12" t="str">
@@ -6433,7 +6460,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="12"/>
       <c r="C388" s="12" t="str">
@@ -6446,7 +6473,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="12"/>
       <c r="C389" s="12" t="s">
@@ -6458,7 +6485,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="12"/>
       <c r="C390" s="12"/>
@@ -6471,7 +6498,7 @@
       </c>
       <c r="F390" s="12"/>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="E391">
@@ -6483,12 +6510,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="393" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A393" s="5" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" s="7" t="s">
         <v>309</v>
       </c>
@@ -6498,7 +6525,7 @@
       <c r="E394" s="8"/>
       <c r="F394" s="8"/>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" s="7"/>
       <c r="B395" s="8"/>
       <c r="C395" s="8"/>
@@ -6506,7 +6533,7 @@
       <c r="E395" s="8"/>
       <c r="F395" s="8"/>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" s="7"/>
       <c r="B396" s="8" t="s">
         <v>157</v>
@@ -6516,7 +6543,7 @@
       <c r="E396" s="8"/>
       <c r="F396" s="8"/>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" s="7"/>
       <c r="B397" s="8" t="s">
         <v>158</v>
@@ -6528,7 +6555,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" s="7"/>
       <c r="B398" s="8" t="s">
         <v>159</v>
@@ -6540,7 +6567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A399" s="7"/>
       <c r="B399" s="8" t="s">
         <v>160</v>
@@ -6554,7 +6581,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A400" s="7"/>
       <c r="B400" s="8"/>
       <c r="C400" s="8" t="s">
@@ -6566,7 +6593,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" s="7"/>
       <c r="B401" s="8" t="s">
         <v>162</v>
@@ -6580,7 +6607,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" s="7"/>
       <c r="B402" s="8"/>
       <c r="C402" s="8" t="s">
@@ -6592,7 +6619,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" s="7"/>
       <c r="B403" s="8"/>
       <c r="C403" s="8" t="s">
@@ -6604,7 +6631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" s="7"/>
       <c r="B404" s="8"/>
       <c r="C404" s="8" t="s">
@@ -6616,7 +6643,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" s="7"/>
       <c r="B405" s="8"/>
       <c r="C405" s="8" t="s">
@@ -6628,7 +6655,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" s="7"/>
       <c r="B406" s="8"/>
       <c r="C406" s="8"/>
@@ -6641,7 +6668,7 @@
       </c>
       <c r="F406" s="8"/>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A407" s="1"/>
       <c r="E407">
         <f>SUM(E394:E406)</f>
@@ -6652,10 +6679,10 @@
         <v>65</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" s="1"/>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" s="9" t="s">
         <v>90</v>
       </c>
@@ -6669,7 +6696,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" s="10"/>
       <c r="B410" s="10" t="s">
         <v>92</v>
@@ -6681,7 +6708,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" s="10"/>
       <c r="B411" s="10" t="s">
         <v>93</v>
@@ -6693,7 +6720,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" s="10"/>
       <c r="B412" s="10" t="s">
         <v>94</v>
@@ -6705,7 +6732,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" s="9" t="s">
         <v>102</v>
       </c>
@@ -6715,7 +6742,7 @@
       <c r="E413" s="10"/>
       <c r="F413" s="10"/>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" s="9"/>
       <c r="B414" s="10" t="s">
         <v>118</v>
@@ -6727,7 +6754,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" s="10"/>
       <c r="B415" s="10" t="s">
         <v>119</v>
@@ -6741,7 +6768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A416" s="10"/>
       <c r="B416" s="10" t="s">
         <v>120</v>
@@ -6755,7 +6782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" s="10"/>
       <c r="B417" s="10" t="s">
         <v>121</v>
@@ -6767,7 +6794,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A418" s="10"/>
       <c r="B418" s="10"/>
       <c r="C418" s="10"/>
@@ -6775,7 +6802,7 @@
       <c r="E418" s="10"/>
       <c r="F418" s="10"/>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" s="10"/>
       <c r="B419" s="10"/>
       <c r="C419" s="10"/>
@@ -6788,7 +6815,7 @@
       </c>
       <c r="F419" s="10"/>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E420">
         <f>SUM(E409:E419)</f>
         <v>0</v>
@@ -6798,12 +6825,12 @@
         <v>550</v>
       </c>
     </row>
-    <row r="421" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A421" s="5" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" s="7" t="s">
         <v>36</v>
       </c>
@@ -6819,7 +6846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" s="7"/>
       <c r="B423" s="8"/>
       <c r="C423" s="8" t="s">
@@ -6831,7 +6858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" s="7"/>
       <c r="B424" s="8"/>
       <c r="C424" s="8" t="s">
@@ -6843,7 +6870,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" s="7"/>
       <c r="B425" s="8"/>
       <c r="C425" s="8" t="s">
@@ -6855,7 +6882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" s="7"/>
       <c r="B426" s="8"/>
       <c r="C426" s="8" t="s">
@@ -6867,7 +6894,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A427" s="8"/>
       <c r="B427" s="8" t="s">
         <v>12</v>
@@ -6879,7 +6906,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" s="8"/>
       <c r="B428" s="8" t="s">
         <v>39</v>
@@ -6891,7 +6918,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" s="8"/>
       <c r="B429" s="8" t="s">
         <v>68</v>
@@ -6903,7 +6930,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A430" s="8"/>
       <c r="B430" s="8" t="s">
         <v>85</v>
@@ -6915,7 +6942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A431" s="8"/>
       <c r="B431" s="8"/>
       <c r="C431" s="8"/>
@@ -6928,7 +6955,7 @@
       </c>
       <c r="F431" s="8"/>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E432">
         <f>SUM(E422:E431)</f>
         <v>0</v>
@@ -6938,7 +6965,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" s="8" t="s">
         <v>122</v>
       </c>
@@ -6952,7 +6979,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" s="8"/>
       <c r="B434" s="8" t="s">
         <v>124</v>
@@ -6964,7 +6991,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" s="8"/>
       <c r="B435" s="8" t="s">
         <v>125</v>
@@ -6976,7 +7003,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" s="8"/>
       <c r="B436" s="8" t="s">
         <v>126</v>
@@ -6988,7 +7015,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" s="8"/>
       <c r="B437" s="8" t="s">
         <v>127</v>
@@ -7000,7 +7027,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A438" s="8"/>
       <c r="B438" s="8" t="s">
         <v>228</v>
@@ -7012,7 +7039,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A439" s="8"/>
       <c r="B439" s="8" t="s">
         <v>128</v>
@@ -7024,7 +7051,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A440" s="8"/>
       <c r="B440" s="8" t="s">
         <v>229</v>
@@ -7036,7 +7063,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A441" s="8"/>
       <c r="B441" s="8" t="s">
         <v>129</v>
@@ -7048,7 +7075,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A442" s="8"/>
       <c r="B442" s="8"/>
       <c r="C442" s="8"/>
@@ -7061,7 +7088,7 @@
       </c>
       <c r="F442" s="8"/>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E443">
         <f>SUM(E433:E442)</f>
         <v>0</v>
@@ -7071,7 +7098,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A444" s="8" t="s">
         <v>130</v>
       </c>
@@ -7085,7 +7112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A445" s="8"/>
       <c r="B445" s="8" t="s">
         <v>132</v>
@@ -7097,7 +7124,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A446" s="8"/>
       <c r="B446" s="8" t="s">
         <v>7</v>
@@ -7109,7 +7136,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A447" s="8"/>
       <c r="B447" s="8" t="s">
         <v>133</v>
@@ -7121,7 +7148,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A448" s="8"/>
       <c r="B448" s="8" t="s">
         <v>134</v>
@@ -7133,7 +7160,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A449" s="8"/>
       <c r="B449" s="8" t="s">
         <v>135</v>
@@ -7145,7 +7172,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A450" s="8"/>
       <c r="B450" s="8" t="s">
         <v>136</v>
@@ -7157,7 +7184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A451" s="8"/>
       <c r="B451" s="8"/>
       <c r="C451" s="8"/>
@@ -7170,7 +7197,7 @@
       </c>
       <c r="F451" s="8"/>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E452">
         <f>SUM(E444:E451)</f>
         <v>0</v>
@@ -7180,7 +7207,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A453" s="7" t="s">
         <v>312</v>
       </c>
@@ -7196,7 +7223,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A454" s="7"/>
       <c r="B454" s="7"/>
       <c r="C454" s="8"/>
@@ -7208,7 +7235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A455" s="7"/>
       <c r="B455" s="7"/>
       <c r="C455" s="8"/>
@@ -7220,7 +7247,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A456" s="7"/>
       <c r="B456" s="7"/>
       <c r="C456" s="8" t="s">
@@ -7234,7 +7261,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A457" s="7"/>
       <c r="B457" s="7"/>
       <c r="C457" s="8"/>
@@ -7246,7 +7273,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A458" s="7"/>
       <c r="B458" s="7"/>
       <c r="C458" s="8"/>
@@ -7258,7 +7285,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A459" s="7"/>
       <c r="B459" s="7"/>
       <c r="C459" s="8"/>
@@ -7270,7 +7297,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A460" s="7"/>
       <c r="B460" s="7"/>
       <c r="C460" s="8"/>
@@ -7282,7 +7309,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E461">
         <f>SUM(E453:E460)</f>
         <v>0</v>
@@ -7292,12 +7319,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="462" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A462" s="5" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A463" s="7" t="s">
         <v>235</v>
       </c>
@@ -7313,7 +7340,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A464" s="7"/>
       <c r="B464" s="8"/>
       <c r="C464" s="8" t="s">
@@ -7325,7 +7352,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A465" s="8"/>
       <c r="B465" s="7" t="s">
         <v>236</v>
@@ -7339,7 +7366,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A466" s="8"/>
       <c r="B466" s="8"/>
       <c r="C466" s="8" t="s">
@@ -7351,7 +7378,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" s="8"/>
       <c r="B467" s="8"/>
       <c r="C467" s="8" t="s">
@@ -7363,7 +7390,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A468" s="8"/>
       <c r="B468" s="8"/>
       <c r="C468" s="8" t="s">
@@ -7375,7 +7402,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" s="8"/>
       <c r="B469" s="8"/>
       <c r="C469" s="8" t="s">
@@ -7387,7 +7414,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A470" s="8"/>
       <c r="B470" s="8"/>
       <c r="C470" s="8"/>
@@ -7399,7 +7426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E471">
         <f>SUM(E463:E470)</f>
         <v>0</v>
@@ -7409,12 +7436,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" s="14" t="s">
         <v>330</v>
       </c>
@@ -7430,7 +7457,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A474" s="14" t="s">
         <v>332</v>
       </c>
@@ -7448,7 +7475,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A475" s="14"/>
       <c r="B475" s="12"/>
       <c r="C475" s="12" t="s">
@@ -7462,7 +7489,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A476" s="1"/>
       <c r="D476" s="20" t="s">
         <v>206</v>
@@ -7472,7 +7499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E477">
         <f>SUM(E473:E476)</f>
         <v>0</v>
@@ -7482,12 +7509,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="479" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A479" s="5" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" s="14" t="s">
         <v>235</v>
       </c>
@@ -7496,12 +7523,17 @@
       </c>
       <c r="C480" s="12"/>
       <c r="D480" s="12"/>
-      <c r="E480" s="12"/>
+      <c r="E480" s="12">
+        <v>10</v>
+      </c>
       <c r="F480" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H480" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" s="14" t="s">
         <v>240</v>
       </c>
@@ -7510,120 +7542,163 @@
       </c>
       <c r="C481" s="12"/>
       <c r="D481" s="12"/>
-      <c r="E481" s="12"/>
+      <c r="E481" s="12">
+        <v>3</v>
+      </c>
       <c r="F481" s="12">
         <v>5</v>
       </c>
-    </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A482" s="12"/>
+      <c r="H481" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A482" s="12" t="s">
+        <v>392</v>
+      </c>
       <c r="B482" s="12" t="s">
         <v>238</v>
       </c>
       <c r="C482" s="12"/>
       <c r="D482" s="12"/>
-      <c r="E482" s="12"/>
+      <c r="E482" s="12">
+        <v>0</v>
+      </c>
       <c r="F482" s="12">
         <v>5</v>
       </c>
-    </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H482" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A483" s="12"/>
       <c r="B483" s="12" t="s">
         <v>237</v>
       </c>
       <c r="C483" s="12"/>
       <c r="D483" s="12"/>
-      <c r="E483" s="12"/>
+      <c r="E483" s="12">
+        <v>3</v>
+      </c>
       <c r="F483" s="12">
         <v>5</v>
       </c>
-    </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H483" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A484" s="12"/>
       <c r="B484" s="12" t="s">
         <v>239</v>
       </c>
       <c r="C484" s="12"/>
       <c r="D484" s="12"/>
-      <c r="E484" s="12"/>
+      <c r="E484" s="12">
+        <v>2</v>
+      </c>
       <c r="F484" s="12">
         <v>5</v>
       </c>
-    </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H484" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A485" s="12"/>
       <c r="B485" s="12" t="s">
         <v>241</v>
       </c>
       <c r="C485" s="12"/>
       <c r="D485" s="12"/>
-      <c r="E485" s="12"/>
+      <c r="E485" s="12">
+        <v>2</v>
+      </c>
       <c r="F485" s="12">
         <v>5</v>
       </c>
-    </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H485" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A486" s="12"/>
       <c r="B486" s="12" t="s">
         <v>242</v>
       </c>
       <c r="C486" s="12"/>
       <c r="D486" s="12"/>
-      <c r="E486" s="12"/>
+      <c r="E486" s="12">
+        <v>0</v>
+      </c>
       <c r="F486" s="12">
         <v>5</v>
       </c>
-    </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H486" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A487" s="12"/>
       <c r="B487" s="12" t="s">
         <v>25</v>
       </c>
       <c r="C487" s="12"/>
       <c r="D487" s="12"/>
-      <c r="E487" s="12"/>
+      <c r="E487" s="12">
+        <v>0</v>
+      </c>
       <c r="F487" s="12">
         <v>5</v>
       </c>
-    </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H487" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A488" s="12"/>
       <c r="B488" s="12" t="s">
         <v>26</v>
       </c>
       <c r="C488" s="12"/>
       <c r="D488" s="12"/>
-      <c r="E488" s="12"/>
+      <c r="E488" s="12">
+        <v>0</v>
+      </c>
       <c r="F488" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A489" s="12"/>
       <c r="B489" s="12" t="s">
         <v>243</v>
       </c>
       <c r="C489" s="12"/>
       <c r="D489" s="12"/>
-      <c r="E489" s="12"/>
+      <c r="E489" s="12">
+        <v>0</v>
+      </c>
       <c r="F489" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A490" s="12"/>
       <c r="B490" s="12" t="s">
         <v>244</v>
       </c>
       <c r="C490" s="12"/>
       <c r="D490" s="12"/>
-      <c r="E490" s="12"/>
+      <c r="E490" s="12">
+        <v>5</v>
+      </c>
       <c r="F490" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" s="12"/>
       <c r="B491" s="12"/>
       <c r="C491" s="12"/>
@@ -7631,21 +7706,21 @@
         <v>206</v>
       </c>
       <c r="E491" s="20">
-        <f>-SUM(E484:E490)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.3">
+        <f>-SUM(E484:E490)*0</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E492">
         <f>SUM(E480:E491)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F492">
         <f>SUM(F480:F491)</f>
         <v>60</v>
       </c>
     </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A494" s="9" t="s">
         <v>235</v>
       </c>
@@ -7662,7 +7737,7 @@
       </c>
       <c r="H494" s="18"/>
     </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A495" s="9" t="s">
         <v>240</v>
       </c>
@@ -7679,7 +7754,7 @@
       </c>
       <c r="H495" s="18"/>
     </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A496" s="10" t="s">
         <v>387</v>
       </c>
@@ -7696,7 +7771,7 @@
       </c>
       <c r="H496" s="18"/>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A497" s="10"/>
       <c r="B497" s="10" t="s">
         <v>237</v>
@@ -7711,7 +7786,7 @@
       </c>
       <c r="H497" s="18"/>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A498" s="10"/>
       <c r="B498" s="10" t="s">
         <v>239</v>
@@ -7725,7 +7800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A499" s="10"/>
       <c r="B499" s="10" t="s">
         <v>241</v>
@@ -7739,7 +7814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A500" s="10"/>
       <c r="B500" s="10" t="s">
         <v>242</v>
@@ -7753,7 +7828,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="501" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A501" s="10"/>
       <c r="B501" s="10" t="s">
         <v>25</v>
@@ -7767,7 +7842,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A502" s="10"/>
       <c r="B502" s="10" t="s">
         <v>26</v>
@@ -7781,7 +7856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="503" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A503" s="10"/>
       <c r="B503" s="10" t="s">
         <v>243</v>
@@ -7798,7 +7873,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A504" s="10"/>
       <c r="B504" s="10" t="s">
         <v>244</v>
@@ -7812,7 +7887,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A505" s="10"/>
       <c r="B505" s="10"/>
       <c r="C505" s="10"/>
@@ -7833,7 +7908,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E506">
         <f>SUM(E494:E505)</f>
         <v>16.5</v>
@@ -7843,7 +7918,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A508" s="13" t="s">
         <v>235</v>
       </c>
@@ -7859,7 +7934,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="509" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A509" s="13" t="s">
         <v>240</v>
       </c>
@@ -7878,7 +7953,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="510" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A510" s="11" t="s">
         <v>380</v>
       </c>
@@ -7894,7 +7969,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="511" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A511" s="11"/>
       <c r="B511" s="11" t="s">
         <v>237</v>
@@ -7911,7 +7986,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="512" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A512" s="11"/>
       <c r="B512" s="11" t="s">
         <v>239</v>
@@ -7925,7 +8000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="513" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A513" s="11"/>
       <c r="B513" s="11" t="s">
         <v>241</v>
@@ -7942,7 +8017,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="514" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A514" s="11"/>
       <c r="B514" s="11" t="s">
         <v>242</v>
@@ -7956,7 +8031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="515" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A515" s="11"/>
       <c r="B515" s="11" t="s">
         <v>25</v>
@@ -7973,7 +8048,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="516" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A516" s="11"/>
       <c r="B516" s="11" t="s">
         <v>26</v>
@@ -7990,7 +8065,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="517" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A517" s="11"/>
       <c r="B517" s="11" t="s">
         <v>243</v>
@@ -8007,7 +8082,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="518" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A518" s="11"/>
       <c r="B518" s="11" t="s">
         <v>244</v>
@@ -8021,7 +8096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="519" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A519" s="11"/>
       <c r="B519" s="11"/>
       <c r="C519" s="11"/>
@@ -8040,7 +8115,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="520" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E520">
         <f>SUM(E508:E519)</f>
         <v>24.5</v>
@@ -8050,7 +8125,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="524" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A524" s="7"/>
       <c r="B524" t="s">
         <v>183</v>
@@ -8068,7 +8143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A525" s="9" t="s">
         <v>364</v>
       </c>
@@ -8088,7 +8163,7 @@
         <v>-0.11762820512820513</v>
       </c>
     </row>
-    <row r="526" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A526" s="13" t="s">
         <v>365</v>
       </c>
@@ -8108,7 +8183,7 @@
         <v>-0.15462555066079295</v>
       </c>
     </row>
-    <row r="527" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A527" s="14" t="s">
         <v>363</v>
       </c>
@@ -8117,7 +8192,7 @@
       </c>
       <c r="E527">
         <f>E67+E29+E32+E98+E136+E173+E391+E312+E360+E492</f>
-        <v>-200</v>
+        <v>-175</v>
       </c>
       <c r="F527">
         <f>F67+F29+F32+F98+F136+F173+F391+F312+F360+F492+F477</f>
@@ -8125,10 +8200,10 @@
       </c>
       <c r="H527" s="18">
         <f>(E527+E524)/(F527+F524)</f>
-        <v>-0.17699115044247787</v>
-      </c>
-    </row>
-    <row r="531" spans="4:7" x14ac:dyDescent="0.3">
+        <v>-0.15486725663716813</v>
+      </c>
+    </row>
+    <row r="531" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F531" t="s">
         <v>230</v>
       </c>
@@ -8136,7 +8211,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="532" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="532" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D532" t="s">
         <v>232</v>
       </c>
@@ -8144,7 +8219,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="533" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="533" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F533" s="23">
         <v>0.45</v>
       </c>
@@ -8152,7 +8227,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="534" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="534" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F534" s="23">
         <f>F533+(F542-F533)/9</f>
         <v>0.5</v>
@@ -8161,7 +8236,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="535" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="535" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F535" s="23">
         <f>F534+(F542-F533)/9</f>
         <v>0.55000000000000004</v>
@@ -8170,7 +8245,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="536" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="536" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F536" s="23">
         <f>F535+(F542-F533)/9</f>
         <v>0.60000000000000009</v>
@@ -8179,7 +8254,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="537" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="537" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F537" s="23">
         <f>F536+(F542-F533)/9</f>
         <v>0.65000000000000013</v>
@@ -8188,7 +8263,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="538" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="538" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F538" s="23">
         <f>F537+(F542-F533)/9</f>
         <v>0.70000000000000018</v>
@@ -8197,7 +8272,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="539" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="539" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F539" s="23">
         <f>F538+(F542-F533)/9</f>
         <v>0.75000000000000022</v>
@@ -8206,7 +8281,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="540" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="540" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F540" s="23">
         <f>F539+(F542-F533)/9</f>
         <v>0.80000000000000027</v>
@@ -8215,7 +8290,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="541" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="541" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F541" s="23">
         <f>F540+(F542-F533)/9</f>
         <v>0.85000000000000031</v>
@@ -8224,7 +8299,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="542" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="542" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F542" s="23">
         <v>0.9</v>
       </c>
@@ -8232,7 +8307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="543" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="543" spans="4:7" x14ac:dyDescent="0.25">
       <c r="E543" t="s">
         <v>234</v>
       </c>
@@ -8262,14 +8337,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="19"/>
+    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.8" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:4" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="30" t="s">
         <v>223</v>
       </c>
@@ -8277,10 +8352,10 @@
       <c r="C1" s="30"/>
       <c r="D1" s="30"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>207</v>
       </c>
@@ -8288,7 +8363,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>38</v>
       </c>
@@ -8296,7 +8371,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>209</v>
       </c>
@@ -8304,7 +8379,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>210</v>
       </c>
@@ -8312,7 +8387,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>211</v>
       </c>
@@ -8320,7 +8395,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>212</v>
       </c>
@@ -8328,7 +8403,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>174</v>
       </c>
@@ -8336,7 +8411,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>208</v>
       </c>
@@ -8344,7 +8419,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>214</v>
       </c>
@@ -8352,7 +8427,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>213</v>
       </c>
@@ -8360,7 +8435,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>215</v>
       </c>
@@ -8368,7 +8443,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>216</v>
       </c>
@@ -8376,7 +8451,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>222</v>
       </c>
@@ -8384,7 +8459,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>224</v>
       </c>
@@ -8392,7 +8467,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>225</v>
       </c>
@@ -8400,7 +8475,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -8414,7 +8489,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
         <v>143</v>
       </c>
@@ -8422,7 +8497,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
         <v>144</v>
       </c>
@@ -8430,7 +8505,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>145</v>
       </c>
@@ -8441,7 +8516,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
         <v>147</v>
       </c>
@@ -8449,7 +8524,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>148</v>
       </c>
@@ -8457,7 +8532,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>149</v>
       </c>
@@ -8465,12 +8540,12 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>162</v>
       </c>
@@ -8481,7 +8556,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
         <v>166</v>
       </c>
@@ -8489,7 +8564,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
         <v>148</v>
       </c>
@@ -8497,7 +8572,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>220</v>
       </c>
@@ -8505,7 +8580,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>167</v>
       </c>
@@ -8516,7 +8591,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
         <v>169</v>
       </c>
@@ -8524,7 +8599,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
         <v>170</v>
       </c>

--- a/ProjectManagement/EvaluationHW.xlsx
+++ b/ProjectManagement/EvaluationHW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Wings_Hub\Wings-Hub\ML2425\ML24-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\Winter 2024-25\ML project\ML24-03-Car-Licence-Plate-Identification-with-a-Jetson-Nano\ProjectManagement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E029D6AF-5957-4AE4-9D0E-1807BE7F4E71}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08FB8EE-4C36-4475-BE82-367E1BCE2F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="2" r:id="rId1"/>
@@ -165,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="406">
   <si>
     <t>Literature</t>
   </si>
@@ -1368,6 +1368,21 @@
   </si>
   <si>
     <t>not used</t>
+  </si>
+  <si>
+    <t>EasyOCR</t>
+  </si>
+  <si>
+    <t>YOLOV5</t>
+  </si>
+  <si>
+    <t>CNN</t>
+  </si>
+  <si>
+    <t>Numpy</t>
+  </si>
+  <si>
+    <t>Pandas</t>
   </si>
 </sst>
 </file>
@@ -1622,8 +1637,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Link" xfId="1" builtinId="8"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1902,40 +1917,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M543"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.6640625" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="33.75" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:6" ht="33.6" x14ac:dyDescent="0.65">
       <c r="A2" s="22" t="s">
         <v>367</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="26" t="s">
         <v>372</v>
       </c>
       <c r="B6" s="26"/>
       <c r="C6" s="26"/>
     </row>
-    <row r="9" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>71</v>
       </c>
@@ -1952,7 +1967,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>369</v>
       </c>
@@ -1969,7 +1984,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>373</v>
       </c>
@@ -1983,7 +1998,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>375</v>
       </c>
@@ -1997,7 +2012,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>75</v>
       </c>
@@ -2005,7 +2020,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>76</v>
       </c>
@@ -2013,7 +2028,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>77</v>
       </c>
@@ -2021,7 +2036,7 @@
         <v>45565</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>78</v>
       </c>
@@ -2029,7 +2044,7 @@
         <v>45688</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>79</v>
       </c>
@@ -2037,7 +2052,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>80</v>
       </c>
@@ -2045,12 +2060,12 @@
         <v>189</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A25" s="6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>82</v>
       </c>
@@ -2058,7 +2073,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
       <c r="B28" s="11" t="s">
         <v>138</v>
@@ -2075,7 +2090,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="12"/>
       <c r="B29" s="12" t="s">
         <v>138</v>
@@ -2092,7 +2107,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
         <v>138</v>
@@ -2109,7 +2124,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="10"/>
       <c r="B31" s="10" t="s">
         <v>139</v>
@@ -2126,7 +2141,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="12"/>
       <c r="B32" s="12" t="s">
         <v>139</v>
@@ -2143,7 +2158,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="11"/>
       <c r="B33" s="11" t="s">
         <v>139</v>
@@ -2160,12 +2175,12 @@
         <v>336</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>0</v>
       </c>
@@ -2179,7 +2194,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>
       <c r="B37" s="11" t="s">
         <v>27</v>
@@ -2191,7 +2206,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="11"/>
       <c r="B38" s="11" t="s">
         <v>3</v>
@@ -2203,7 +2218,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="11"/>
       <c r="B39" s="11" t="s">
         <v>4</v>
@@ -2215,7 +2230,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="11"/>
       <c r="B40" s="11" t="s">
         <v>5</v>
@@ -2227,7 +2242,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="11"/>
       <c r="B41" s="11" t="s">
         <v>337</v>
@@ -2239,7 +2254,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>
       <c r="B42" s="11" t="s">
         <v>1</v>
@@ -2253,7 +2268,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>
       <c r="B43" s="11"/>
       <c r="C43" s="11" t="s">
@@ -2265,7 +2280,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="11"/>
       <c r="B44" s="11"/>
       <c r="C44" s="11" t="s">
@@ -2277,7 +2292,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="11"/>
       <c r="B45" s="11"/>
       <c r="C45" s="11" t="s">
@@ -2289,7 +2304,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="11"/>
       <c r="B46" s="11"/>
       <c r="C46" s="11" t="s">
@@ -2301,7 +2316,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="11"/>
       <c r="B47" s="11"/>
       <c r="C47" s="11" t="s">
@@ -2313,7 +2328,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="11"/>
       <c r="B48" s="11"/>
       <c r="C48" s="11" t="s">
@@ -2325,7 +2340,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="11"/>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
@@ -2338,7 +2353,7 @@
       </c>
       <c r="F49" s="11"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="11"/>
       <c r="E50">
         <f>SUM(E36:E49)</f>
@@ -2349,14 +2364,14 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:12" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>339</v>
       </c>
       <c r="K52"/>
       <c r="L52"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
         <v>111</v>
       </c>
@@ -2375,7 +2390,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="14"/>
       <c r="B54" s="14" t="s">
         <v>236</v>
@@ -2390,7 +2405,7 @@
       </c>
       <c r="G54" s="27"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="14"/>
       <c r="B55" s="14"/>
       <c r="C55" s="12" t="s">
@@ -2403,7 +2418,7 @@
       </c>
       <c r="G55" s="27"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="14"/>
       <c r="B56" s="12"/>
       <c r="C56" s="12" t="s">
@@ -2416,7 +2431,7 @@
       </c>
       <c r="G56" s="27"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="14"/>
       <c r="B57" s="14"/>
       <c r="C57" s="12" t="s">
@@ -2429,7 +2444,7 @@
       </c>
       <c r="G57" s="27"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="14"/>
       <c r="B58" s="14"/>
       <c r="C58" s="12" t="s">
@@ -2442,7 +2457,7 @@
       </c>
       <c r="G58" s="27"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="14"/>
       <c r="B59" s="14"/>
       <c r="C59" s="12" t="s">
@@ -2455,7 +2470,7 @@
       </c>
       <c r="G59" s="27"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="14"/>
       <c r="B60" s="14"/>
       <c r="C60" s="12" t="s">
@@ -2468,7 +2483,7 @@
       </c>
       <c r="G60" s="27"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="14"/>
       <c r="B61" s="14"/>
       <c r="C61" s="12" t="s">
@@ -2481,7 +2496,7 @@
       </c>
       <c r="G61" s="27"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="14"/>
       <c r="B62" s="14"/>
       <c r="C62" s="12" t="s">
@@ -2494,7 +2509,7 @@
       </c>
       <c r="G62" s="27"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="14"/>
       <c r="B63" s="14" t="s">
         <v>223</v>
@@ -2509,7 +2524,7 @@
       </c>
       <c r="G63" s="27"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="14"/>
       <c r="B64" s="14"/>
       <c r="C64" s="12" t="s">
@@ -2522,7 +2537,7 @@
       </c>
       <c r="G64" s="27"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="14"/>
       <c r="B65" s="14"/>
       <c r="C65" s="12" t="s">
@@ -2535,7 +2550,7 @@
       </c>
       <c r="G65" s="27"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="14"/>
       <c r="B66" s="14"/>
       <c r="C66" s="12"/>
@@ -2549,7 +2564,7 @@
       <c r="F66" s="12"/>
       <c r="G66" s="27"/>
     </row>
-    <row r="67" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="E67">
@@ -2563,14 +2578,14 @@
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
     </row>
-    <row r="68" spans="1:13" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
         <v>340</v>
       </c>
       <c r="K68"/>
       <c r="L68"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="str">
         <f>$A$68</f>
         <v>Document Manufacturing and Assembly</v>
@@ -2587,7 +2602,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="9"/>
       <c r="B70" s="9" t="s">
         <v>236</v>
@@ -2601,7 +2616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="9"/>
       <c r="B71" s="9"/>
       <c r="C71" s="10" t="s">
@@ -2613,7 +2628,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="9"/>
       <c r="B72" s="9"/>
       <c r="C72" s="10" t="s">
@@ -2625,7 +2640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="9"/>
       <c r="B73" s="9"/>
       <c r="C73" s="10" t="s">
@@ -2637,7 +2652,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="9"/>
       <c r="B74" s="9"/>
       <c r="C74" s="10" t="s">
@@ -2649,7 +2664,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="9"/>
       <c r="B75" s="9"/>
       <c r="C75" s="10"/>
@@ -2662,7 +2677,7 @@
       </c>
       <c r="F75" s="10"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="E76">
@@ -2674,15 +2689,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
     </row>
-    <row r="78" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="13" t="s">
         <v>283</v>
       </c>
@@ -2698,7 +2713,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="13"/>
       <c r="B80" s="11"/>
       <c r="C80" s="11" t="s">
@@ -2710,7 +2725,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="13"/>
       <c r="B81" s="11"/>
       <c r="C81" s="11" t="s">
@@ -2722,7 +2737,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="13"/>
       <c r="B82" s="13" t="s">
         <v>236</v>
@@ -2736,7 +2751,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="13"/>
       <c r="B83" s="13"/>
       <c r="C83" s="11" t="s">
@@ -2748,7 +2763,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="13"/>
       <c r="B84" s="13"/>
       <c r="C84" s="11" t="s">
@@ -2760,7 +2775,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="13"/>
       <c r="B85" s="13"/>
       <c r="C85" s="11" t="s">
@@ -2772,7 +2787,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="13"/>
       <c r="B86" s="13"/>
       <c r="C86" s="13"/>
@@ -2785,7 +2800,7 @@
       </c>
       <c r="F86" s="13"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="E87">
@@ -2797,18 +2812,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:6" ht="21" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="1:6" ht="21" x14ac:dyDescent="0.4">
       <c r="A89" s="21" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="14" t="s">
         <v>6</v>
       </c>
@@ -2822,7 +2837,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="12"/>
       <c r="B92" s="12"/>
       <c r="C92" s="12" t="s">
@@ -2834,7 +2849,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="12"/>
       <c r="B93" s="12"/>
       <c r="C93" s="12" t="s">
@@ -2846,7 +2861,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="12"/>
       <c r="B94" s="12"/>
       <c r="C94" s="12" t="s">
@@ -2858,7 +2873,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="12"/>
       <c r="B95" s="12"/>
       <c r="C95" s="12" t="s">
@@ -2870,7 +2885,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="12"/>
       <c r="B96" s="12"/>
       <c r="C96" s="12" t="s">
@@ -2882,7 +2897,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="12"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
@@ -2895,7 +2910,7 @@
       </c>
       <c r="F97" s="12"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E98">
         <f>SUM(E91:E97)</f>
         <v>0</v>
@@ -2905,12 +2920,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="9" t="s">
         <v>273</v>
       </c>
@@ -2924,7 +2939,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="9"/>
       <c r="B101" s="10" t="s">
         <v>13</v>
@@ -2936,7 +2951,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="10"/>
       <c r="B102" s="10" t="s">
         <v>14</v>
@@ -2948,7 +2963,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="10"/>
       <c r="B103" s="10" t="s">
         <v>15</v>
@@ -2960,7 +2975,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="10"/>
       <c r="B104" s="10" t="s">
         <v>16</v>
@@ -2972,7 +2987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="10"/>
       <c r="B105" s="10" t="s">
         <v>17</v>
@@ -2984,7 +2999,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="10"/>
       <c r="B106" s="10" t="s">
         <v>19</v>
@@ -2996,7 +3011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="10"/>
       <c r="B107" s="16" t="s">
         <v>18</v>
@@ -3008,7 +3023,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="10"/>
       <c r="B108" s="16"/>
       <c r="C108" s="10"/>
@@ -3020,7 +3035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E109">
         <f>SUM(E100:E108)</f>
         <v>0</v>
@@ -3030,7 +3045,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="13" t="s">
         <v>299</v>
       </c>
@@ -3053,7 +3068,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="13" t="s">
         <v>295</v>
       </c>
@@ -3070,7 +3085,7 @@
       </c>
       <c r="G114" s="28"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="11"/>
       <c r="B115" s="11"/>
       <c r="C115" s="11" t="s">
@@ -3085,7 +3100,7 @@
       </c>
       <c r="G115" s="28"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="11"/>
       <c r="B116" s="11"/>
       <c r="C116" s="11" t="s">
@@ -3100,7 +3115,7 @@
       </c>
       <c r="G116" s="28"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="13"/>
       <c r="B117" s="11"/>
       <c r="C117" s="11" t="s">
@@ -3115,7 +3130,7 @@
       </c>
       <c r="G117" s="28"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="11"/>
       <c r="B118" s="11"/>
       <c r="C118" s="11" t="s">
@@ -3132,7 +3147,7 @@
       </c>
       <c r="G118" s="28"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="11"/>
       <c r="B119" s="11"/>
       <c r="C119" s="11"/>
@@ -3147,7 +3162,7 @@
       </c>
       <c r="G119" s="28"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="13"/>
       <c r="B120" s="11"/>
       <c r="C120" s="11"/>
@@ -3162,7 +3177,7 @@
       </c>
       <c r="G120" s="28"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="13"/>
       <c r="B121" s="11"/>
       <c r="C121" s="11"/>
@@ -3177,7 +3192,7 @@
       </c>
       <c r="G121" s="28"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="13"/>
       <c r="B122" s="11"/>
       <c r="C122" s="11" t="s">
@@ -3192,7 +3207,7 @@
       </c>
       <c r="G122" s="28"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="11"/>
       <c r="B123" s="11"/>
       <c r="C123" s="11"/>
@@ -3205,7 +3220,7 @@
       </c>
       <c r="G123" s="28"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E124">
         <f>SUM(E117:E123)</f>
         <v>0</v>
@@ -3216,10 +3231,10 @@
       </c>
       <c r="G124" s="28"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G125" s="28"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="14" t="s">
         <v>298</v>
       </c>
@@ -3238,7 +3253,7 @@
       </c>
       <c r="G126" s="28"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="14" t="s">
         <v>352</v>
       </c>
@@ -3253,7 +3268,7 @@
       </c>
       <c r="G127" s="28"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="14"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12" t="s">
@@ -3266,7 +3281,7 @@
       </c>
       <c r="G128" s="28"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="14"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12" t="s">
@@ -3281,7 +3296,7 @@
       </c>
       <c r="G129" s="28"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12" t="s">
@@ -3296,7 +3311,7 @@
       </c>
       <c r="G130" s="28"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="12"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12" t="s">
@@ -3311,7 +3326,7 @@
       </c>
       <c r="G131" s="28"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="12"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12" t="s">
@@ -3326,7 +3341,7 @@
       </c>
       <c r="G132" s="28"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12" t="s">
@@ -3339,7 +3354,7 @@
       </c>
       <c r="G133" s="28"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12" t="s">
@@ -3354,7 +3369,7 @@
       </c>
       <c r="G134" s="28"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="12"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
@@ -3367,7 +3382,7 @@
       </c>
       <c r="G135" s="28"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E136">
         <f>SUM(E126:E135)</f>
         <v>0</v>
@@ -3378,10 +3393,10 @@
       </c>
       <c r="G136" s="28"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G137" s="28"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="9" t="s">
         <v>351</v>
       </c>
@@ -3402,7 +3417,7 @@
       </c>
       <c r="G138" s="28"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="10" t="str">
         <f>$A$127</f>
         <v>e.g. camera, IMU, SPI</v>
@@ -3422,7 +3437,7 @@
       </c>
       <c r="G139" s="28"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="10"/>
       <c r="B140" s="10"/>
       <c r="C140" s="10" t="str">
@@ -3439,7 +3454,7 @@
       </c>
       <c r="G140" s="28"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="9"/>
       <c r="B141" s="10"/>
       <c r="C141" s="10" t="str">
@@ -3456,7 +3471,7 @@
       </c>
       <c r="G141" s="28"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="9"/>
       <c r="B142" s="10"/>
       <c r="C142" s="10" t="str">
@@ -3473,7 +3488,7 @@
       </c>
       <c r="G142" s="28"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="9"/>
       <c r="B143" s="10"/>
       <c r="C143" s="10" t="str">
@@ -3488,7 +3503,7 @@
       </c>
       <c r="G143" s="28"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="9"/>
       <c r="B144" s="10"/>
       <c r="C144" s="10" t="str">
@@ -3505,7 +3520,7 @@
       </c>
       <c r="G144" s="28"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="10"/>
       <c r="B145" s="10"/>
       <c r="C145" s="10" t="str">
@@ -3522,7 +3537,7 @@
       </c>
       <c r="G145" s="28"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="10"/>
       <c r="B146" s="10"/>
       <c r="C146" s="10" t="str">
@@ -3539,7 +3554,7 @@
       </c>
       <c r="G146" s="28"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="10"/>
       <c r="B147" s="10"/>
       <c r="C147" s="10"/>
@@ -3552,7 +3567,7 @@
       </c>
       <c r="G147" s="28"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E148">
         <f>SUM(E138:E147)</f>
         <v>0</v>
@@ -3563,7 +3578,7 @@
       </c>
       <c r="G148" s="28"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="13" t="str">
         <f t="shared" ref="A149" si="2">A138</f>
         <v>domain sensor/actor</v>
@@ -3584,7 +3599,7 @@
       </c>
       <c r="G149" s="28"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="13" t="s">
         <v>391</v>
       </c>
@@ -3601,7 +3616,7 @@
       </c>
       <c r="G150" s="28"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="13"/>
       <c r="B151" s="13"/>
       <c r="C151" s="11" t="str">
@@ -3616,7 +3631,7 @@
       </c>
       <c r="G151" s="28"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="13"/>
       <c r="B152" s="13"/>
       <c r="C152" s="11" t="str">
@@ -3631,7 +3646,7 @@
       </c>
       <c r="G152" s="28"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="13"/>
       <c r="B153" s="13"/>
       <c r="C153" s="11" t="str">
@@ -3646,7 +3661,7 @@
       </c>
       <c r="G153" s="28"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="13"/>
       <c r="B154" s="13"/>
       <c r="C154" s="11" t="str">
@@ -3661,7 +3676,7 @@
       </c>
       <c r="G154" s="28"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="13"/>
       <c r="B155" s="13"/>
       <c r="C155" s="11" t="str">
@@ -3676,7 +3691,7 @@
       </c>
       <c r="G155" s="28"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="13"/>
       <c r="B156" s="13"/>
       <c r="C156" s="11" t="str">
@@ -3691,7 +3706,7 @@
       </c>
       <c r="G156" s="28"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="13"/>
       <c r="B157" s="13"/>
       <c r="C157" s="11" t="str">
@@ -3706,7 +3721,7 @@
       </c>
       <c r="G157" s="28"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="13"/>
       <c r="B158" s="13"/>
       <c r="C158" s="11"/>
@@ -3720,7 +3735,7 @@
       <c r="F158" s="11"/>
       <c r="G158" s="28"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="E159">
@@ -3733,7 +3748,7 @@
       </c>
       <c r="G159" s="28"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="14" t="s">
         <v>301</v>
       </c>
@@ -3750,7 +3765,7 @@
       </c>
       <c r="G160" s="28"/>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="14" t="s">
         <v>302</v>
       </c>
@@ -3765,7 +3780,7 @@
       </c>
       <c r="G161" s="28"/>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="14"/>
       <c r="B162" s="12"/>
       <c r="C162" s="12" t="s">
@@ -3778,7 +3793,7 @@
       </c>
       <c r="G162" s="28"/>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="14"/>
       <c r="B163" s="12"/>
       <c r="C163" s="12" t="s">
@@ -3791,7 +3806,7 @@
       </c>
       <c r="G163" s="28"/>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="14"/>
       <c r="B164" s="12"/>
       <c r="C164" s="12" t="s">
@@ -3804,7 +3819,7 @@
       </c>
       <c r="G164" s="28"/>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="14"/>
       <c r="B165" s="12"/>
       <c r="C165" s="12" t="s">
@@ -3817,7 +3832,7 @@
       </c>
       <c r="G165" s="28"/>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="14"/>
       <c r="B166" s="12"/>
       <c r="C166" s="12" t="s">
@@ -3830,7 +3845,7 @@
       </c>
       <c r="G166" s="28"/>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="14"/>
       <c r="B167" s="12"/>
       <c r="C167" s="12" t="s">
@@ -3847,7 +3862,7 @@
       </c>
       <c r="G167" s="28"/>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="12"/>
       <c r="B168" s="12"/>
       <c r="C168" s="12"/>
@@ -3862,7 +3877,7 @@
       </c>
       <c r="G168" s="28"/>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="12"/>
       <c r="B169" s="12"/>
       <c r="C169" s="12" t="s">
@@ -3877,7 +3892,7 @@
       </c>
       <c r="G169" s="28"/>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="12"/>
       <c r="B170" s="12"/>
       <c r="C170" s="12" t="s">
@@ -3892,7 +3907,7 @@
       </c>
       <c r="G170" s="28"/>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="12"/>
       <c r="B171" s="12"/>
       <c r="C171" s="12" t="s">
@@ -3907,7 +3922,7 @@
       </c>
       <c r="G171" s="28"/>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="12"/>
       <c r="B172" s="12"/>
       <c r="C172" s="12"/>
@@ -3920,7 +3935,7 @@
       </c>
       <c r="G172" s="28"/>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E173">
         <f>SUM(E160:E172)</f>
         <v>0</v>
@@ -3931,20 +3946,20 @@
       </c>
       <c r="G173" s="28"/>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="G174" s="28"/>
     </row>
-    <row r="175" spans="1:12" s="5" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" s="5" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A175" s="5" t="s">
         <v>307</v>
       </c>
       <c r="K175"/>
       <c r="L175"/>
     </row>
-    <row r="176" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" s="13" t="s">
         <v>21</v>
       </c>
@@ -3958,8 +3973,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A178" s="11"/>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A178" s="11" t="s">
+        <v>401</v>
+      </c>
       <c r="B178" s="11"/>
       <c r="C178" s="11" t="s">
         <v>23</v>
@@ -3970,8 +3987,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A179" s="11"/>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A179" s="11" t="s">
+        <v>402</v>
+      </c>
       <c r="B179" s="11"/>
       <c r="C179" s="11" t="s">
         <v>27</v>
@@ -3982,8 +4001,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A180" s="11"/>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A180" s="11" t="s">
+        <v>403</v>
+      </c>
       <c r="B180" s="11"/>
       <c r="C180" s="11" t="s">
         <v>22</v>
@@ -3994,7 +4015,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" s="11"/>
       <c r="B181" s="11"/>
       <c r="C181" s="11" t="s">
@@ -4006,7 +4027,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" s="11"/>
       <c r="B182" s="11"/>
       <c r="C182" s="11" t="s">
@@ -4018,7 +4039,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" s="11"/>
       <c r="B183" s="11"/>
       <c r="C183" s="11" t="s">
@@ -4030,7 +4051,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" s="11"/>
       <c r="B184" s="11"/>
       <c r="C184" s="11" t="s">
@@ -4042,7 +4063,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" s="11"/>
       <c r="B185" s="11"/>
       <c r="C185" s="11"/>
@@ -4054,7 +4075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E186">
         <f>SUM(E177:E185)</f>
         <v>0</v>
@@ -4064,12 +4085,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A188" s="5" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" s="9" t="s">
         <v>176</v>
       </c>
@@ -4086,7 +4107,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" s="9" t="s">
         <v>290</v>
       </c>
@@ -4101,7 +4122,7 @@
       </c>
       <c r="G190" s="29"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="9"/>
       <c r="B191" s="9"/>
       <c r="C191" s="10" t="s">
@@ -4114,7 +4135,7 @@
       </c>
       <c r="G191" s="29"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="9"/>
       <c r="B192" s="9"/>
       <c r="C192" s="10" t="s">
@@ -4127,7 +4148,7 @@
       </c>
       <c r="G192" s="29"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" s="9"/>
       <c r="B193" s="9"/>
       <c r="C193" s="10" t="s">
@@ -4140,7 +4161,7 @@
       </c>
       <c r="G193" s="29"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" s="9"/>
       <c r="B194" s="9"/>
       <c r="C194" s="10" t="s">
@@ -4153,7 +4174,7 @@
       </c>
       <c r="G194" s="29"/>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" s="9"/>
       <c r="B195" s="9"/>
       <c r="C195" s="10"/>
@@ -4167,7 +4188,7 @@
       <c r="F195" s="10"/>
       <c r="G195" s="29"/>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="E196">
@@ -4180,7 +4201,7 @@
       </c>
       <c r="G196" s="29"/>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" s="9" t="s">
         <v>176</v>
       </c>
@@ -4195,7 +4216,7 @@
       </c>
       <c r="G197" s="29"/>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" s="9" t="s">
         <v>292</v>
       </c>
@@ -4210,7 +4231,7 @@
       </c>
       <c r="G198" s="29"/>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="9" t="s">
         <v>291</v>
       </c>
@@ -4225,7 +4246,7 @@
       </c>
       <c r="G199" s="29"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="9"/>
       <c r="B200" s="9"/>
       <c r="C200" s="10" t="s">
@@ -4238,7 +4259,7 @@
       </c>
       <c r="G200" s="29"/>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" s="9"/>
       <c r="B201" s="9"/>
       <c r="C201" s="10" t="s">
@@ -4251,7 +4272,7 @@
       </c>
       <c r="G201" s="29"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" s="9"/>
       <c r="B202" s="9"/>
       <c r="C202" s="10" t="s">
@@ -4264,7 +4285,7 @@
       </c>
       <c r="G202" s="29"/>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="9"/>
       <c r="B203" s="9"/>
       <c r="C203" s="10"/>
@@ -4278,7 +4299,7 @@
       <c r="F203" s="10"/>
       <c r="G203" s="29"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="E204">
@@ -4291,12 +4312,12 @@
       </c>
       <c r="G204" s="29"/>
     </row>
-    <row r="205" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A205" s="5" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" s="7" t="s">
         <v>28</v>
       </c>
@@ -4308,7 +4329,7 @@
       <c r="E206" s="8"/>
       <c r="F206" s="8"/>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" s="8"/>
       <c r="B207" s="8"/>
       <c r="C207" s="8" t="s">
@@ -4320,7 +4341,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" s="8"/>
       <c r="B208" s="8"/>
       <c r="C208" s="8" t="s">
@@ -4330,7 +4351,7 @@
       <c r="E208" s="8"/>
       <c r="F208" s="8"/>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A209" s="8"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8" t="s">
@@ -4340,7 +4361,7 @@
       <c r="E209" s="8"/>
       <c r="F209" s="8"/>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A210" s="8"/>
       <c r="B210" s="8"/>
       <c r="C210" s="8" t="s">
@@ -4352,18 +4373,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F211">
         <f>SUM(F206:F210)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="212" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A212" s="5" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A213" s="13" t="s">
         <v>325</v>
       </c>
@@ -4377,7 +4398,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A214" s="13"/>
       <c r="B214" s="11"/>
       <c r="C214" s="11"/>
@@ -4389,7 +4410,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A215" s="13"/>
       <c r="B215" s="11"/>
       <c r="C215" s="11"/>
@@ -4401,7 +4422,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A216" s="13"/>
       <c r="B216" s="11"/>
       <c r="C216" s="11"/>
@@ -4413,7 +4434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A217" s="13"/>
       <c r="B217" s="11"/>
       <c r="C217" s="11"/>
@@ -4425,7 +4446,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A218" s="13"/>
       <c r="B218" s="11"/>
       <c r="C218" s="11"/>
@@ -4438,7 +4459,7 @@
       </c>
       <c r="F218" s="11"/>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A219" s="1"/>
       <c r="E219">
         <f>-SUM(E213:E218)</f>
@@ -4450,7 +4471,7 @@
       </c>
       <c r="M219" s="19"/>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A221" s="9" t="s">
         <v>66</v>
       </c>
@@ -4464,7 +4485,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A222" s="9"/>
       <c r="B222" s="10" t="s">
         <v>42</v>
@@ -4476,7 +4497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A223" s="9"/>
       <c r="B223" s="10" t="s">
         <v>328</v>
@@ -4488,7 +4509,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A224" s="9"/>
       <c r="B224" s="10" t="s">
         <v>67</v>
@@ -4500,7 +4521,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="9"/>
       <c r="B225" s="10"/>
       <c r="C225" s="10"/>
@@ -4513,7 +4534,7 @@
       </c>
       <c r="F225" s="10"/>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="1"/>
       <c r="E226">
         <f>-SUM(E221:E225)</f>
@@ -4524,7 +4545,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="9" t="s">
         <v>261</v>
       </c>
@@ -4542,7 +4563,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="10"/>
       <c r="B228" s="10"/>
       <c r="C228" s="10"/>
@@ -4554,7 +4575,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="10"/>
       <c r="B229" s="10"/>
       <c r="C229" s="10"/>
@@ -4566,7 +4587,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="10"/>
       <c r="B230" s="10"/>
       <c r="C230" s="10"/>
@@ -4578,7 +4599,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="10"/>
       <c r="B231" s="10"/>
       <c r="C231" s="10"/>
@@ -4590,7 +4611,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="10"/>
       <c r="B232" s="10"/>
       <c r="C232" s="10"/>
@@ -4602,7 +4623,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="10"/>
       <c r="B233" s="10"/>
       <c r="C233" s="10" t="s">
@@ -4616,7 +4637,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="10"/>
       <c r="B234" s="10"/>
       <c r="C234" s="10"/>
@@ -4628,7 +4649,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="10"/>
       <c r="B235" s="10"/>
       <c r="C235" s="10"/>
@@ -4640,7 +4661,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="10"/>
       <c r="B236" s="10"/>
       <c r="C236" s="10"/>
@@ -4652,7 +4673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="10"/>
       <c r="B237" s="10"/>
       <c r="C237" s="10"/>
@@ -4664,7 +4685,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="10"/>
       <c r="B238" s="10"/>
       <c r="C238" s="10"/>
@@ -4677,7 +4698,7 @@
       </c>
       <c r="F238" s="10"/>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E239">
         <f>SUM(E227:E232)</f>
         <v>0</v>
@@ -4687,7 +4708,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="7" t="s">
         <v>261</v>
       </c>
@@ -4701,7 +4722,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="8"/>
       <c r="B241" s="7" t="s">
         <v>20</v>
@@ -4715,7 +4736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="8"/>
       <c r="B242" s="8"/>
       <c r="C242" s="8" t="s">
@@ -4727,7 +4748,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="8"/>
       <c r="B243" s="8"/>
       <c r="C243" s="8" t="s">
@@ -4739,7 +4760,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="8"/>
       <c r="B244" s="8"/>
       <c r="C244" s="8" t="s">
@@ -4751,7 +4772,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="8"/>
       <c r="B245" s="8"/>
       <c r="C245" s="8" t="s">
@@ -4763,7 +4784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="8"/>
       <c r="B246" s="8"/>
       <c r="C246" s="8" t="s">
@@ -4775,7 +4796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="8"/>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
@@ -4788,7 +4809,7 @@
       </c>
       <c r="F247" s="8"/>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E248">
         <f>SUM(E240:E246)</f>
         <v>0</v>
@@ -4798,7 +4819,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="7" t="s">
         <v>66</v>
       </c>
@@ -4812,7 +4833,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="7"/>
       <c r="B250" s="8" t="s">
         <v>42</v>
@@ -4824,7 +4845,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="7"/>
       <c r="B251" s="8" t="s">
         <v>217</v>
@@ -4836,7 +4857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="7"/>
       <c r="B252" s="8" t="s">
         <v>140</v>
@@ -4848,7 +4869,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="7"/>
       <c r="B253" s="8" t="s">
         <v>65</v>
@@ -4860,7 +4881,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="7"/>
       <c r="B254" s="8" t="s">
         <v>67</v>
@@ -4872,7 +4893,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="7"/>
       <c r="B255" s="7" t="s">
         <v>49</v>
@@ -4886,7 +4907,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="7"/>
       <c r="B256" s="7"/>
       <c r="C256" s="8" t="s">
@@ -4898,7 +4919,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="7"/>
       <c r="B257" s="7"/>
       <c r="C257" s="8" t="s">
@@ -4910,7 +4931,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="7"/>
       <c r="B258" s="7"/>
       <c r="C258" s="8" t="s">
@@ -4922,7 +4943,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="7"/>
       <c r="B259" s="7"/>
       <c r="C259" s="8" t="s">
@@ -4934,7 +4955,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="7"/>
       <c r="B260" s="7"/>
       <c r="C260" s="8" t="s">
@@ -4948,7 +4969,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="7"/>
       <c r="B261" s="7"/>
       <c r="C261" s="8"/>
@@ -4960,7 +4981,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="7"/>
       <c r="B262" s="7"/>
       <c r="C262" s="8"/>
@@ -4972,7 +4993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="7"/>
       <c r="B263" s="7"/>
       <c r="C263" s="8"/>
@@ -4984,7 +5005,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="7"/>
       <c r="B264" s="7"/>
       <c r="C264" s="8"/>
@@ -4996,7 +5017,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="7"/>
       <c r="B265" s="7"/>
       <c r="C265" s="8"/>
@@ -5009,7 +5030,7 @@
       </c>
       <c r="F265" s="8"/>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E266">
         <f>SUM(E249:E265)</f>
         <v>0</v>
@@ -5019,7 +5040,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" s="7" t="s">
         <v>267</v>
       </c>
@@ -5033,7 +5054,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="7" t="s">
         <v>269</v>
       </c>
@@ -5047,7 +5068,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="7"/>
       <c r="B270" s="8" t="s">
         <v>318</v>
@@ -5059,7 +5080,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="8"/>
       <c r="B271" s="8" t="s">
         <v>316</v>
@@ -5071,7 +5092,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="8"/>
       <c r="B272" s="8" t="s">
         <v>317</v>
@@ -5083,7 +5104,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="8"/>
       <c r="B273" s="8"/>
       <c r="C273" s="8"/>
@@ -5096,7 +5117,7 @@
       </c>
       <c r="F273" s="8"/>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E274">
         <f>SUM(E268:E272)</f>
         <v>0</v>
@@ -5106,7 +5127,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="9" t="s">
         <v>34</v>
       </c>
@@ -5120,7 +5141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="10"/>
       <c r="B276" s="10" t="s">
         <v>221</v>
@@ -5132,7 +5153,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="9"/>
       <c r="B277" s="10" t="s">
         <v>285</v>
@@ -5146,7 +5167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="10"/>
       <c r="B278" s="10" t="s">
         <v>278</v>
@@ -5160,7 +5181,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="9"/>
       <c r="B279" s="10" t="s">
         <v>200</v>
@@ -5174,7 +5195,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="9"/>
       <c r="B280" s="10" t="s">
         <v>286</v>
@@ -5188,7 +5209,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="9"/>
       <c r="B281" s="10" t="s">
         <v>287</v>
@@ -5200,7 +5221,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="10"/>
       <c r="B282" s="10" t="s">
         <v>279</v>
@@ -5212,7 +5233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="10"/>
       <c r="B283" s="10" t="s">
         <v>280</v>
@@ -5224,7 +5245,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="10"/>
       <c r="B284" s="10" t="s">
         <v>36</v>
@@ -5236,7 +5257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285" s="10"/>
       <c r="B285" s="10"/>
       <c r="C285" s="10"/>
@@ -5249,7 +5270,7 @@
       </c>
       <c r="F285" s="10"/>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E286">
         <f>SUM(E275:E284)</f>
         <v>0</v>
@@ -5259,12 +5280,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="289" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A289" s="5" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="12" t="s">
         <v>191</v>
       </c>
@@ -5278,7 +5299,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="14"/>
       <c r="B291" s="14"/>
       <c r="C291" s="12" t="s">
@@ -5290,7 +5311,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" s="14"/>
       <c r="B292" s="14"/>
       <c r="C292" s="12" t="s">
@@ -5302,7 +5323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" s="14"/>
       <c r="B293" s="14"/>
       <c r="C293" s="12" t="s">
@@ -5314,7 +5335,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" s="14"/>
       <c r="B294" s="14"/>
       <c r="C294" s="12" t="s">
@@ -5326,7 +5347,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" s="12"/>
       <c r="B295" s="12" t="s">
         <v>192</v>
@@ -5340,7 +5361,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="12"/>
       <c r="B296" s="12"/>
       <c r="C296" s="12" t="s">
@@ -5352,7 +5373,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="12"/>
       <c r="B297" s="12"/>
       <c r="C297" s="12" t="s">
@@ -5364,7 +5385,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" s="12"/>
       <c r="B298" s="12" t="s">
         <v>194</v>
@@ -5378,7 +5399,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" s="12"/>
       <c r="B299" s="12"/>
       <c r="C299" s="12" t="s">
@@ -5390,7 +5411,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="12"/>
       <c r="B300" s="12"/>
       <c r="C300" s="12" t="s">
@@ -5402,7 +5423,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" s="14" t="s">
         <v>49</v>
       </c>
@@ -5416,7 +5437,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" s="14"/>
       <c r="B302" s="14"/>
       <c r="C302" s="12" t="s">
@@ -5428,7 +5449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" s="14"/>
       <c r="B303" s="14"/>
       <c r="C303" s="12" t="s">
@@ -5440,7 +5461,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" s="14"/>
       <c r="B304" s="14"/>
       <c r="C304" s="12" t="s">
@@ -5452,7 +5473,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" s="14"/>
       <c r="B305" s="14"/>
       <c r="C305" s="12" t="s">
@@ -5464,7 +5485,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" s="14"/>
       <c r="B306" s="14"/>
       <c r="C306" s="12" t="s">
@@ -5478,7 +5499,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" s="14"/>
       <c r="B307" s="14"/>
       <c r="C307" s="12"/>
@@ -5490,7 +5511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308" s="14"/>
       <c r="B308" s="14"/>
       <c r="C308" s="12"/>
@@ -5502,7 +5523,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309" s="14"/>
       <c r="B309" s="14"/>
       <c r="C309" s="12"/>
@@ -5514,7 +5535,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310" s="14"/>
       <c r="B310" s="14"/>
       <c r="C310" s="12"/>
@@ -5526,7 +5547,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311" s="12"/>
       <c r="B311" s="12"/>
       <c r="C311" s="12"/>
@@ -5539,7 +5560,7 @@
       </c>
       <c r="F311" s="12"/>
     </row>
-    <row r="312" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E312">
         <f>SUM(E290:E311)</f>
         <v>0</v>
@@ -5551,7 +5572,7 @@
       <c r="K312" s="17"/>
       <c r="L312" s="17"/>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" s="9" t="s">
         <v>355</v>
       </c>
@@ -5567,7 +5588,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A314" s="10" t="s">
         <v>302</v>
       </c>
@@ -5581,7 +5602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315" s="9"/>
       <c r="B315" s="10"/>
       <c r="C315" s="10" t="s">
@@ -5593,7 +5614,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316" s="10"/>
       <c r="B316" s="10"/>
       <c r="C316" s="10" t="s">
@@ -5607,7 +5628,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317" s="10"/>
       <c r="B317" s="10"/>
       <c r="C317" s="10" t="s">
@@ -5621,7 +5642,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" s="9"/>
       <c r="B318" s="10"/>
       <c r="C318" s="10" t="s">
@@ -5635,7 +5656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A319" s="9"/>
       <c r="B319" s="10"/>
       <c r="C319" s="10" t="s">
@@ -5649,7 +5670,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A320" s="10"/>
       <c r="B320" s="10"/>
       <c r="C320" s="10"/>
@@ -5661,7 +5682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E321">
         <f>SUM(E313:E320)</f>
         <v>0</v>
@@ -5673,15 +5694,15 @@
       <c r="K321" s="17"/>
       <c r="L321" s="17"/>
     </row>
-    <row r="322" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K322" s="17"/>
       <c r="L322" s="17"/>
     </row>
-    <row r="323" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K323" s="17"/>
       <c r="L323" s="17"/>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A324" s="13" t="s">
         <v>271</v>
       </c>
@@ -5695,7 +5716,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A325" s="11"/>
       <c r="B325" s="11" t="s">
         <v>273</v>
@@ -5707,7 +5728,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A326" s="11"/>
       <c r="B326" s="11" t="s">
         <v>110</v>
@@ -5719,7 +5740,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A327" s="13" t="s">
         <v>274</v>
       </c>
@@ -5733,7 +5754,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A328" s="11"/>
       <c r="B328" s="11" t="s">
         <v>276</v>
@@ -5745,7 +5766,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329" s="13" t="s">
         <v>319</v>
       </c>
@@ -5759,7 +5780,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A330" s="11"/>
       <c r="B330" s="11"/>
       <c r="C330" s="11" t="s">
@@ -5771,7 +5792,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" s="11"/>
       <c r="B331" s="11"/>
       <c r="C331" s="11" t="s">
@@ -5783,7 +5804,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A332" s="11"/>
       <c r="B332" s="11"/>
       <c r="C332" s="11"/>
@@ -5796,7 +5817,7 @@
       </c>
       <c r="F332" s="11"/>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E333">
         <f>SUM(E324:E328)</f>
         <v>0</v>
@@ -5806,14 +5827,14 @@
         <v>60</v>
       </c>
     </row>
-    <row r="335" spans="1:12" s="17" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:12" s="17" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A335" s="5" t="s">
         <v>251</v>
       </c>
       <c r="K335"/>
       <c r="L335"/>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A336" s="11" t="s">
         <v>153</v>
       </c>
@@ -5831,7 +5852,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337" s="11"/>
       <c r="B337" s="11"/>
       <c r="C337" s="11" t="s">
@@ -5845,7 +5866,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A338" s="11"/>
       <c r="B338" s="11"/>
       <c r="C338" s="11" t="s">
@@ -5859,7 +5880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A339" s="11"/>
       <c r="B339" s="11"/>
       <c r="C339" s="11" t="s">
@@ -5873,7 +5894,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A340" s="11"/>
       <c r="B340" s="11"/>
       <c r="C340" s="11" t="s">
@@ -5887,7 +5908,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A341" s="11"/>
       <c r="B341" s="11"/>
       <c r="C341" s="11" t="s">
@@ -5901,7 +5922,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A342" s="11"/>
       <c r="B342" s="11"/>
       <c r="C342" s="11"/>
@@ -5913,7 +5934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E343">
         <f>SUM(E336:E342)</f>
         <v>0</v>
@@ -5923,7 +5944,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344" s="13" t="s">
         <v>40</v>
       </c>
@@ -5937,7 +5958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A345" s="13"/>
       <c r="B345" s="13"/>
       <c r="C345" s="15" t="s">
@@ -5949,7 +5970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A346" s="13"/>
       <c r="B346" s="13"/>
       <c r="C346" s="15" t="s">
@@ -5961,7 +5982,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A347" s="13"/>
       <c r="B347" s="13"/>
       <c r="C347" s="11"/>
@@ -5969,7 +5990,7 @@
       <c r="E347" s="11"/>
       <c r="F347" s="11"/>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A348" s="13" t="s">
         <v>103</v>
       </c>
@@ -5983,7 +6004,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A349" s="13"/>
       <c r="B349" s="13"/>
       <c r="C349" s="11" t="s">
@@ -5995,7 +6016,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A350" s="13"/>
       <c r="B350" s="13"/>
       <c r="C350" s="11" t="s">
@@ -6007,7 +6028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A351" s="13"/>
       <c r="B351" s="13"/>
       <c r="C351" s="11"/>
@@ -6015,7 +6036,7 @@
       <c r="E351" s="11"/>
       <c r="F351" s="11"/>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A352" s="13" t="s">
         <v>199</v>
       </c>
@@ -6029,7 +6050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A353" s="13"/>
       <c r="B353" s="13"/>
       <c r="C353" s="11" t="s">
@@ -6041,7 +6062,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A354" s="13"/>
       <c r="B354" s="13"/>
       <c r="C354" s="11" t="s">
@@ -6053,7 +6074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A355" s="13"/>
       <c r="B355" s="13"/>
       <c r="C355" s="11"/>
@@ -6066,7 +6087,7 @@
       </c>
       <c r="F355" s="11"/>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="E356">
@@ -6079,7 +6100,7 @@
       </c>
       <c r="M356" s="19"/>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A357" s="14" t="s">
         <v>41</v>
       </c>
@@ -6094,7 +6115,7 @@
       </c>
       <c r="M357" s="19"/>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A358" s="14"/>
       <c r="B358" s="14"/>
       <c r="C358" s="12" t="s">
@@ -6107,7 +6128,7 @@
       </c>
       <c r="M358" s="19"/>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A359" s="14"/>
       <c r="B359" s="14"/>
       <c r="C359" s="12"/>
@@ -6121,7 +6142,7 @@
       <c r="F359" s="12"/>
       <c r="M359" s="19"/>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="E360">
@@ -6133,7 +6154,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>5</v>
       </c>
@@ -6149,7 +6170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
         <v>314</v>
       </c>
@@ -6163,7 +6184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A364" s="1"/>
       <c r="B364" s="10"/>
       <c r="C364" s="10" t="s">
@@ -6175,7 +6196,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A365" s="1"/>
       <c r="B365" s="10"/>
       <c r="C365" s="10" t="s">
@@ -6187,7 +6208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A366" s="1"/>
       <c r="B366" s="10"/>
       <c r="C366" s="10" t="s">
@@ -6199,7 +6220,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A367" s="1"/>
       <c r="B367" s="10"/>
       <c r="C367" s="10" t="s">
@@ -6211,7 +6232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A368" s="1"/>
       <c r="B368" s="10"/>
       <c r="C368" s="10" t="s">
@@ -6223,7 +6244,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A369" s="1"/>
       <c r="B369" s="10"/>
       <c r="C369" s="10" t="s">
@@ -6235,7 +6256,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A370" s="1"/>
       <c r="B370" s="10"/>
       <c r="C370" s="10"/>
@@ -6248,7 +6269,7 @@
       </c>
       <c r="F370" s="10"/>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="E371">
@@ -6260,7 +6281,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A372" s="1"/>
       <c r="B372" s="13" t="s">
         <v>54</v>
@@ -6274,9 +6295,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A373" s="1"/>
-      <c r="B373" s="11"/>
+      <c r="B373" s="11" t="s">
+        <v>404</v>
+      </c>
       <c r="C373" s="11" t="s">
         <v>56</v>
       </c>
@@ -6286,9 +6309,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A374" s="1"/>
-      <c r="B374" s="11"/>
+      <c r="B374" s="11" t="s">
+        <v>405</v>
+      </c>
       <c r="C374" s="11" t="s">
         <v>45</v>
       </c>
@@ -6298,7 +6323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A375" s="1"/>
       <c r="B375" s="11"/>
       <c r="C375" s="11" t="s">
@@ -6310,7 +6335,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A376" s="1"/>
       <c r="B376" s="11"/>
       <c r="C376" s="11" t="s">
@@ -6322,7 +6347,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A377" s="1"/>
       <c r="B377" s="11"/>
       <c r="C377" s="11" t="s">
@@ -6334,7 +6359,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A378" s="1"/>
       <c r="B378" s="11"/>
       <c r="C378" s="11" t="s">
@@ -6346,7 +6371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A379" s="1"/>
       <c r="B379" s="11"/>
       <c r="C379" s="11" t="s">
@@ -6358,7 +6383,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A380" s="1"/>
       <c r="B380" s="11"/>
       <c r="C380" s="11"/>
@@ -6371,7 +6396,7 @@
       </c>
       <c r="F380" s="11"/>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="E381">
@@ -6383,7 +6408,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A382" s="1"/>
       <c r="B382" s="14" t="s">
         <v>54</v>
@@ -6397,7 +6422,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A383" s="1"/>
       <c r="B383" s="12"/>
       <c r="C383" s="12" t="s">
@@ -6409,7 +6434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A384" s="1"/>
       <c r="B384" s="12"/>
       <c r="C384" s="12" t="s">
@@ -6421,7 +6446,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A385" s="1"/>
       <c r="B385" s="12"/>
       <c r="C385" s="12" t="str">
@@ -6434,7 +6459,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A386" s="1"/>
       <c r="B386" s="12"/>
       <c r="C386" s="12" t="str">
@@ -6447,7 +6472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A387" s="1"/>
       <c r="B387" s="12"/>
       <c r="C387" s="12" t="str">
@@ -6460,7 +6485,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A388" s="1"/>
       <c r="B388" s="12"/>
       <c r="C388" s="12" t="str">
@@ -6473,7 +6498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A389" s="1"/>
       <c r="B389" s="12"/>
       <c r="C389" s="12" t="s">
@@ -6485,7 +6510,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A390" s="1"/>
       <c r="B390" s="12"/>
       <c r="C390" s="12"/>
@@ -6498,7 +6523,7 @@
       </c>
       <c r="F390" s="12"/>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="E391">
@@ -6510,12 +6535,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="393" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A393" s="5" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A394" s="7" t="s">
         <v>309</v>
       </c>
@@ -6525,7 +6550,7 @@
       <c r="E394" s="8"/>
       <c r="F394" s="8"/>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A395" s="7"/>
       <c r="B395" s="8"/>
       <c r="C395" s="8"/>
@@ -6533,7 +6558,7 @@
       <c r="E395" s="8"/>
       <c r="F395" s="8"/>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A396" s="7"/>
       <c r="B396" s="8" t="s">
         <v>157</v>
@@ -6543,7 +6568,7 @@
       <c r="E396" s="8"/>
       <c r="F396" s="8"/>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A397" s="7"/>
       <c r="B397" s="8" t="s">
         <v>158</v>
@@ -6555,7 +6580,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A398" s="7"/>
       <c r="B398" s="8" t="s">
         <v>159</v>
@@ -6567,7 +6592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A399" s="7"/>
       <c r="B399" s="8" t="s">
         <v>160</v>
@@ -6581,7 +6606,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A400" s="7"/>
       <c r="B400" s="8"/>
       <c r="C400" s="8" t="s">
@@ -6593,7 +6618,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A401" s="7"/>
       <c r="B401" s="8" t="s">
         <v>162</v>
@@ -6607,7 +6632,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A402" s="7"/>
       <c r="B402" s="8"/>
       <c r="C402" s="8" t="s">
@@ -6619,7 +6644,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A403" s="7"/>
       <c r="B403" s="8"/>
       <c r="C403" s="8" t="s">
@@ -6631,7 +6656,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A404" s="7"/>
       <c r="B404" s="8"/>
       <c r="C404" s="8" t="s">
@@ -6643,7 +6668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A405" s="7"/>
       <c r="B405" s="8"/>
       <c r="C405" s="8" t="s">
@@ -6655,7 +6680,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A406" s="7"/>
       <c r="B406" s="8"/>
       <c r="C406" s="8"/>
@@ -6668,7 +6693,7 @@
       </c>
       <c r="F406" s="8"/>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A407" s="1"/>
       <c r="E407">
         <f>SUM(E394:E406)</f>
@@ -6679,10 +6704,10 @@
         <v>65</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A408" s="1"/>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A409" s="9" t="s">
         <v>90</v>
       </c>
@@ -6696,7 +6721,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A410" s="10"/>
       <c r="B410" s="10" t="s">
         <v>92</v>
@@ -6708,7 +6733,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A411" s="10"/>
       <c r="B411" s="10" t="s">
         <v>93</v>
@@ -6720,7 +6745,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A412" s="10"/>
       <c r="B412" s="10" t="s">
         <v>94</v>
@@ -6732,7 +6757,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A413" s="9" t="s">
         <v>102</v>
       </c>
@@ -6742,7 +6767,7 @@
       <c r="E413" s="10"/>
       <c r="F413" s="10"/>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A414" s="9"/>
       <c r="B414" s="10" t="s">
         <v>118</v>
@@ -6754,7 +6779,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A415" s="10"/>
       <c r="B415" s="10" t="s">
         <v>119</v>
@@ -6768,7 +6793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A416" s="10"/>
       <c r="B416" s="10" t="s">
         <v>120</v>
@@ -6782,7 +6807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A417" s="10"/>
       <c r="B417" s="10" t="s">
         <v>121</v>
@@ -6794,7 +6819,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A418" s="10"/>
       <c r="B418" s="10"/>
       <c r="C418" s="10"/>
@@ -6802,7 +6827,7 @@
       <c r="E418" s="10"/>
       <c r="F418" s="10"/>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A419" s="10"/>
       <c r="B419" s="10"/>
       <c r="C419" s="10"/>
@@ -6815,7 +6840,7 @@
       </c>
       <c r="F419" s="10"/>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E420">
         <f>SUM(E409:E419)</f>
         <v>0</v>
@@ -6825,12 +6850,12 @@
         <v>550</v>
       </c>
     </row>
-    <row r="421" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A421" s="5" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A422" s="7" t="s">
         <v>36</v>
       </c>
@@ -6846,7 +6871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A423" s="7"/>
       <c r="B423" s="8"/>
       <c r="C423" s="8" t="s">
@@ -6858,7 +6883,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A424" s="7"/>
       <c r="B424" s="8"/>
       <c r="C424" s="8" t="s">
@@ -6870,7 +6895,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A425" s="7"/>
       <c r="B425" s="8"/>
       <c r="C425" s="8" t="s">
@@ -6882,7 +6907,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A426" s="7"/>
       <c r="B426" s="8"/>
       <c r="C426" s="8" t="s">
@@ -6894,7 +6919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A427" s="8"/>
       <c r="B427" s="8" t="s">
         <v>12</v>
@@ -6906,7 +6931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A428" s="8"/>
       <c r="B428" s="8" t="s">
         <v>39</v>
@@ -6918,7 +6943,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A429" s="8"/>
       <c r="B429" s="8" t="s">
         <v>68</v>
@@ -6930,7 +6955,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A430" s="8"/>
       <c r="B430" s="8" t="s">
         <v>85</v>
@@ -6942,7 +6967,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A431" s="8"/>
       <c r="B431" s="8"/>
       <c r="C431" s="8"/>
@@ -6955,7 +6980,7 @@
       </c>
       <c r="F431" s="8"/>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E432">
         <f>SUM(E422:E431)</f>
         <v>0</v>
@@ -6965,7 +6990,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A433" s="8" t="s">
         <v>122</v>
       </c>
@@ -6979,7 +7004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A434" s="8"/>
       <c r="B434" s="8" t="s">
         <v>124</v>
@@ -6991,7 +7016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A435" s="8"/>
       <c r="B435" s="8" t="s">
         <v>125</v>
@@ -7003,7 +7028,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A436" s="8"/>
       <c r="B436" s="8" t="s">
         <v>126</v>
@@ -7015,7 +7040,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A437" s="8"/>
       <c r="B437" s="8" t="s">
         <v>127</v>
@@ -7027,7 +7052,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A438" s="8"/>
       <c r="B438" s="8" t="s">
         <v>228</v>
@@ -7039,7 +7064,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A439" s="8"/>
       <c r="B439" s="8" t="s">
         <v>128</v>
@@ -7051,7 +7076,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A440" s="8"/>
       <c r="B440" s="8" t="s">
         <v>229</v>
@@ -7063,7 +7088,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A441" s="8"/>
       <c r="B441" s="8" t="s">
         <v>129</v>
@@ -7075,7 +7100,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A442" s="8"/>
       <c r="B442" s="8"/>
       <c r="C442" s="8"/>
@@ -7088,7 +7113,7 @@
       </c>
       <c r="F442" s="8"/>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E443">
         <f>SUM(E433:E442)</f>
         <v>0</v>
@@ -7098,7 +7123,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A444" s="8" t="s">
         <v>130</v>
       </c>
@@ -7112,7 +7137,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A445" s="8"/>
       <c r="B445" s="8" t="s">
         <v>132</v>
@@ -7124,7 +7149,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A446" s="8"/>
       <c r="B446" s="8" t="s">
         <v>7</v>
@@ -7136,7 +7161,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A447" s="8"/>
       <c r="B447" s="8" t="s">
         <v>133</v>
@@ -7148,7 +7173,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A448" s="8"/>
       <c r="B448" s="8" t="s">
         <v>134</v>
@@ -7160,7 +7185,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A449" s="8"/>
       <c r="B449" s="8" t="s">
         <v>135</v>
@@ -7172,7 +7197,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A450" s="8"/>
       <c r="B450" s="8" t="s">
         <v>136</v>
@@ -7184,7 +7209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A451" s="8"/>
       <c r="B451" s="8"/>
       <c r="C451" s="8"/>
@@ -7197,7 +7222,7 @@
       </c>
       <c r="F451" s="8"/>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E452">
         <f>SUM(E444:E451)</f>
         <v>0</v>
@@ -7207,7 +7232,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A453" s="7" t="s">
         <v>312</v>
       </c>
@@ -7223,7 +7248,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A454" s="7"/>
       <c r="B454" s="7"/>
       <c r="C454" s="8"/>
@@ -7235,7 +7260,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A455" s="7"/>
       <c r="B455" s="7"/>
       <c r="C455" s="8"/>
@@ -7247,7 +7272,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A456" s="7"/>
       <c r="B456" s="7"/>
       <c r="C456" s="8" t="s">
@@ -7261,7 +7286,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A457" s="7"/>
       <c r="B457" s="7"/>
       <c r="C457" s="8"/>
@@ -7273,7 +7298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A458" s="7"/>
       <c r="B458" s="7"/>
       <c r="C458" s="8"/>
@@ -7285,7 +7310,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A459" s="7"/>
       <c r="B459" s="7"/>
       <c r="C459" s="8"/>
@@ -7297,7 +7322,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A460" s="7"/>
       <c r="B460" s="7"/>
       <c r="C460" s="8"/>
@@ -7309,7 +7334,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.3">
       <c r="E461">
         <f>SUM(E453:E460)</f>
         <v>0</v>
@@ -7319,12 +7344,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="462" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A462" s="5" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A463" s="7" t="s">
         <v>235</v>
       </c>
@@ -7340,7 +7365,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A464" s="7"/>
       <c r="B464" s="8"/>
       <c r="C464" s="8" t="s">
@@ -7352,7 +7377,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A465" s="8"/>
       <c r="B465" s="7" t="s">
         <v>236</v>
@@ -7366,7 +7391,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A466" s="8"/>
       <c r="B466" s="8"/>
       <c r="C466" s="8" t="s">
@@ -7378,7 +7403,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A467" s="8"/>
       <c r="B467" s="8"/>
       <c r="C467" s="8" t="s">
@@ -7390,7 +7415,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A468" s="8"/>
       <c r="B468" s="8"/>
       <c r="C468" s="8" t="s">
@@ -7402,7 +7427,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A469" s="8"/>
       <c r="B469" s="8"/>
       <c r="C469" s="8" t="s">
@@ -7414,7 +7439,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A470" s="8"/>
       <c r="B470" s="8"/>
       <c r="C470" s="8"/>
@@ -7426,7 +7451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E471">
         <f>SUM(E463:E470)</f>
         <v>0</v>
@@ -7436,12 +7461,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A473" s="14" t="s">
         <v>330</v>
       </c>
@@ -7457,7 +7482,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A474" s="14" t="s">
         <v>332</v>
       </c>
@@ -7475,7 +7500,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A475" s="14"/>
       <c r="B475" s="12"/>
       <c r="C475" s="12" t="s">
@@ -7489,7 +7514,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A476" s="1"/>
       <c r="D476" s="20" t="s">
         <v>206</v>
@@ -7499,7 +7524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E477">
         <f>SUM(E473:E476)</f>
         <v>0</v>
@@ -7509,12 +7534,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="479" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A479" s="5" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A480" s="14" t="s">
         <v>235</v>
       </c>
@@ -7533,7 +7558,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A481" s="14" t="s">
         <v>240</v>
       </c>
@@ -7552,7 +7577,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A482" s="12" t="s">
         <v>392</v>
       </c>
@@ -7571,7 +7596,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A483" s="12"/>
       <c r="B483" s="12" t="s">
         <v>237</v>
@@ -7588,7 +7613,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A484" s="12"/>
       <c r="B484" s="12" t="s">
         <v>239</v>
@@ -7605,7 +7630,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A485" s="12"/>
       <c r="B485" s="12" t="s">
         <v>241</v>
@@ -7622,7 +7647,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A486" s="12"/>
       <c r="B486" s="12" t="s">
         <v>242</v>
@@ -7639,7 +7664,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A487" s="12"/>
       <c r="B487" s="12" t="s">
         <v>25</v>
@@ -7656,7 +7681,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A488" s="12"/>
       <c r="B488" s="12" t="s">
         <v>26</v>
@@ -7670,7 +7695,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A489" s="12"/>
       <c r="B489" s="12" t="s">
         <v>243</v>
@@ -7684,7 +7709,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A490" s="12"/>
       <c r="B490" s="12" t="s">
         <v>244</v>
@@ -7698,7 +7723,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A491" s="12"/>
       <c r="B491" s="12"/>
       <c r="C491" s="12"/>
@@ -7710,7 +7735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E492">
         <f>SUM(E480:E491)</f>
         <v>25</v>
@@ -7720,7 +7745,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A494" s="9" t="s">
         <v>235</v>
       </c>
@@ -7737,7 +7762,7 @@
       </c>
       <c r="H494" s="18"/>
     </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A495" s="9" t="s">
         <v>240</v>
       </c>
@@ -7754,7 +7779,7 @@
       </c>
       <c r="H495" s="18"/>
     </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A496" s="10" t="s">
         <v>387</v>
       </c>
@@ -7771,7 +7796,7 @@
       </c>
       <c r="H496" s="18"/>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A497" s="10"/>
       <c r="B497" s="10" t="s">
         <v>237</v>
@@ -7786,7 +7811,7 @@
       </c>
       <c r="H497" s="18"/>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A498" s="10"/>
       <c r="B498" s="10" t="s">
         <v>239</v>
@@ -7800,7 +7825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A499" s="10"/>
       <c r="B499" s="10" t="s">
         <v>241</v>
@@ -7814,7 +7839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A500" s="10"/>
       <c r="B500" s="10" t="s">
         <v>242</v>
@@ -7828,7 +7853,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="501" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A501" s="10"/>
       <c r="B501" s="10" t="s">
         <v>25</v>
@@ -7842,7 +7867,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A502" s="10"/>
       <c r="B502" s="10" t="s">
         <v>26</v>
@@ -7856,7 +7881,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="503" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A503" s="10"/>
       <c r="B503" s="10" t="s">
         <v>243</v>
@@ -7873,7 +7898,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A504" s="10"/>
       <c r="B504" s="10" t="s">
         <v>244</v>
@@ -7887,7 +7912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A505" s="10"/>
       <c r="B505" s="10"/>
       <c r="C505" s="10"/>
@@ -7908,7 +7933,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E506">
         <f>SUM(E494:E505)</f>
         <v>16.5</v>
@@ -7918,7 +7943,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A508" s="13" t="s">
         <v>235</v>
       </c>
@@ -7934,7 +7959,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="509" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A509" s="13" t="s">
         <v>240</v>
       </c>
@@ -7953,7 +7978,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="510" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A510" s="11" t="s">
         <v>380</v>
       </c>
@@ -7969,7 +7994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="511" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A511" s="11"/>
       <c r="B511" s="11" t="s">
         <v>237</v>
@@ -7986,7 +8011,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="512" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A512" s="11"/>
       <c r="B512" s="11" t="s">
         <v>239</v>
@@ -8000,7 +8025,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="513" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A513" s="11"/>
       <c r="B513" s="11" t="s">
         <v>241</v>
@@ -8017,7 +8042,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="514" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A514" s="11"/>
       <c r="B514" s="11" t="s">
         <v>242</v>
@@ -8031,7 +8056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="515" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A515" s="11"/>
       <c r="B515" s="11" t="s">
         <v>25</v>
@@ -8048,7 +8073,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="516" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A516" s="11"/>
       <c r="B516" s="11" t="s">
         <v>26</v>
@@ -8065,7 +8090,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="517" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A517" s="11"/>
       <c r="B517" s="11" t="s">
         <v>243</v>
@@ -8082,7 +8107,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="518" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A518" s="11"/>
       <c r="B518" s="11" t="s">
         <v>244</v>
@@ -8096,7 +8121,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="519" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A519" s="11"/>
       <c r="B519" s="11"/>
       <c r="C519" s="11"/>
@@ -8115,7 +8140,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="520" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E520">
         <f>SUM(E508:E519)</f>
         <v>24.5</v>
@@ -8125,7 +8150,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="524" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A524" s="7"/>
       <c r="B524" t="s">
         <v>183</v>
@@ -8143,7 +8168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A525" s="9" t="s">
         <v>364</v>
       </c>
@@ -8163,7 +8188,7 @@
         <v>-0.11762820512820513</v>
       </c>
     </row>
-    <row r="526" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A526" s="13" t="s">
         <v>365</v>
       </c>
@@ -8183,7 +8208,7 @@
         <v>-0.15462555066079295</v>
       </c>
     </row>
-    <row r="527" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A527" s="14" t="s">
         <v>363</v>
       </c>
@@ -8203,7 +8228,7 @@
         <v>-0.15486725663716813</v>
       </c>
     </row>
-    <row r="531" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="531" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F531" t="s">
         <v>230</v>
       </c>
@@ -8211,7 +8236,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="532" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="532" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D532" t="s">
         <v>232</v>
       </c>
@@ -8219,7 +8244,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="533" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="533" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F533" s="23">
         <v>0.45</v>
       </c>
@@ -8227,7 +8252,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="534" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="534" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F534" s="23">
         <f>F533+(F542-F533)/9</f>
         <v>0.5</v>
@@ -8236,7 +8261,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="535" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="535" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F535" s="23">
         <f>F534+(F542-F533)/9</f>
         <v>0.55000000000000004</v>
@@ -8245,7 +8270,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="536" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="536" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F536" s="23">
         <f>F535+(F542-F533)/9</f>
         <v>0.60000000000000009</v>
@@ -8254,7 +8279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="537" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="537" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F537" s="23">
         <f>F536+(F542-F533)/9</f>
         <v>0.65000000000000013</v>
@@ -8263,7 +8288,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="538" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="538" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F538" s="23">
         <f>F537+(F542-F533)/9</f>
         <v>0.70000000000000018</v>
@@ -8272,7 +8297,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="539" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="539" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F539" s="23">
         <f>F538+(F542-F533)/9</f>
         <v>0.75000000000000022</v>
@@ -8281,7 +8306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="540" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="540" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F540" s="23">
         <f>F539+(F542-F533)/9</f>
         <v>0.80000000000000027</v>
@@ -8290,7 +8315,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="541" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="541" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F541" s="23">
         <f>F540+(F542-F533)/9</f>
         <v>0.85000000000000031</v>
@@ -8299,7 +8324,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="542" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="542" spans="4:7" x14ac:dyDescent="0.3">
       <c r="F542" s="23">
         <v>0.9</v>
       </c>
@@ -8307,7 +8332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="543" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="543" spans="4:7" x14ac:dyDescent="0.3">
       <c r="E543" t="s">
         <v>234</v>
       </c>
@@ -8337,14 +8362,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="19"/>
+    <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A1" s="30" t="s">
         <v>223</v>
       </c>
@@ -8352,10 +8377,10 @@
       <c r="C1" s="30"/>
       <c r="D1" s="30"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>207</v>
       </c>
@@ -8363,7 +8388,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>38</v>
       </c>
@@ -8371,7 +8396,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>209</v>
       </c>
@@ -8379,7 +8404,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>210</v>
       </c>
@@ -8387,7 +8412,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>211</v>
       </c>
@@ -8395,7 +8420,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>212</v>
       </c>
@@ -8403,7 +8428,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>174</v>
       </c>
@@ -8411,7 +8436,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>208</v>
       </c>
@@ -8419,7 +8444,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>214</v>
       </c>
@@ -8427,7 +8452,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>213</v>
       </c>
@@ -8435,7 +8460,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>215</v>
       </c>
@@ -8443,7 +8468,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>216</v>
       </c>
@@ -8451,7 +8476,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>222</v>
       </c>
@@ -8459,7 +8484,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>224</v>
       </c>
@@ -8467,7 +8492,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>225</v>
       </c>
@@ -8475,7 +8500,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -8489,7 +8514,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
         <v>143</v>
       </c>
@@ -8497,7 +8522,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>144</v>
       </c>
@@ -8505,7 +8530,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>145</v>
       </c>
@@ -8516,7 +8541,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
         <v>147</v>
       </c>
@@ -8524,7 +8549,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
         <v>148</v>
       </c>
@@ -8532,7 +8557,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
         <v>149</v>
       </c>
@@ -8540,12 +8565,12 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>162</v>
       </c>
@@ -8556,7 +8581,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
         <v>166</v>
       </c>
@@ -8564,7 +8589,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>148</v>
       </c>
@@ -8572,7 +8597,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>220</v>
       </c>
@@ -8580,7 +8605,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>167</v>
       </c>
@@ -8591,7 +8616,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
         <v>169</v>
       </c>
@@ -8599,7 +8624,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C37" t="s">
         <v>170</v>
       </c>
